--- a/NG Scheduling.xlsx
+++ b/NG Scheduling.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://my.wal-mart.com/personal/k0m0eg1_homeoffice_wal-mart_com/Documents/Desktop/Code Puppy Saved Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1895" documentId="8_{3CD9A91E-A1DC-493E-B251-6A7E654DFCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F43286D-E8F8-4A01-B963-46D5338EDD9C}"/>
+  <xr:revisionPtr revIDLastSave="1926" documentId="8_{3CD9A91E-A1DC-493E-B251-6A7E654DFCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4765751-D525-45D9-B898-F8D4FD33921A}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="90" yWindow="90" windowWidth="23028" windowHeight="13668" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2100" yWindow="2295" windowWidth="38220" windowHeight="17205" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TUE FC Asset Plan SteerCo" sheetId="2" state="hidden" r:id="rId1"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="661">
   <si>
     <t>Fulfillment New Assets SteerCo (Tuesday's)</t>
   </si>
@@ -2411,6 +2411,21 @@
   </si>
   <si>
     <t xml:space="preserve">Advaith Venkataraman / Andrew </t>
+  </si>
+  <si>
+    <t>Not approved to move forward with Spec Building</t>
+  </si>
+  <si>
+    <t>26_01_29 Northeast Spec Bld Analysis.pptx</t>
+  </si>
+  <si>
+    <t>Adam Dunbar, Vik Gopalakrishnan, Jack Anderson, Jacob Shub</t>
+  </si>
+  <si>
+    <t>Spec Building Analysis for Northeast</t>
+  </si>
+  <si>
+    <t>26_05_08 SteerCo.pptx</t>
   </si>
 </sst>
 </file>
@@ -2547,7 +2562,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2587,6 +2602,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2874,7 +2895,7 @@
     <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3265,6 +3286,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -11802,7 +11826,7 @@
       </c>
       <c r="AI67" s="91"/>
     </row>
-    <row r="68" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="33">
         <f>IF(ISBLANK(E68),"",_xlfn.XLOOKUP(E68,Info!A:A,Info!B:B))</f>
         <v>14</v>
@@ -11851,7 +11875,7 @@
       <c r="P68" s="92"/>
       <c r="AI68" s="91"/>
     </row>
-    <row r="69" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="33">
         <f>IF(ISBLANK(E69),"",_xlfn.XLOOKUP(E69,Info!A:A,Info!B:B))</f>
         <v>14</v>
@@ -11941,6 +11965,9 @@
       <c r="L70" s="33"/>
       <c r="M70" s="67"/>
       <c r="N70" s="92"/>
+      <c r="O70" s="118" t="s">
+        <v>660</v>
+      </c>
       <c r="P70" s="92"/>
       <c r="AI70" s="91"/>
     </row>
@@ -12395,28 +12422,58 @@
       </c>
       <c r="AI80" s="91"/>
     </row>
-    <row r="81" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="33" t="str">
+    <row r="81" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="33" t="e">
         <f>IF(ISBLANK(E81),"",_xlfn.XLOOKUP(E81,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="B81" s="33"/>
-      <c r="C81" s="33"/>
-      <c r="D81" s="54"/>
-      <c r="E81" s="91"/>
-      <c r="F81" s="54"/>
-      <c r="G81" s="33" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B81" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="C81" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="D81" s="54" t="s">
+        <v>240</v>
+      </c>
+      <c r="E81" s="91">
+        <v>46051</v>
+      </c>
+      <c r="F81" s="54" t="s">
+        <v>659</v>
+      </c>
+      <c r="G81" s="33" t="e">
         <f>IF(ISBLANK(H81),"",_xlfn.XLOOKUP(H81,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H81" s="98"/>
-      <c r="I81" s="103"/>
-      <c r="J81" s="33"/>
-      <c r="K81" s="33"/>
-      <c r="L81" s="33"/>
-      <c r="M81" s="67"/>
-      <c r="N81" s="92"/>
-      <c r="P81" s="92"/>
+        <v>#N/A</v>
+      </c>
+      <c r="H81" s="98">
+        <f>E81-1</f>
+        <v>46050</v>
+      </c>
+      <c r="I81" s="103">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J81" s="33">
+        <v>30</v>
+      </c>
+      <c r="K81" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="L81" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="M81" s="67" t="s">
+        <v>249</v>
+      </c>
+      <c r="N81" s="92" t="s">
+        <v>656</v>
+      </c>
+      <c r="O81" s="118" t="s">
+        <v>657</v>
+      </c>
+      <c r="P81" s="92" t="s">
+        <v>658</v>
+      </c>
       <c r="AI81" s="91"/>
     </row>
     <row r="82" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
@@ -20671,6 +20728,8 @@
     <hyperlink ref="O62" r:id="rId50" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_30 SteerCo.pptx?d=wdb87420320c440f3a352dd4f0e632eb9&amp;csf=1&amp;web=1&amp;e=B6iMdT" xr:uid="{6BF12395-B556-46A4-85ED-12F1DEAE5FDB}"/>
     <hyperlink ref="O61" r:id="rId51" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_30 SteerCo.pptx?d=wdb87420320c440f3a352dd4f0e632eb9&amp;csf=1&amp;web=1&amp;e=B6iMdT" xr:uid="{F70C6EE1-3B65-42A7-BDCF-59B2DC98581C}"/>
     <hyperlink ref="O68" r:id="rId52" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_04 SteerCo.pptx?d=wd44f71dddce1499cb3c5f8a6f9c7fd63&amp;csf=1&amp;web=1&amp;e=40F5If" xr:uid="{60F2AB70-8A56-4F25-B312-E392A4388BC6}"/>
+    <hyperlink ref="O81" r:id="rId53" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_01_29 Northeast Spec Bld Analysis.pptx?d=w9c538d8635b94c129ba00ea7eac27a0e&amp;csf=1&amp;web=1&amp;e=Cn3L1m" xr:uid="{4A6DDCAA-2AC4-4B9D-9AB3-D4FFDD8113C4}"/>
+    <hyperlink ref="O70" r:id="rId54" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_08 SteerCo.pptx?d=wd863957755e742f8bfaaadcb434b30d7&amp;csf=1&amp;web=1&amp;e=6FERxe" xr:uid="{A06FD16C-22D9-4F10-9FC7-D919C3472D73}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21074,13 +21133,13 @@
       <c r="A16" s="97" t="s">
         <v>621</v>
       </c>
-      <c r="B16" s="98">
+      <c r="B16" s="144">
         <v>45859</v>
       </c>
-      <c r="C16" s="98">
+      <c r="C16" s="144">
         <v>46083</v>
       </c>
-      <c r="D16" s="98">
+      <c r="D16" s="144">
         <v>45992</v>
       </c>
       <c r="E16" s="98"/>
@@ -22283,7 +22342,7 @@
         <v>125</v>
       </c>
       <c r="D63" s="98">
-        <v>46170</v>
+        <v>46156</v>
       </c>
       <c r="E63" s="98" t="s">
         <v>125</v>
@@ -22475,21 +22534,21 @@
         <v>297</v>
       </c>
       <c r="N2" s="123">
-        <v>943000</v>
+        <v>643300</v>
       </c>
       <c r="O2" s="123">
-        <v>73205</v>
+        <v>432505</v>
       </c>
       <c r="P2" s="123">
         <v>144708</v>
       </c>
       <c r="Q2" s="123">
         <f>O2+P2</f>
-        <v>217913</v>
+        <v>577213</v>
       </c>
       <c r="R2" s="124">
         <f>Q2/N2</f>
-        <v>0.23108483563096502</v>
+        <v>0.89726877040261155</v>
       </c>
       <c r="S2" t="s">
         <v>497</v>
@@ -22652,7 +22711,7 @@
         <v>308</v>
       </c>
       <c r="N5" s="123">
-        <v>4700300</v>
+        <v>5000000</v>
       </c>
       <c r="O5" s="123">
         <v>1364948</v>
@@ -22666,7 +22725,7 @@
       </c>
       <c r="R5" s="124">
         <f>Q5/N5</f>
-        <v>0.75638789013467222</v>
+        <v>0.71104999999999996</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -26912,15 +26971,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2EBBACD82105340A91324964E93FF49" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7329edaaee89349510b5fe31ddec06b8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a8552d75-6f1f-4d52-93a3-fcd36dc2752d" xmlns:ns3="1785dff3-9909-4165-bde0-36ec47a4b18f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="52e457d9bdc8fb3aec099fc7d60c5993" ns2:_="" ns3:_="">
     <xsd:import namespace="a8552d75-6f1f-4d52-93a3-fcd36dc2752d"/>
@@ -27155,6 +27205,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{752F9F6E-B88F-40CF-A00D-5A52044E6B25}">
   <ds:schemaRefs>
@@ -27173,14 +27232,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8993D78-ABDB-48CF-A6AD-3E9555EB10CC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89752E9E-F7C9-411F-9EA3-B9C1D8EEB123}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27197,4 +27248,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8993D78-ABDB-48CF-A6AD-3E9555EB10CC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/NG Scheduling.xlsx
+++ b/NG Scheduling.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://my.wal-mart.com/personal/k0m0eg1_homeoffice_wal-mart_com/Documents/Desktop/Code Puppy Saved Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1926" documentId="8_{3CD9A91E-A1DC-493E-B251-6A7E654DFCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4765751-D525-45D9-B898-F8D4FD33921A}"/>
+  <xr:revisionPtr revIDLastSave="2081" documentId="8_{3CD9A91E-A1DC-493E-B251-6A7E654DFCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9DC4251-BB90-459C-88AB-C9E951EC4102}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2100" yWindow="2295" windowWidth="38220" windowHeight="17205" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="780" windowWidth="21015" windowHeight="19395" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TUE FC Asset Plan SteerCo" sheetId="2" state="hidden" r:id="rId1"/>
@@ -56,6 +56,7 @@
     <author>tc={FD9F783E-8E52-497E-AE04-AD1241596A30}</author>
     <author>tc={1D534BCA-8427-4D56-835E-F766105CE292}</author>
     <author>tc={B4072AC4-A8EE-4056-AF55-77278AA1688F}</author>
+    <author>tc={6D15E7A5-F995-46E6-93A8-A476159ABD56}</author>
     <author>tc={CF413314-5518-4487-9E68-E5576FB49E1E}</author>
   </authors>
   <commentList>
@@ -123,7 +124,15 @@
     At Risk due Karisa availability.  Site Selection Trip not planned until 8/25</t>
       </text>
     </comment>
-    <comment ref="D63" authorId="8" shapeId="0" xr:uid="{CF413314-5518-4487-9E68-E5576FB49E1E}">
+    <comment ref="A16" authorId="8" shapeId="0" xr:uid="{6D15E7A5-F995-46E6-93A8-A476159ABD56}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Start of Desing is the first Monday after receiving 30% Design DD</t>
+      </text>
+    </comment>
+    <comment ref="D63" authorId="9" shapeId="0" xr:uid="{CF413314-5518-4487-9E68-E5576FB49E1E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -154,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="667">
   <si>
     <t>Fulfillment New Assets SteerCo (Tuesday's)</t>
   </si>
@@ -1135,9 +1144,6 @@
     <t>*-</t>
   </si>
   <si>
-    <t xml:space="preserve">Presenter </t>
-  </si>
-  <si>
     <t>Forum</t>
   </si>
   <si>
@@ -1189,9 +1195,6 @@
     <t>Discuss</t>
   </si>
   <si>
-    <t xml:space="preserve">Prepare </t>
-  </si>
-  <si>
     <t>Decide</t>
   </si>
   <si>
@@ -1216,9 +1219,6 @@
     <t>Wallkill VS Update</t>
   </si>
   <si>
-    <t xml:space="preserve">Carnesville May ASM </t>
-  </si>
-  <si>
     <t>SteerCo 4/3</t>
   </si>
   <si>
@@ -1237,9 +1237,6 @@
     <t>Rob's 1:1 w/Kieran</t>
   </si>
   <si>
-    <t xml:space="preserve">CFO Review </t>
-  </si>
-  <si>
     <t>CPC</t>
   </si>
   <si>
@@ -1264,15 +1261,9 @@
     <t>Walmart Week</t>
   </si>
   <si>
-    <t xml:space="preserve">Mechanisms </t>
-  </si>
-  <si>
     <t>DD for MCO, MSP, DEN, SEA</t>
   </si>
   <si>
-    <t xml:space="preserve">Socialization Strategy </t>
-  </si>
-  <si>
     <t>Submitter</t>
   </si>
   <si>
@@ -1474,9 +1465,6 @@
     <t>WW Turn-in Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Turn-in Date </t>
-  </si>
-  <si>
     <t>Turn-in Time</t>
   </si>
   <si>
@@ -1561,18 +1549,12 @@
     <t>Quarter</t>
   </si>
   <si>
-    <t>Phase 1 Go-Live</t>
-  </si>
-  <si>
     <t>FY29 3Q</t>
   </si>
   <si>
     <t>FY30 2Q</t>
   </si>
   <si>
-    <t>Phase 2 Go-Live</t>
-  </si>
-  <si>
     <t>FY30 Q2</t>
   </si>
   <si>
@@ -1606,9 +1588,6 @@
     <t>Seattle, WA</t>
   </si>
   <si>
-    <t xml:space="preserve">Buckeye, AZ </t>
-  </si>
-  <si>
     <t xml:space="preserve">Location </t>
   </si>
   <si>
@@ -1633,9 +1612,6 @@
     <t>Stockton, CA</t>
   </si>
   <si>
-    <t xml:space="preserve">Joliet, IL </t>
-  </si>
-  <si>
     <t>Lancaster, TX</t>
   </si>
   <si>
@@ -1669,15 +1645,9 @@
     <t>NextGen Greenfield</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Sort New Site </t>
-  </si>
-  <si>
     <t>Pheonix, AZ</t>
   </si>
   <si>
-    <t xml:space="preserve">In Flight </t>
-  </si>
-  <si>
     <t>Charlotte, NC</t>
   </si>
   <si>
@@ -1693,9 +1663,6 @@
     <t>Shoemakersville, PA</t>
   </si>
   <si>
-    <t xml:space="preserve">August ASM </t>
-  </si>
-  <si>
     <t>East Hartford, CT</t>
   </si>
   <si>
@@ -1705,12 +1672,6 @@
     <t>Chino, CA</t>
   </si>
   <si>
-    <t xml:space="preserve">IND1 ICC + Two-Tier </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indianapolis, IN </t>
-  </si>
-  <si>
     <t>FY28 Q1</t>
   </si>
   <si>
@@ -1720,18 +1681,9 @@
     <t>FY27 Q3</t>
   </si>
   <si>
-    <t xml:space="preserve"> FY28 Q2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FY28 Q1</t>
-  </si>
-  <si>
     <t>FY29 Q1</t>
   </si>
   <si>
-    <t xml:space="preserve"> FY29 Q1 </t>
-  </si>
-  <si>
     <t>SteerCo</t>
   </si>
   <si>
@@ -1945,9 +1897,6 @@
     <t>4/16: $500K funded for campus site selection</t>
   </si>
   <si>
-    <t xml:space="preserve">Pivot from Las Vegas to Phoenix </t>
-  </si>
-  <si>
     <t>Approved</t>
   </si>
   <si>
@@ -1969,12 +1918,6 @@
     <t>Carnesville Business Case</t>
   </si>
   <si>
-    <t xml:space="preserve">Matt Termeer </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Increase IP from 60% to 80% </t>
-  </si>
-  <si>
     <t>Hrishi Badve</t>
   </si>
   <si>
@@ -1984,9 +1927,6 @@
     <t>Brook Weeks</t>
   </si>
   <si>
-    <t xml:space="preserve">Buckeye Site Selection </t>
-  </si>
-  <si>
     <t>Allison Coontz</t>
   </si>
   <si>
@@ -1996,9 +1936,6 @@
     <t>Impact to Increase in IP Increase</t>
   </si>
   <si>
-    <t xml:space="preserve">IP Limit </t>
-  </si>
-  <si>
     <t>IP Increase Impact to Business Case</t>
   </si>
   <si>
@@ -2017,18 +1954,9 @@
     <t>Wallkill Timeline push from Nov FY30 to May FY31</t>
   </si>
   <si>
-    <t xml:space="preserve">Karen Slatton </t>
-  </si>
-  <si>
     <t>Wallkill BDR Sign-off</t>
   </si>
   <si>
-    <t xml:space="preserve"> Adding Project Antelope to Carnesville Business Case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost to Serve Alignment </t>
-  </si>
-  <si>
     <t>Decision &amp; Outcome</t>
   </si>
   <si>
@@ -2038,18 +1966,12 @@
     <t>Follow-up</t>
   </si>
   <si>
-    <t>Need Rob's feedback.  Follow up required</t>
-  </si>
-  <si>
     <t>Move forward to CPC</t>
   </si>
   <si>
     <t>Pivot from Las Vegas to Phoenix</t>
   </si>
   <si>
-    <t xml:space="preserve">Carnesville Full Capital Ask </t>
-  </si>
-  <si>
     <t>Wallkill Go Live date push from Nov to May</t>
   </si>
   <si>
@@ -2077,21 +1999,12 @@
     <t>FY26</t>
   </si>
   <si>
-    <t xml:space="preserve">Aligned to Pivot to Phoenix </t>
-  </si>
-  <si>
-    <t xml:space="preserve">NextGen vs Depot Strategy </t>
-  </si>
-  <si>
     <t>Carnesville May ASM Content Alignment</t>
   </si>
   <si>
     <t>Wallkill status update with pollical risk</t>
   </si>
   <si>
-    <t xml:space="preserve">Wallkill business case </t>
-  </si>
-  <si>
     <t>Stop due diligence for Douglas</t>
   </si>
   <si>
@@ -2146,15 +2059,9 @@
     <t>26_03_12 SteerCo.pptx</t>
   </si>
   <si>
-    <t xml:space="preserve">Additional follow-up Required </t>
-  </si>
-  <si>
     <t>26_04_02 SteerCo Cost to Server Carnesville Maintenance Strategy.pptx</t>
   </si>
   <si>
-    <t xml:space="preserve">Approved to adding Project Antelope to all NextGen Business Cases </t>
-  </si>
-  <si>
     <t>Proceed with Option 1</t>
   </si>
   <si>
@@ -2179,18 +2086,12 @@
     <t xml:space="preserve">FY Capacity Added </t>
   </si>
   <si>
-    <t>Moratorium Vote</t>
-  </si>
-  <si>
     <t>Site Selection Trip</t>
   </si>
   <si>
     <t>Follow up Buckeye: Transportation &amp; Solar Land Requirements</t>
   </si>
   <si>
-    <t xml:space="preserve"> Karisa Sprague, Adam Dunbar, John Clinton</t>
-  </si>
-  <si>
     <t>Burn Testing for NextGen</t>
   </si>
   <si>
@@ -2200,9 +2101,6 @@
     <t>Talking Points &amp; FAQ Updated</t>
   </si>
   <si>
-    <t xml:space="preserve">Carnesville Pre-socialization </t>
-  </si>
-  <si>
     <t>FOX</t>
   </si>
   <si>
@@ -2257,24 +2155,12 @@
     <t>26_02_26 SteerCo Carnesville BC_IP Increase Yard Trucks.pptx</t>
   </si>
   <si>
-    <t xml:space="preserve">Fulfillment Ecosystem </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seth Dallaire &amp; Manish Joneja </t>
-  </si>
-  <si>
-    <t>Carnesville Pre-socialization + MSM  w/ Tracy Poulliot , Camilo Canedo, Dan Fleming</t>
-  </si>
-  <si>
     <t>Carnesville Pre-socialization w/ Latriece Watkins &amp; Tom Ward</t>
   </si>
   <si>
     <t>Carnesville Pre-socialization + MSM / Todd Sears</t>
   </si>
   <si>
-    <t xml:space="preserve">Carnesville Pre-socialization + MSM w/ Seth Dallaire &amp; Manish Joneja </t>
-  </si>
-  <si>
     <t>Carnesville Pre-socialization / Tim Skinner</t>
   </si>
   <si>
@@ -2284,9 +2170,6 @@
     <t>Carnesville Pre-socialization + MSM / Julie Barber</t>
   </si>
   <si>
-    <t xml:space="preserve">Buckeye Transportation Land Requirements w/ Rob Montgomery </t>
-  </si>
-  <si>
     <t>Rob Montgomery and Ryan McDaniels</t>
   </si>
   <si>
@@ -2302,9 +2185,6 @@
     <t>Not approved - Scheduling follow up</t>
   </si>
   <si>
-    <t xml:space="preserve">Approved </t>
-  </si>
-  <si>
     <t>26_04_24 Buckeye Land Purchase Alignment.pptx</t>
   </si>
   <si>
@@ -2317,9 +2197,6 @@
     <t>Van Delivery Requirements / Flow</t>
   </si>
   <si>
-    <t xml:space="preserve">Solar location for Buckeye </t>
-  </si>
-  <si>
     <t>Logan Jones</t>
   </si>
   <si>
@@ -2338,18 +2215,9 @@
     <t>Preliminary IRR for PHX, MCO, MSP, DEN, SEA</t>
   </si>
   <si>
-    <t xml:space="preserve">Reassess 450-mile centroid radius with impact to same day for MCO, MSP, DEN, SEA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Market Model Coverage with peak and off-peak (Stores, Depots, NextGen Conventional FC) </t>
-  </si>
-  <si>
     <t>Dave Guggina</t>
   </si>
   <si>
-    <t xml:space="preserve">Jon Furner </t>
-  </si>
-  <si>
     <t>Ellen Sloneker, Phil Herr</t>
   </si>
   <si>
@@ -2362,9 +2230,6 @@
     <t>26_04_30 SteerCo.pptx</t>
   </si>
   <si>
-    <t xml:space="preserve">Site Selection Date Scheduling - MCO, MSP, SEA, DEN </t>
-  </si>
-  <si>
     <t>26_05_04 SteerCo.pptx</t>
   </si>
   <si>
@@ -2383,24 +2248,9 @@
     <t>Advaith Venkataraman</t>
   </si>
   <si>
-    <t>4:00PM</t>
-  </si>
-  <si>
     <t>Andrew Skinkle</t>
   </si>
   <si>
-    <t>Approved.  Matt Termeer finding funding</t>
-  </si>
-  <si>
-    <t>Wallkill  Next Steps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallkill IRR &amp; CapEx </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Need follow up </t>
-  </si>
-  <si>
     <t>Approved: Option 1 Carport + Zone 3</t>
   </si>
   <si>
@@ -2410,9 +2260,6 @@
     <t>Adam Dunbar, Jack Anderson</t>
   </si>
   <si>
-    <t xml:space="preserve">Advaith Venkataraman / Andrew </t>
-  </si>
-  <si>
     <t>Not approved to move forward with Spec Building</t>
   </si>
   <si>
@@ -2426,6 +2273,186 @@
   </si>
   <si>
     <t>26_05_08 SteerCo.pptx</t>
+  </si>
+  <si>
+    <t>Focus on Building Options (1) ORD Style, (2) BDL (3) Reduced footprint maintain 2M SKU</t>
+  </si>
+  <si>
+    <t>Wallkill IRR &amp; CapEx (Building Scenario's)</t>
+  </si>
+  <si>
+    <t>26_05_14 SteerCo.pptx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moratorium Termination </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Town Board Review Height Variance </t>
+  </si>
+  <si>
+    <t>Zoning Board Review Heigh Variance</t>
+  </si>
+  <si>
+    <t>Nicole Blyth</t>
+  </si>
+  <si>
+    <t>Approved to move to ASM</t>
+  </si>
+  <si>
+    <t>Pending decision if this is Karisa's OpEx or Vik's R&amp;D</t>
+  </si>
+  <si>
+    <t>PK Sabherwal &amp; Matt Termeer</t>
+  </si>
+  <si>
+    <t>26_04_30 NextGen Burn Testing OpEx Required.pptx</t>
+  </si>
+  <si>
+    <t>Burn Testing for NextGen (Decision Needed by June 1st)</t>
+  </si>
+  <si>
+    <t>PSA Signing</t>
+  </si>
+  <si>
+    <t>Carnesville ASM Dry Run</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>Feedback for Talking Points and FAQ prior to ASM</t>
+  </si>
+  <si>
+    <t>Mechanisms</t>
+  </si>
+  <si>
+    <t>Increase IP from 60% to 80%</t>
+  </si>
+  <si>
+    <t>NextGen vs Depot Strategy</t>
+  </si>
+  <si>
+    <t>Buckeye Site Selection</t>
+  </si>
+  <si>
+    <t>IP Limit</t>
+  </si>
+  <si>
+    <t>Fulfillment Ecosystem</t>
+  </si>
+  <si>
+    <t>Adding Project Antelope to Carnesville Business Case</t>
+  </si>
+  <si>
+    <t>Cost to Serve Alignment</t>
+  </si>
+  <si>
+    <t>REC Dry Run</t>
+  </si>
+  <si>
+    <t>Socialization Strategy</t>
+  </si>
+  <si>
+    <t>Carnesville Pre-socialization + MSM w/ Seth Dallaire &amp; Manish Joneja</t>
+  </si>
+  <si>
+    <t>Buckeye Transportation Land Requirements w/ Rob Montgomery</t>
+  </si>
+  <si>
+    <t>Carnesville Pre-socialization + MSM w/ Tracy Poulliot , Camilo Canedo, Dan Fleming</t>
+  </si>
+  <si>
+    <t>Solar location for Buckeye</t>
+  </si>
+  <si>
+    <t>Wallkill Next Steps</t>
+  </si>
+  <si>
+    <t>Wallkill IRR &amp; CapEx</t>
+  </si>
+  <si>
+    <t>Reassess 450-mile centroid radius with impact to same day for MCO, MSP, DEN, SEA</t>
+  </si>
+  <si>
+    <t>Review Market Model Coverage with peak and off-peak (Stores, Depots, NextGen Conventional FC)</t>
+  </si>
+  <si>
+    <t>Site Selection Date Scheduling - MCO, MSP, SEA, DEN</t>
+  </si>
+  <si>
+    <t>Turn-in Date</t>
+  </si>
+  <si>
+    <t>Presenter</t>
+  </si>
+  <si>
+    <t>Karen Slatton</t>
+  </si>
+  <si>
+    <t>Advaith Venkataraman / Andrew</t>
+  </si>
+  <si>
+    <t>Prepare</t>
+  </si>
+  <si>
+    <t>Aligned to Pivot to Phoenix</t>
+  </si>
+  <si>
+    <t>Additional follow-up Required</t>
+  </si>
+  <si>
+    <t>Carnesville Pre-socialization</t>
+  </si>
+  <si>
+    <t>Approved to adding Project Antelope to all NextGen Business Cases</t>
+  </si>
+  <si>
+    <t>Need Rob's feedback. Follow up required</t>
+  </si>
+  <si>
+    <t>Approved. Matt Termeer finding funding</t>
+  </si>
+  <si>
+    <t>Need follow up</t>
+  </si>
+  <si>
+    <t>Carnesville May ASM</t>
+  </si>
+  <si>
+    <t>Seth Dallaire &amp; Manish Joneja</t>
+  </si>
+  <si>
+    <t>Karisa Sprague, Adam Dunbar, John Clinton</t>
+  </si>
+  <si>
+    <t>Jon Furner</t>
+  </si>
+  <si>
+    <t>Warning / Callout</t>
+  </si>
+  <si>
+    <t>Placeholder until real date/information is updated</t>
+  </si>
+  <si>
+    <t>Project Start</t>
+  </si>
+  <si>
+    <t>Joliet, IL</t>
+  </si>
+  <si>
+    <t>Non-Sort New Site</t>
+  </si>
+  <si>
+    <t>August ASM</t>
+  </si>
+  <si>
+    <t>LAX2 ICC Expansion</t>
+  </si>
+  <si>
+    <t>IND1 ICC + Two-Tier</t>
+  </si>
+  <si>
+    <t>26_05_20 SteerCo Wallkill Scenarios.pptx</t>
   </si>
 </sst>
 </file>
@@ -2439,7 +2466,7 @@
     <numFmt numFmtId="166" formatCode="[$-409]h:mm\ AM/PM;@"/>
     <numFmt numFmtId="167" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2561,8 +2588,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2596,12 +2631,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2895,7 +2924,7 @@
     <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3263,9 +3292,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3279,6 +3305,12 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3286,9 +3318,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3746,6 +3775,9 @@
   <threadedComment ref="F15" dT="2026-04-23T21:00:07.11" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{B4072AC4-A8EE-4056-AF55-77278AA1688F}">
     <text>At Risk due Karisa availability.  Site Selection Trip not planned until 8/25</text>
   </threadedComment>
+  <threadedComment ref="A16" dT="2026-05-08T20:34:59.47" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{6D15E7A5-F995-46E6-93A8-A476159ABD56}">
+    <text>Start of Desing is the first Monday after receiving 30% Design DD</text>
+  </threadedComment>
   <threadedComment ref="D63" dT="2026-04-23T19:26:15.32" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{CF413314-5518-4487-9E68-E5576FB49E1E}">
     <text>Got pulled from the agenda on 4/23/26 due to a legal not having the right signature.  Pending Rescheduling</text>
   </threadedComment>
@@ -8393,82 +8425,82 @@
   <sheetData>
     <row r="1" spans="1:35" s="7" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A1" s="100" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B1" s="66" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C1" s="87" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="133" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E1" s="101" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F1" s="66" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="66" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="H1" s="106" t="s">
-        <v>343</v>
+        <v>642</v>
       </c>
       <c r="I1" s="102" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="J1" s="66" t="s">
         <v>4</v>
       </c>
       <c r="K1" s="66" t="s">
-        <v>230</v>
+        <v>643</v>
       </c>
       <c r="L1" s="88" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="M1" s="88" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N1" s="87" t="s">
-        <v>528</v>
+        <v>501</v>
       </c>
       <c r="O1" s="87" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="P1" s="88" t="s">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="AI1" s="99" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>543</v>
+        <v>514</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C2" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D2" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E2" s="132">
         <v>46044</v>
       </c>
       <c r="F2" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="G2" s="33" t="str">
         <f>A2</f>
         <v>FY26</v>
       </c>
       <c r="H2" s="98">
-        <f t="shared" ref="H2:H30" si="0">E2-1</f>
+        <f t="shared" ref="H2:H32" si="0">E2-1</f>
         <v>46043</v>
       </c>
       <c r="I2" s="103">
@@ -8484,32 +8516,32 @@
         <v>142</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="N2" s="32" t="s">
-        <v>544</v>
+        <v>517</v>
       </c>
       <c r="P2" s="92"/>
       <c r="AI2" s="91"/>
     </row>
     <row r="3" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>543</v>
+        <v>514</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C3" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D3" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E3" s="132">
         <v>46044</v>
       </c>
       <c r="F3" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="G3" s="33" t="str">
         <f>A3</f>
@@ -8532,7 +8564,7 @@
         <v>142</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="P3" s="92"/>
       <c r="AI3" s="91">
@@ -8542,22 +8574,22 @@
     </row>
     <row r="4" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
-        <v>543</v>
+        <v>514</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C4" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D4" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E4" s="132">
         <v>46044</v>
       </c>
       <c r="F4" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G4" s="33" t="str">
         <f>A4</f>
@@ -8580,10 +8612,10 @@
         <v>142</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="N4" s="32" t="s">
-        <v>549</v>
+        <v>647</v>
       </c>
       <c r="P4" s="92"/>
       <c r="AI4" s="91">
@@ -8593,22 +8625,22 @@
     </row>
     <row r="5" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
-        <v>543</v>
+        <v>514</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C5" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E5" s="132">
         <v>46045</v>
       </c>
       <c r="F5" t="s">
-        <v>533</v>
+        <v>505</v>
       </c>
       <c r="G5" s="33" t="str">
         <f>A5</f>
@@ -8625,16 +8657,16 @@
         <v>30</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N5" s="32" t="s">
-        <v>544</v>
+        <v>647</v>
       </c>
       <c r="P5" s="92"/>
       <c r="AI5" s="91">
@@ -8643,55 +8675,60 @@
       </c>
     </row>
     <row r="6" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="33">
+      <c r="A6" s="33" t="e">
         <f>IF(ISBLANK(E6),"",_xlfn.XLOOKUP(E6,Info!A:A,Info!B:B))</f>
-        <v>1</v>
+        <v>#N/A</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="D6" s="134" t="s">
-        <v>273</v>
-      </c>
-      <c r="E6" s="132">
-        <v>46056</v>
-      </c>
-      <c r="F6" t="s">
-        <v>533</v>
-      </c>
-      <c r="G6" s="33">
+      <c r="D6" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E6" s="91">
+        <v>46051</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>605</v>
+      </c>
+      <c r="G6" s="33" t="e">
         <f>IF(ISBLANK(H6),"",_xlfn.XLOOKUP(H6,Info!A:A,Info!B:B))</f>
-        <v>1</v>
+        <v>#N/A</v>
       </c>
       <c r="H6" s="98">
         <f t="shared" si="0"/>
-        <v>46055</v>
+        <v>46050</v>
       </c>
       <c r="I6" s="103">
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J6" s="33">
         <v>30</v>
       </c>
       <c r="K6" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="L6" s="33" t="s">
         <v>244</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>501</v>
+      <c r="M6" s="67" t="s">
+        <v>247</v>
       </c>
       <c r="N6" s="92" t="s">
-        <v>544</v>
-      </c>
-      <c r="P6" s="92"/>
+        <v>602</v>
+      </c>
+      <c r="O6" s="118" t="s">
+        <v>603</v>
+      </c>
+      <c r="P6" s="92" t="s">
+        <v>604</v>
+      </c>
       <c r="AI6" s="91">
         <f t="shared" si="1"/>
-        <v>46055</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="7" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
@@ -8700,19 +8737,19 @@
         <v>1</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C7" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D7" s="134" t="s">
-        <v>273</v>
+        <v>623</v>
       </c>
       <c r="E7" s="132">
         <v>46056</v>
       </c>
       <c r="F7" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="G7" s="33">
         <f>IF(ISBLANK(H7),"",_xlfn.XLOOKUP(H7,Info!A:A,Info!B:B))</f>
@@ -8729,15 +8766,17 @@
         <v>30</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="N7" s="92"/>
+        <v>511</v>
+      </c>
+      <c r="N7" s="92" t="s">
+        <v>518</v>
+      </c>
       <c r="P7" s="92"/>
       <c r="AI7" s="91">
         <f t="shared" si="1"/>
@@ -8750,19 +8789,19 @@
         <v>1</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C8" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D8" s="134" t="s">
-        <v>273</v>
+        <v>623</v>
       </c>
       <c r="E8" s="132">
         <v>46056</v>
       </c>
       <c r="F8" t="s">
-        <v>538</v>
+        <v>509</v>
       </c>
       <c r="G8" s="33">
         <f>IF(ISBLANK(H8),"",_xlfn.XLOOKUP(H8,Info!A:A,Info!B:B))</f>
@@ -8779,16 +8818,16 @@
         <v>30</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>540</v>
+        <v>511</v>
       </c>
       <c r="N8" s="92" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="P8" s="92"/>
       <c r="AI8" s="91">
@@ -8802,19 +8841,19 @@
         <v>1</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D9" s="134" t="s">
-        <v>273</v>
+        <v>623</v>
       </c>
       <c r="E9" s="132">
         <v>46056</v>
       </c>
       <c r="F9" t="s">
-        <v>539</v>
+        <v>482</v>
       </c>
       <c r="G9" s="33">
         <f>IF(ISBLANK(H9),"",_xlfn.XLOOKUP(H9,Info!A:A,Info!B:B))</f>
@@ -8831,17 +8870,15 @@
         <v>30</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="N9" s="92" t="s">
-        <v>550</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="N9" s="92"/>
       <c r="P9" s="92"/>
       <c r="AI9" s="91">
         <f t="shared" si="1"/>
@@ -8851,30 +8888,30 @@
     <row r="10" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <f>IF(ISBLANK(E10),"",_xlfn.XLOOKUP(E10,Info!A:A,Info!B:B))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C10" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="D10" s="54" t="s">
-        <v>429</v>
+      <c r="D10" s="134" t="s">
+        <v>623</v>
       </c>
       <c r="E10" s="132">
-        <v>46073</v>
+        <v>46056</v>
       </c>
       <c r="F10" t="s">
         <v>505</v>
       </c>
       <c r="G10" s="33">
         <f>IF(ISBLANK(H10),"",_xlfn.XLOOKUP(H10,Info!A:A,Info!B:B))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" s="98">
         <f t="shared" si="0"/>
-        <v>46072</v>
+        <v>46055</v>
       </c>
       <c r="I10" s="103">
         <v>0.625</v>
@@ -8882,22 +8919,22 @@
       <c r="J10" s="33">
         <v>30</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>207</v>
+      <c r="K10" s="33" t="s">
+        <v>243</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="N10" s="32" t="s">
-        <v>602</v>
+        <v>481</v>
+      </c>
+      <c r="N10" s="92" t="s">
+        <v>647</v>
       </c>
       <c r="P10" s="92"/>
       <c r="AI10" s="91">
         <f t="shared" si="1"/>
-        <v>46072</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="11" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
@@ -8906,19 +8943,19 @@
         <v>3</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D11" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E11" s="132">
         <v>46073</v>
       </c>
       <c r="F11" t="s">
-        <v>506</v>
+        <v>485</v>
       </c>
       <c r="G11" s="33">
         <f>IF(ISBLANK(H11),"",_xlfn.XLOOKUP(H11,Info!A:A,Info!B:B))</f>
@@ -8941,13 +8978,10 @@
         <v>142</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="N11" s="32" t="s">
-        <v>551</v>
-      </c>
-      <c r="O11" s="118" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="P11" s="92"/>
       <c r="AI11" s="91">
@@ -8958,30 +8992,30 @@
     <row r="12" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33">
         <f>IF(ISBLANK(E12),"",_xlfn.XLOOKUP(E12,Info!A:A,Info!B:B))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C12" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D12" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E12" s="132">
-        <v>46079</v>
+        <v>46073</v>
       </c>
       <c r="F12" t="s">
-        <v>507</v>
+        <v>486</v>
       </c>
       <c r="G12" s="33">
         <f>IF(ISBLANK(H12),"",_xlfn.XLOOKUP(H12,Info!A:A,Info!B:B))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" s="98">
         <f t="shared" si="0"/>
-        <v>46078</v>
+        <v>46072</v>
       </c>
       <c r="I12" s="103">
         <v>0.625</v>
@@ -8990,19 +9024,24 @@
         <v>30</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>508</v>
+        <v>207</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="O12" s="118"/>
+        <v>484</v>
+      </c>
+      <c r="N12" s="32" t="s">
+        <v>519</v>
+      </c>
+      <c r="O12" s="118" t="s">
+        <v>520</v>
+      </c>
       <c r="P12" s="92"/>
       <c r="AI12" s="91">
         <f t="shared" si="1"/>
-        <v>46078</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="13" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
@@ -9011,19 +9050,19 @@
         <v>4</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C13" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D13" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E13" s="132">
         <v>46079</v>
       </c>
       <c r="F13" t="s">
-        <v>509</v>
+        <v>487</v>
       </c>
       <c r="G13" s="33">
         <f>IF(ISBLANK(H13),"",_xlfn.XLOOKUP(H13,Info!A:A,Info!B:B))</f>
@@ -9040,17 +9079,15 @@
         <v>30</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>510</v>
+        <v>234</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="O13" s="118" t="s">
-        <v>603</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="O13" s="118"/>
       <c r="P13" s="92"/>
       <c r="AI13" s="91">
         <f t="shared" si="1"/>
@@ -9063,19 +9100,19 @@
         <v>4</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C14" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D14" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E14" s="132">
         <v>46079</v>
       </c>
       <c r="F14" t="s">
-        <v>511</v>
+        <v>489</v>
       </c>
       <c r="G14" s="33">
         <f>IF(ISBLANK(H14),"",_xlfn.XLOOKUP(H14,Info!A:A,Info!B:B))</f>
@@ -9092,16 +9129,16 @@
         <v>30</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>512</v>
+        <v>490</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="O14" s="118" t="s">
-        <v>603</v>
+        <v>566</v>
       </c>
       <c r="P14" s="92"/>
       <c r="AI14" s="91">
@@ -9115,19 +9152,19 @@
         <v>4</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="D15" s="134" t="s">
-        <v>263</v>
+      <c r="D15" s="54" t="s">
+        <v>410</v>
       </c>
       <c r="E15" s="132">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="F15" t="s">
-        <v>538</v>
+        <v>624</v>
       </c>
       <c r="G15" s="33">
         <f>IF(ISBLANK(H15),"",_xlfn.XLOOKUP(H15,Info!A:A,Info!B:B))</f>
@@ -9135,7 +9172,7 @@
       </c>
       <c r="H15" s="98">
         <f t="shared" si="0"/>
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="I15" s="103">
         <v>0.625</v>
@@ -9143,20 +9180,22 @@
       <c r="J15" s="33">
         <v>30</v>
       </c>
-      <c r="K15" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="L15" s="33" t="s">
-        <v>244</v>
+      <c r="K15" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="N15" s="92"/>
+        <v>481</v>
+      </c>
+      <c r="O15" s="118" t="s">
+        <v>566</v>
+      </c>
       <c r="P15" s="92"/>
       <c r="AI15" s="91">
         <f>H15</f>
-        <v>46079</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="16" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
@@ -9165,19 +9204,19 @@
         <v>4</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C16" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D16" s="134" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E16" s="132">
         <v>46080</v>
       </c>
       <c r="F16" t="s">
-        <v>545</v>
+        <v>509</v>
       </c>
       <c r="G16" s="33">
         <f>IF(ISBLANK(H16),"",_xlfn.XLOOKUP(H16,Info!A:A,Info!B:B))</f>
@@ -9194,13 +9233,13 @@
         <v>30</v>
       </c>
       <c r="K16" s="33" t="s">
-        <v>542</v>
+        <v>243</v>
       </c>
       <c r="L16" s="33" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>541</v>
+        <v>481</v>
       </c>
       <c r="N16" s="92"/>
       <c r="P16" s="92"/>
@@ -9212,30 +9251,30 @@
     <row r="17" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <f>IF(ISBLANK(E17),"",_xlfn.XLOOKUP(E17,Info!A:A,Info!B:B))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C17" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="D17" s="54" t="s">
-        <v>429</v>
+      <c r="D17" s="134" t="s">
+        <v>260</v>
       </c>
       <c r="E17" s="132">
-        <v>46083</v>
+        <v>46080</v>
       </c>
       <c r="F17" t="s">
-        <v>513</v>
+        <v>625</v>
       </c>
       <c r="G17" s="33">
         <f>IF(ISBLANK(H17),"",_xlfn.XLOOKUP(H17,Info!A:A,Info!B:B))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H17" s="98">
         <f t="shared" si="0"/>
-        <v>46082</v>
+        <v>46079</v>
       </c>
       <c r="I17" s="103">
         <v>0.625</v>
@@ -9243,19 +9282,20 @@
       <c r="J17" s="33">
         <v>30</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>142</v>
+      <c r="K17" s="33" t="s">
+        <v>513</v>
+      </c>
+      <c r="L17" s="33" t="s">
+        <v>243</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>515</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="N17" s="92"/>
       <c r="P17" s="92"/>
       <c r="AI17" s="91">
         <f t="shared" si="1"/>
-        <v>46082</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="18" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
@@ -9264,19 +9304,19 @@
         <v>5</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C18" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D18" s="54" t="s">
-        <v>232</v>
+        <v>410</v>
       </c>
       <c r="E18" s="132">
         <v>46083</v>
       </c>
       <c r="F18" t="s">
-        <v>513</v>
+        <v>626</v>
       </c>
       <c r="G18" s="33">
         <f>IF(ISBLANK(H18),"",_xlfn.XLOOKUP(H18,Info!A:A,Info!B:B))</f>
@@ -9293,15 +9333,14 @@
         <v>30</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="L18" s="33" t="s">
+        <v>491</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="N18" s="92"/>
+        <v>492</v>
+      </c>
       <c r="P18" s="92"/>
       <c r="AI18" s="91">
         <f t="shared" si="1"/>
@@ -9314,19 +9353,19 @@
         <v>5</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C19" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D19" s="54" t="s">
-        <v>429</v>
+        <v>231</v>
       </c>
       <c r="E19" s="132">
-        <v>46086</v>
+        <v>46083</v>
       </c>
       <c r="F19" t="s">
-        <v>516</v>
+        <v>626</v>
       </c>
       <c r="G19" s="33">
         <f>IF(ISBLANK(H19),"",_xlfn.XLOOKUP(H19,Info!A:A,Info!B:B))</f>
@@ -9334,7 +9373,7 @@
       </c>
       <c r="H19" s="98">
         <f t="shared" si="0"/>
-        <v>46085</v>
+        <v>46082</v>
       </c>
       <c r="I19" s="103">
         <v>0.625</v>
@@ -9343,21 +9382,19 @@
         <v>30</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="L19" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="L19" s="33" t="s">
         <v>142</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="O19" s="118" t="s">
-        <v>563</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="N19" s="92"/>
       <c r="P19" s="92"/>
       <c r="AI19" s="91">
         <f t="shared" si="1"/>
-        <v>46085</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="20" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
@@ -9366,19 +9403,19 @@
         <v>5</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C20" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D20" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E20" s="132">
         <v>46086</v>
       </c>
       <c r="F20" t="s">
-        <v>517</v>
+        <v>493</v>
       </c>
       <c r="G20" s="33">
         <f>IF(ISBLANK(H20),"",_xlfn.XLOOKUP(H20,Info!A:A,Info!B:B))</f>
@@ -9395,17 +9432,18 @@
         <v>30</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>510</v>
+        <v>207</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O20" s="118" t="s">
-        <v>563</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="P20" s="92"/>
       <c r="AI20" s="91">
         <f t="shared" si="1"/>
         <v>46085</v>
@@ -9417,19 +9455,19 @@
         <v>5</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C21" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D21" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E21" s="132">
         <v>46086</v>
       </c>
       <c r="F21" t="s">
-        <v>518</v>
+        <v>494</v>
       </c>
       <c r="G21" s="33">
         <f>IF(ISBLANK(H21),"",_xlfn.XLOOKUP(H21,Info!A:A,Info!B:B))</f>
@@ -9446,19 +9484,19 @@
         <v>30</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>508</v>
+        <v>234</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N21" s="32" t="s">
-        <v>602</v>
+        <v>565</v>
       </c>
       <c r="O21" s="118" t="s">
-        <v>563</v>
+        <v>531</v>
       </c>
       <c r="P21" s="92"/>
       <c r="AI21" s="91">
@@ -9472,19 +9510,19 @@
         <v>5</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C22" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E22" s="132">
         <v>46086</v>
       </c>
       <c r="F22" t="s">
-        <v>519</v>
+        <v>627</v>
       </c>
       <c r="G22" s="33">
         <f>IF(ISBLANK(H22),"",_xlfn.XLOOKUP(H22,Info!A:A,Info!B:B))</f>
@@ -9501,47 +9539,46 @@
         <v>30</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>142</v>
+        <v>488</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O22" s="118" t="s">
-        <v>563</v>
-      </c>
-      <c r="P22" s="92"/>
+        <v>531</v>
+      </c>
       <c r="AI22" s="91"/>
     </row>
     <row r="23" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <f>IF(ISBLANK(E23),"",_xlfn.XLOOKUP(E23,Info!A:A,Info!B:B))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C23" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D23" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E23" s="132">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="F23" t="s">
-        <v>564</v>
+        <v>495</v>
       </c>
       <c r="G23" s="33">
         <f>IF(ISBLANK(H23),"",_xlfn.XLOOKUP(H23,Info!A:A,Info!B:B))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23" s="98">
         <f t="shared" si="0"/>
-        <v>46092</v>
+        <v>46085</v>
       </c>
       <c r="I23" s="103">
         <v>0.625</v>
@@ -9550,19 +9587,16 @@
         <v>30</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>520</v>
+        <v>142</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="N23" s="32" t="s">
-        <v>565</v>
+        <v>237</v>
       </c>
       <c r="O23" s="118" t="s">
-        <v>617</v>
+        <v>531</v>
       </c>
       <c r="P23" s="92"/>
       <c r="AI23" s="91"/>
@@ -9573,19 +9607,19 @@
         <v>6</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C24" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D24" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E24" s="132">
         <v>46093</v>
       </c>
       <c r="F24" t="s">
-        <v>521</v>
+        <v>497</v>
       </c>
       <c r="G24" s="33">
         <f>IF(ISBLANK(H24),"",_xlfn.XLOOKUP(H24,Info!A:A,Info!B:B))</f>
@@ -9602,19 +9636,19 @@
         <v>30</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>510</v>
+        <v>488</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>504</v>
+        <v>484</v>
       </c>
       <c r="N24" s="32" t="s">
-        <v>567</v>
+        <v>648</v>
       </c>
       <c r="O24" s="118" t="s">
-        <v>566</v>
+        <v>534</v>
       </c>
       <c r="P24" s="92"/>
       <c r="AI24" s="91"/>
@@ -9625,19 +9659,19 @@
         <v>6</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C25" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D25" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E25" s="132">
         <v>46093</v>
       </c>
       <c r="F25" t="s">
-        <v>522</v>
+        <v>498</v>
       </c>
       <c r="G25" s="33">
         <f>IF(ISBLANK(H25),"",_xlfn.XLOOKUP(H25,Info!A:A,Info!B:B))</f>
@@ -9654,16 +9688,16 @@
         <v>30</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>508</v>
+        <v>234</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O25" s="118" t="s">
-        <v>566</v>
+        <v>534</v>
       </c>
       <c r="P25" s="92"/>
       <c r="AI25" s="91"/>
@@ -9674,19 +9708,19 @@
         <v>6</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C26" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D26" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E26" s="132">
         <v>46093</v>
       </c>
       <c r="F26" t="s">
-        <v>546</v>
+        <v>515</v>
       </c>
       <c r="G26" s="33">
         <f>IF(ISBLANK(H26),"",_xlfn.XLOOKUP(H26,Info!A:A,Info!B:B))</f>
@@ -9709,10 +9743,10 @@
         <v>142</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O26" s="118" t="s">
-        <v>566</v>
+        <v>534</v>
       </c>
       <c r="P26" s="92"/>
       <c r="AI26" s="91"/>
@@ -9720,30 +9754,30 @@
     <row r="27" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33">
         <f>IF(ISBLANK(E27),"",_xlfn.XLOOKUP(E27,Info!A:A,Info!B:B))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C27" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D27" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E27" s="132">
-        <v>46100</v>
+        <v>46093</v>
       </c>
       <c r="F27" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="G27" s="33">
         <f>IF(ISBLANK(H27),"",_xlfn.XLOOKUP(H27,Info!A:A,Info!B:B))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H27" s="98">
         <f t="shared" si="0"/>
-        <v>46099</v>
+        <v>46092</v>
       </c>
       <c r="I27" s="103">
         <v>0.625</v>
@@ -9752,16 +9786,19 @@
         <v>30</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>524</v>
+        <v>496</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>501</v>
+        <v>481</v>
+      </c>
+      <c r="N27" s="32" t="s">
+        <v>533</v>
       </c>
       <c r="O27" s="118" t="s">
-        <v>553</v>
+        <v>575</v>
       </c>
       <c r="P27" s="92"/>
       <c r="AI27" s="91"/>
@@ -9772,19 +9809,19 @@
         <v>7</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C28" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D28" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E28" s="132">
         <v>46100</v>
       </c>
       <c r="F28" t="s">
-        <v>521</v>
+        <v>497</v>
       </c>
       <c r="G28" s="33">
         <f>IF(ISBLANK(H28),"",_xlfn.XLOOKUP(H28,Info!A:A,Info!B:B))</f>
@@ -9801,19 +9838,19 @@
         <v>30</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="N28" s="32" t="s">
-        <v>554</v>
+        <v>522</v>
       </c>
       <c r="O28" s="118" t="s">
-        <v>553</v>
+        <v>521</v>
       </c>
       <c r="P28" s="92"/>
       <c r="AI28" s="91"/>
@@ -9824,19 +9861,19 @@
         <v>7</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C29" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D29" s="54" t="s">
-        <v>429</v>
+        <v>231</v>
       </c>
       <c r="E29" s="132">
         <v>46100</v>
       </c>
       <c r="F29" t="s">
-        <v>525</v>
+        <v>257</v>
       </c>
       <c r="G29" s="33">
         <f>IF(ISBLANK(H29),"",_xlfn.XLOOKUP(H29,Info!A:A,Info!B:B))</f>
@@ -9853,20 +9890,15 @@
         <v>30</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="L29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L29" s="33" t="s">
         <v>142</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="N29" s="32" t="s">
-        <v>555</v>
-      </c>
-      <c r="O29" s="118" t="s">
-        <v>553</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="N29" s="92"/>
       <c r="P29" s="92"/>
       <c r="AI29" s="91"/>
     </row>
@@ -9876,19 +9908,19 @@
         <v>7</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C30" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D30" s="54" t="s">
-        <v>232</v>
+        <v>410</v>
       </c>
       <c r="E30" s="132">
         <v>46100</v>
       </c>
       <c r="F30" t="s">
-        <v>534</v>
+        <v>500</v>
       </c>
       <c r="G30" s="33">
         <f>IF(ISBLANK(H30),"",_xlfn.XLOOKUP(H30,Info!A:A,Info!B:B))</f>
@@ -9905,67 +9937,70 @@
         <v>30</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L30" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="N30" s="92"/>
+        <v>481</v>
+      </c>
+      <c r="N30" s="32" t="s">
+        <v>523</v>
+      </c>
+      <c r="O30" s="118" t="s">
+        <v>521</v>
+      </c>
       <c r="P30" s="92"/>
       <c r="AI30" s="91"/>
     </row>
     <row r="31" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="33">
         <f>IF(ISBLANK(E31),"",_xlfn.XLOOKUP(E31,Info!A:A,Info!B:B))</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C31" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D31" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="E31" s="91">
-        <v>46114</v>
-      </c>
-      <c r="F31" s="54" t="s">
-        <v>233</v>
+        <v>410</v>
+      </c>
+      <c r="E31" s="132">
+        <v>46100</v>
+      </c>
+      <c r="F31" t="s">
+        <v>499</v>
       </c>
       <c r="G31" s="33">
         <f>IF(ISBLANK(H31),"",_xlfn.XLOOKUP(H31,Info!A:A,Info!B:B))</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H31" s="98">
-        <v>46113</v>
+        <f t="shared" si="0"/>
+        <v>46099</v>
       </c>
       <c r="I31" s="103">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="J31" s="33">
-        <v>15</v>
-      </c>
-      <c r="K31" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="L31" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="M31" s="67" t="s">
-        <v>238</v>
-      </c>
-      <c r="N31" s="92"/>
-      <c r="O31" s="93" t="s">
-        <v>256</v>
-      </c>
-      <c r="P31" s="92" t="s">
-        <v>251</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="O31" s="118" t="s">
+        <v>521</v>
+      </c>
+      <c r="P31" s="92"/>
       <c r="AI31" s="91"/>
     </row>
     <row r="32" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
@@ -9974,48 +10009,49 @@
         <v>9</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C32" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D32" s="54" t="s">
-        <v>232</v>
+        <v>549</v>
       </c>
       <c r="E32" s="91">
         <v>46114</v>
       </c>
       <c r="F32" s="54" t="s">
-        <v>234</v>
+        <v>628</v>
       </c>
       <c r="G32" s="33">
         <f>IF(ISBLANK(H32),"",_xlfn.XLOOKUP(H32,Info!A:A,Info!B:B))</f>
         <v>9</v>
       </c>
       <c r="H32" s="98">
+        <f t="shared" si="0"/>
         <v>46113</v>
       </c>
       <c r="I32" s="103">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="J32" s="33">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="L32" s="33" t="s">
-        <v>236</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="L32" s="33"/>
       <c r="M32" s="67" t="s">
-        <v>238</v>
-      </c>
-      <c r="N32" s="92"/>
+        <v>237</v>
+      </c>
+      <c r="N32" s="92" t="s">
+        <v>649</v>
+      </c>
       <c r="O32" s="93" t="s">
-        <v>256</v>
+        <v>654</v>
       </c>
       <c r="P32" s="92" t="s">
-        <v>237</v>
+        <v>554</v>
       </c>
       <c r="AI32" s="91"/>
     </row>
@@ -10025,19 +10061,19 @@
         <v>9</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C33" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D33" s="54" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E33" s="91">
         <v>46114</v>
       </c>
       <c r="F33" s="54" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="G33" s="33">
         <f>IF(ISBLANK(H33),"",_xlfn.XLOOKUP(H33,Info!A:A,Info!B:B))</f>
@@ -10053,20 +10089,20 @@
         <v>15</v>
       </c>
       <c r="K33" s="33" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L33" s="33" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M33" s="67" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N33" s="92"/>
       <c r="O33" s="93" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="P33" s="92" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="AI33" s="91"/>
     </row>
@@ -10076,19 +10112,19 @@
         <v>9</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C34" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D34" s="54" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E34" s="132">
         <v>46114</v>
       </c>
       <c r="F34" t="s">
-        <v>547</v>
+        <v>232</v>
       </c>
       <c r="G34" s="33">
         <f>IF(ISBLANK(H34),"",_xlfn.XLOOKUP(H34,Info!A:A,Info!B:B))</f>
@@ -10105,13 +10141,13 @@
         <v>30</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L34" s="33" t="s">
         <v>142</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N34" s="92"/>
       <c r="P34" s="92"/>
@@ -10123,19 +10159,19 @@
         <v>9</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C35" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D35" s="54" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E35" s="132">
         <v>46114</v>
       </c>
       <c r="F35" t="s">
-        <v>535</v>
+        <v>506</v>
       </c>
       <c r="G35" s="33">
         <f>IF(ISBLANK(H35),"",_xlfn.XLOOKUP(H35,Info!A:A,Info!B:B))</f>
@@ -10152,13 +10188,13 @@
         <v>30</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L35" s="33" t="s">
         <v>142</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N35" s="92"/>
       <c r="P35" s="92"/>
@@ -10170,45 +10206,49 @@
         <v>9</v>
       </c>
       <c r="B36" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C36" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D36" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="E36" s="132">
+        <v>231</v>
+      </c>
+      <c r="E36" s="91">
         <v>46114</v>
       </c>
-      <c r="F36" t="s">
-        <v>548</v>
+      <c r="F36" s="54" t="s">
+        <v>233</v>
       </c>
       <c r="G36" s="33">
         <f>IF(ISBLANK(H36),"",_xlfn.XLOOKUP(H36,Info!A:A,Info!B:B))</f>
         <v>9</v>
       </c>
       <c r="H36" s="98">
-        <f>E36-1</f>
         <v>46113</v>
       </c>
       <c r="I36" s="103">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="J36" s="33">
-        <v>30</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>508</v>
+        <v>15</v>
+      </c>
+      <c r="K36" s="33" t="s">
+        <v>235</v>
       </c>
       <c r="L36" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
+      </c>
+      <c r="M36" s="67" t="s">
+        <v>237</v>
       </c>
       <c r="N36" s="92"/>
-      <c r="P36" s="92"/>
+      <c r="O36" s="93" t="s">
+        <v>254</v>
+      </c>
+      <c r="P36" s="92" t="s">
+        <v>236</v>
+      </c>
       <c r="AI36" s="91"/>
     </row>
     <row r="37" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
@@ -10217,19 +10257,19 @@
         <v>9</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C37" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D37" s="54" t="s">
-        <v>586</v>
-      </c>
-      <c r="E37" s="91">
+        <v>231</v>
+      </c>
+      <c r="E37" s="132">
         <v>46114</v>
       </c>
-      <c r="F37" s="54" t="s">
-        <v>604</v>
+      <c r="F37" t="s">
+        <v>516</v>
       </c>
       <c r="G37" s="33">
         <f>IF(ISBLANK(H37),"",_xlfn.XLOOKUP(H37,Info!A:A,Info!B:B))</f>
@@ -10243,24 +10283,19 @@
         <v>0.625</v>
       </c>
       <c r="J37" s="33">
-        <v>60</v>
-      </c>
-      <c r="K37" s="33" t="s">
-        <v>589</v>
-      </c>
-      <c r="L37" s="33"/>
-      <c r="M37" s="67" t="s">
-        <v>238</v>
-      </c>
-      <c r="N37" s="92" t="s">
-        <v>585</v>
-      </c>
-      <c r="O37" s="93" t="s">
-        <v>257</v>
-      </c>
-      <c r="P37" s="92" t="s">
-        <v>591</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="L37" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="N37" s="92"/>
+      <c r="P37" s="92"/>
       <c r="AI37" s="91"/>
     </row>
     <row r="38" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
@@ -10269,50 +10304,48 @@
         <v>9</v>
       </c>
       <c r="B38" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C38" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D38" s="54" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="E38" s="91">
-        <v>46115</v>
+        <v>46114</v>
       </c>
       <c r="F38" s="54" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G38" s="33">
         <f>IF(ISBLANK(H38),"",_xlfn.XLOOKUP(H38,Info!A:A,Info!B:B))</f>
         <v>9</v>
       </c>
       <c r="H38" s="98">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="I38" s="103">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="J38" s="33">
         <v>15</v>
       </c>
       <c r="K38" s="33" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="L38" s="33" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="M38" s="67" t="s">
-        <v>249</v>
-      </c>
-      <c r="N38" s="92" t="s">
-        <v>250</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N38" s="92"/>
       <c r="O38" s="93" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="P38" s="92" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AI38" s="91"/>
     </row>
@@ -10322,45 +10355,48 @@
         <v>9</v>
       </c>
       <c r="B39" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C39" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D39" s="54" t="s">
-        <v>240</v>
-      </c>
-      <c r="E39" s="91">
+        <v>410</v>
+      </c>
+      <c r="E39" s="132">
         <v>46115</v>
       </c>
-      <c r="F39" s="54" t="s">
-        <v>241</v>
+      <c r="F39" t="s">
+        <v>629</v>
       </c>
       <c r="G39" s="33">
         <f>IF(ISBLANK(H39),"",_xlfn.XLOOKUP(H39,Info!A:A,Info!B:B))</f>
         <v>9</v>
       </c>
       <c r="H39" s="98">
+        <f>E39-1</f>
         <v>46114</v>
       </c>
       <c r="I39" s="103">
         <v>0.625</v>
       </c>
       <c r="J39" s="33">
-        <v>15</v>
-      </c>
-      <c r="K39" s="33" t="s">
-        <v>245</v>
-      </c>
-      <c r="L39" s="33" t="s">
-        <v>245</v>
-      </c>
-      <c r="M39" s="67" t="s">
-        <v>247</v>
-      </c>
-      <c r="N39" s="92"/>
-      <c r="O39" s="93" t="s">
-        <v>259</v>
+        <v>30</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="N39" s="32" t="s">
+        <v>650</v>
+      </c>
+      <c r="O39" s="118" t="s">
+        <v>535</v>
       </c>
       <c r="P39" s="92"/>
       <c r="AI39" s="91"/>
@@ -10371,48 +10407,50 @@
         <v>9</v>
       </c>
       <c r="B40" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C40" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D40" s="54" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E40" s="91">
         <v>46115</v>
       </c>
       <c r="F40" s="54" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="G40" s="33">
         <f>IF(ISBLANK(H40),"",_xlfn.XLOOKUP(H40,Info!A:A,Info!B:B))</f>
         <v>9</v>
       </c>
       <c r="H40" s="98">
-        <v>46115</v>
-      </c>
-      <c r="I40" s="103" t="s">
-        <v>125</v>
+        <v>46114</v>
+      </c>
+      <c r="I40" s="103">
+        <v>0.625</v>
       </c>
       <c r="J40" s="33">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="K40" s="33" t="s">
         <v>244</v>
       </c>
       <c r="L40" s="33" t="s">
-        <v>142</v>
+        <v>244</v>
       </c>
       <c r="M40" s="67" t="s">
+        <v>247</v>
+      </c>
+      <c r="N40" s="92" t="s">
         <v>248</v>
       </c>
-      <c r="N40" s="92"/>
       <c r="O40" s="93" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P40" s="92" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AI40" s="91"/>
     </row>
@@ -10422,19 +10460,19 @@
         <v>9</v>
       </c>
       <c r="B41" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C41" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D41" s="54" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E41" s="132">
         <v>46115</v>
       </c>
       <c r="F41" t="s">
-        <v>526</v>
+        <v>630</v>
       </c>
       <c r="G41" s="33">
         <f>IF(ISBLANK(H41),"",_xlfn.XLOOKUP(H41,Info!A:A,Info!B:B))</f>
@@ -10457,13 +10495,13 @@
         <v>142</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="N41" s="32" t="s">
-        <v>569</v>
+        <v>536</v>
       </c>
       <c r="O41" s="118" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="P41" s="92"/>
       <c r="AI41" s="91"/>
@@ -10474,48 +10512,45 @@
         <v>9</v>
       </c>
       <c r="B42" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C42" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D42" s="54" t="s">
-        <v>429</v>
-      </c>
-      <c r="E42" s="132">
+        <v>239</v>
+      </c>
+      <c r="E42" s="91">
         <v>46115</v>
       </c>
-      <c r="F42" t="s">
-        <v>527</v>
+      <c r="F42" s="54" t="s">
+        <v>240</v>
       </c>
       <c r="G42" s="33">
         <f>IF(ISBLANK(H42),"",_xlfn.XLOOKUP(H42,Info!A:A,Info!B:B))</f>
         <v>9</v>
       </c>
       <c r="H42" s="98">
-        <f>E42-1</f>
         <v>46114</v>
       </c>
       <c r="I42" s="103">
         <v>0.625</v>
       </c>
       <c r="J42" s="33">
-        <v>30</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="N42" s="32" t="s">
-        <v>570</v>
-      </c>
-      <c r="O42" s="118" t="s">
-        <v>568</v>
+        <v>15</v>
+      </c>
+      <c r="K42" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="L42" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="M42" s="67" t="s">
+        <v>246</v>
+      </c>
+      <c r="N42" s="92"/>
+      <c r="O42" s="93" t="s">
+        <v>256</v>
       </c>
       <c r="P42" s="92"/>
       <c r="AI42" s="91"/>
@@ -10523,48 +10558,52 @@
     <row r="43" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="33">
         <f>IF(ISBLANK(E43),"",_xlfn.XLOOKUP(E43,Info!A:A,Info!B:B))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B43" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C43" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D43" s="54" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="E43" s="91">
-        <v>46119</v>
+        <v>46115</v>
       </c>
       <c r="F43" s="54" t="s">
-        <v>274</v>
+        <v>631</v>
       </c>
       <c r="G43" s="33">
         <f>IF(ISBLANK(H43),"",_xlfn.XLOOKUP(H43,Info!A:A,Info!B:B))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H43" s="98">
-        <v>46118</v>
-      </c>
-      <c r="I43" s="103">
-        <v>0.5</v>
-      </c>
-      <c r="J43" s="33"/>
+        <v>46115</v>
+      </c>
+      <c r="I43" s="103" t="s">
+        <v>125</v>
+      </c>
+      <c r="J43" s="33">
+        <v>60</v>
+      </c>
       <c r="K43" s="33" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L43" s="33" t="s">
-        <v>244</v>
+        <v>142</v>
       </c>
       <c r="M43" s="67" t="s">
-        <v>249</v>
+        <v>646</v>
       </c>
       <c r="N43" s="92"/>
       <c r="O43" s="93" t="s">
-        <v>346</v>
-      </c>
-      <c r="P43" s="92"/>
+        <v>654</v>
+      </c>
+      <c r="P43" s="92" t="s">
+        <v>249</v>
+      </c>
       <c r="AI43" s="91"/>
     </row>
     <row r="44" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
@@ -10573,50 +10612,45 @@
         <v>10</v>
       </c>
       <c r="B44" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C44" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D44" s="54" t="s">
-        <v>243</v>
+        <v>623</v>
       </c>
       <c r="E44" s="91">
         <v>46119</v>
       </c>
       <c r="F44" s="54" t="s">
-        <v>628</v>
+        <v>269</v>
       </c>
       <c r="G44" s="33">
         <f>IF(ISBLANK(H44),"",_xlfn.XLOOKUP(H44,Info!A:A,Info!B:B))</f>
         <v>10</v>
       </c>
       <c r="H44" s="98">
-        <f>E44-1</f>
         <v>46118</v>
       </c>
       <c r="I44" s="103">
-        <v>0.625</v>
-      </c>
-      <c r="J44" s="33">
-        <v>60</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="J44" s="33"/>
       <c r="K44" s="33" t="s">
-        <v>588</v>
-      </c>
-      <c r="L44" s="33"/>
+        <v>243</v>
+      </c>
+      <c r="L44" s="33" t="s">
+        <v>243</v>
+      </c>
       <c r="M44" s="67" t="s">
-        <v>238</v>
-      </c>
-      <c r="N44" s="92" t="s">
-        <v>585</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="N44" s="92"/>
       <c r="O44" s="93" t="s">
-        <v>257</v>
-      </c>
-      <c r="P44" s="92" t="s">
-        <v>590</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="P44" s="92"/>
       <c r="AI44" s="91"/>
     </row>
     <row r="45" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
@@ -10625,48 +10659,49 @@
         <v>10</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C45" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D45" s="54" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E45" s="91">
-        <v>46121</v>
+        <v>46119</v>
       </c>
       <c r="F45" s="54" t="s">
-        <v>242</v>
+        <v>584</v>
       </c>
       <c r="G45" s="33">
         <f>IF(ISBLANK(H45),"",_xlfn.XLOOKUP(H45,Info!A:A,Info!B:B))</f>
         <v>10</v>
       </c>
       <c r="H45" s="98">
-        <v>46120</v>
-      </c>
-      <c r="I45" s="103" t="s">
-        <v>125</v>
+        <f>E45-1</f>
+        <v>46118</v>
+      </c>
+      <c r="I45" s="103">
+        <v>0.625</v>
       </c>
       <c r="J45" s="33">
         <v>60</v>
       </c>
       <c r="K45" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="L45" s="33" t="s">
-        <v>142</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="L45" s="33"/>
       <c r="M45" s="67" t="s">
-        <v>248</v>
-      </c>
-      <c r="N45" s="92"/>
+        <v>237</v>
+      </c>
+      <c r="N45" s="92" t="s">
+        <v>649</v>
+      </c>
       <c r="O45" s="93" t="s">
-        <v>257</v>
+        <v>654</v>
       </c>
       <c r="P45" s="92" t="s">
-        <v>251</v>
+        <v>553</v>
       </c>
       <c r="AI45" s="91"/>
     </row>
@@ -10676,19 +10711,19 @@
         <v>10</v>
       </c>
       <c r="B46" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C46" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D46" s="54" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E46" s="91">
         <v>46121</v>
       </c>
       <c r="F46" s="54" t="s">
-        <v>275</v>
+        <v>631</v>
       </c>
       <c r="G46" s="33">
         <f>IF(ISBLANK(H46),"",_xlfn.XLOOKUP(H46,Info!A:A,Info!B:B))</f>
@@ -10697,26 +10732,28 @@
       <c r="H46" s="98">
         <v>46120</v>
       </c>
-      <c r="I46" s="103">
-        <v>0.625</v>
+      <c r="I46" s="103" t="s">
+        <v>125</v>
       </c>
       <c r="J46" s="33">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K46" s="33" t="s">
-        <v>142</v>
+        <v>243</v>
       </c>
       <c r="L46" s="33" t="s">
         <v>142</v>
       </c>
       <c r="M46" s="67" t="s">
-        <v>248</v>
+        <v>646</v>
       </c>
       <c r="N46" s="92"/>
       <c r="O46" s="93" t="s">
-        <v>349</v>
-      </c>
-      <c r="P46" s="92"/>
+        <v>654</v>
+      </c>
+      <c r="P46" s="92" t="s">
+        <v>249</v>
+      </c>
       <c r="AI46" s="91"/>
     </row>
     <row r="47" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
@@ -10725,103 +10762,99 @@
         <v>10</v>
       </c>
       <c r="B47" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C47" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D47" s="54" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="E47" s="91">
-        <v>46122</v>
+        <v>46121</v>
       </c>
       <c r="F47" s="54" t="s">
-        <v>260</v>
+        <v>632</v>
       </c>
       <c r="G47" s="33">
         <f>IF(ISBLANK(H47),"",_xlfn.XLOOKUP(H47,Info!A:A,Info!B:B))</f>
         <v>10</v>
       </c>
       <c r="H47" s="98">
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="I47" s="103">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="J47" s="33">
         <v>30</v>
       </c>
       <c r="K47" s="33" t="s">
-        <v>261</v>
+        <v>142</v>
       </c>
       <c r="L47" s="33" t="s">
         <v>142</v>
       </c>
       <c r="M47" s="67" t="s">
-        <v>249</v>
-      </c>
-      <c r="N47" s="92" t="s">
-        <v>268</v>
-      </c>
+        <v>646</v>
+      </c>
+      <c r="N47" s="92"/>
       <c r="O47" s="93" t="s">
-        <v>257</v>
-      </c>
-      <c r="P47" s="92" t="s">
-        <v>351</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="P47" s="92"/>
       <c r="AI47" s="91"/>
     </row>
     <row r="48" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="33">
         <f>IF(ISBLANK(E48),"",_xlfn.XLOOKUP(E48,Info!A:A,Info!B:B))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B48" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C48" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D48" s="54" t="s">
-        <v>429</v>
+        <v>260</v>
       </c>
       <c r="E48" s="91">
-        <v>46125</v>
+        <v>46122</v>
       </c>
       <c r="F48" s="54" t="s">
-        <v>430</v>
+        <v>257</v>
       </c>
       <c r="G48" s="33">
         <f>IF(ISBLANK(H48),"",_xlfn.XLOOKUP(H48,Info!A:A,Info!B:B))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H48" s="98">
-        <v>46125</v>
+        <v>46121</v>
       </c>
       <c r="I48" s="103">
         <v>0.5</v>
       </c>
       <c r="J48" s="33">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K48" s="33" t="s">
-        <v>142</v>
+        <v>258</v>
       </c>
       <c r="L48" s="33" t="s">
         <v>142</v>
       </c>
       <c r="M48" s="67" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N48" s="92" t="s">
-        <v>431</v>
-      </c>
-      <c r="O48" s="118" t="s">
-        <v>432</v>
+        <v>264</v>
+      </c>
+      <c r="O48" s="93" t="s">
+        <v>654</v>
       </c>
       <c r="P48" s="92" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AI48" s="91"/>
     </row>
@@ -10831,19 +10864,19 @@
         <v>11</v>
       </c>
       <c r="B49" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C49" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D49" s="54" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E49" s="91">
         <v>46125</v>
       </c>
       <c r="F49" s="54" t="s">
-        <v>612</v>
+        <v>571</v>
       </c>
       <c r="G49" s="33">
         <f>IF(ISBLANK(H49),"",_xlfn.XLOOKUP(H49,Info!A:A,Info!B:B))</f>
@@ -10860,20 +10893,20 @@
         <v>60</v>
       </c>
       <c r="K49" s="33" t="s">
-        <v>597</v>
+        <v>560</v>
       </c>
       <c r="L49" s="33"/>
       <c r="M49" s="67" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N49" s="92" t="s">
-        <v>585</v>
+        <v>649</v>
       </c>
       <c r="O49" s="93" t="s">
-        <v>257</v>
+        <v>654</v>
       </c>
       <c r="P49" s="92" t="s">
-        <v>592</v>
+        <v>555</v>
       </c>
       <c r="AI49" s="91"/>
     </row>
@@ -10883,50 +10916,50 @@
         <v>11</v>
       </c>
       <c r="B50" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C50" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D50" s="54" t="s">
-        <v>262</v>
+        <v>410</v>
       </c>
       <c r="E50" s="91">
-        <v>46127</v>
+        <v>46125</v>
       </c>
       <c r="F50" s="54" t="s">
-        <v>260</v>
+        <v>411</v>
       </c>
       <c r="G50" s="33">
         <f>IF(ISBLANK(H50),"",_xlfn.XLOOKUP(H50,Info!A:A,Info!B:B))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H50" s="98">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="I50" s="103">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="J50" s="33">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K50" s="33" t="s">
-        <v>267</v>
+        <v>142</v>
       </c>
       <c r="L50" s="33" t="s">
         <v>142</v>
       </c>
       <c r="M50" s="67" t="s">
-        <v>501</v>
+        <v>247</v>
       </c>
       <c r="N50" s="92" t="s">
-        <v>532</v>
-      </c>
-      <c r="O50" s="93" t="s">
-        <v>257</v>
+        <v>412</v>
+      </c>
+      <c r="O50" s="118" t="s">
+        <v>413</v>
       </c>
       <c r="P50" s="92" t="s">
-        <v>442</v>
+        <v>340</v>
       </c>
       <c r="AI50" s="91"/>
     </row>
@@ -10936,27 +10969,26 @@
         <v>11</v>
       </c>
       <c r="B51" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C51" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D51" s="54" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="E51" s="91">
-        <v>46129</v>
+        <v>46127</v>
       </c>
       <c r="F51" s="54" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="G51" s="33">
         <f>IF(ISBLANK(H51),"",_xlfn.XLOOKUP(H51,Info!A:A,Info!B:B))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H51" s="98">
-        <f t="shared" ref="H51:H57" si="2">E51-1</f>
-        <v>46128</v>
+        <v>46122</v>
       </c>
       <c r="I51" s="103">
         <v>0.625</v>
@@ -10965,22 +10997,22 @@
         <v>30</v>
       </c>
       <c r="K51" s="33" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="L51" s="33" t="s">
-        <v>277</v>
+        <v>142</v>
       </c>
       <c r="M51" s="67" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="N51" s="92" t="s">
-        <v>529</v>
+        <v>504</v>
       </c>
       <c r="O51" s="93" t="s">
-        <v>354</v>
+        <v>654</v>
       </c>
       <c r="P51" s="92" t="s">
-        <v>347</v>
+        <v>423</v>
       </c>
       <c r="AI51" s="91"/>
     </row>
@@ -10990,26 +11022,26 @@
         <v>11</v>
       </c>
       <c r="B52" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C52" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D52" s="54" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E52" s="91">
         <v>46129</v>
       </c>
       <c r="F52" s="54" t="s">
-        <v>353</v>
+        <v>272</v>
       </c>
       <c r="G52" s="33">
         <f>IF(ISBLANK(H52),"",_xlfn.XLOOKUP(H52,Info!A:A,Info!B:B))</f>
         <v>11</v>
       </c>
       <c r="H52" s="98">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H52:H58" si="2">E52-1</f>
         <v>46128</v>
       </c>
       <c r="I52" s="103">
@@ -11019,76 +11051,76 @@
         <v>30</v>
       </c>
       <c r="K52" s="33" t="s">
-        <v>440</v>
+        <v>271</v>
       </c>
       <c r="L52" s="33" t="s">
-        <v>440</v>
+        <v>271</v>
       </c>
       <c r="M52" s="67" t="s">
-        <v>530</v>
+        <v>481</v>
       </c>
       <c r="N52" s="92" t="s">
-        <v>531</v>
+        <v>502</v>
       </c>
       <c r="O52" s="93" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="P52" s="92" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AI52" s="91"/>
     </row>
     <row r="53" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="33">
         <f>IF(ISBLANK(E53),"",_xlfn.XLOOKUP(E53,Info!A:A,Info!B:B))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B53" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C53" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D53" s="54" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E53" s="91">
-        <v>46133</v>
+        <v>46129</v>
       </c>
       <c r="F53" s="54" t="s">
-        <v>611</v>
+        <v>346</v>
       </c>
       <c r="G53" s="33">
         <f>IF(ISBLANK(H53),"",_xlfn.XLOOKUP(H53,Info!A:A,Info!B:B))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H53" s="98">
         <f t="shared" si="2"/>
-        <v>46132</v>
+        <v>46128</v>
       </c>
       <c r="I53" s="103">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="J53" s="33">
         <v>30</v>
       </c>
       <c r="K53" s="33" t="s">
-        <v>261</v>
+        <v>421</v>
       </c>
       <c r="L53" s="33" t="s">
-        <v>142</v>
+        <v>421</v>
       </c>
       <c r="M53" s="67" t="s">
-        <v>238</v>
+        <v>503</v>
       </c>
       <c r="N53" s="92" t="s">
-        <v>281</v>
+        <v>651</v>
       </c>
       <c r="O53" s="93" t="s">
-        <v>257</v>
+        <v>347</v>
       </c>
       <c r="P53" s="92" t="s">
-        <v>280</v>
+        <v>343</v>
       </c>
       <c r="AI53" s="91"/>
     </row>
@@ -11098,19 +11130,19 @@
         <v>12</v>
       </c>
       <c r="B54" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C54" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D54" s="54" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E54" s="91">
         <v>46133</v>
       </c>
       <c r="F54" s="54" t="s">
-        <v>610</v>
+        <v>569</v>
       </c>
       <c r="G54" s="33">
         <f>IF(ISBLANK(H54),"",_xlfn.XLOOKUP(H54,Info!A:A,Info!B:B))</f>
@@ -11127,20 +11159,20 @@
         <v>60</v>
       </c>
       <c r="K54" s="33" t="s">
-        <v>598</v>
+        <v>561</v>
       </c>
       <c r="L54" s="33"/>
       <c r="M54" s="67" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N54" s="92" t="s">
-        <v>585</v>
+        <v>649</v>
       </c>
       <c r="O54" s="93" t="s">
-        <v>257</v>
+        <v>654</v>
       </c>
       <c r="P54" s="92" t="s">
-        <v>595</v>
+        <v>558</v>
       </c>
       <c r="AI54" s="91"/>
     </row>
@@ -11150,19 +11182,19 @@
         <v>12</v>
       </c>
       <c r="B55" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C55" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D55" s="54" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E55" s="91">
-        <v>46135</v>
+        <v>46133</v>
       </c>
       <c r="F55" s="54" t="s">
-        <v>279</v>
+        <v>570</v>
       </c>
       <c r="G55" s="33">
         <f>IF(ISBLANK(H55),"",_xlfn.XLOOKUP(H55,Info!A:A,Info!B:B))</f>
@@ -11170,31 +11202,31 @@
       </c>
       <c r="H55" s="98">
         <f t="shared" si="2"/>
-        <v>46134</v>
+        <v>46132</v>
       </c>
       <c r="I55" s="103">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="J55" s="33">
         <v>30</v>
       </c>
       <c r="K55" s="33" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="L55" s="33" t="s">
-        <v>277</v>
+        <v>142</v>
       </c>
       <c r="M55" s="67" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="N55" s="92" t="s">
-        <v>618</v>
+        <v>275</v>
       </c>
       <c r="O55" s="93" t="s">
-        <v>348</v>
+        <v>654</v>
       </c>
       <c r="P55" s="92" t="s">
-        <v>347</v>
+        <v>274</v>
       </c>
       <c r="AI55" s="91"/>
     </row>
@@ -11204,19 +11236,19 @@
         <v>12</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C56" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D56" s="54" t="s">
-        <v>429</v>
+        <v>239</v>
       </c>
       <c r="E56" s="91">
         <v>46135</v>
       </c>
       <c r="F56" s="54" t="s">
-        <v>580</v>
+        <v>273</v>
       </c>
       <c r="G56" s="33">
         <f>IF(ISBLANK(H56),"",_xlfn.XLOOKUP(H56,Info!A:A,Info!B:B))</f>
@@ -11227,27 +11259,29 @@
         <v>46134</v>
       </c>
       <c r="I56" s="103">
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="J56" s="33">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K56" s="33" t="s">
-        <v>440</v>
+        <v>271</v>
       </c>
       <c r="L56" s="33" t="s">
-        <v>440</v>
+        <v>271</v>
       </c>
       <c r="M56" s="67" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N56" s="92" t="s">
-        <v>619</v>
+        <v>576</v>
       </c>
       <c r="O56" s="93" t="s">
-        <v>348</v>
-      </c>
-      <c r="P56" s="92"/>
+        <v>341</v>
+      </c>
+      <c r="P56" s="92" t="s">
+        <v>340</v>
+      </c>
       <c r="AI56" s="91"/>
     </row>
     <row r="57" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
@@ -11256,19 +11290,19 @@
         <v>12</v>
       </c>
       <c r="B57" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C57" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D57" s="54" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E57" s="91">
         <v>46135</v>
       </c>
       <c r="F57" s="54" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="G57" s="33">
         <f>IF(ISBLANK(H57),"",_xlfn.XLOOKUP(H57,Info!A:A,Info!B:B))</f>
@@ -11285,20 +11319,20 @@
         <v>60</v>
       </c>
       <c r="K57" s="33" t="s">
-        <v>599</v>
+        <v>562</v>
       </c>
       <c r="L57" s="33"/>
       <c r="M57" s="67" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N57" s="92" t="s">
-        <v>585</v>
+        <v>649</v>
       </c>
       <c r="O57" s="93" t="s">
-        <v>257</v>
+        <v>654</v>
       </c>
       <c r="P57" s="92" t="s">
-        <v>605</v>
+        <v>655</v>
       </c>
       <c r="AI57" s="91"/>
     </row>
@@ -11308,102 +11342,102 @@
         <v>12</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C58" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D58" s="54" t="s">
-        <v>243</v>
+        <v>410</v>
       </c>
       <c r="E58" s="91">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="F58" s="54" t="s">
-        <v>613</v>
+        <v>545</v>
       </c>
       <c r="G58" s="33">
         <f>IF(ISBLANK(H58),"",_xlfn.XLOOKUP(H58,Info!A:A,Info!B:B))</f>
         <v>12</v>
       </c>
       <c r="H58" s="98">
-        <v>46135</v>
+        <f t="shared" si="2"/>
+        <v>46134</v>
       </c>
       <c r="I58" s="103">
         <v>0.66666666666666663</v>
       </c>
       <c r="J58" s="33">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="K58" s="33" t="s">
-        <v>244</v>
+        <v>421</v>
       </c>
       <c r="L58" s="33" t="s">
-        <v>244</v>
+        <v>421</v>
       </c>
       <c r="M58" s="67" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N58" s="92" t="s">
-        <v>629</v>
-      </c>
-      <c r="O58" s="118" t="s">
-        <v>620</v>
-      </c>
-      <c r="P58" s="92" t="s">
-        <v>614</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="O58" s="93" t="s">
+        <v>341</v>
+      </c>
+      <c r="P58" s="92"/>
       <c r="AI58" s="91"/>
     </row>
     <row r="59" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="33">
         <f>IF(ISBLANK(E59),"",_xlfn.XLOOKUP(E59,Info!A:A,Info!B:B))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C59" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D59" s="54" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E59" s="91">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="F59" s="54" t="s">
-        <v>608</v>
+        <v>634</v>
       </c>
       <c r="G59" s="33">
         <f>IF(ISBLANK(H59),"",_xlfn.XLOOKUP(H59,Info!A:A,Info!B:B))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H59" s="98">
-        <f>E59-1</f>
-        <v>46138</v>
+        <v>46135</v>
       </c>
       <c r="I59" s="103">
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J59" s="33">
         <v>60</v>
       </c>
       <c r="K59" s="33" t="s">
-        <v>601</v>
-      </c>
-      <c r="L59" s="33"/>
+        <v>243</v>
+      </c>
+      <c r="L59" s="33" t="s">
+        <v>243</v>
+      </c>
       <c r="M59" s="67" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="N59" s="92" t="s">
         <v>585</v>
       </c>
-      <c r="O59" s="93" t="s">
-        <v>257</v>
+      <c r="O59" s="118" t="s">
+        <v>577</v>
       </c>
       <c r="P59" s="92" t="s">
-        <v>596</v>
+        <v>572</v>
       </c>
       <c r="AI59" s="91"/>
     </row>
@@ -11413,47 +11447,49 @@
         <v>13</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C60" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D60" s="54" t="s">
-        <v>429</v>
+        <v>242</v>
       </c>
       <c r="E60" s="91">
         <v>46139</v>
       </c>
       <c r="F60" s="54" t="s">
-        <v>615</v>
+        <v>568</v>
       </c>
       <c r="G60" s="33">
         <f>IF(ISBLANK(H60),"",_xlfn.XLOOKUP(H60,Info!A:A,Info!B:B))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H60" s="98">
-        <v>46136</v>
+        <f>E60-1</f>
+        <v>46138</v>
       </c>
       <c r="I60" s="103">
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="J60" s="33">
         <v>60</v>
       </c>
       <c r="K60" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="L60" s="33" t="s">
-        <v>142</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="L60" s="33"/>
       <c r="M60" s="67" t="s">
-        <v>238</v>
-      </c>
-      <c r="O60" s="118" t="s">
-        <v>616</v>
+        <v>237</v>
+      </c>
+      <c r="N60" s="92" t="s">
+        <v>649</v>
+      </c>
+      <c r="O60" s="93" t="s">
+        <v>654</v>
       </c>
       <c r="P60" s="92" t="s">
-        <v>347</v>
+        <v>559</v>
       </c>
       <c r="AI60" s="91"/>
     </row>
@@ -11463,51 +11499,47 @@
         <v>13</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C61" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D61" s="54" t="s">
-        <v>240</v>
+        <v>410</v>
       </c>
       <c r="E61" s="91">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="F61" s="54" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="G61" s="33">
         <f>IF(ISBLANK(H61),"",_xlfn.XLOOKUP(H61,Info!A:A,Info!B:B))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H61" s="98">
-        <f>E61-1</f>
-        <v>46141</v>
+        <v>46136</v>
       </c>
       <c r="I61" s="103">
         <v>0.66666666666666663</v>
       </c>
       <c r="J61" s="33">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K61" s="33" t="s">
-        <v>236</v>
+        <v>142</v>
       </c>
       <c r="L61" s="33" t="s">
-        <v>236</v>
+        <v>142</v>
       </c>
       <c r="M61" s="67" t="s">
-        <v>249</v>
-      </c>
-      <c r="N61" s="92" t="s">
-        <v>648</v>
+        <v>237</v>
       </c>
       <c r="O61" s="118" t="s">
-        <v>638</v>
+        <v>574</v>
       </c>
       <c r="P61" s="92" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AI61" s="91"/>
     </row>
@@ -11517,19 +11549,19 @@
         <v>13</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C62" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D62" s="54" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E62" s="91">
         <v>46142</v>
       </c>
       <c r="F62" s="54" t="s">
-        <v>233</v>
+        <v>546</v>
       </c>
       <c r="G62" s="33">
         <f>IF(ISBLANK(H62),"",_xlfn.XLOOKUP(H62,Info!A:A,Info!B:B))</f>
@@ -11540,26 +11572,28 @@
         <v>46141</v>
       </c>
       <c r="I62" s="103">
-        <v>0.16666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J62" s="33">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="K62" s="33" t="s">
-        <v>142</v>
+        <v>235</v>
       </c>
       <c r="L62" s="33" t="s">
-        <v>142</v>
+        <v>235</v>
       </c>
       <c r="M62" s="67" t="s">
-        <v>238</v>
-      </c>
-      <c r="N62" s="92"/>
+        <v>247</v>
+      </c>
+      <c r="N62" s="92" t="s">
+        <v>652</v>
+      </c>
       <c r="O62" s="118" t="s">
-        <v>638</v>
+        <v>591</v>
       </c>
       <c r="P62" s="92" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AI62" s="91"/>
     </row>
@@ -11569,49 +11603,49 @@
         <v>13</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C63" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D63" s="54" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E63" s="91">
-        <v>46143</v>
+        <v>46142</v>
       </c>
       <c r="F63" s="54" t="s">
-        <v>644</v>
+        <v>232</v>
       </c>
       <c r="G63" s="33">
         <f>IF(ISBLANK(H63),"",_xlfn.XLOOKUP(H63,Info!A:A,Info!B:B))</f>
         <v>13</v>
       </c>
       <c r="H63" s="98">
-        <f>E63-2</f>
+        <f>E63-1</f>
         <v>46141</v>
       </c>
       <c r="I63" s="103">
-        <v>0.66666666666666663</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="J63" s="33">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="K63" s="33" t="s">
-        <v>267</v>
+        <v>142</v>
       </c>
       <c r="L63" s="33" t="s">
         <v>142</v>
       </c>
       <c r="M63" s="67" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="N63" s="92"/>
-      <c r="O63" s="93" t="s">
-        <v>257</v>
+      <c r="O63" s="118" t="s">
+        <v>591</v>
       </c>
       <c r="P63" s="92" t="s">
-        <v>581</v>
+        <v>340</v>
       </c>
       <c r="AI63" s="91"/>
     </row>
@@ -11621,102 +11655,101 @@
         <v>13</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C64" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D64" s="54" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E64" s="91">
         <v>46143</v>
       </c>
       <c r="F64" s="54" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="G64" s="33">
         <f>IF(ISBLANK(H64),"",_xlfn.XLOOKUP(H64,Info!A:A,Info!B:B))</f>
         <v>13</v>
       </c>
       <c r="H64" s="98">
-        <f>E64-1</f>
-        <v>46142</v>
+        <f>E64-2</f>
+        <v>46141</v>
       </c>
       <c r="I64" s="103">
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J64" s="33">
         <v>60</v>
       </c>
       <c r="K64" s="33" t="s">
-        <v>598</v>
-      </c>
-      <c r="L64" s="33"/>
+        <v>263</v>
+      </c>
+      <c r="L64" s="33" t="s">
+        <v>142</v>
+      </c>
       <c r="M64" s="67" t="s">
-        <v>238</v>
-      </c>
-      <c r="N64" s="92" t="s">
-        <v>585</v>
-      </c>
+        <v>646</v>
+      </c>
+      <c r="N64" s="92"/>
       <c r="O64" s="93" t="s">
-        <v>257</v>
+        <v>654</v>
       </c>
       <c r="P64" s="92" t="s">
-        <v>593</v>
+        <v>656</v>
       </c>
       <c r="AI64" s="91"/>
     </row>
     <row r="65" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="33">
         <f>IF(ISBLANK(E65),"",_xlfn.XLOOKUP(E65,Info!A:A,Info!B:B))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C65" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D65" s="54" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="E65" s="91">
-        <v>46146</v>
+        <v>46143</v>
       </c>
       <c r="F65" s="54" t="s">
-        <v>260</v>
+        <v>635</v>
       </c>
       <c r="G65" s="33">
         <f>IF(ISBLANK(H65),"",_xlfn.XLOOKUP(H65,Info!A:A,Info!B:B))</f>
         <v>13</v>
       </c>
       <c r="H65" s="98">
-        <v>46139</v>
+        <f>E65-1</f>
+        <v>46142</v>
       </c>
       <c r="I65" s="103">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="J65" s="33">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K65" s="33" t="s">
-        <v>441</v>
-      </c>
-      <c r="L65" s="33" t="s">
-        <v>142</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="L65" s="33"/>
       <c r="M65" s="67" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="N65" s="92" t="s">
-        <v>268</v>
+        <v>649</v>
       </c>
       <c r="O65" s="93" t="s">
-        <v>257</v>
+        <v>654</v>
       </c>
       <c r="P65" s="92" t="s">
-        <v>596</v>
+        <v>556</v>
       </c>
       <c r="AI65" s="91"/>
     </row>
@@ -11726,50 +11759,50 @@
         <v>14</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C66" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D66" s="54" t="s">
-        <v>240</v>
+        <v>297</v>
       </c>
       <c r="E66" s="91">
         <v>46146</v>
       </c>
       <c r="F66" s="54" t="s">
-        <v>623</v>
+        <v>257</v>
       </c>
       <c r="G66" s="33">
         <f>IF(ISBLANK(H66),"",_xlfn.XLOOKUP(H66,Info!A:A,Info!B:B))</f>
         <v>13</v>
       </c>
       <c r="H66" s="98">
-        <v>46143</v>
+        <v>46139</v>
       </c>
       <c r="I66" s="103">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="J66" s="33">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K66" s="33" t="s">
-        <v>645</v>
+        <v>422</v>
       </c>
       <c r="L66" s="33" t="s">
-        <v>645</v>
+        <v>142</v>
       </c>
       <c r="M66" s="67" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N66" s="92" t="s">
-        <v>651</v>
-      </c>
-      <c r="O66" s="118" t="s">
-        <v>640</v>
+        <v>264</v>
+      </c>
+      <c r="O66" s="93" t="s">
+        <v>654</v>
       </c>
       <c r="P66" s="92" t="s">
-        <v>347</v>
+        <v>559</v>
       </c>
       <c r="AI66" s="91"/>
     </row>
@@ -11779,19 +11812,19 @@
         <v>14</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C67" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D67" s="54" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E67" s="91">
         <v>46146</v>
       </c>
       <c r="F67" s="54" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="G67" s="33">
         <f>IF(ISBLANK(H67),"",_xlfn.XLOOKUP(H67,Info!A:A,Info!B:B))</f>
@@ -11807,22 +11840,22 @@
         <v>20</v>
       </c>
       <c r="K67" s="33" t="s">
-        <v>625</v>
+        <v>581</v>
       </c>
       <c r="L67" s="33" t="s">
         <v>142</v>
       </c>
       <c r="M67" s="67" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N67" s="92" t="s">
-        <v>652</v>
+        <v>599</v>
       </c>
       <c r="O67" s="118" t="s">
-        <v>640</v>
+        <v>592</v>
       </c>
       <c r="P67" s="92" t="s">
-        <v>637</v>
+        <v>590</v>
       </c>
       <c r="AI67" s="91"/>
     </row>
@@ -11832,19 +11865,19 @@
         <v>14</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C68" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D68" s="54" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E68" s="91">
         <v>46146</v>
       </c>
       <c r="F68" s="54" t="s">
-        <v>649</v>
+        <v>580</v>
       </c>
       <c r="G68" s="33">
         <f>IF(ISBLANK(H68),"",_xlfn.XLOOKUP(H68,Info!A:A,Info!B:B))</f>
@@ -11860,19 +11893,23 @@
         <v>20</v>
       </c>
       <c r="K68" s="33" t="s">
-        <v>142</v>
+        <v>597</v>
       </c>
       <c r="L68" s="33" t="s">
-        <v>142</v>
+        <v>597</v>
       </c>
       <c r="M68" s="67" t="s">
-        <v>249</v>
-      </c>
-      <c r="N68" s="92"/>
+        <v>247</v>
+      </c>
+      <c r="N68" s="92" t="s">
+        <v>653</v>
+      </c>
       <c r="O68" s="118" t="s">
-        <v>640</v>
-      </c>
-      <c r="P68" s="92"/>
+        <v>592</v>
+      </c>
+      <c r="P68" s="92" t="s">
+        <v>340</v>
+      </c>
       <c r="AI68" s="91"/>
     </row>
     <row r="69" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
@@ -11881,71 +11918,68 @@
         <v>14</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C69" s="33" t="s">
         <v>187</v>
       </c>
       <c r="D69" s="54" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E69" s="91">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="F69" s="54" t="s">
-        <v>607</v>
+        <v>637</v>
       </c>
       <c r="G69" s="33">
         <f>IF(ISBLANK(H69),"",_xlfn.XLOOKUP(H69,Info!A:A,Info!B:B))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H69" s="98">
-        <f>E69-1</f>
-        <v>46146</v>
+        <v>46143</v>
       </c>
       <c r="I69" s="103">
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J69" s="33">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K69" s="33" t="s">
-        <v>600</v>
-      </c>
-      <c r="L69" s="33"/>
+        <v>142</v>
+      </c>
+      <c r="L69" s="33" t="s">
+        <v>142</v>
+      </c>
       <c r="M69" s="67" t="s">
-        <v>238</v>
-      </c>
-      <c r="N69" s="92" t="s">
-        <v>585</v>
-      </c>
-      <c r="O69" s="93" t="s">
-        <v>257</v>
-      </c>
-      <c r="P69" s="92" t="s">
-        <v>594</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="N69" s="92"/>
+      <c r="O69" s="118" t="s">
+        <v>592</v>
+      </c>
+      <c r="P69" s="92"/>
       <c r="AI69" s="91"/>
     </row>
-    <row r="70" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="33">
         <f>IF(ISBLANK(E70),"",_xlfn.XLOOKUP(E70,Info!A:A,Info!B:B))</f>
         <v>14</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C70" s="33" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="D70" s="54" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E70" s="91">
-        <v>46150</v>
+        <v>46147</v>
       </c>
       <c r="F70" s="54" t="s">
-        <v>650</v>
+        <v>567</v>
       </c>
       <c r="G70" s="33">
         <f>IF(ISBLANK(H70),"",_xlfn.XLOOKUP(H70,Info!A:A,Info!B:B))</f>
@@ -11953,262 +11987,290 @@
       </c>
       <c r="H70" s="98">
         <f>E70-1</f>
-        <v>46149</v>
+        <v>46146</v>
       </c>
       <c r="I70" s="103">
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="J70" s="33">
-        <v>45</v>
-      </c>
-      <c r="K70" s="33"/>
+        <v>60</v>
+      </c>
+      <c r="K70" s="33" t="s">
+        <v>563</v>
+      </c>
       <c r="L70" s="33"/>
-      <c r="M70" s="67"/>
-      <c r="N70" s="92"/>
-      <c r="O70" s="118" t="s">
-        <v>660</v>
-      </c>
-      <c r="P70" s="92"/>
+      <c r="M70" s="67" t="s">
+        <v>237</v>
+      </c>
+      <c r="N70" s="92" t="s">
+        <v>649</v>
+      </c>
+      <c r="O70" s="93" t="s">
+        <v>654</v>
+      </c>
+      <c r="P70" s="92" t="s">
+        <v>557</v>
+      </c>
       <c r="AI70" s="91"/>
     </row>
-    <row r="71" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" s="32" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="33">
         <f>IF(ISBLANK(E71),"",_xlfn.XLOOKUP(E71,Info!A:A,Info!B:B))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C71" s="33" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="D71" s="54" t="s">
-        <v>641</v>
+        <v>239</v>
       </c>
       <c r="E71" s="91">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="F71" s="54" t="s">
-        <v>260</v>
+        <v>638</v>
       </c>
       <c r="G71" s="33">
         <f>IF(ISBLANK(H71),"",_xlfn.XLOOKUP(H71,Info!A:A,Info!B:B))</f>
         <v>14</v>
       </c>
       <c r="H71" s="98">
-        <v>46147</v>
+        <f>E71-1</f>
+        <v>46149</v>
       </c>
       <c r="I71" s="103">
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J71" s="33">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K71" s="33" t="s">
-        <v>267</v>
+        <v>142</v>
       </c>
       <c r="L71" s="33" t="s">
         <v>142</v>
       </c>
       <c r="M71" s="67" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N71" s="92" t="s">
-        <v>268</v>
-      </c>
-      <c r="O71" s="93" t="s">
-        <v>257</v>
-      </c>
-      <c r="P71" s="92" t="s">
-        <v>633</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="O71" s="118" t="s">
+        <v>606</v>
+      </c>
+      <c r="P71" s="92"/>
       <c r="AI71" s="91"/>
     </row>
-    <row r="72" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="33">
         <f>IF(ISBLANK(E72),"",_xlfn.XLOOKUP(E72,Info!A:A,Info!B:B))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C72" s="33" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="D72" s="54" t="s">
-        <v>240</v>
+        <v>593</v>
       </c>
       <c r="E72" s="91">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="F72" s="54" t="s">
-        <v>622</v>
+        <v>257</v>
       </c>
       <c r="G72" s="33">
         <f>IF(ISBLANK(H72),"",_xlfn.XLOOKUP(H72,Info!A:A,Info!B:B))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H72" s="98">
-        <v>46157</v>
-      </c>
-      <c r="I72" s="103" t="s">
-        <v>646</v>
+        <v>46147</v>
+      </c>
+      <c r="I72" s="103">
+        <v>0.5</v>
       </c>
       <c r="J72" s="33">
         <v>30</v>
       </c>
       <c r="K72" s="33" t="s">
-        <v>647</v>
+        <v>263</v>
       </c>
       <c r="L72" s="33" t="s">
-        <v>647</v>
+        <v>142</v>
       </c>
       <c r="M72" s="67" t="s">
-        <v>249</v>
-      </c>
-      <c r="N72" s="92"/>
+        <v>247</v>
+      </c>
+      <c r="N72" s="92" t="s">
+        <v>614</v>
+      </c>
+      <c r="O72" s="93" t="s">
+        <v>654</v>
+      </c>
       <c r="P72" s="92" t="s">
-        <v>347</v>
+        <v>587</v>
       </c>
       <c r="AI72" s="91"/>
     </row>
-    <row r="73" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="33">
         <f>IF(ISBLANK(E73),"",_xlfn.XLOOKUP(E73,Info!A:A,Info!B:B))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C73" s="33" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="D73" s="54" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="E73" s="91">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="F73" s="54" t="s">
-        <v>260</v>
+        <v>608</v>
       </c>
       <c r="G73" s="33">
         <f>IF(ISBLANK(H73),"",_xlfn.XLOOKUP(H73,Info!A:A,Info!B:B))</f>
         <v>15</v>
       </c>
       <c r="H73" s="98">
-        <v>46154</v>
+        <f>E73-1</f>
+        <v>46155</v>
       </c>
       <c r="I73" s="103">
-        <v>0.5</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="J73" s="33">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K73" s="33" t="s">
-        <v>267</v>
+        <v>613</v>
       </c>
       <c r="L73" s="33" t="s">
-        <v>142</v>
+        <v>244</v>
       </c>
       <c r="M73" s="67" t="s">
-        <v>249</v>
-      </c>
-      <c r="N73" s="92" t="s">
-        <v>268</v>
-      </c>
-      <c r="O73" s="93" t="s">
+        <v>237</v>
+      </c>
+      <c r="N73" s="92"/>
+      <c r="O73" s="118" t="s">
+        <v>609</v>
+      </c>
+      <c r="P73" s="92" t="s">
+        <v>340</v>
+      </c>
+      <c r="AI73" s="91"/>
+    </row>
+    <row r="74" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="33">
+        <f>IF(ISBLANK(E74),"",_xlfn.XLOOKUP(E74,Info!A:A,Info!B:B))</f>
+        <v>16</v>
+      </c>
+      <c r="B74" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C74" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="D74" s="54" t="s">
+        <v>262</v>
+      </c>
+      <c r="E74" s="91">
+        <v>46162</v>
+      </c>
+      <c r="F74" s="54" t="s">
         <v>257</v>
-      </c>
-      <c r="P73" s="92" t="s">
-        <v>634</v>
-      </c>
-      <c r="AI73" s="91"/>
-    </row>
-    <row r="74" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="33" t="e">
-        <f>IF(ISBLANK(E74),"",_xlfn.XLOOKUP(E74,Info!A:A,Info!B:B))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="B74" s="33" t="s">
-        <v>270</v>
-      </c>
-      <c r="C74" s="33" t="s">
-        <v>587</v>
-      </c>
-      <c r="D74" s="54" t="s">
-        <v>243</v>
-      </c>
-      <c r="E74" s="91" t="s">
-        <v>84</v>
-      </c>
-      <c r="F74" s="54" t="s">
-        <v>639</v>
       </c>
       <c r="G74" s="33">
         <f>IF(ISBLANK(H74),"",_xlfn.XLOOKUP(H74,Info!A:A,Info!B:B))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H74" s="98">
-        <v>46143</v>
-      </c>
-      <c r="I74" s="103"/>
+        <v>46155</v>
+      </c>
+      <c r="I74" s="103">
+        <v>0.625</v>
+      </c>
       <c r="J74" s="33">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K74" s="33" t="s">
-        <v>142</v>
+        <v>263</v>
       </c>
       <c r="L74" s="33" t="s">
         <v>142</v>
       </c>
       <c r="M74" s="67" t="s">
-        <v>249</v>
-      </c>
-      <c r="N74" s="92"/>
+        <v>247</v>
+      </c>
+      <c r="N74" s="92" t="s">
+        <v>264</v>
+      </c>
+      <c r="O74" s="93" t="s">
+        <v>654</v>
+      </c>
       <c r="P74" s="92" t="s">
-        <v>261</v>
+        <v>657</v>
       </c>
       <c r="AI74" s="91"/>
     </row>
     <row r="75" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="33" t="e">
+      <c r="A75" s="33">
         <f>IF(ISBLANK(E75),"",_xlfn.XLOOKUP(E75,Info!A:A,Info!B:B))</f>
-        <v>#N/A</v>
+        <v>16</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C75" s="33" t="s">
-        <v>587</v>
+        <v>550</v>
       </c>
       <c r="D75" s="54" t="s">
-        <v>243</v>
-      </c>
-      <c r="E75" s="91" t="s">
-        <v>84</v>
+        <v>239</v>
+      </c>
+      <c r="E75" s="91">
+        <v>46162</v>
       </c>
       <c r="F75" s="54" t="s">
-        <v>626</v>
-      </c>
-      <c r="G75" s="33" t="str">
+        <v>608</v>
+      </c>
+      <c r="G75" s="33">
         <f>IF(ISBLANK(H75),"",_xlfn.XLOOKUP(H75,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H75" s="98"/>
-      <c r="I75" s="103"/>
-      <c r="J75" s="33"/>
-      <c r="K75" s="33"/>
+        <v>16</v>
+      </c>
+      <c r="H75" s="98">
+        <f>E75-1</f>
+        <v>46161</v>
+      </c>
+      <c r="I75" s="103">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="J75" s="33">
+        <v>60</v>
+      </c>
+      <c r="K75" s="33" t="s">
+        <v>24</v>
+      </c>
       <c r="L75" s="33" t="s">
-        <v>142</v>
+        <v>24</v>
       </c>
       <c r="M75" s="67" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N75" s="92"/>
-      <c r="P75" s="92" t="s">
-        <v>635</v>
-      </c>
+      <c r="O75" s="118" t="s">
+        <v>666</v>
+      </c>
+      <c r="P75" s="92"/>
       <c r="AI75" s="91"/>
     </row>
     <row r="76" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
@@ -12217,46 +12279,39 @@
         <v>#N/A</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C76" s="33" t="s">
-        <v>587</v>
+        <v>550</v>
       </c>
       <c r="D76" s="54" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E76" s="91" t="s">
         <v>84</v>
       </c>
       <c r="F76" s="54" t="s">
-        <v>636</v>
+        <v>579</v>
       </c>
       <c r="G76" s="33" t="str">
         <f>IF(ISBLANK(H76),"",_xlfn.XLOOKUP(H76,Info!A:A,Info!B:B))</f>
         <v/>
       </c>
       <c r="H76" s="98"/>
-      <c r="I76" s="103">
-        <v>0.625</v>
-      </c>
-      <c r="J76" s="33">
-        <v>30</v>
-      </c>
+      <c r="I76" s="103"/>
+      <c r="J76" s="33"/>
       <c r="K76" s="33" t="s">
-        <v>277</v>
+        <v>598</v>
       </c>
       <c r="L76" s="33" t="s">
-        <v>277</v>
+        <v>598</v>
       </c>
       <c r="M76" s="67" t="s">
-        <v>249</v>
-      </c>
-      <c r="N76" s="92" t="s">
-        <v>352</v>
-      </c>
-      <c r="O76" s="93"/>
+        <v>247</v>
+      </c>
+      <c r="N76" s="92"/>
       <c r="P76" s="92" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AI76" s="91"/>
     </row>
@@ -12266,37 +12321,46 @@
         <v>#N/A</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C77" s="33" t="s">
-        <v>587</v>
+        <v>550</v>
       </c>
       <c r="D77" s="54" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E77" s="91" t="s">
         <v>84</v>
       </c>
       <c r="F77" s="54" t="s">
-        <v>630</v>
+        <v>589</v>
       </c>
       <c r="G77" s="33" t="str">
         <f>IF(ISBLANK(H77),"",_xlfn.XLOOKUP(H77,Info!A:A,Info!B:B))</f>
         <v/>
       </c>
       <c r="H77" s="98"/>
-      <c r="I77" s="103"/>
-      <c r="J77" s="33"/>
+      <c r="I77" s="103">
+        <v>0.625</v>
+      </c>
+      <c r="J77" s="33">
+        <v>30</v>
+      </c>
       <c r="K77" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="L77" s="33"/>
+        <v>271</v>
+      </c>
+      <c r="L77" s="33" t="s">
+        <v>271</v>
+      </c>
       <c r="M77" s="67" t="s">
-        <v>249</v>
-      </c>
-      <c r="N77" s="92"/>
+        <v>247</v>
+      </c>
+      <c r="N77" s="92" t="s">
+        <v>345</v>
+      </c>
+      <c r="O77" s="93"/>
       <c r="P77" s="92" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AI77" s="91"/>
     </row>
@@ -12306,19 +12370,19 @@
         <v>#N/A</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C78" s="33" t="s">
-        <v>587</v>
+        <v>550</v>
       </c>
       <c r="D78" s="54" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E78" s="91" t="s">
         <v>84</v>
       </c>
       <c r="F78" s="54" t="s">
-        <v>631</v>
+        <v>582</v>
       </c>
       <c r="G78" s="33" t="str">
         <f>IF(ISBLANK(H78),"",_xlfn.XLOOKUP(H78,Info!A:A,Info!B:B))</f>
@@ -12327,16 +12391,16 @@
       <c r="H78" s="98"/>
       <c r="I78" s="103"/>
       <c r="J78" s="33"/>
-      <c r="K78" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="L78" s="33"/>
+      <c r="K78" s="33"/>
+      <c r="L78" s="33" t="s">
+        <v>142</v>
+      </c>
       <c r="M78" s="67" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N78" s="92"/>
       <c r="P78" s="92" t="s">
-        <v>347</v>
+        <v>588</v>
       </c>
       <c r="AI78" s="91"/>
     </row>
@@ -12346,35 +12410,37 @@
         <v>#N/A</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C79" s="33" t="s">
-        <v>587</v>
+        <v>550</v>
       </c>
       <c r="D79" s="54" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E79" s="91" t="s">
         <v>84</v>
       </c>
       <c r="F79" s="54" t="s">
-        <v>632</v>
+        <v>586</v>
       </c>
       <c r="G79" s="33" t="str">
         <f>IF(ISBLANK(H79),"",_xlfn.XLOOKUP(H79,Info!A:A,Info!B:B))</f>
         <v/>
       </c>
+      <c r="H79" s="98"/>
+      <c r="I79" s="103"/>
       <c r="J79" s="33"/>
       <c r="K79" s="33" t="s">
-        <v>542</v>
+        <v>234</v>
       </c>
       <c r="L79" s="33"/>
       <c r="M79" s="67" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N79" s="92"/>
       <c r="P79" s="92" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AI79" s="91"/>
     </row>
@@ -12384,19 +12450,19 @@
         <v>#N/A</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C80" s="33" t="s">
-        <v>587</v>
+        <v>550</v>
       </c>
       <c r="D80" s="54" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E80" s="91" t="s">
         <v>84</v>
       </c>
       <c r="F80" s="54" t="s">
-        <v>653</v>
+        <v>639</v>
       </c>
       <c r="G80" s="33" t="str">
         <f>IF(ISBLANK(H80),"",_xlfn.XLOOKUP(H80,Info!A:A,Info!B:B))</f>
@@ -12404,136 +12470,168 @@
       </c>
       <c r="H80" s="98"/>
       <c r="I80" s="103"/>
-      <c r="J80" s="33">
-        <v>30</v>
-      </c>
+      <c r="J80" s="33"/>
       <c r="K80" s="33" t="s">
-        <v>655</v>
-      </c>
-      <c r="L80" s="33" t="s">
-        <v>645</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="L80" s="33"/>
       <c r="M80" s="67" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N80" s="92"/>
       <c r="P80" s="92" t="s">
-        <v>654</v>
+        <v>340</v>
       </c>
       <c r="AI80" s="91"/>
     </row>
-    <row r="81" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="33" t="e">
         <f>IF(ISBLANK(E81),"",_xlfn.XLOOKUP(E81,Info!A:A,Info!B:B))</f>
         <v>#N/A</v>
       </c>
       <c r="B81" s="33" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C81" s="33" t="s">
-        <v>187</v>
+        <v>550</v>
       </c>
       <c r="D81" s="54" t="s">
-        <v>240</v>
-      </c>
-      <c r="E81" s="91">
-        <v>46051</v>
+        <v>239</v>
+      </c>
+      <c r="E81" s="91" t="s">
+        <v>84</v>
       </c>
       <c r="F81" s="54" t="s">
-        <v>659</v>
-      </c>
-      <c r="G81" s="33" t="e">
+        <v>640</v>
+      </c>
+      <c r="G81" s="33" t="str">
         <f>IF(ISBLANK(H81),"",_xlfn.XLOOKUP(H81,Info!A:A,Info!B:B))</f>
+        <v/>
+      </c>
+      <c r="J81" s="33"/>
+      <c r="K81" s="33" t="s">
+        <v>513</v>
+      </c>
+      <c r="L81" s="33"/>
+      <c r="M81" s="67" t="s">
+        <v>247</v>
+      </c>
+      <c r="N81" s="92"/>
+      <c r="P81" s="92" t="s">
+        <v>340</v>
+      </c>
+      <c r="AI81" s="91"/>
+    </row>
+    <row r="82" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="33" t="e">
+        <f>IF(ISBLANK(E82),"",_xlfn.XLOOKUP(E82,Info!A:A,Info!B:B))</f>
         <v>#N/A</v>
       </c>
-      <c r="H81" s="98">
-        <f>E81-1</f>
-        <v>46050</v>
-      </c>
-      <c r="I81" s="103">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J81" s="33">
-        <v>30</v>
-      </c>
-      <c r="K81" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="L81" s="33" t="s">
-        <v>245</v>
-      </c>
-      <c r="M81" s="67" t="s">
-        <v>249</v>
-      </c>
-      <c r="N81" s="92" t="s">
-        <v>656</v>
-      </c>
-      <c r="O81" s="118" t="s">
-        <v>657</v>
-      </c>
-      <c r="P81" s="92" t="s">
-        <v>658</v>
-      </c>
-      <c r="AI81" s="91"/>
-    </row>
-    <row r="82" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="33" t="str">
-        <f>IF(ISBLANK(E82),"",_xlfn.XLOOKUP(E82,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="B82" s="33"/>
-      <c r="C82" s="33"/>
-      <c r="D82" s="54"/>
-      <c r="E82" s="91"/>
-      <c r="F82" s="54"/>
-      <c r="G82" s="33" t="str">
+      <c r="B82" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C82" s="33" t="s">
+        <v>550</v>
+      </c>
+      <c r="D82" s="54" t="s">
+        <v>242</v>
+      </c>
+      <c r="E82" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="F82" s="54" t="s">
+        <v>641</v>
+      </c>
+      <c r="G82" s="33">
         <f>IF(ISBLANK(H82),"",_xlfn.XLOOKUP(H82,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H82" s="98"/>
+        <v>13</v>
+      </c>
+      <c r="H82" s="98">
+        <v>46143</v>
+      </c>
       <c r="I82" s="103"/>
-      <c r="J82" s="33"/>
-      <c r="K82" s="33"/>
-      <c r="L82" s="33"/>
-      <c r="M82" s="67"/>
+      <c r="J82" s="33">
+        <v>15</v>
+      </c>
+      <c r="K82" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="L82" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M82" s="67" t="s">
+        <v>247</v>
+      </c>
       <c r="N82" s="92"/>
-      <c r="P82" s="92"/>
+      <c r="P82" s="92" t="s">
+        <v>258</v>
+      </c>
       <c r="AI82" s="91"/>
     </row>
     <row r="83" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="33" t="str">
+      <c r="A83" s="33" t="e">
         <f>IF(ISBLANK(E83),"",_xlfn.XLOOKUP(E83,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="B83" s="33"/>
-      <c r="C83" s="33"/>
-      <c r="D83" s="54"/>
-      <c r="E83" s="91"/>
-      <c r="F83" s="54"/>
+        <v>#N/A</v>
+      </c>
+      <c r="B83" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C83" s="33" t="s">
+        <v>550</v>
+      </c>
+      <c r="D83" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E83" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="F83" s="54" t="s">
+        <v>600</v>
+      </c>
       <c r="G83" s="33" t="str">
         <f>IF(ISBLANK(H83),"",_xlfn.XLOOKUP(H83,Info!A:A,Info!B:B))</f>
         <v/>
       </c>
       <c r="H83" s="98"/>
       <c r="I83" s="103"/>
-      <c r="J83" s="33"/>
-      <c r="K83" s="33"/>
-      <c r="L83" s="33"/>
-      <c r="M83" s="67"/>
+      <c r="J83" s="33">
+        <v>30</v>
+      </c>
+      <c r="K83" s="33" t="s">
+        <v>645</v>
+      </c>
+      <c r="L83" s="33" t="s">
+        <v>597</v>
+      </c>
+      <c r="M83" s="67" t="s">
+        <v>247</v>
+      </c>
       <c r="N83" s="92"/>
-      <c r="P83" s="92"/>
+      <c r="P83" s="92" t="s">
+        <v>601</v>
+      </c>
       <c r="AI83" s="91"/>
     </row>
     <row r="84" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="33" t="str">
+      <c r="A84" s="33" t="e">
         <f>IF(ISBLANK(E84),"",_xlfn.XLOOKUP(E84,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="B84" s="33"/>
-      <c r="C84" s="33"/>
-      <c r="D84" s="54"/>
-      <c r="E84" s="91"/>
-      <c r="F84" s="54"/>
+        <v>#N/A</v>
+      </c>
+      <c r="B84" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C84" s="33" t="s">
+        <v>550</v>
+      </c>
+      <c r="D84" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E84" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="F84" s="54" t="s">
+        <v>618</v>
+      </c>
       <c r="G84" s="33" t="str">
         <f>IF(ISBLANK(H84),"",_xlfn.XLOOKUP(H84,Info!A:A,Info!B:B))</f>
         <v/>
@@ -12543,33 +12641,68 @@
       <c r="J84" s="33"/>
       <c r="K84" s="33"/>
       <c r="L84" s="33"/>
-      <c r="M84" s="67"/>
-      <c r="N84" s="92"/>
-      <c r="P84" s="92"/>
+      <c r="M84" s="67" t="s">
+        <v>247</v>
+      </c>
+      <c r="N84" s="92" t="s">
+        <v>615</v>
+      </c>
+      <c r="O84" s="118" t="s">
+        <v>617</v>
+      </c>
+      <c r="P84" s="92" t="s">
+        <v>616</v>
+      </c>
       <c r="AI84" s="91"/>
     </row>
     <row r="85" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="33" t="str">
+      <c r="A85" s="33">
         <f>IF(ISBLANK(E85),"",_xlfn.XLOOKUP(E85,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="B85" s="33"/>
-      <c r="C85" s="33"/>
-      <c r="D85" s="54"/>
-      <c r="E85" s="91"/>
-      <c r="F85" s="54"/>
-      <c r="G85" s="33" t="str">
+        <v>16</v>
+      </c>
+      <c r="B85" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C85" s="33" t="s">
+        <v>550</v>
+      </c>
+      <c r="D85" s="54" t="s">
+        <v>242</v>
+      </c>
+      <c r="E85" s="91">
+        <v>46160</v>
+      </c>
+      <c r="F85" s="54" t="s">
+        <v>620</v>
+      </c>
+      <c r="G85" s="33">
         <f>IF(ISBLANK(H85),"",_xlfn.XLOOKUP(H85,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H85" s="98"/>
-      <c r="I85" s="103"/>
-      <c r="J85" s="33"/>
-      <c r="K85" s="33"/>
-      <c r="L85" s="33"/>
-      <c r="M85" s="67"/>
-      <c r="N85" s="92"/>
-      <c r="P85" s="92"/>
+        <v>15</v>
+      </c>
+      <c r="H85" s="98">
+        <v>46157</v>
+      </c>
+      <c r="I85" s="103">
+        <v>0.5</v>
+      </c>
+      <c r="J85" s="33">
+        <v>60</v>
+      </c>
+      <c r="K85" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="L85" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M85" s="67" t="s">
+        <v>621</v>
+      </c>
+      <c r="N85" s="92" t="s">
+        <v>622</v>
+      </c>
+      <c r="P85" s="92" t="s">
+        <v>263</v>
+      </c>
       <c r="AI85" s="91"/>
     </row>
     <row r="86" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
@@ -20670,66 +20803,69 @@
         <filter val="Scheduled"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A68:P446">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A73:P446">
       <sortCondition ref="E1:E446"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="O31" r:id="rId1" xr:uid="{4AB47A6A-4758-468E-9ABE-A8478398929C}"/>
-    <hyperlink ref="O32" r:id="rId2" xr:uid="{3C470CFD-30AC-427C-81D6-04534F0AD790}"/>
-    <hyperlink ref="O33" r:id="rId3" xr:uid="{C8246BB3-CE1F-4696-B6EB-0777A4A22E90}"/>
-    <hyperlink ref="O40" r:id="rId4" xr:uid="{1C14914A-252F-46CD-8B60-6A7EA10AF4F8}"/>
-    <hyperlink ref="O38" r:id="rId5" xr:uid="{1E8FF064-FA07-4571-9477-8D3F9147FEAA}"/>
-    <hyperlink ref="O39" r:id="rId6" display="SteerCo 4/3" xr:uid="{3608671F-7368-4A4A-93F7-9A80B18C8BAB}"/>
-    <hyperlink ref="O47" r:id="rId7" xr:uid="{9136A310-9369-41C6-BAED-32CB002CE94A}"/>
-    <hyperlink ref="O50" r:id="rId8" xr:uid="{E2F31F07-DB89-40C8-AE9E-A987A8D1E4B4}"/>
-    <hyperlink ref="O65" r:id="rId9" xr:uid="{8F58BE38-7A42-460E-B08F-4BCBD11D4EF2}"/>
-    <hyperlink ref="O71" r:id="rId10" xr:uid="{FAFF2A5C-B437-4651-AEC0-F9FBBEA1F708}"/>
-    <hyperlink ref="O73" r:id="rId11" xr:uid="{46908BF7-DCEE-4296-AA65-B2F566D75749}"/>
-    <hyperlink ref="O45" r:id="rId12" xr:uid="{19A3457D-0B43-40CB-9075-45A9F282F442}"/>
-    <hyperlink ref="O53" r:id="rId13" xr:uid="{A441FB20-94DE-446F-97E5-DB600A08E719}"/>
-    <hyperlink ref="O43" r:id="rId14" xr:uid="{8630D048-1902-45FA-B70D-BC195B21388A}"/>
-    <hyperlink ref="O55" r:id="rId15" xr:uid="{347AA809-6F53-49C7-83DD-9966348FF275}"/>
-    <hyperlink ref="O46" r:id="rId16" xr:uid="{05047BFC-AF28-4F80-A560-2CACDBF803A7}"/>
-    <hyperlink ref="O51" r:id="rId17" xr:uid="{6CAF9855-3E96-4B1A-AA82-DC4E4C2F8C3B}"/>
-    <hyperlink ref="O52" r:id="rId18" xr:uid="{DFDA96C4-FFDD-4DAC-816F-A9A3497B8845}"/>
-    <hyperlink ref="O48" r:id="rId19" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_13 SteerCo NG %26 NS Campus.pptx?d=w41173a6f757f4cfc818111ad35e8a3cd&amp;csf=1&amp;web=1&amp;e=FsS4WG" xr:uid="{EC54F4CA-F5DF-4135-BC35-4B317B458D3A}"/>
+    <hyperlink ref="O33" r:id="rId1" xr:uid="{4AB47A6A-4758-468E-9ABE-A8478398929C}"/>
+    <hyperlink ref="O36" r:id="rId2" xr:uid="{3C470CFD-30AC-427C-81D6-04534F0AD790}"/>
+    <hyperlink ref="O38" r:id="rId3" xr:uid="{C8246BB3-CE1F-4696-B6EB-0777A4A22E90}"/>
+    <hyperlink ref="O43" r:id="rId4" display="Carnesville May ASM " xr:uid="{1C14914A-252F-46CD-8B60-6A7EA10AF4F8}"/>
+    <hyperlink ref="O40" r:id="rId5" xr:uid="{1E8FF064-FA07-4571-9477-8D3F9147FEAA}"/>
+    <hyperlink ref="O42" r:id="rId6" display="SteerCo 4/3" xr:uid="{3608671F-7368-4A4A-93F7-9A80B18C8BAB}"/>
+    <hyperlink ref="O48" r:id="rId7" display="Carnesville May ASM " xr:uid="{9136A310-9369-41C6-BAED-32CB002CE94A}"/>
+    <hyperlink ref="O51" r:id="rId8" display="Carnesville May ASM " xr:uid="{E2F31F07-DB89-40C8-AE9E-A987A8D1E4B4}"/>
+    <hyperlink ref="O66" r:id="rId9" display="Carnesville May ASM " xr:uid="{8F58BE38-7A42-460E-B08F-4BCBD11D4EF2}"/>
+    <hyperlink ref="O72" r:id="rId10" display="Carnesville May ASM " xr:uid="{FAFF2A5C-B437-4651-AEC0-F9FBBEA1F708}"/>
+    <hyperlink ref="O74" r:id="rId11" display="Carnesville May ASM " xr:uid="{46908BF7-DCEE-4296-AA65-B2F566D75749}"/>
+    <hyperlink ref="O46" r:id="rId12" display="Carnesville May ASM " xr:uid="{19A3457D-0B43-40CB-9075-45A9F282F442}"/>
+    <hyperlink ref="O55" r:id="rId13" display="Carnesville May ASM " xr:uid="{A441FB20-94DE-446F-97E5-DB600A08E719}"/>
+    <hyperlink ref="O44" r:id="rId14" xr:uid="{8630D048-1902-45FA-B70D-BC195B21388A}"/>
+    <hyperlink ref="O56" r:id="rId15" xr:uid="{347AA809-6F53-49C7-83DD-9966348FF275}"/>
+    <hyperlink ref="O47" r:id="rId16" xr:uid="{05047BFC-AF28-4F80-A560-2CACDBF803A7}"/>
+    <hyperlink ref="O52" r:id="rId17" xr:uid="{6CAF9855-3E96-4B1A-AA82-DC4E4C2F8C3B}"/>
+    <hyperlink ref="O53" r:id="rId18" xr:uid="{DFDA96C4-FFDD-4DAC-816F-A9A3497B8845}"/>
+    <hyperlink ref="O50" r:id="rId19" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_13 SteerCo NG %26 NS Campus.pptx?d=w41173a6f757f4cfc818111ad35e8a3cd&amp;csf=1&amp;web=1&amp;e=FsS4WG" xr:uid="{EC54F4CA-F5DF-4135-BC35-4B317B458D3A}"/>
     <hyperlink ref="O14" r:id="rId20" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_02_26 SteerCo Carnesville BC_IP Increase_EV Yard Trucks.pptx?d=w483415fbde51469688ade05b37b8542f&amp;csf=1&amp;web=1&amp;e=aU0OaP" xr:uid="{24F5FFB2-D300-40A9-B4F0-AFA7EF810791}"/>
-    <hyperlink ref="O13" r:id="rId21" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_02_26 SteerCo Carnesville BC_IP Increase_EV Yard Trucks.pptx?d=w483415fbde51469688ade05b37b8542f&amp;csf=1&amp;web=1&amp;e=aU0OaP" xr:uid="{DA7742A1-779F-4BC9-AAB8-2FE8CB66A994}"/>
-    <hyperlink ref="O11" r:id="rId22" display="https://teams.wal-mart.com/:b:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_02_20 Carnesville CapEx Reduction Slides-SteerCo.pdf?csf=1&amp;web=1&amp;e=qGXObA" xr:uid="{636211AD-4B43-425E-B121-68B4EE7E3A34}"/>
-    <hyperlink ref="O29" r:id="rId23" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_19 SteerCo BDR Buckeye %26 Wallkill_ Wallkill Timeline.pptx?d=w0e7c34317d1a4d97b16574d08ad8a49d&amp;csf=1&amp;web=1&amp;e=mOqfbx" xr:uid="{F51BEFD5-5F34-4461-BE42-FE2DB48B06E6}"/>
+    <hyperlink ref="O15" r:id="rId21" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_02_26 SteerCo Carnesville BC_IP Increase_EV Yard Trucks.pptx?d=w483415fbde51469688ade05b37b8542f&amp;csf=1&amp;web=1&amp;e=aU0OaP" xr:uid="{DA7742A1-779F-4BC9-AAB8-2FE8CB66A994}"/>
+    <hyperlink ref="O12" r:id="rId22" display="https://teams.wal-mart.com/:b:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_02_20 Carnesville CapEx Reduction Slides-SteerCo.pdf?csf=1&amp;web=1&amp;e=qGXObA" xr:uid="{636211AD-4B43-425E-B121-68B4EE7E3A34}"/>
+    <hyperlink ref="O30" r:id="rId23" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_19 SteerCo BDR Buckeye %26 Wallkill_ Wallkill Timeline.pptx?d=w0e7c34317d1a4d97b16574d08ad8a49d&amp;csf=1&amp;web=1&amp;e=mOqfbx" xr:uid="{F51BEFD5-5F34-4461-BE42-FE2DB48B06E6}"/>
     <hyperlink ref="O28" r:id="rId24" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_19 SteerCo BDR Buckeye %26 Wallkill_ Wallkill Timeline.pptx?d=w0e7c34317d1a4d97b16574d08ad8a49d&amp;csf=1&amp;web=1&amp;e=mOqfbx" xr:uid="{9934D181-A94E-4129-AB6E-B4FFEF352F38}"/>
-    <hyperlink ref="O27" r:id="rId25" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_19 SteerCo BDR Buckeye %26 Wallkill_ Wallkill Timeline.pptx?d=w0e7c34317d1a4d97b16574d08ad8a49d&amp;csf=1&amp;web=1&amp;e=mOqfbx" xr:uid="{4C338460-DE1B-47BA-84DD-5240EAD0D1BD}"/>
-    <hyperlink ref="O19" r:id="rId26" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_05 SteerCo IP Moved to 80%25_Wallkill Political Update %26 Business Case.pptx?d=w07127f8f0a314e8395c570ec3c7753b7&amp;csf=1&amp;web=1&amp;e=mJzRFA" xr:uid="{0FDC6EFF-6E17-4A8B-AE33-568E8FA72C60}"/>
-    <hyperlink ref="O20" r:id="rId27" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_05 SteerCo IP Moved to 80%25_Wallkill Political Update %26 Business Case.pptx?d=w07127f8f0a314e8395c570ec3c7753b7&amp;csf=1&amp;web=1&amp;e=mJzRFA" xr:uid="{B9473B94-9018-4845-8232-60338DAE9609}"/>
+    <hyperlink ref="O31" r:id="rId25" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_19 SteerCo BDR Buckeye %26 Wallkill_ Wallkill Timeline.pptx?d=w0e7c34317d1a4d97b16574d08ad8a49d&amp;csf=1&amp;web=1&amp;e=mOqfbx" xr:uid="{4C338460-DE1B-47BA-84DD-5240EAD0D1BD}"/>
+    <hyperlink ref="O20" r:id="rId26" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_05 SteerCo IP Moved to 80%25_Wallkill Political Update %26 Business Case.pptx?d=w07127f8f0a314e8395c570ec3c7753b7&amp;csf=1&amp;web=1&amp;e=mJzRFA" xr:uid="{0FDC6EFF-6E17-4A8B-AE33-568E8FA72C60}"/>
+    <hyperlink ref="O22" r:id="rId27" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_05 SteerCo IP Moved to 80%25_Wallkill Political Update %26 Business Case.pptx?d=w07127f8f0a314e8395c570ec3c7753b7&amp;csf=1&amp;web=1&amp;e=mJzRFA" xr:uid="{B9473B94-9018-4845-8232-60338DAE9609}"/>
     <hyperlink ref="O21" r:id="rId28" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_05 SteerCo IP Moved to 80%25_Wallkill Political Update %26 Business Case.pptx?d=w07127f8f0a314e8395c570ec3c7753b7&amp;csf=1&amp;web=1&amp;e=mJzRFA" xr:uid="{72203D11-1018-447F-88C6-A2BB905BB8CB}"/>
-    <hyperlink ref="O22" r:id="rId29" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_05 SteerCo IP Moved to 80%25_Wallkill Political Update %26 Business Case.pptx?d=w07127f8f0a314e8395c570ec3c7753b7&amp;csf=1&amp;web=1&amp;e=mJzRFA" xr:uid="{A524FA2A-B666-49E4-B627-A9CA3064B45C}"/>
+    <hyperlink ref="O23" r:id="rId29" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_05 SteerCo IP Moved to 80%25_Wallkill Political Update %26 Business Case.pptx?d=w07127f8f0a314e8395c570ec3c7753b7&amp;csf=1&amp;web=1&amp;e=mJzRFA" xr:uid="{A524FA2A-B666-49E4-B627-A9CA3064B45C}"/>
     <hyperlink ref="O24" r:id="rId30" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_12 SteerCo.pptx?d=w970d351de1e84db7811c7aa78bae01a9&amp;csf=1&amp;web=1&amp;e=V0ELec" xr:uid="{10D9CE32-C70D-4E13-B166-4E9E65FDB112}"/>
     <hyperlink ref="O25" r:id="rId31" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_12 SteerCo.pptx?d=w970d351de1e84db7811c7aa78bae01a9&amp;csf=1&amp;web=1&amp;e=V0ELec" xr:uid="{2E11D159-43B6-47AB-B4A8-369CFFB98244}"/>
     <hyperlink ref="O26" r:id="rId32" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_12 SteerCo.pptx?d=w970d351de1e84db7811c7aa78bae01a9&amp;csf=1&amp;web=1&amp;e=V0ELec" xr:uid="{127E3107-1547-4977-A66A-34A6DEA03DB0}"/>
-    <hyperlink ref="O41" r:id="rId33" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_02 SteerCo Cost to Server Carnesville Maintenance Strategy.pptx?d=w876d4d25a3a3479f9703ef581bdc54c8&amp;csf=1&amp;web=1&amp;e=lfF9uT" xr:uid="{94DDBDAF-82F7-4692-98D5-7FCED8E7CD84}"/>
-    <hyperlink ref="O42" r:id="rId34" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_02 SteerCo Cost to Server Carnesville Maintenance Strategy.pptx?d=w876d4d25a3a3479f9703ef581bdc54c8&amp;csf=1&amp;web=1&amp;e=lfF9uT" xr:uid="{01C07C0F-994A-47E2-8CAB-F2A5A805807D}"/>
-    <hyperlink ref="O56" r:id="rId35" xr:uid="{03B1410F-8E16-457F-AC07-01F42694D756}"/>
-    <hyperlink ref="O63" r:id="rId36" xr:uid="{ED20F09F-4695-46D7-B337-0CB9D9CA0AE1}"/>
-    <hyperlink ref="O44" r:id="rId37" xr:uid="{79069AD2-A8F8-4072-821A-21BC63F7C68D}"/>
-    <hyperlink ref="O37" r:id="rId38" xr:uid="{45DE746D-3394-418B-972F-E8D9F19F7C07}"/>
-    <hyperlink ref="O49" r:id="rId39" xr:uid="{38D1352B-3F87-4D84-8086-F2C6D9134A42}"/>
-    <hyperlink ref="O64" r:id="rId40" xr:uid="{4D79B66D-8082-4C4E-8A10-51D37220AFA6}"/>
-    <hyperlink ref="O57" r:id="rId41" xr:uid="{BFB200FF-12D4-429E-92C1-18437F29C6BA}"/>
-    <hyperlink ref="O69" r:id="rId42" xr:uid="{92FE8EC6-22B4-496F-A1B6-8E96247465FD}"/>
-    <hyperlink ref="O54" r:id="rId43" xr:uid="{7A5B02B9-251F-48BB-985E-F9666B486C06}"/>
-    <hyperlink ref="O59" r:id="rId44" xr:uid="{D5A5B25C-6B7F-4594-B395-B6C31E7938D6}"/>
-    <hyperlink ref="O60" r:id="rId45" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_27 Wallkill IRR Deep Dive.pptx?d=w5d08b18b5ec84bd1b9aa93de82721232&amp;csf=1&amp;web=1&amp;e=PGWwPK" xr:uid="{DAEB8D4F-C074-454C-8618-0742CC79C2CE}"/>
-    <hyperlink ref="O23" r:id="rId46" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_12 SteerCo Energy CapEx Increase.pptx?d=w970d351de1e84db7811c7aa78bae01a9&amp;csf=1&amp;web=1&amp;e=OwhQ0n" xr:uid="{B254335B-B5C3-476A-800E-457192F58110}"/>
-    <hyperlink ref="O58" r:id="rId47" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/Rob Presentations/26_04_24 Buckeye Land Purchase Alignment.pptx?d=w79ea097951a34a778b4d3c07a8ae8405&amp;csf=1&amp;web=1&amp;e=q8Rf3o" xr:uid="{4E7BEC15-6F02-4AF5-B0D0-1AA7D34A030D}"/>
+    <hyperlink ref="O39" r:id="rId33" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_02 SteerCo Cost to Server Carnesville Maintenance Strategy.pptx?d=w876d4d25a3a3479f9703ef581bdc54c8&amp;csf=1&amp;web=1&amp;e=lfF9uT" xr:uid="{94DDBDAF-82F7-4692-98D5-7FCED8E7CD84}"/>
+    <hyperlink ref="O41" r:id="rId34" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_02 SteerCo Cost to Server Carnesville Maintenance Strategy.pptx?d=w876d4d25a3a3479f9703ef581bdc54c8&amp;csf=1&amp;web=1&amp;e=lfF9uT" xr:uid="{01C07C0F-994A-47E2-8CAB-F2A5A805807D}"/>
+    <hyperlink ref="O58" r:id="rId35" xr:uid="{03B1410F-8E16-457F-AC07-01F42694D756}"/>
+    <hyperlink ref="O64" r:id="rId36" display="Carnesville May ASM " xr:uid="{ED20F09F-4695-46D7-B337-0CB9D9CA0AE1}"/>
+    <hyperlink ref="O45" r:id="rId37" display="Carnesville May ASM " xr:uid="{79069AD2-A8F8-4072-821A-21BC63F7C68D}"/>
+    <hyperlink ref="O32" r:id="rId38" display="Carnesville May ASM " xr:uid="{45DE746D-3394-418B-972F-E8D9F19F7C07}"/>
+    <hyperlink ref="O49" r:id="rId39" display="Carnesville May ASM " xr:uid="{38D1352B-3F87-4D84-8086-F2C6D9134A42}"/>
+    <hyperlink ref="O65" r:id="rId40" display="Carnesville May ASM " xr:uid="{4D79B66D-8082-4C4E-8A10-51D37220AFA6}"/>
+    <hyperlink ref="O57" r:id="rId41" display="Carnesville May ASM " xr:uid="{BFB200FF-12D4-429E-92C1-18437F29C6BA}"/>
+    <hyperlink ref="O70" r:id="rId42" display="Carnesville May ASM " xr:uid="{92FE8EC6-22B4-496F-A1B6-8E96247465FD}"/>
+    <hyperlink ref="O54" r:id="rId43" display="Carnesville May ASM " xr:uid="{7A5B02B9-251F-48BB-985E-F9666B486C06}"/>
+    <hyperlink ref="O60" r:id="rId44" display="Carnesville May ASM " xr:uid="{D5A5B25C-6B7F-4594-B395-B6C31E7938D6}"/>
+    <hyperlink ref="O61" r:id="rId45" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_27 Wallkill IRR Deep Dive.pptx?d=w5d08b18b5ec84bd1b9aa93de82721232&amp;csf=1&amp;web=1&amp;e=PGWwPK" xr:uid="{DAEB8D4F-C074-454C-8618-0742CC79C2CE}"/>
+    <hyperlink ref="O27" r:id="rId46" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_03_12 SteerCo Energy CapEx Increase.pptx?d=w970d351de1e84db7811c7aa78bae01a9&amp;csf=1&amp;web=1&amp;e=OwhQ0n" xr:uid="{B254335B-B5C3-476A-800E-457192F58110}"/>
+    <hyperlink ref="O59" r:id="rId47" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/Rob Presentations/26_04_24 Buckeye Land Purchase Alignment.pptx?d=w79ea097951a34a778b4d3c07a8ae8405&amp;csf=1&amp;web=1&amp;e=q8Rf3o" xr:uid="{4E7BEC15-6F02-4AF5-B0D0-1AA7D34A030D}"/>
     <hyperlink ref="O67" r:id="rId48" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_04 SteerCo.pptx?d=wd44f71dddce1499cb3c5f8a6f9c7fd63&amp;csf=1&amp;web=1&amp;e=40F5If" xr:uid="{7C1BC644-7E0E-4546-BFB5-D723B14FB576}"/>
-    <hyperlink ref="O66" r:id="rId49" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_04 SteerCo.pptx?d=wd44f71dddce1499cb3c5f8a6f9c7fd63&amp;csf=1&amp;web=1&amp;e=40F5If" xr:uid="{40641C77-008F-4F12-A0D4-E35FE66E2971}"/>
-    <hyperlink ref="O62" r:id="rId50" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_30 SteerCo.pptx?d=wdb87420320c440f3a352dd4f0e632eb9&amp;csf=1&amp;web=1&amp;e=B6iMdT" xr:uid="{6BF12395-B556-46A4-85ED-12F1DEAE5FDB}"/>
-    <hyperlink ref="O61" r:id="rId51" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_30 SteerCo.pptx?d=wdb87420320c440f3a352dd4f0e632eb9&amp;csf=1&amp;web=1&amp;e=B6iMdT" xr:uid="{F70C6EE1-3B65-42A7-BDCF-59B2DC98581C}"/>
-    <hyperlink ref="O68" r:id="rId52" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_04 SteerCo.pptx?d=wd44f71dddce1499cb3c5f8a6f9c7fd63&amp;csf=1&amp;web=1&amp;e=40F5If" xr:uid="{60F2AB70-8A56-4F25-B312-E392A4388BC6}"/>
-    <hyperlink ref="O81" r:id="rId53" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_01_29 Northeast Spec Bld Analysis.pptx?d=w9c538d8635b94c129ba00ea7eac27a0e&amp;csf=1&amp;web=1&amp;e=Cn3L1m" xr:uid="{4A6DDCAA-2AC4-4B9D-9AB3-D4FFDD8113C4}"/>
-    <hyperlink ref="O70" r:id="rId54" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_08 SteerCo.pptx?d=wd863957755e742f8bfaaadcb434b30d7&amp;csf=1&amp;web=1&amp;e=6FERxe" xr:uid="{A06FD16C-22D9-4F10-9FC7-D919C3472D73}"/>
+    <hyperlink ref="O68" r:id="rId49" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_04 SteerCo.pptx?d=wd44f71dddce1499cb3c5f8a6f9c7fd63&amp;csf=1&amp;web=1&amp;e=40F5If" xr:uid="{40641C77-008F-4F12-A0D4-E35FE66E2971}"/>
+    <hyperlink ref="O63" r:id="rId50" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_30 SteerCo.pptx?d=wdb87420320c440f3a352dd4f0e632eb9&amp;csf=1&amp;web=1&amp;e=B6iMdT" xr:uid="{6BF12395-B556-46A4-85ED-12F1DEAE5FDB}"/>
+    <hyperlink ref="O62" r:id="rId51" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_30 SteerCo.pptx?d=wdb87420320c440f3a352dd4f0e632eb9&amp;csf=1&amp;web=1&amp;e=B6iMdT" xr:uid="{F70C6EE1-3B65-42A7-BDCF-59B2DC98581C}"/>
+    <hyperlink ref="O69" r:id="rId52" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_04 SteerCo.pptx?d=wd44f71dddce1499cb3c5f8a6f9c7fd63&amp;csf=1&amp;web=1&amp;e=40F5If" xr:uid="{60F2AB70-8A56-4F25-B312-E392A4388BC6}"/>
+    <hyperlink ref="O6" r:id="rId53" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_01_29 Northeast Spec Bld Analysis.pptx?d=w9c538d8635b94c129ba00ea7eac27a0e&amp;csf=1&amp;web=1&amp;e=Cn3L1m" xr:uid="{4A6DDCAA-2AC4-4B9D-9AB3-D4FFDD8113C4}"/>
+    <hyperlink ref="O71" r:id="rId54" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_08 SteerCo.pptx?d=wd863957755e742f8bfaaadcb434b30d7&amp;csf=1&amp;web=1&amp;e=6FERxe" xr:uid="{A06FD16C-22D9-4F10-9FC7-D919C3472D73}"/>
+    <hyperlink ref="O73" r:id="rId55" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_14 SteerCo.pptx?d=wfcde045a0ff1452686c02d98bf7836c7&amp;csf=1&amp;web=1&amp;e=8aJxB1" xr:uid="{46143575-5EB8-4C9E-807B-5850612A768D}"/>
+    <hyperlink ref="O84" r:id="rId56" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_30 NextGen Burn Testing OpEx Required.pptx?d=wd99f0bea311e458c940769f98e41f64d&amp;csf=1&amp;web=1&amp;e=TJNOEa" xr:uid="{73104FA3-48DC-41E6-A8B4-8FCD3A15AD50}"/>
+    <hyperlink ref="O75" r:id="rId57" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_20 SteerCo Wallkill Scenarios.pptx?d=waa33fa32cdff4b44be75eb893feb1364&amp;csf=1&amp;web=1&amp;e=oF1OhE" xr:uid="{ADF03195-F8AA-4911-8755-98E024B646AF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20740,122 +20876,134 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:R68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" style="98" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" style="98" bestFit="1" customWidth="1"/>
     <col min="3" max="8" width="15.85546875" style="33" customWidth="1"/>
     <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="46.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B1" s="98" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C1" s="98" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D1" s="98" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E1" s="98" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F1" s="98" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G1" s="98" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H1" s="98" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+      <c r="Q1" s="141" t="s">
+        <v>658</v>
+      </c>
+      <c r="R1" s="97"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B2" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>304</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q2" s="142" t="s">
+        <v>659</v>
+      </c>
+      <c r="R2" s="97"/>
+    </row>
+    <row r="3" spans="1:18" s="97" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="97" t="s">
+        <v>378</v>
+      </c>
+      <c r="B3" s="104" t="s">
+        <v>300</v>
+      </c>
+      <c r="C3" s="105" t="s">
+        <v>373</v>
+      </c>
+      <c r="D3" s="105" t="s">
+        <v>374</v>
+      </c>
+      <c r="E3" s="105" t="s">
+        <v>395</v>
+      </c>
+      <c r="F3" s="105" t="s">
+        <v>375</v>
+      </c>
+      <c r="G3" s="105" t="s">
+        <v>376</v>
+      </c>
+      <c r="H3" s="105" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q3" s="143" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B4" s="98" t="s">
+        <v>312</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="B2" s="98" t="s">
-        <v>307</v>
-      </c>
-      <c r="C2" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>312</v>
-      </c>
-      <c r="F2" s="33" t="s">
-        <v>313</v>
-      </c>
-      <c r="G2" s="33" t="s">
+      <c r="E4" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>314</v>
-      </c>
-      <c r="H2" s="33" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="97" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="97" t="s">
-        <v>388</v>
-      </c>
-      <c r="B3" s="104" t="s">
-        <v>306</v>
-      </c>
-      <c r="C3" s="105" t="s">
-        <v>382</v>
-      </c>
-      <c r="D3" s="105" t="s">
-        <v>383</v>
-      </c>
-      <c r="E3" s="105" t="s">
-        <v>406</v>
-      </c>
-      <c r="F3" s="105" t="s">
-        <v>384</v>
-      </c>
-      <c r="G3" s="105" t="s">
-        <v>385</v>
-      </c>
-      <c r="H3" s="105" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B4" s="98" t="s">
-        <v>318</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>321</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>322</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>325</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>326</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>320</v>
       </c>
       <c r="B5" s="33">
         <v>4843</v>
@@ -20879,37 +21027,37 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B6" s="98" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C6" s="33" t="s">
         <v>84</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>573</v>
+        <v>539</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>574</v>
+        <v>540</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>575</v>
+        <v>541</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>332</v>
-      </c>
-      <c r="B7" s="135">
+        <v>326</v>
+      </c>
+      <c r="B7" s="119">
         <v>45923</v>
       </c>
       <c r="C7" s="98">
@@ -20934,14 +21082,14 @@
         <v>218</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="139" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="138" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>572</v>
+        <v>538</v>
       </c>
       <c r="B9" s="98">
         <v>45792</v>
@@ -20966,9 +21114,9 @@
       </c>
       <c r="I9" s="96"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B10" s="98">
         <v>45792</v>
@@ -20993,9 +21141,9 @@
       </c>
       <c r="I10" s="96"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B11" s="98">
         <v>45855</v>
@@ -21020,9 +21168,9 @@
       </c>
       <c r="I11" s="96"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B12" s="98">
         <v>45971</v>
@@ -21047,9 +21195,9 @@
       </c>
       <c r="I12" s="96"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>583</v>
+        <v>547</v>
       </c>
       <c r="B13" s="98">
         <v>45971</v>
@@ -21074,9 +21222,9 @@
       </c>
       <c r="I13" s="96"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B14" s="98">
         <v>45971</v>
@@ -21101,9 +21249,9 @@
       </c>
       <c r="I14" s="96"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="97" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B15" s="98">
         <v>45800</v>
@@ -21129,17 +21277,17 @@
       <c r="I15" s="96"/>
       <c r="K15" s="117"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="97" t="s">
-        <v>621</v>
-      </c>
-      <c r="B16" s="144">
+        <v>578</v>
+      </c>
+      <c r="B16" s="140">
         <v>45859</v>
       </c>
-      <c r="C16" s="144">
+      <c r="C16" s="140">
         <v>46083</v>
       </c>
-      <c r="D16" s="144">
+      <c r="D16" s="140">
         <v>45992</v>
       </c>
       <c r="E16" s="98"/>
@@ -21151,169 +21299,169 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B17" s="98">
         <v>45958</v>
       </c>
       <c r="C17" s="98">
-        <v>46185</v>
+        <v>46199</v>
       </c>
       <c r="D17" s="98">
         <v>46080</v>
       </c>
-      <c r="E17" s="137">
+      <c r="E17" s="136">
         <v>46367</v>
       </c>
-      <c r="F17" s="137">
+      <c r="F17" s="136">
         <v>46269</v>
       </c>
-      <c r="G17" s="137">
+      <c r="G17" s="136">
         <v>46395</v>
       </c>
-      <c r="H17" s="137">
+      <c r="H17" s="136">
         <v>46395</v>
       </c>
       <c r="I17" s="96"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="97" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B18" s="98">
         <v>45982</v>
       </c>
       <c r="C18" s="98">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="D18" s="98">
         <v>46115</v>
       </c>
-      <c r="E18" s="137">
+      <c r="E18" s="136">
         <v>46416</v>
       </c>
-      <c r="F18" s="137">
+      <c r="F18" s="136">
         <v>46416</v>
       </c>
-      <c r="G18" s="137">
+      <c r="G18" s="136">
         <v>46430</v>
       </c>
-      <c r="H18" s="137">
+      <c r="H18" s="136">
         <v>46430</v>
       </c>
       <c r="I18" s="96"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B19" s="98">
         <v>46087</v>
       </c>
       <c r="C19" s="98">
-        <v>46255</v>
+        <v>46269</v>
       </c>
       <c r="D19" s="98">
         <v>46171</v>
       </c>
-      <c r="E19" s="137">
+      <c r="E19" s="136">
         <v>46451</v>
       </c>
-      <c r="F19" s="137">
+      <c r="F19" s="136">
         <v>46451</v>
       </c>
-      <c r="G19" s="137">
+      <c r="G19" s="136">
         <v>46465</v>
       </c>
-      <c r="H19" s="137">
+      <c r="H19" s="136">
         <v>46465</v>
       </c>
       <c r="I19" s="96"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="97" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B20" s="98">
         <v>46122</v>
       </c>
       <c r="C20" s="98">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="D20" s="98">
         <v>46206</v>
       </c>
-      <c r="E20" s="137">
+      <c r="E20" s="136">
         <v>46486</v>
       </c>
-      <c r="F20" s="137">
+      <c r="F20" s="136">
         <v>46486</v>
       </c>
-      <c r="G20" s="137">
+      <c r="G20" s="136">
         <v>46500</v>
       </c>
-      <c r="H20" s="137">
+      <c r="H20" s="136">
         <v>46500</v>
       </c>
       <c r="I20" s="96"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B21" s="98">
         <v>46143</v>
       </c>
       <c r="C21" s="98">
-        <v>46325</v>
+        <v>46339</v>
       </c>
       <c r="D21" s="98">
         <v>46241</v>
       </c>
-      <c r="E21" s="137">
+      <c r="E21" s="136">
         <v>46521</v>
       </c>
-      <c r="F21" s="137">
+      <c r="F21" s="136">
         <v>46521</v>
       </c>
-      <c r="G21" s="137">
+      <c r="G21" s="136">
         <v>46535</v>
       </c>
-      <c r="H21" s="137">
+      <c r="H21" s="136">
         <v>46535</v>
       </c>
       <c r="I21" s="96"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B22" s="98">
         <v>46153</v>
       </c>
       <c r="C22" s="98">
-        <v>46391</v>
+        <v>46370</v>
       </c>
       <c r="D22" s="98">
         <v>46132</v>
       </c>
-      <c r="E22" s="137">
+      <c r="E22" s="136">
         <v>46531</v>
       </c>
-      <c r="F22" s="137">
+      <c r="F22" s="136">
         <v>46531</v>
       </c>
-      <c r="G22" s="137">
+      <c r="G22" s="136">
         <v>46545</v>
       </c>
-      <c r="H22" s="137">
+      <c r="H22" s="136">
         <v>46545</v>
       </c>
       <c r="I22" s="96"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B23" s="98">
         <v>46248</v>
@@ -21324,23 +21472,23 @@
       <c r="D23" s="98">
         <v>46780</v>
       </c>
-      <c r="E23" s="137">
+      <c r="E23" s="136">
         <v>46731</v>
       </c>
-      <c r="F23" s="137">
+      <c r="F23" s="136">
         <v>46731</v>
       </c>
-      <c r="G23" s="137">
+      <c r="G23" s="136">
         <v>46913</v>
       </c>
-      <c r="H23" s="137">
+      <c r="H23" s="136">
         <v>46913</v>
       </c>
       <c r="I23" s="96"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="97" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B24" s="98">
         <v>46272</v>
@@ -21351,23 +21499,23 @@
       <c r="D24" s="98">
         <v>46811</v>
       </c>
-      <c r="E24" s="137">
+      <c r="E24" s="136">
         <v>46762</v>
       </c>
-      <c r="F24" s="137">
+      <c r="F24" s="136">
         <v>46762</v>
       </c>
-      <c r="G24" s="137">
+      <c r="G24" s="136">
         <v>46944</v>
       </c>
-      <c r="H24" s="137">
+      <c r="H24" s="136">
         <v>46944</v>
       </c>
       <c r="I24" s="96"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="97" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B25" s="98">
         <v>46878</v>
@@ -21378,23 +21526,23 @@
       <c r="D25" s="98">
         <v>47417</v>
       </c>
-      <c r="E25" s="137">
+      <c r="E25" s="136">
         <v>47375</v>
       </c>
-      <c r="F25" s="137">
+      <c r="F25" s="136">
         <v>47375</v>
       </c>
-      <c r="G25" s="137">
+      <c r="G25" s="136">
         <v>47543</v>
       </c>
-      <c r="H25" s="137">
+      <c r="H25" s="136">
         <v>47543</v>
       </c>
       <c r="I25" s="96"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B26" s="98">
         <v>47056</v>
@@ -21403,25 +21551,25 @@
         <v>47291</v>
       </c>
       <c r="D26" s="98">
-        <v>47615</v>
-      </c>
-      <c r="E26" s="137">
+        <v>47616</v>
+      </c>
+      <c r="E26" s="136">
         <v>47553</v>
       </c>
-      <c r="F26" s="137">
+      <c r="F26" s="136">
         <v>47553</v>
       </c>
-      <c r="G26" s="137">
+      <c r="G26" s="136">
         <v>47735</v>
       </c>
-      <c r="H26" s="137">
+      <c r="H26" s="136">
         <v>47735</v>
       </c>
       <c r="I26" s="96"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="97" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B27" s="98">
         <v>47245</v>
@@ -21432,77 +21580,77 @@
       <c r="D27" s="98">
         <v>47791</v>
       </c>
-      <c r="E27" s="137">
+      <c r="E27" s="136">
         <v>47728</v>
       </c>
-      <c r="F27" s="137">
+      <c r="F27" s="136">
         <v>47728</v>
       </c>
-      <c r="G27" s="137">
+      <c r="G27" s="136">
         <v>47917</v>
       </c>
-      <c r="H27" s="137">
+      <c r="H27" s="136">
         <v>47917</v>
       </c>
       <c r="I27" s="96"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="97" t="s">
-        <v>571</v>
+        <v>537</v>
       </c>
       <c r="B28" s="98" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C28" s="98" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D28" s="98" t="s">
-        <v>357</v>
-      </c>
-      <c r="E28" s="137" t="s">
-        <v>357</v>
-      </c>
-      <c r="F28" s="137" t="s">
-        <v>357</v>
-      </c>
-      <c r="G28" s="137" t="s">
-        <v>357</v>
-      </c>
-      <c r="H28" s="137" t="s">
-        <v>357</v>
+        <v>350</v>
+      </c>
+      <c r="E28" s="136" t="s">
+        <v>350</v>
+      </c>
+      <c r="F28" s="136" t="s">
+        <v>350</v>
+      </c>
+      <c r="G28" s="136" t="s">
+        <v>350</v>
+      </c>
+      <c r="H28" s="136" t="s">
+        <v>350</v>
       </c>
       <c r="I28" s="96"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="97" t="s">
-        <v>577</v>
+        <v>543</v>
       </c>
       <c r="B29" s="98" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C29" s="98" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D29" s="98" t="s">
-        <v>357</v>
-      </c>
-      <c r="E29" s="137" t="s">
-        <v>357</v>
-      </c>
-      <c r="F29" s="137" t="s">
-        <v>357</v>
-      </c>
-      <c r="G29" s="137" t="s">
-        <v>357</v>
-      </c>
-      <c r="H29" s="137" t="s">
-        <v>357</v>
+        <v>350</v>
+      </c>
+      <c r="E29" s="136" t="s">
+        <v>350</v>
+      </c>
+      <c r="F29" s="136" t="s">
+        <v>350</v>
+      </c>
+      <c r="G29" s="136" t="s">
+        <v>350</v>
+      </c>
+      <c r="H29" s="136" t="s">
+        <v>350</v>
       </c>
       <c r="I29" s="96"/>
     </row>
     <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="140" t="s">
-        <v>330</v>
+      <c r="A30" s="139" t="s">
+        <v>324</v>
       </c>
       <c r="C30" s="98"/>
       <c r="D30" s="98"/>
@@ -21514,7 +21662,7 @@
     </row>
     <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="94" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B31" s="98">
         <v>46107</v>
@@ -21541,7 +21689,7 @@
     </row>
     <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="94" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B32" s="98">
         <v>46100</v>
@@ -21568,7 +21716,7 @@
     </row>
     <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="95" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B33" s="98">
         <v>46108</v>
@@ -21595,7 +21743,7 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="94" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B34" s="98">
         <v>46111</v>
@@ -21622,7 +21770,7 @@
     </row>
     <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="95" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B35" s="98">
         <v>46107</v>
@@ -21649,7 +21797,7 @@
     </row>
     <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="94" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B36" s="98">
         <v>46114</v>
@@ -21676,7 +21824,7 @@
     </row>
     <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="95" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B37" s="98">
         <v>46122</v>
@@ -21703,7 +21851,7 @@
     </row>
     <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="94" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B38" s="98">
         <v>46127</v>
@@ -21730,7 +21878,7 @@
     </row>
     <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="95" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="B39" s="98">
         <v>46139</v>
@@ -21757,7 +21905,7 @@
     </row>
     <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="94" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B40" s="98">
         <v>46146</v>
@@ -21784,7 +21932,7 @@
     </row>
     <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="95" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B41" s="98">
         <v>46147</v>
@@ -21811,7 +21959,7 @@
     </row>
     <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="94" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B42" s="98">
         <v>46153</v>
@@ -21838,7 +21986,7 @@
     </row>
     <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="95" t="s">
-        <v>642</v>
+        <v>594</v>
       </c>
       <c r="B43" s="98">
         <v>46148</v>
@@ -21853,7 +22001,7 @@
     </row>
     <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="94" t="s">
-        <v>643</v>
+        <v>595</v>
       </c>
       <c r="B44" s="98">
         <v>46154</v>
@@ -21868,7 +22016,7 @@
     </row>
     <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="95" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B45" s="98">
         <v>46154</v>
@@ -21895,7 +22043,7 @@
     </row>
     <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="94" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B46" s="98">
         <v>46162</v>
@@ -21906,28 +22054,28 @@
       <c r="D46" s="98">
         <v>46253</v>
       </c>
-      <c r="E46" s="137">
+      <c r="E46" s="136">
         <v>46555</v>
       </c>
-      <c r="F46" s="137">
+      <c r="F46" s="136">
         <v>46555</v>
       </c>
-      <c r="G46" s="137">
+      <c r="G46" s="136">
         <v>46583</v>
       </c>
-      <c r="H46" s="137">
+      <c r="H46" s="136">
         <v>46583</v>
       </c>
       <c r="I46" s="96"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="139" t="s">
-        <v>345</v>
+      <c r="A47" s="138" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>559</v>
+        <v>527</v>
       </c>
       <c r="B48" s="98">
         <f t="shared" ref="B48:H48" si="0">B17-30</f>
@@ -21935,7 +22083,7 @@
       </c>
       <c r="C48" s="98">
         <f t="shared" si="0"/>
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="D48" s="98">
         <f t="shared" si="0"/>
@@ -21960,7 +22108,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>560</v>
+        <v>528</v>
       </c>
       <c r="B49" s="98">
         <f t="shared" ref="B49:H49" si="1">B19-30</f>
@@ -21968,7 +22116,7 @@
       </c>
       <c r="C49" s="98">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46239</v>
       </c>
       <c r="D49" s="98">
         <f t="shared" si="1"/>
@@ -21993,7 +22141,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>561</v>
+        <v>529</v>
       </c>
       <c r="B50" s="98">
         <f t="shared" ref="B50:H50" si="2">B21-30</f>
@@ -22001,7 +22149,7 @@
       </c>
       <c r="C50" s="98">
         <f t="shared" si="2"/>
-        <v>46295</v>
+        <v>46309</v>
       </c>
       <c r="D50" s="98">
         <f t="shared" si="2"/>
@@ -22026,7 +22174,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>562</v>
+        <v>530</v>
       </c>
       <c r="B51" s="98">
         <f t="shared" ref="B51:C51" si="3">B46+7</f>
@@ -22059,7 +22207,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>556</v>
+        <v>524</v>
       </c>
       <c r="B52" s="98">
         <f t="shared" ref="B52:C52" si="5">B26-517</f>
@@ -22071,7 +22219,7 @@
       </c>
       <c r="D52" s="98">
         <f>D26-517</f>
-        <v>47098</v>
+        <v>47099</v>
       </c>
       <c r="E52" s="98">
         <f>E26-517</f>
@@ -22092,7 +22240,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>557</v>
+        <v>525</v>
       </c>
       <c r="B53" s="33" t="s">
         <v>84</v>
@@ -22118,7 +22266,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>558</v>
+        <v>526</v>
       </c>
       <c r="B54" s="33" t="s">
         <v>84</v>
@@ -22143,13 +22291,13 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="139" t="s">
-        <v>433</v>
+      <c r="A55" s="138" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>435</v>
+        <v>416</v>
       </c>
       <c r="B56" s="98">
         <v>46097</v>
@@ -22176,7 +22324,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="B57" s="98">
         <v>46118</v>
@@ -22203,7 +22351,7 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="B58" s="98">
         <v>46122</v>
@@ -22229,7 +22377,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="B59" s="98" t="s">
         <v>84</v>
@@ -22255,7 +22403,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B60" s="98">
         <v>46121</v>
@@ -22281,7 +22429,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="B61" s="98">
         <v>46143</v>
@@ -22307,10 +22455,10 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>439</v>
-      </c>
-      <c r="B62" s="98" t="s">
-        <v>84</v>
+        <v>420</v>
+      </c>
+      <c r="B62" s="98">
+        <v>46160</v>
       </c>
       <c r="C62" s="33" t="s">
         <v>84</v>
@@ -22333,7 +22481,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>578</v>
+        <v>610</v>
       </c>
       <c r="B63" s="98" t="s">
         <v>125</v>
@@ -22342,7 +22490,7 @@
         <v>125</v>
       </c>
       <c r="D63" s="98">
-        <v>46156</v>
+        <v>46171</v>
       </c>
       <c r="E63" s="98" t="s">
         <v>125</v>
@@ -22359,21 +22507,21 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>579</v>
+        <v>544</v>
       </c>
       <c r="B64" s="98">
         <v>45800</v>
       </c>
-      <c r="C64" s="136">
+      <c r="C64" s="135">
         <v>46113</v>
       </c>
-      <c r="D64" s="136">
+      <c r="D64" s="135">
         <v>45983</v>
       </c>
-      <c r="E64" s="138">
+      <c r="E64" s="137">
         <v>46231</v>
       </c>
-      <c r="F64" s="138">
+      <c r="F64" s="137">
         <v>46259</v>
       </c>
       <c r="G64" s="33" t="s">
@@ -22385,7 +22533,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>584</v>
+        <v>548</v>
       </c>
       <c r="B65" s="98">
         <v>46141</v>
@@ -22407,6 +22555,30 @@
       </c>
       <c r="H65" s="33" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>611</v>
+      </c>
+      <c r="D66" s="135">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>612</v>
+      </c>
+      <c r="D67" s="135">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>619</v>
+      </c>
+      <c r="C68" s="135">
+        <v>46231</v>
       </c>
     </row>
   </sheetData>
@@ -22444,52 +22616,52 @@
   <sheetData>
     <row r="1" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="120" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="B1" s="120" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="C1" s="120" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="D1" s="120" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="E1" s="120" t="s">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="F1" s="120" t="s">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="G1" s="120" t="s">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="H1" s="120" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="I1" s="120" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="J1" s="120" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="K1" s="120" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="N1" s="121" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="O1" s="121" t="s">
-        <v>490</v>
+        <v>471</v>
       </c>
       <c r="P1" s="121" t="s">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="Q1" s="121" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
       <c r="R1" s="121" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="S1" s="121" t="s">
         <v>8</v>
@@ -22500,31 +22672,31 @@
         <v>17</v>
       </c>
       <c r="B2" s="122" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>492</v>
+        <v>473</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="K2" t="str">
         <f>CONCATENATE(C2,"|",G2,"|",H2)</f>
@@ -22551,7 +22723,7 @@
         <v>0.89726877040261155</v>
       </c>
       <c r="S2" t="s">
-        <v>497</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -22559,31 +22731,31 @@
         <v>17</v>
       </c>
       <c r="B3" s="122" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="H3" s="1">
         <v>4844</v>
       </c>
       <c r="I3" s="130" t="s">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="K3" t="str">
         <f>CONCATENATE(C3,"|",G3,"|",H3)</f>
@@ -22610,7 +22782,7 @@
         <v>0.6280226326503473</v>
       </c>
       <c r="S3" t="s">
-        <v>496</v>
+        <v>477</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -22618,31 +22790,31 @@
         <v>17</v>
       </c>
       <c r="B4" s="122" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>494</v>
+        <v>475</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="K4" t="str">
         <f>CONCATENATE(C4,"|",G4,"|",H4)</f>
@@ -22669,7 +22841,7 @@
         <v>0.79850407978241156</v>
       </c>
       <c r="S4" t="s">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="T4" s="125" t="s">
         <v>218</v>
@@ -22677,31 +22849,31 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B5" s="126" t="s">
-        <v>471</v>
+        <v>452</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="H5" s="1">
         <v>7028</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="K5" t="str">
         <f>CONCATENATE(C5,"|",G5,"|",H5)</f>
@@ -22730,31 +22902,31 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B6" s="126" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="K6" t="str">
         <f>CONCATENATE(C6,"|",G6,"|",H6)</f>
@@ -22783,31 +22955,31 @@
     </row>
     <row r="7" spans="1:20" s="127" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="128" t="s">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="C7" s="129" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="D7" s="129" t="s">
+        <v>440</v>
+      </c>
+      <c r="E7" s="129" t="s">
+        <v>441</v>
+      </c>
+      <c r="F7" s="129" t="s">
+        <v>442</v>
+      </c>
+      <c r="G7" s="129" t="s">
         <v>459</v>
-      </c>
-      <c r="E7" s="129" t="s">
-        <v>460</v>
-      </c>
-      <c r="F7" s="129" t="s">
-        <v>461</v>
-      </c>
-      <c r="G7" s="129" t="s">
-        <v>478</v>
       </c>
       <c r="H7" s="129" t="s">
         <v>84</v>
       </c>
       <c r="I7" s="129" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" ref="K7:K10" si="1">CONCATENATE(C7,"|",G7,"|",H7)</f>
@@ -22822,36 +22994,36 @@
         <v>218</v>
       </c>
       <c r="S7" s="127" t="s">
-        <v>498</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B8" s="126" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="1"/>
@@ -22875,36 +23047,36 @@
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B9" s="126" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="1"/>
@@ -22928,36 +23100,36 @@
         <v>0</v>
       </c>
       <c r="S9" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B10" s="126" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>487</v>
+        <v>468</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>495</v>
+        <v>476</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
@@ -22970,47 +23142,47 @@
         <v>0</v>
       </c>
       <c r="P10" s="123">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="Q10" s="123">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="R10" s="124">
         <f>Q10/N10</f>
-        <v>0</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="S10" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B11" s="126" t="s">
-        <v>488</v>
+        <v>469</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>489</v>
+        <v>470</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="K11" t="str">
         <f>CONCATENATE(C11,"|",G11,"|",H11)</f>
@@ -23034,7 +23206,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -23109,132 +23281,132 @@
   <sheetData>
     <row r="1" spans="1:22" s="97" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="97" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="B1" s="104" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="C1" s="104" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="F1" s="104" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="G1" s="104" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="H1" s="104" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="I1" s="104" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="J1" s="104" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="K1" s="104" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="L1" s="104" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="M1" s="104" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="N1" s="97" t="s">
-        <v>408</v>
+        <v>662</v>
       </c>
       <c r="O1" s="97" t="s">
-        <v>408</v>
+        <v>662</v>
       </c>
       <c r="P1" s="97" t="s">
-        <v>408</v>
+        <v>662</v>
       </c>
       <c r="Q1" s="115" t="s">
-        <v>408</v>
+        <v>662</v>
       </c>
       <c r="R1" s="115" t="s">
-        <v>408</v>
+        <v>662</v>
       </c>
       <c r="S1" s="115" t="s">
-        <v>408</v>
+        <v>662</v>
       </c>
       <c r="T1" s="115" t="s">
-        <v>160</v>
+        <v>664</v>
       </c>
       <c r="U1" s="115" t="s">
-        <v>420</v>
+        <v>665</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="97" t="s">
+        <v>387</v>
+      </c>
+      <c r="B2" s="115" t="s">
+        <v>385</v>
+      </c>
+      <c r="C2" s="115" t="s">
+        <v>381</v>
+      </c>
+      <c r="D2" s="115" t="s">
+        <v>661</v>
+      </c>
+      <c r="E2" s="115" t="s">
+        <v>386</v>
+      </c>
+      <c r="F2" s="115" t="s">
+        <v>384</v>
+      </c>
+      <c r="G2" s="104" t="s">
+        <v>300</v>
+      </c>
+      <c r="H2" s="105" t="s">
+        <v>373</v>
+      </c>
+      <c r="I2" s="105" t="s">
+        <v>374</v>
+      </c>
+      <c r="J2" s="105" t="s">
+        <v>395</v>
+      </c>
+      <c r="K2" s="105" t="s">
+        <v>375</v>
+      </c>
+      <c r="L2" s="105" t="s">
+        <v>376</v>
+      </c>
+      <c r="M2" s="105" t="s">
+        <v>377</v>
+      </c>
+      <c r="N2" s="105" t="s">
+        <v>397</v>
+      </c>
+      <c r="O2" s="105" t="s">
         <v>398</v>
       </c>
-      <c r="B2" s="115" t="s">
-        <v>395</v>
-      </c>
-      <c r="C2" s="115" t="s">
-        <v>391</v>
-      </c>
-      <c r="D2" s="115" t="s">
-        <v>396</v>
-      </c>
-      <c r="E2" s="115" t="s">
-        <v>397</v>
-      </c>
-      <c r="F2" s="115" t="s">
-        <v>394</v>
-      </c>
-      <c r="G2" s="104" t="s">
-        <v>306</v>
-      </c>
-      <c r="H2" s="105" t="s">
-        <v>387</v>
-      </c>
-      <c r="I2" s="105" t="s">
-        <v>383</v>
-      </c>
-      <c r="J2" s="105" t="s">
-        <v>406</v>
-      </c>
-      <c r="K2" s="105" t="s">
-        <v>384</v>
-      </c>
-      <c r="L2" s="105" t="s">
-        <v>385</v>
-      </c>
-      <c r="M2" s="105" t="s">
-        <v>386</v>
-      </c>
-      <c r="N2" s="105" t="s">
-        <v>409</v>
-      </c>
-      <c r="O2" s="105" t="s">
-        <v>411</v>
-      </c>
       <c r="P2" s="105" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="Q2" s="105" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="R2" s="105" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="S2" s="105" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="T2" s="105" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="U2" s="105" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="V2" s="105"/>
     </row>
@@ -23243,69 +23415,69 @@
         <v>2</v>
       </c>
       <c r="B3" s="115" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="C3" s="115" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="D3" s="115" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="E3" s="115" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="F3" s="115" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="G3" s="104" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="H3" s="104" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="I3" s="104" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="J3" s="104" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="K3" s="104" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="L3" s="104" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="M3" s="104" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="N3" s="115" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="O3" s="115" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="P3" s="115" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="Q3" s="115" t="s">
-        <v>416</v>
+        <v>663</v>
       </c>
       <c r="R3" s="115" t="s">
-        <v>416</v>
+        <v>663</v>
       </c>
       <c r="S3" s="115" t="s">
-        <v>416</v>
+        <v>663</v>
       </c>
       <c r="T3" s="115" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="U3" s="115" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B4" s="116">
         <v>46258</v>
@@ -23323,39 +23495,39 @@
         <v>45457</v>
       </c>
       <c r="G4" s="98" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="H4" s="98" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="I4" s="98" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="J4" s="98" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="L4" s="98" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="M4" s="98" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="N4" s="96" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="O4" s="98" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="P4" s="117" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C5" s="116">
         <v>46596</v>
@@ -23366,132 +23538,132 @@
       <c r="E5" s="116"/>
       <c r="F5" s="116"/>
       <c r="G5" s="98" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="H5" s="98" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I5" s="98" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="J5" s="98" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="L5" s="98" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="M5" s="98" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="N5" s="96"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="97" t="s">
+        <v>288</v>
+      </c>
+      <c r="B7" s="115" t="s">
+        <v>379</v>
+      </c>
+      <c r="C7" s="115" t="s">
+        <v>379</v>
+      </c>
+      <c r="D7" s="115" t="s">
+        <v>379</v>
+      </c>
+      <c r="E7" s="115" t="s">
+        <v>383</v>
+      </c>
+      <c r="F7" s="115" t="s">
+        <v>383</v>
+      </c>
+      <c r="G7" s="115" t="s">
+        <v>365</v>
+      </c>
+      <c r="H7" s="115" t="s">
+        <v>367</v>
+      </c>
+      <c r="I7" s="115" t="s">
+        <v>369</v>
+      </c>
+      <c r="J7" s="115" t="s">
+        <v>371</v>
+      </c>
+      <c r="K7" s="115" t="s">
+        <v>371</v>
+      </c>
+      <c r="L7" s="115" t="s">
         <v>372</v>
       </c>
-      <c r="B7" s="115" t="s">
-        <v>389</v>
-      </c>
-      <c r="C7" s="115" t="s">
-        <v>389</v>
-      </c>
-      <c r="D7" s="115" t="s">
-        <v>389</v>
-      </c>
-      <c r="E7" s="115" t="s">
-        <v>393</v>
-      </c>
-      <c r="F7" s="115" t="s">
-        <v>393</v>
-      </c>
-      <c r="G7" s="115" t="s">
-        <v>373</v>
-      </c>
-      <c r="H7" s="115" t="s">
-        <v>376</v>
-      </c>
-      <c r="I7" s="115" t="s">
-        <v>378</v>
-      </c>
-      <c r="J7" s="115" t="s">
-        <v>380</v>
-      </c>
-      <c r="K7" s="115" t="s">
-        <v>380</v>
-      </c>
-      <c r="L7" s="115" t="s">
-        <v>381</v>
-      </c>
       <c r="M7" s="115" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="N7" s="115" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="O7" s="115" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="P7" s="115" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="Q7" s="115" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="R7" s="115" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="S7" s="115" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="T7" s="115" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="U7" s="115" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="V7" s="115"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="97" t="s">
-        <v>375</v>
+        <v>289</v>
       </c>
       <c r="B8" s="115" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="C8" s="115" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D8" s="115" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="E8" s="115"/>
       <c r="F8" s="115"/>
       <c r="G8" s="115" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="H8" s="115" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="I8" s="115" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="J8" s="115" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="K8" s="115" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="L8" s="115" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="M8" s="115" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="N8" s="115" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="O8" s="115"/>
       <c r="P8" s="115"/>
@@ -23499,10 +23671,10 @@
       <c r="R8" s="115"/>
       <c r="S8" s="115"/>
       <c r="T8" s="115" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="U8" s="115" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -23530,19 +23702,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="111" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="I1" s="111" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="J1" s="111" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="M1" s="111" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="N1" s="111" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -23553,15 +23725,15 @@
         <v>1</v>
       </c>
       <c r="I2" s="108" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="J2" s="108">
         <v>1</v>
       </c>
       <c r="M2" s="112" t="s">
-        <v>358</v>
-      </c>
-      <c r="N2" s="141">
+        <v>351</v>
+      </c>
+      <c r="N2" s="144">
         <v>1</v>
       </c>
     </row>
@@ -23573,15 +23745,15 @@
         <v>1</v>
       </c>
       <c r="I3" s="108" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="J3" s="108">
         <v>1</v>
       </c>
       <c r="M3" s="113" t="s">
-        <v>359</v>
-      </c>
-      <c r="N3" s="142"/>
+        <v>352</v>
+      </c>
+      <c r="N3" s="145"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="109">
@@ -23591,15 +23763,15 @@
         <v>1</v>
       </c>
       <c r="I4" s="108" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="J4" s="108">
         <v>1</v>
       </c>
       <c r="M4" s="114" t="s">
-        <v>360</v>
-      </c>
-      <c r="N4" s="143"/>
+        <v>353</v>
+      </c>
+      <c r="N4" s="146"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="109">
@@ -23609,15 +23781,15 @@
         <v>1</v>
       </c>
       <c r="I5" s="108" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="J5" s="108">
         <v>2</v>
       </c>
       <c r="M5" s="112" t="s">
-        <v>361</v>
-      </c>
-      <c r="N5" s="141">
+        <v>354</v>
+      </c>
+      <c r="N5" s="144">
         <v>2</v>
       </c>
     </row>
@@ -23629,15 +23801,15 @@
         <v>1</v>
       </c>
       <c r="I6" s="108" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="J6" s="108">
         <v>2</v>
       </c>
       <c r="M6" s="113" t="s">
-        <v>362</v>
-      </c>
-      <c r="N6" s="142"/>
+        <v>355</v>
+      </c>
+      <c r="N6" s="145"/>
     </row>
     <row r="7" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="109">
@@ -23647,15 +23819,15 @@
         <v>1</v>
       </c>
       <c r="I7" s="108" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="J7" s="108">
         <v>2</v>
       </c>
       <c r="M7" s="114" t="s">
-        <v>363</v>
-      </c>
-      <c r="N7" s="143"/>
+        <v>356</v>
+      </c>
+      <c r="N7" s="146"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="109">
@@ -23665,15 +23837,15 @@
         <v>2</v>
       </c>
       <c r="I8" s="108" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="J8" s="108">
         <v>3</v>
       </c>
       <c r="M8" s="112" t="s">
-        <v>364</v>
-      </c>
-      <c r="N8" s="141">
+        <v>357</v>
+      </c>
+      <c r="N8" s="144">
         <v>3</v>
       </c>
     </row>
@@ -23685,15 +23857,15 @@
         <v>2</v>
       </c>
       <c r="I9" s="108" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="J9" s="108">
         <v>3</v>
       </c>
       <c r="M9" s="113" t="s">
-        <v>365</v>
-      </c>
-      <c r="N9" s="142"/>
+        <v>358</v>
+      </c>
+      <c r="N9" s="145"/>
     </row>
     <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="109">
@@ -23703,15 +23875,15 @@
         <v>2</v>
       </c>
       <c r="I10" s="108" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="J10" s="108">
         <v>3</v>
       </c>
       <c r="M10" s="114" t="s">
-        <v>366</v>
-      </c>
-      <c r="N10" s="143"/>
+        <v>359</v>
+      </c>
+      <c r="N10" s="146"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="109">
@@ -23721,15 +23893,15 @@
         <v>2</v>
       </c>
       <c r="I11" s="108" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="J11" s="108">
         <v>4</v>
       </c>
       <c r="M11" s="112" t="s">
-        <v>367</v>
-      </c>
-      <c r="N11" s="141">
+        <v>360</v>
+      </c>
+      <c r="N11" s="144">
         <v>4</v>
       </c>
     </row>
@@ -23741,15 +23913,15 @@
         <v>2</v>
       </c>
       <c r="I12" s="108" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="J12" s="108">
         <v>4</v>
       </c>
       <c r="M12" s="113" t="s">
-        <v>368</v>
-      </c>
-      <c r="N12" s="142"/>
+        <v>361</v>
+      </c>
+      <c r="N12" s="145"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="109">
@@ -23759,15 +23931,15 @@
         <v>2</v>
       </c>
       <c r="I13" s="108" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="J13" s="108">
         <v>4</v>
       </c>
       <c r="M13" s="114" t="s">
-        <v>369</v>
-      </c>
-      <c r="N13" s="143"/>
+        <v>362</v>
+      </c>
+      <c r="N13" s="146"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="109">
@@ -27217,16 +27389,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{752F9F6E-B88F-40CF-A00D-5A52044E6B25}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1785dff3-9909-4165-bde0-36ec47a4b18f"/>
+    <ds:schemaRef ds:uri="a8552d75-6f1f-4d52-93a3-fcd36dc2752d"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="1785dff3-9909-4165-bde0-36ec47a4b18f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a8552d75-6f1f-4d52-93a3-fcd36dc2752d"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/NG Scheduling.xlsx
+++ b/NG Scheduling.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://my.wal-mart.com/personal/k0m0eg1_homeoffice_wal-mart_com/Documents/Desktop/Code Puppy Saved Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2081" documentId="8_{3CD9A91E-A1DC-493E-B251-6A7E654DFCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9DC4251-BB90-459C-88AB-C9E951EC4102}"/>
+  <xr:revisionPtr revIDLastSave="2344" documentId="8_{3CD9A91E-A1DC-493E-B251-6A7E654DFCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45BE24A5-DC1A-4982-9B2C-8D57ADB6FF3B}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="780" windowWidth="21015" windowHeight="19395" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17385" yWindow="2370" windowWidth="29385" windowHeight="17580" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TUE FC Asset Plan SteerCo" sheetId="2" state="hidden" r:id="rId1"/>
@@ -57,7 +57,10 @@
     <author>tc={1D534BCA-8427-4D56-835E-F766105CE292}</author>
     <author>tc={B4072AC4-A8EE-4056-AF55-77278AA1688F}</author>
     <author>tc={6D15E7A5-F995-46E6-93A8-A476159ABD56}</author>
+    <author>tc={861FB389-D1F5-4AFE-95B4-775718CE9B1A}</author>
     <author>tc={CF413314-5518-4487-9E68-E5576FB49E1E}</author>
+    <author>tc={D54FEB2C-162B-4CB7-845C-B43BAADC4E31}</author>
+    <author>tc={3287D6A5-72FD-444E-8875-2CE4F39DE81F}</author>
   </authors>
   <commentList>
     <comment ref="B7" authorId="0" shapeId="0" xr:uid="{0183F037-2CBE-4112-8426-8E454945119D}">
@@ -68,7 +71,7 @@
     Not sure the exact date.  BDR was redone after Aug ASM Rejection.</t>
       </text>
     </comment>
-    <comment ref="E9" authorId="1" shapeId="0" xr:uid="{D93B35F1-6126-49F0-BC60-653F046222E9}">
+    <comment ref="E10" authorId="1" shapeId="0" xr:uid="{D93B35F1-6126-49F0-BC60-653F046222E9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -76,7 +79,7 @@
     $500K was loaded.  The remaining $500K has not been approved</t>
       </text>
     </comment>
-    <comment ref="F9" authorId="2" shapeId="0" xr:uid="{5A8E346F-E53D-4BBB-848F-A1C20039CBBB}">
+    <comment ref="F10" authorId="2" shapeId="0" xr:uid="{5A8E346F-E53D-4BBB-848F-A1C20039CBBB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -84,7 +87,7 @@
     $500K was loaded.  The remaining $500K has not been approved</t>
       </text>
     </comment>
-    <comment ref="G9" authorId="3" shapeId="0" xr:uid="{F79C2972-297C-41CA-8843-CA47CB135351}">
+    <comment ref="G10" authorId="3" shapeId="0" xr:uid="{F79C2972-297C-41CA-8843-CA47CB135351}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -92,7 +95,7 @@
     $500K was loaded.  The remaining $500K has not been approved</t>
       </text>
     </comment>
-    <comment ref="H9" authorId="4" shapeId="0" xr:uid="{5867599F-CE04-4790-AFAF-AFD33A816A73}">
+    <comment ref="H10" authorId="4" shapeId="0" xr:uid="{5867599F-CE04-4790-AFAF-AFD33A816A73}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -100,7 +103,7 @@
     $500K was loaded.  The remaining $500K has not been approved</t>
       </text>
     </comment>
-    <comment ref="C12" authorId="5" shapeId="0" xr:uid="{FD9F783E-8E52-497E-AE04-AD1241596A30}">
+    <comment ref="C13" authorId="5" shapeId="0" xr:uid="{FD9F783E-8E52-497E-AE04-AD1241596A30}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -108,15 +111,15 @@
     Received partial 60% need remaining $784.5K that requires CPC approval by 6/26/26</t>
       </text>
     </comment>
-    <comment ref="D13" authorId="6" shapeId="0" xr:uid="{1D534BCA-8427-4D56-835E-F766105CE292}">
+    <comment ref="D14" authorId="6" shapeId="0" xr:uid="{1D534BCA-8427-4D56-835E-F766105CE292}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Partial 90% approved.  Need additional 417K requires CPC approval by 5/22/26</t>
+    Partial 90% approved.  Need additional 417K requires CPC approval by 6/12/26</t>
       </text>
     </comment>
-    <comment ref="F15" authorId="7" shapeId="0" xr:uid="{B4072AC4-A8EE-4056-AF55-77278AA1688F}">
+    <comment ref="F16" authorId="7" shapeId="0" xr:uid="{B4072AC4-A8EE-4056-AF55-77278AA1688F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -124,7 +127,7 @@
     At Risk due Karisa availability.  Site Selection Trip not planned until 8/25</t>
       </text>
     </comment>
-    <comment ref="A16" authorId="8" shapeId="0" xr:uid="{6D15E7A5-F995-46E6-93A8-A476159ABD56}">
+    <comment ref="A17" authorId="8" shapeId="0" xr:uid="{6D15E7A5-F995-46E6-93A8-A476159ABD56}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -132,12 +135,36 @@
     Start of Desing is the first Monday after receiving 30% Design DD</t>
       </text>
     </comment>
-    <comment ref="D63" authorId="9" shapeId="0" xr:uid="{CF413314-5518-4487-9E68-E5576FB49E1E}">
+    <comment ref="B64" authorId="9" shapeId="0" xr:uid="{861FB389-D1F5-4AFE-95B4-775718CE9B1A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    KNAPP PO needs cut by 6/10 Construction PO needs cut by 6/16</t>
+      </text>
+    </comment>
+    <comment ref="D65" authorId="10" shapeId="0" xr:uid="{CF413314-5518-4487-9E68-E5576FB49E1E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Got pulled from the agenda on 4/23/26 due to a legal not having the right signature.  Pending Rescheduling</t>
+      </text>
+    </comment>
+    <comment ref="E69" authorId="11" shapeId="0" xr:uid="{D54FEB2C-162B-4CB7-845C-B43BAADC4E31}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Karisa will leave after REC</t>
+      </text>
+    </comment>
+    <comment ref="G69" authorId="12" shapeId="0" xr:uid="{3287D6A5-72FD-444E-8875-2CE4F39DE81F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Karisa will be in Denver for Holiday Meeting and will do site selection</t>
       </text>
     </comment>
   </commentList>
@@ -163,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="688">
   <si>
     <t>Fulfillment New Assets SteerCo (Tuesday's)</t>
   </si>
@@ -1873,9 +1900,6 @@
     <t>Open Commits</t>
   </si>
   <si>
-    <t>Doulas, MA</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Carnesville, GA</t>
   </si>
   <si>
@@ -2290,18 +2314,12 @@
     <t xml:space="preserve">Town Board Review Height Variance </t>
   </si>
   <si>
-    <t>Zoning Board Review Heigh Variance</t>
-  </si>
-  <si>
     <t>Nicole Blyth</t>
   </si>
   <si>
     <t>Approved to move to ASM</t>
   </si>
   <si>
-    <t>Pending decision if this is Karisa's OpEx or Vik's R&amp;D</t>
-  </si>
-  <si>
     <t>PK Sabherwal &amp; Matt Termeer</t>
   </si>
   <si>
@@ -2453,6 +2471,78 @@
   </si>
   <si>
     <t>26_05_20 SteerCo Wallkill Scenarios.pptx</t>
+  </si>
+  <si>
+    <t>Carnesville Incentives Funding: ~$1M OpEx needed for closing to secure ~$70M in incentives.</t>
+  </si>
+  <si>
+    <t>Greg Nunn</t>
+  </si>
+  <si>
+    <t>ASM for Land Purchase</t>
+  </si>
+  <si>
+    <t>Test Fits Complete</t>
+  </si>
+  <si>
+    <t>Real Estate Milestones</t>
+  </si>
+  <si>
+    <t>Land Purchase (Cash Flow)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approved and will use Karisa OpEx </t>
+  </si>
+  <si>
+    <t>Aligned on scenarios</t>
+  </si>
+  <si>
+    <t>26_05_29 SteerCo.pptx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallkill Preparation for Aug ASM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicole Blyth / Matt Termeer </t>
+  </si>
+  <si>
+    <t>Adam Dunbar, Vik Gopalakrishnan, Jack Anderson, John Clinton, Steve Larsen</t>
+  </si>
+  <si>
+    <t>MCO Test Fits</t>
+  </si>
+  <si>
+    <t>Allison Coontz / Jonathan Lietzke</t>
+  </si>
+  <si>
+    <t>Carnesville Permitting Update</t>
+  </si>
+  <si>
+    <t>Budget Load</t>
+  </si>
+  <si>
+    <t>NextGen Budget Meeting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NextGen Budget Forecast - Working Team </t>
+  </si>
+  <si>
+    <t>Allison/Andrew/KJ/MaryEllen/Logan/Steve</t>
+  </si>
+  <si>
+    <t>FC Network Budget Tracker.xlsx</t>
+  </si>
+  <si>
+    <t>Douglas, MA</t>
+  </si>
+  <si>
+    <t>Funding Approved. Pending FIN guidance</t>
+  </si>
+  <si>
+    <t>Wallkill CapEx Scenarios</t>
+  </si>
+  <si>
+    <t>26_06_03 SteerCo.pptx</t>
   </si>
 </sst>
 </file>
@@ -2924,7 +3014,7 @@
     <xf numFmtId="44" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3296,9 +3386,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3754,32 +3841,41 @@
   <threadedComment ref="B7" dT="2026-04-21T14:16:42.47" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{0183F037-2CBE-4112-8426-8E454945119D}">
     <text>Not sure the exact date.  BDR was redone after Aug ASM Rejection.</text>
   </threadedComment>
-  <threadedComment ref="E9" dT="2026-04-21T12:30:08.65" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{D93B35F1-6126-49F0-BC60-653F046222E9}">
+  <threadedComment ref="E10" dT="2026-04-21T12:30:08.65" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{D93B35F1-6126-49F0-BC60-653F046222E9}">
     <text>$500K was loaded.  The remaining $500K has not been approved</text>
   </threadedComment>
-  <threadedComment ref="F9" dT="2026-04-21T12:30:08.65" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{5A8E346F-E53D-4BBB-848F-A1C20039CBBB}">
+  <threadedComment ref="F10" dT="2026-04-21T12:30:08.65" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{5A8E346F-E53D-4BBB-848F-A1C20039CBBB}">
     <text>$500K was loaded.  The remaining $500K has not been approved</text>
   </threadedComment>
-  <threadedComment ref="G9" dT="2026-04-21T12:30:08.65" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{F79C2972-297C-41CA-8843-CA47CB135351}">
+  <threadedComment ref="G10" dT="2026-04-21T12:30:08.65" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{F79C2972-297C-41CA-8843-CA47CB135351}">
     <text>$500K was loaded.  The remaining $500K has not been approved</text>
   </threadedComment>
-  <threadedComment ref="H9" dT="2026-04-21T12:30:08.65" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{5867599F-CE04-4790-AFAF-AFD33A816A73}">
+  <threadedComment ref="H10" dT="2026-04-21T12:30:08.65" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{5867599F-CE04-4790-AFAF-AFD33A816A73}">
     <text>$500K was loaded.  The remaining $500K has not been approved</text>
   </threadedComment>
-  <threadedComment ref="C12" dT="2026-04-22T12:48:52.19" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{FD9F783E-8E52-497E-AE04-AD1241596A30}">
+  <threadedComment ref="C13" dT="2026-04-22T12:48:52.19" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{FD9F783E-8E52-497E-AE04-AD1241596A30}">
     <text>Received partial 60% need remaining $784.5K that requires CPC approval by 6/26/26</text>
   </threadedComment>
-  <threadedComment ref="D13" dT="2026-04-22T12:47:24.77" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{1D534BCA-8427-4D56-835E-F766105CE292}">
-    <text>Partial 90% approved.  Need additional 417K requires CPC approval by 5/22/26</text>
+  <threadedComment ref="D14" dT="2026-04-22T12:47:24.77" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{1D534BCA-8427-4D56-835E-F766105CE292}">
+    <text>Partial 90% approved.  Need additional 417K requires CPC approval by 6/12/26</text>
   </threadedComment>
-  <threadedComment ref="F15" dT="2026-04-23T21:00:07.11" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{B4072AC4-A8EE-4056-AF55-77278AA1688F}">
+  <threadedComment ref="F16" dT="2026-04-23T21:00:07.11" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{B4072AC4-A8EE-4056-AF55-77278AA1688F}">
     <text>At Risk due Karisa availability.  Site Selection Trip not planned until 8/25</text>
   </threadedComment>
-  <threadedComment ref="A16" dT="2026-05-08T20:34:59.47" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{6D15E7A5-F995-46E6-93A8-A476159ABD56}">
+  <threadedComment ref="A17" dT="2026-05-08T20:34:59.47" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{6D15E7A5-F995-46E6-93A8-A476159ABD56}">
     <text>Start of Desing is the first Monday after receiving 30% Design DD</text>
   </threadedComment>
-  <threadedComment ref="D63" dT="2026-04-23T19:26:15.32" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{CF413314-5518-4487-9E68-E5576FB49E1E}">
+  <threadedComment ref="B64" dT="2026-05-27T20:30:04.30" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{861FB389-D1F5-4AFE-95B4-775718CE9B1A}">
+    <text>KNAPP PO needs cut by 6/10 Construction PO needs cut by 6/16</text>
+  </threadedComment>
+  <threadedComment ref="D65" dT="2026-04-23T19:26:15.32" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{CF413314-5518-4487-9E68-E5576FB49E1E}">
     <text>Got pulled from the agenda on 4/23/26 due to a legal not having the right signature.  Pending Rescheduling</text>
+  </threadedComment>
+  <threadedComment ref="E69" dT="2026-05-21T18:06:58.65" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{D54FEB2C-162B-4CB7-845C-B43BAADC4E31}">
+    <text>Karisa will leave after REC</text>
+  </threadedComment>
+  <threadedComment ref="G69" dT="2026-05-21T18:13:15.81" personId="{0AD45BD6-9908-41E4-80DD-381203A5D1C1}" id="{3287D6A5-72FD-444E-8875-2CE4F39DE81F}">
+    <text>Karisa will be in Denver for Holiday Meeting and will do site selection</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -8446,7 +8542,7 @@
         <v>335</v>
       </c>
       <c r="H1" s="106" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="I1" s="102" t="s">
         <v>337</v>
@@ -8455,7 +8551,7 @@
         <v>4</v>
       </c>
       <c r="K1" s="66" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="L1" s="88" t="s">
         <v>270</v>
@@ -8464,13 +8560,13 @@
         <v>238</v>
       </c>
       <c r="N1" s="87" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="O1" s="87" t="s">
         <v>253</v>
       </c>
       <c r="P1" s="88" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AI1" s="99" t="s">
         <v>336</v>
@@ -8478,7 +8574,7 @@
     </row>
     <row r="2" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>266</v>
@@ -8493,7 +8589,7 @@
         <v>46044</v>
       </c>
       <c r="F2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G2" s="33" t="str">
         <f>A2</f>
@@ -8516,17 +8612,17 @@
         <v>142</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N2" s="32" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="P2" s="92"/>
       <c r="AI2" s="91"/>
     </row>
     <row r="3" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>266</v>
@@ -8541,7 +8637,7 @@
         <v>46044</v>
       </c>
       <c r="F3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G3" s="33" t="str">
         <f>A3</f>
@@ -8564,7 +8660,7 @@
         <v>142</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="P3" s="92"/>
       <c r="AI3" s="91">
@@ -8574,7 +8670,7 @@
     </row>
     <row r="4" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>266</v>
@@ -8589,7 +8685,7 @@
         <v>46044</v>
       </c>
       <c r="F4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G4" s="33" t="str">
         <f>A4</f>
@@ -8612,10 +8708,10 @@
         <v>142</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N4" s="32" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="P4" s="92"/>
       <c r="AI4" s="91">
@@ -8625,7 +8721,7 @@
     </row>
     <row r="5" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>266</v>
@@ -8640,7 +8736,7 @@
         <v>46045</v>
       </c>
       <c r="F5" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G5" s="33" t="str">
         <f>A5</f>
@@ -8666,7 +8762,7 @@
         <v>237</v>
       </c>
       <c r="N5" s="32" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="P5" s="92"/>
       <c r="AI5" s="91">
@@ -8674,7 +8770,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="6" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="e">
         <f>IF(ISBLANK(E6),"",_xlfn.XLOOKUP(E6,Info!A:A,Info!B:B))</f>
         <v>#N/A</v>
@@ -8692,7 +8788,7 @@
         <v>46051</v>
       </c>
       <c r="F6" s="54" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G6" s="33" t="e">
         <f>IF(ISBLANK(H6),"",_xlfn.XLOOKUP(H6,Info!A:A,Info!B:B))</f>
@@ -8718,13 +8814,13 @@
         <v>247</v>
       </c>
       <c r="N6" s="92" t="s">
+        <v>601</v>
+      </c>
+      <c r="O6" s="118" t="s">
         <v>602</v>
       </c>
-      <c r="O6" s="118" t="s">
+      <c r="P6" s="92" t="s">
         <v>603</v>
-      </c>
-      <c r="P6" s="92" t="s">
-        <v>604</v>
       </c>
       <c r="AI6" s="91">
         <f t="shared" si="1"/>
@@ -8743,13 +8839,13 @@
         <v>187</v>
       </c>
       <c r="D7" s="134" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E7" s="132">
         <v>46056</v>
       </c>
       <c r="F7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G7" s="33">
         <f>IF(ISBLANK(H7),"",_xlfn.XLOOKUP(H7,Info!A:A,Info!B:B))</f>
@@ -8772,10 +8868,10 @@
         <v>142</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="N7" s="92" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="P7" s="92"/>
       <c r="AI7" s="91">
@@ -8795,13 +8891,13 @@
         <v>187</v>
       </c>
       <c r="D8" s="134" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E8" s="132">
         <v>46056</v>
       </c>
       <c r="F8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G8" s="33">
         <f>IF(ISBLANK(H8),"",_xlfn.XLOOKUP(H8,Info!A:A,Info!B:B))</f>
@@ -8824,10 +8920,10 @@
         <v>142</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="N8" s="92" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="P8" s="92"/>
       <c r="AI8" s="91">
@@ -8847,13 +8943,13 @@
         <v>187</v>
       </c>
       <c r="D9" s="134" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E9" s="132">
         <v>46056</v>
       </c>
       <c r="F9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G9" s="33">
         <f>IF(ISBLANK(H9),"",_xlfn.XLOOKUP(H9,Info!A:A,Info!B:B))</f>
@@ -8876,7 +8972,7 @@
         <v>142</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="N9" s="92"/>
       <c r="P9" s="92"/>
@@ -8897,13 +8993,13 @@
         <v>187</v>
       </c>
       <c r="D10" s="134" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E10" s="132">
         <v>46056</v>
       </c>
       <c r="F10" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G10" s="33">
         <f>IF(ISBLANK(H10),"",_xlfn.XLOOKUP(H10,Info!A:A,Info!B:B))</f>
@@ -8926,10 +9022,10 @@
         <v>142</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N10" s="92" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="P10" s="92"/>
       <c r="AI10" s="91">
@@ -8955,7 +9051,7 @@
         <v>46073</v>
       </c>
       <c r="F11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G11" s="33">
         <f>IF(ISBLANK(H11),"",_xlfn.XLOOKUP(H11,Info!A:A,Info!B:B))</f>
@@ -8978,10 +9074,10 @@
         <v>142</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N11" s="32" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="P11" s="92"/>
       <c r="AI11" s="91">
@@ -9007,7 +9103,7 @@
         <v>46073</v>
       </c>
       <c r="F12" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G12" s="33">
         <f>IF(ISBLANK(H12),"",_xlfn.XLOOKUP(H12,Info!A:A,Info!B:B))</f>
@@ -9030,13 +9126,13 @@
         <v>142</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N12" s="32" t="s">
+        <v>518</v>
+      </c>
+      <c r="O12" s="118" t="s">
         <v>519</v>
-      </c>
-      <c r="O12" s="118" t="s">
-        <v>520</v>
       </c>
       <c r="P12" s="92"/>
       <c r="AI12" s="91">
@@ -9062,7 +9158,7 @@
         <v>46079</v>
       </c>
       <c r="F13" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G13" s="33">
         <f>IF(ISBLANK(H13),"",_xlfn.XLOOKUP(H13,Info!A:A,Info!B:B))</f>
@@ -9112,7 +9208,7 @@
         <v>46079</v>
       </c>
       <c r="F14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G14" s="33">
         <f>IF(ISBLANK(H14),"",_xlfn.XLOOKUP(H14,Info!A:A,Info!B:B))</f>
@@ -9129,16 +9225,16 @@
         <v>30</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="O14" s="118" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="P14" s="92"/>
       <c r="AI14" s="91">
@@ -9164,7 +9260,7 @@
         <v>46079</v>
       </c>
       <c r="F15" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="G15" s="33">
         <f>IF(ISBLANK(H15),"",_xlfn.XLOOKUP(H15,Info!A:A,Info!B:B))</f>
@@ -9181,16 +9277,16 @@
         <v>30</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="O15" s="118" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="P15" s="92"/>
       <c r="AI15" s="91">
@@ -9216,7 +9312,7 @@
         <v>46080</v>
       </c>
       <c r="F16" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G16" s="33">
         <f>IF(ISBLANK(H16),"",_xlfn.XLOOKUP(H16,Info!A:A,Info!B:B))</f>
@@ -9239,7 +9335,7 @@
         <v>243</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N16" s="92"/>
       <c r="P16" s="92"/>
@@ -9266,7 +9362,7 @@
         <v>46080</v>
       </c>
       <c r="F17" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="G17" s="33">
         <f>IF(ISBLANK(H17),"",_xlfn.XLOOKUP(H17,Info!A:A,Info!B:B))</f>
@@ -9283,13 +9379,13 @@
         <v>30</v>
       </c>
       <c r="K17" s="33" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L17" s="33" t="s">
         <v>243</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="N17" s="92"/>
       <c r="P17" s="92"/>
@@ -9316,7 +9412,7 @@
         <v>46083</v>
       </c>
       <c r="F18" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="G18" s="33">
         <f>IF(ISBLANK(H18),"",_xlfn.XLOOKUP(H18,Info!A:A,Info!B:B))</f>
@@ -9333,13 +9429,13 @@
         <v>30</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="P18" s="92"/>
       <c r="AI18" s="91">
@@ -9365,7 +9461,7 @@
         <v>46083</v>
       </c>
       <c r="F19" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="G19" s="33">
         <f>IF(ISBLANK(H19),"",_xlfn.XLOOKUP(H19,Info!A:A,Info!B:B))</f>
@@ -9382,13 +9478,13 @@
         <v>30</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L19" s="33" t="s">
         <v>142</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="N19" s="92"/>
       <c r="P19" s="92"/>
@@ -9415,7 +9511,7 @@
         <v>46086</v>
       </c>
       <c r="F20" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G20" s="33">
         <f>IF(ISBLANK(H20),"",_xlfn.XLOOKUP(H20,Info!A:A,Info!B:B))</f>
@@ -9441,7 +9537,7 @@
         <v>237</v>
       </c>
       <c r="O20" s="118" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P20" s="92"/>
       <c r="AI20" s="91">
@@ -9467,7 +9563,7 @@
         <v>46086</v>
       </c>
       <c r="F21" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G21" s="33">
         <f>IF(ISBLANK(H21),"",_xlfn.XLOOKUP(H21,Info!A:A,Info!B:B))</f>
@@ -9493,10 +9589,10 @@
         <v>237</v>
       </c>
       <c r="N21" s="32" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="O21" s="118" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P21" s="92"/>
       <c r="AI21" s="91">
@@ -9522,7 +9618,7 @@
         <v>46086</v>
       </c>
       <c r="F22" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="G22" s="33">
         <f>IF(ISBLANK(H22),"",_xlfn.XLOOKUP(H22,Info!A:A,Info!B:B))</f>
@@ -9539,7 +9635,7 @@
         <v>30</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>142</v>
@@ -9548,7 +9644,7 @@
         <v>237</v>
       </c>
       <c r="O22" s="118" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AI22" s="91"/>
     </row>
@@ -9570,7 +9666,7 @@
         <v>46086</v>
       </c>
       <c r="F23" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G23" s="33">
         <f>IF(ISBLANK(H23),"",_xlfn.XLOOKUP(H23,Info!A:A,Info!B:B))</f>
@@ -9596,7 +9692,7 @@
         <v>237</v>
       </c>
       <c r="O23" s="118" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P23" s="92"/>
       <c r="AI23" s="91"/>
@@ -9619,7 +9715,7 @@
         <v>46093</v>
       </c>
       <c r="F24" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G24" s="33">
         <f>IF(ISBLANK(H24),"",_xlfn.XLOOKUP(H24,Info!A:A,Info!B:B))</f>
@@ -9636,19 +9732,19 @@
         <v>30</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N24" s="32" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="O24" s="118" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="P24" s="92"/>
       <c r="AI24" s="91"/>
@@ -9671,7 +9767,7 @@
         <v>46093</v>
       </c>
       <c r="F25" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G25" s="33">
         <f>IF(ISBLANK(H25),"",_xlfn.XLOOKUP(H25,Info!A:A,Info!B:B))</f>
@@ -9697,7 +9793,7 @@
         <v>237</v>
       </c>
       <c r="O25" s="118" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="P25" s="92"/>
       <c r="AI25" s="91"/>
@@ -9720,7 +9816,7 @@
         <v>46093</v>
       </c>
       <c r="F26" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G26" s="33">
         <f>IF(ISBLANK(H26),"",_xlfn.XLOOKUP(H26,Info!A:A,Info!B:B))</f>
@@ -9746,7 +9842,7 @@
         <v>237</v>
       </c>
       <c r="O26" s="118" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="P26" s="92"/>
       <c r="AI26" s="91"/>
@@ -9769,7 +9865,7 @@
         <v>46093</v>
       </c>
       <c r="F27" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G27" s="33">
         <f>IF(ISBLANK(H27),"",_xlfn.XLOOKUP(H27,Info!A:A,Info!B:B))</f>
@@ -9786,19 +9882,19 @@
         <v>30</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N27" s="32" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="O27" s="118" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="P27" s="92"/>
       <c r="AI27" s="91"/>
@@ -9821,7 +9917,7 @@
         <v>46100</v>
       </c>
       <c r="F28" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G28" s="33">
         <f>IF(ISBLANK(H28),"",_xlfn.XLOOKUP(H28,Info!A:A,Info!B:B))</f>
@@ -9844,13 +9940,13 @@
         <v>142</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N28" s="32" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="O28" s="118" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="P28" s="92"/>
       <c r="AI28" s="91"/>
@@ -9896,7 +9992,7 @@
         <v>142</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="N29" s="92"/>
       <c r="P29" s="92"/>
@@ -9920,7 +10016,7 @@
         <v>46100</v>
       </c>
       <c r="F30" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G30" s="33">
         <f>IF(ISBLANK(H30),"",_xlfn.XLOOKUP(H30,Info!A:A,Info!B:B))</f>
@@ -9943,13 +10039,13 @@
         <v>142</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N30" s="32" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="O30" s="118" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="P30" s="92"/>
       <c r="AI30" s="91"/>
@@ -9972,7 +10068,7 @@
         <v>46100</v>
       </c>
       <c r="F31" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G31" s="33">
         <f>IF(ISBLANK(H31),"",_xlfn.XLOOKUP(H31,Info!A:A,Info!B:B))</f>
@@ -9989,16 +10085,16 @@
         <v>30</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="O31" s="118" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="P31" s="92"/>
       <c r="AI31" s="91"/>
@@ -10015,13 +10111,13 @@
         <v>187</v>
       </c>
       <c r="D32" s="54" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E32" s="91">
         <v>46114</v>
       </c>
       <c r="F32" s="54" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="G32" s="33">
         <f>IF(ISBLANK(H32),"",_xlfn.XLOOKUP(H32,Info!A:A,Info!B:B))</f>
@@ -10038,20 +10134,20 @@
         <v>60</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L32" s="33"/>
       <c r="M32" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N32" s="92" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="O32" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P32" s="92" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AI32" s="91"/>
     </row>
@@ -10171,7 +10267,7 @@
         <v>46114</v>
       </c>
       <c r="F35" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G35" s="33">
         <f>IF(ISBLANK(H35),"",_xlfn.XLOOKUP(H35,Info!A:A,Info!B:B))</f>
@@ -10269,7 +10365,7 @@
         <v>46114</v>
       </c>
       <c r="F37" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G37" s="33">
         <f>IF(ISBLANK(H37),"",_xlfn.XLOOKUP(H37,Info!A:A,Info!B:B))</f>
@@ -10367,7 +10463,7 @@
         <v>46115</v>
       </c>
       <c r="F39" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="G39" s="33">
         <f>IF(ISBLANK(H39),"",_xlfn.XLOOKUP(H39,Info!A:A,Info!B:B))</f>
@@ -10390,13 +10486,13 @@
         <v>142</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N39" s="32" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="O39" s="118" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="P39" s="92"/>
       <c r="AI39" s="91"/>
@@ -10472,7 +10568,7 @@
         <v>46115</v>
       </c>
       <c r="F41" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="G41" s="33">
         <f>IF(ISBLANK(H41),"",_xlfn.XLOOKUP(H41,Info!A:A,Info!B:B))</f>
@@ -10495,13 +10591,13 @@
         <v>142</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N41" s="32" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="O41" s="118" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="P41" s="92"/>
       <c r="AI41" s="91"/>
@@ -10573,7 +10669,7 @@
         <v>46115</v>
       </c>
       <c r="F43" s="54" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="G43" s="33">
         <f>IF(ISBLANK(H43),"",_xlfn.XLOOKUP(H43,Info!A:A,Info!B:B))</f>
@@ -10595,11 +10691,11 @@
         <v>142</v>
       </c>
       <c r="M43" s="67" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="N43" s="92"/>
       <c r="O43" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P43" s="92" t="s">
         <v>249</v>
@@ -10618,7 +10714,7 @@
         <v>187</v>
       </c>
       <c r="D44" s="54" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E44" s="91">
         <v>46119</v>
@@ -10671,7 +10767,7 @@
         <v>46119</v>
       </c>
       <c r="F45" s="54" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G45" s="33">
         <f>IF(ISBLANK(H45),"",_xlfn.XLOOKUP(H45,Info!A:A,Info!B:B))</f>
@@ -10688,20 +10784,20 @@
         <v>60</v>
       </c>
       <c r="K45" s="33" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L45" s="33"/>
       <c r="M45" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N45" s="92" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="O45" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P45" s="92" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AI45" s="91"/>
     </row>
@@ -10723,7 +10819,7 @@
         <v>46121</v>
       </c>
       <c r="F46" s="54" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="G46" s="33">
         <f>IF(ISBLANK(H46),"",_xlfn.XLOOKUP(H46,Info!A:A,Info!B:B))</f>
@@ -10745,11 +10841,11 @@
         <v>142</v>
       </c>
       <c r="M46" s="67" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="N46" s="92"/>
       <c r="O46" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P46" s="92" t="s">
         <v>249</v>
@@ -10774,7 +10870,7 @@
         <v>46121</v>
       </c>
       <c r="F47" s="54" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G47" s="33">
         <f>IF(ISBLANK(H47),"",_xlfn.XLOOKUP(H47,Info!A:A,Info!B:B))</f>
@@ -10796,7 +10892,7 @@
         <v>142</v>
       </c>
       <c r="M47" s="67" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="N47" s="92"/>
       <c r="O47" s="93" t="s">
@@ -10851,7 +10947,7 @@
         <v>264</v>
       </c>
       <c r="O48" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P48" s="92" t="s">
         <v>344</v>
@@ -10876,7 +10972,7 @@
         <v>46125</v>
       </c>
       <c r="F49" s="54" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G49" s="33">
         <f>IF(ISBLANK(H49),"",_xlfn.XLOOKUP(H49,Info!A:A,Info!B:B))</f>
@@ -10893,20 +10989,20 @@
         <v>60</v>
       </c>
       <c r="K49" s="33" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L49" s="33"/>
       <c r="M49" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N49" s="92" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="O49" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P49" s="92" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AI49" s="91"/>
     </row>
@@ -11003,13 +11099,13 @@
         <v>142</v>
       </c>
       <c r="M51" s="67" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N51" s="92" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="O51" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P51" s="92" t="s">
         <v>423</v>
@@ -11057,10 +11153,10 @@
         <v>271</v>
       </c>
       <c r="M52" s="67" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N52" s="92" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="O52" s="93" t="s">
         <v>347</v>
@@ -11111,10 +11207,10 @@
         <v>421</v>
       </c>
       <c r="M53" s="67" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="N53" s="92" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="O53" s="93" t="s">
         <v>347</v>
@@ -11142,7 +11238,7 @@
         <v>46133</v>
       </c>
       <c r="F54" s="54" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G54" s="33">
         <f>IF(ISBLANK(H54),"",_xlfn.XLOOKUP(H54,Info!A:A,Info!B:B))</f>
@@ -11159,20 +11255,20 @@
         <v>60</v>
       </c>
       <c r="K54" s="33" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L54" s="33"/>
       <c r="M54" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N54" s="92" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="O54" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P54" s="92" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AI54" s="91"/>
     </row>
@@ -11194,7 +11290,7 @@
         <v>46133</v>
       </c>
       <c r="F55" s="54" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G55" s="33">
         <f>IF(ISBLANK(H55),"",_xlfn.XLOOKUP(H55,Info!A:A,Info!B:B))</f>
@@ -11223,7 +11319,7 @@
         <v>275</v>
       </c>
       <c r="O55" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P55" s="92" t="s">
         <v>274</v>
@@ -11274,7 +11370,7 @@
         <v>247</v>
       </c>
       <c r="N56" s="92" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="O56" s="93" t="s">
         <v>341</v>
@@ -11302,7 +11398,7 @@
         <v>46135</v>
       </c>
       <c r="F57" s="54" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="G57" s="33">
         <f>IF(ISBLANK(H57),"",_xlfn.XLOOKUP(H57,Info!A:A,Info!B:B))</f>
@@ -11319,20 +11415,20 @@
         <v>60</v>
       </c>
       <c r="K57" s="33" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L57" s="33"/>
       <c r="M57" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N57" s="92" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="O57" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P57" s="92" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="AI57" s="91"/>
     </row>
@@ -11354,7 +11450,7 @@
         <v>46135</v>
       </c>
       <c r="F58" s="54" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G58" s="33">
         <f>IF(ISBLANK(H58),"",_xlfn.XLOOKUP(H58,Info!A:A,Info!B:B))</f>
@@ -11380,7 +11476,7 @@
         <v>247</v>
       </c>
       <c r="N58" s="92" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="O58" s="93" t="s">
         <v>341</v>
@@ -11406,7 +11502,7 @@
         <v>46136</v>
       </c>
       <c r="F59" s="54" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="G59" s="33">
         <f>IF(ISBLANK(H59),"",_xlfn.XLOOKUP(H59,Info!A:A,Info!B:B))</f>
@@ -11431,13 +11527,13 @@
         <v>247</v>
       </c>
       <c r="N59" s="92" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="O59" s="118" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="P59" s="92" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AI59" s="91"/>
     </row>
@@ -11459,7 +11555,7 @@
         <v>46139</v>
       </c>
       <c r="F60" s="54" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G60" s="33">
         <f>IF(ISBLANK(H60),"",_xlfn.XLOOKUP(H60,Info!A:A,Info!B:B))</f>
@@ -11476,20 +11572,20 @@
         <v>60</v>
       </c>
       <c r="K60" s="33" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L60" s="33"/>
       <c r="M60" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N60" s="92" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="O60" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P60" s="92" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AI60" s="91"/>
     </row>
@@ -11511,7 +11607,7 @@
         <v>46139</v>
       </c>
       <c r="F61" s="54" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G61" s="33">
         <f>IF(ISBLANK(H61),"",_xlfn.XLOOKUP(H61,Info!A:A,Info!B:B))</f>
@@ -11536,7 +11632,7 @@
         <v>237</v>
       </c>
       <c r="O61" s="118" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="P61" s="92" t="s">
         <v>340</v>
@@ -11561,7 +11657,7 @@
         <v>46142</v>
       </c>
       <c r="F62" s="54" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G62" s="33">
         <f>IF(ISBLANK(H62),"",_xlfn.XLOOKUP(H62,Info!A:A,Info!B:B))</f>
@@ -11587,10 +11683,10 @@
         <v>247</v>
       </c>
       <c r="N62" s="92" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="O62" s="118" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="P62" s="92" t="s">
         <v>340</v>
@@ -11642,7 +11738,7 @@
       </c>
       <c r="N63" s="92"/>
       <c r="O63" s="118" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="P63" s="92" t="s">
         <v>340</v>
@@ -11667,7 +11763,7 @@
         <v>46143</v>
       </c>
       <c r="F64" s="54" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G64" s="33">
         <f>IF(ISBLANK(H64),"",_xlfn.XLOOKUP(H64,Info!A:A,Info!B:B))</f>
@@ -11690,14 +11786,14 @@
         <v>142</v>
       </c>
       <c r="M64" s="67" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="N64" s="92"/>
       <c r="O64" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P64" s="92" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="AI64" s="91"/>
     </row>
@@ -11719,7 +11815,7 @@
         <v>46143</v>
       </c>
       <c r="F65" s="54" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="G65" s="33">
         <f>IF(ISBLANK(H65),"",_xlfn.XLOOKUP(H65,Info!A:A,Info!B:B))</f>
@@ -11736,20 +11832,20 @@
         <v>60</v>
       </c>
       <c r="K65" s="33" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L65" s="33"/>
       <c r="M65" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N65" s="92" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="O65" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P65" s="92" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AI65" s="91"/>
     </row>
@@ -11799,10 +11895,10 @@
         <v>264</v>
       </c>
       <c r="O66" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P66" s="92" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AI66" s="91"/>
     </row>
@@ -11824,7 +11920,7 @@
         <v>46146</v>
       </c>
       <c r="F67" s="54" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="G67" s="33">
         <f>IF(ISBLANK(H67),"",_xlfn.XLOOKUP(H67,Info!A:A,Info!B:B))</f>
@@ -11840,7 +11936,7 @@
         <v>20</v>
       </c>
       <c r="K67" s="33" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L67" s="33" t="s">
         <v>142</v>
@@ -11849,13 +11945,13 @@
         <v>247</v>
       </c>
       <c r="N67" s="92" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O67" s="118" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="P67" s="92" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AI67" s="91"/>
     </row>
@@ -11877,7 +11973,7 @@
         <v>46146</v>
       </c>
       <c r="F68" s="54" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G68" s="33">
         <f>IF(ISBLANK(H68),"",_xlfn.XLOOKUP(H68,Info!A:A,Info!B:B))</f>
@@ -11893,19 +11989,19 @@
         <v>20</v>
       </c>
       <c r="K68" s="33" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L68" s="33" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="M68" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N68" s="92" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="O68" s="118" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="P68" s="92" t="s">
         <v>340</v>
@@ -11930,7 +12026,7 @@
         <v>46146</v>
       </c>
       <c r="F69" s="54" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G69" s="33">
         <f>IF(ISBLANK(H69),"",_xlfn.XLOOKUP(H69,Info!A:A,Info!B:B))</f>
@@ -11956,7 +12052,7 @@
       </c>
       <c r="N69" s="92"/>
       <c r="O69" s="118" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="P69" s="92"/>
       <c r="AI69" s="91"/>
@@ -11979,7 +12075,7 @@
         <v>46147</v>
       </c>
       <c r="F70" s="54" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G70" s="33">
         <f>IF(ISBLANK(H70),"",_xlfn.XLOOKUP(H70,Info!A:A,Info!B:B))</f>
@@ -11996,20 +12092,20 @@
         <v>60</v>
       </c>
       <c r="K70" s="33" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="L70" s="33"/>
       <c r="M70" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N70" s="92" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="O70" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P70" s="92" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AI70" s="91"/>
     </row>
@@ -12031,7 +12127,7 @@
         <v>46150</v>
       </c>
       <c r="F71" s="54" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="G71" s="33">
         <f>IF(ISBLANK(H71),"",_xlfn.XLOOKUP(H71,Info!A:A,Info!B:B))</f>
@@ -12057,10 +12153,10 @@
         <v>247</v>
       </c>
       <c r="N71" s="92" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="O71" s="118" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="P71" s="92"/>
       <c r="AI71" s="91"/>
@@ -12077,7 +12173,7 @@
         <v>187</v>
       </c>
       <c r="D72" s="54" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E72" s="91">
         <v>46154</v>
@@ -12108,13 +12204,13 @@
         <v>247</v>
       </c>
       <c r="N72" s="92" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="O72" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="P72" s="92" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AI72" s="91"/>
     </row>
@@ -12136,7 +12232,7 @@
         <v>46156</v>
       </c>
       <c r="F73" s="54" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G73" s="33">
         <f>IF(ISBLANK(H73),"",_xlfn.XLOOKUP(H73,Info!A:A,Info!B:B))</f>
@@ -12153,7 +12249,7 @@
         <v>60</v>
       </c>
       <c r="K73" s="33" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="L73" s="33" t="s">
         <v>244</v>
@@ -12163,14 +12259,14 @@
       </c>
       <c r="N73" s="92"/>
       <c r="O73" s="118" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P73" s="92" t="s">
         <v>340</v>
       </c>
       <c r="AI73" s="91"/>
     </row>
-    <row r="74" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="33">
         <f>IF(ISBLANK(E74),"",_xlfn.XLOOKUP(E74,Info!A:A,Info!B:B))</f>
         <v>16</v>
@@ -12179,7 +12275,7 @@
         <v>266</v>
       </c>
       <c r="C74" s="33" t="s">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="D74" s="54" t="s">
         <v>262</v>
@@ -12216,14 +12312,14 @@
         <v>264</v>
       </c>
       <c r="O74" s="93" t="s">
+        <v>651</v>
+      </c>
+      <c r="P74" s="92" t="s">
         <v>654</v>
       </c>
-      <c r="P74" s="92" t="s">
-        <v>657</v>
-      </c>
       <c r="AI74" s="91"/>
     </row>
-    <row r="75" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="33">
         <f>IF(ISBLANK(E75),"",_xlfn.XLOOKUP(E75,Info!A:A,Info!B:B))</f>
         <v>16</v>
@@ -12232,7 +12328,7 @@
         <v>266</v>
       </c>
       <c r="C75" s="33" t="s">
-        <v>550</v>
+        <v>187</v>
       </c>
       <c r="D75" s="54" t="s">
         <v>239</v>
@@ -12241,7 +12337,7 @@
         <v>46162</v>
       </c>
       <c r="F75" s="54" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G75" s="33">
         <f>IF(ISBLANK(H75),"",_xlfn.XLOOKUP(H75,Info!A:A,Info!B:B))</f>
@@ -12266,396 +12362,471 @@
       <c r="M75" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="N75" s="92"/>
+      <c r="N75" s="92" t="s">
+        <v>671</v>
+      </c>
       <c r="O75" s="118" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="P75" s="92"/>
       <c r="AI75" s="91"/>
     </row>
-    <row r="76" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="33" t="e">
+    <row r="76" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="33">
         <f>IF(ISBLANK(E76),"",_xlfn.XLOOKUP(E76,Info!A:A,Info!B:B))</f>
-        <v>#N/A</v>
+        <v>16</v>
       </c>
       <c r="B76" s="33" t="s">
         <v>266</v>
       </c>
       <c r="C76" s="33" t="s">
-        <v>550</v>
+        <v>187</v>
       </c>
       <c r="D76" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="E76" s="91" t="s">
-        <v>84</v>
+      <c r="E76" s="91">
+        <v>46162</v>
       </c>
       <c r="F76" s="54" t="s">
-        <v>579</v>
-      </c>
-      <c r="G76" s="33" t="str">
+        <v>615</v>
+      </c>
+      <c r="G76" s="33">
         <f>IF(ISBLANK(H76),"",_xlfn.XLOOKUP(H76,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H76" s="98"/>
-      <c r="I76" s="103"/>
-      <c r="J76" s="33"/>
+        <v>16</v>
+      </c>
+      <c r="H76" s="98">
+        <v>46162</v>
+      </c>
+      <c r="I76" s="103">
+        <v>0.625</v>
+      </c>
+      <c r="J76" s="33">
+        <v>10</v>
+      </c>
       <c r="K76" s="33" t="s">
-        <v>598</v>
+        <v>641</v>
       </c>
       <c r="L76" s="33" t="s">
-        <v>598</v>
+        <v>142</v>
       </c>
       <c r="M76" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="N76" s="92"/>
+      <c r="N76" s="92" t="s">
+        <v>670</v>
+      </c>
+      <c r="O76" s="118" t="s">
+        <v>614</v>
+      </c>
       <c r="P76" s="92" t="s">
-        <v>340</v>
+        <v>613</v>
       </c>
       <c r="AI76" s="91"/>
     </row>
-    <row r="77" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="33" t="e">
+    <row r="77" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="33">
         <f>IF(ISBLANK(E77),"",_xlfn.XLOOKUP(E77,Info!A:A,Info!B:B))</f>
-        <v>#N/A</v>
+        <v>17</v>
       </c>
       <c r="B77" s="33" t="s">
         <v>266</v>
       </c>
       <c r="C77" s="33" t="s">
-        <v>550</v>
+        <v>187</v>
       </c>
       <c r="D77" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="E77" s="91" t="s">
-        <v>84</v>
+      <c r="E77" s="91">
+        <v>46171</v>
       </c>
       <c r="F77" s="54" t="s">
-        <v>589</v>
-      </c>
-      <c r="G77" s="33" t="str">
+        <v>664</v>
+      </c>
+      <c r="G77" s="33">
         <f>IF(ISBLANK(H77),"",_xlfn.XLOOKUP(H77,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H77" s="98"/>
+        <v>17</v>
+      </c>
+      <c r="H77" s="98">
+        <f>E77-1</f>
+        <v>46170</v>
+      </c>
       <c r="I77" s="103">
-        <v>0.625</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="J77" s="33">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K77" s="33" t="s">
-        <v>271</v>
+        <v>665</v>
       </c>
       <c r="L77" s="33" t="s">
-        <v>271</v>
+        <v>665</v>
       </c>
       <c r="M77" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N77" s="92" t="s">
-        <v>345</v>
-      </c>
-      <c r="O77" s="93"/>
+        <v>685</v>
+      </c>
+      <c r="O77" s="118" t="s">
+        <v>672</v>
+      </c>
       <c r="P77" s="92" t="s">
         <v>340</v>
       </c>
       <c r="AI77" s="91"/>
     </row>
-    <row r="78" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="33" t="e">
+    <row r="78" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="33">
         <f>IF(ISBLANK(E78),"",_xlfn.XLOOKUP(E78,Info!A:A,Info!B:B))</f>
-        <v>#N/A</v>
+        <v>17</v>
       </c>
       <c r="B78" s="33" t="s">
         <v>266</v>
       </c>
       <c r="C78" s="33" t="s">
-        <v>550</v>
+        <v>187</v>
       </c>
       <c r="D78" s="54" t="s">
-        <v>242</v>
-      </c>
-      <c r="E78" s="91" t="s">
-        <v>84</v>
+        <v>239</v>
+      </c>
+      <c r="E78" s="91">
+        <v>46171</v>
       </c>
       <c r="F78" s="54" t="s">
-        <v>582</v>
-      </c>
-      <c r="G78" s="33" t="str">
+        <v>673</v>
+      </c>
+      <c r="G78" s="33">
         <f>IF(ISBLANK(H78),"",_xlfn.XLOOKUP(H78,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H78" s="98"/>
-      <c r="I78" s="103"/>
-      <c r="J78" s="33"/>
-      <c r="K78" s="33"/>
+        <v>17</v>
+      </c>
+      <c r="H78" s="98">
+        <f>E78-1</f>
+        <v>46170</v>
+      </c>
+      <c r="I78" s="103">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J78" s="33">
+        <v>45</v>
+      </c>
+      <c r="K78" s="33" t="s">
+        <v>674</v>
+      </c>
       <c r="L78" s="33" t="s">
-        <v>142</v>
+        <v>244</v>
       </c>
       <c r="M78" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N78" s="92"/>
+      <c r="O78" s="118" t="s">
+        <v>672</v>
+      </c>
       <c r="P78" s="92" t="s">
-        <v>588</v>
+        <v>675</v>
       </c>
       <c r="AI78" s="91"/>
     </row>
-    <row r="79" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="33" t="e">
+    <row r="79" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="33">
         <f>IF(ISBLANK(E79),"",_xlfn.XLOOKUP(E79,Info!A:A,Info!B:B))</f>
-        <v>#N/A</v>
+        <v>17</v>
       </c>
       <c r="B79" s="33" t="s">
         <v>266</v>
       </c>
       <c r="C79" s="33" t="s">
-        <v>550</v>
+        <v>187</v>
       </c>
       <c r="D79" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="E79" s="91" t="s">
-        <v>84</v>
+      <c r="E79" s="91">
+        <v>46171</v>
       </c>
       <c r="F79" s="54" t="s">
-        <v>586</v>
-      </c>
-      <c r="G79" s="33" t="str">
+        <v>678</v>
+      </c>
+      <c r="G79" s="33">
         <f>IF(ISBLANK(H79),"",_xlfn.XLOOKUP(H79,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H79" s="98"/>
-      <c r="I79" s="103"/>
-      <c r="J79" s="33"/>
+        <v>17</v>
+      </c>
+      <c r="H79" s="98">
+        <f>E79-1</f>
+        <v>46170</v>
+      </c>
+      <c r="I79" s="103">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J79" s="33">
+        <v>15</v>
+      </c>
       <c r="K79" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="L79" s="33"/>
+        <v>490</v>
+      </c>
+      <c r="L79" s="33" t="s">
+        <v>490</v>
+      </c>
       <c r="M79" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N79" s="92"/>
-      <c r="P79" s="92" t="s">
-        <v>340</v>
-      </c>
+      <c r="O79" s="118" t="s">
+        <v>672</v>
+      </c>
+      <c r="P79" s="92"/>
       <c r="AI79" s="91"/>
     </row>
-    <row r="80" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="33" t="e">
+    <row r="80" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="33">
         <f>IF(ISBLANK(E80),"",_xlfn.XLOOKUP(E80,Info!A:A,Info!B:B))</f>
-        <v>#N/A</v>
+        <v>17</v>
       </c>
       <c r="B80" s="33" t="s">
         <v>266</v>
       </c>
       <c r="C80" s="33" t="s">
-        <v>550</v>
+        <v>187</v>
       </c>
       <c r="D80" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="E80" s="91" t="s">
-        <v>84</v>
+      <c r="E80" s="91">
+        <v>46171</v>
       </c>
       <c r="F80" s="54" t="s">
-        <v>639</v>
-      </c>
-      <c r="G80" s="33" t="str">
+        <v>572</v>
+      </c>
+      <c r="G80" s="33">
         <f>IF(ISBLANK(H80),"",_xlfn.XLOOKUP(H80,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H80" s="98"/>
-      <c r="I80" s="103"/>
-      <c r="J80" s="33"/>
+        <v>17</v>
+      </c>
+      <c r="H80" s="98">
+        <f>E80-1</f>
+        <v>46170</v>
+      </c>
+      <c r="I80" s="103">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J80" s="33">
+        <v>15</v>
+      </c>
       <c r="K80" s="33" t="s">
-        <v>271</v>
-      </c>
-      <c r="L80" s="33"/>
+        <v>487</v>
+      </c>
+      <c r="L80" s="33" t="s">
+        <v>487</v>
+      </c>
       <c r="M80" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N80" s="92"/>
-      <c r="P80" s="92" t="s">
-        <v>340</v>
-      </c>
+      <c r="O80" s="118" t="s">
+        <v>672</v>
+      </c>
+      <c r="P80" s="92"/>
       <c r="AI80" s="91"/>
     </row>
-    <row r="81" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="33" t="e">
+    <row r="81" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="33">
         <f>IF(ISBLANK(E81),"",_xlfn.XLOOKUP(E81,Info!A:A,Info!B:B))</f>
-        <v>#N/A</v>
+        <v>18</v>
       </c>
       <c r="B81" s="33" t="s">
         <v>266</v>
       </c>
       <c r="C81" s="33" t="s">
-        <v>550</v>
+        <v>104</v>
       </c>
       <c r="D81" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="E81" s="91" t="s">
-        <v>84</v>
+      <c r="E81" s="91">
+        <v>46176</v>
       </c>
       <c r="F81" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G81" s="33" t="str">
+        <v>572</v>
+      </c>
+      <c r="G81" s="33">
         <f>IF(ISBLANK(H81),"",_xlfn.XLOOKUP(H81,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="J81" s="33"/>
+        <v>18</v>
+      </c>
+      <c r="H81" s="98">
+        <v>46175</v>
+      </c>
+      <c r="I81" s="103">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J81" s="33">
+        <v>30</v>
+      </c>
       <c r="K81" s="33" t="s">
-        <v>513</v>
-      </c>
-      <c r="L81" s="33"/>
+        <v>487</v>
+      </c>
+      <c r="L81" s="33" t="s">
+        <v>487</v>
+      </c>
       <c r="M81" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N81" s="92"/>
+      <c r="O81" s="118" t="s">
+        <v>687</v>
+      </c>
       <c r="P81" s="92" t="s">
         <v>340</v>
       </c>
       <c r="AI81" s="91"/>
     </row>
-    <row r="82" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="33" t="e">
+    <row r="82" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="33">
         <f>IF(ISBLANK(E82),"",_xlfn.XLOOKUP(E82,Info!A:A,Info!B:B))</f>
-        <v>#N/A</v>
+        <v>18</v>
       </c>
       <c r="B82" s="33" t="s">
         <v>266</v>
       </c>
       <c r="C82" s="33" t="s">
-        <v>550</v>
+        <v>104</v>
       </c>
       <c r="D82" s="54" t="s">
-        <v>242</v>
-      </c>
-      <c r="E82" s="91" t="s">
-        <v>84</v>
+        <v>239</v>
+      </c>
+      <c r="E82" s="91">
+        <v>46176</v>
       </c>
       <c r="F82" s="54" t="s">
-        <v>641</v>
+        <v>686</v>
       </c>
       <c r="G82" s="33">
         <f>IF(ISBLANK(H82),"",_xlfn.XLOOKUP(H82,Info!A:A,Info!B:B))</f>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H82" s="98">
-        <v>46143</v>
-      </c>
-      <c r="I82" s="103"/>
+        <v>46175</v>
+      </c>
+      <c r="I82" s="103">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="J82" s="33">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K82" s="33" t="s">
-        <v>142</v>
+        <v>244</v>
       </c>
       <c r="L82" s="33" t="s">
-        <v>142</v>
+        <v>244</v>
       </c>
       <c r="M82" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N82" s="92"/>
+      <c r="O82" s="118" t="s">
+        <v>687</v>
+      </c>
       <c r="P82" s="92" t="s">
-        <v>258</v>
+        <v>340</v>
       </c>
       <c r="AI82" s="91"/>
     </row>
-    <row r="83" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="33" t="e">
+    <row r="83" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="33">
         <f>IF(ISBLANK(E83),"",_xlfn.XLOOKUP(E83,Info!A:A,Info!B:B))</f>
-        <v>#N/A</v>
+        <v>18</v>
       </c>
       <c r="B83" s="33" t="s">
         <v>266</v>
       </c>
       <c r="C83" s="33" t="s">
-        <v>550</v>
+        <v>104</v>
       </c>
       <c r="D83" s="54" t="s">
-        <v>239</v>
-      </c>
-      <c r="E83" s="91" t="s">
-        <v>84</v>
+        <v>680</v>
+      </c>
+      <c r="E83" s="91">
+        <v>46177</v>
       </c>
       <c r="F83" s="54" t="s">
-        <v>600</v>
-      </c>
-      <c r="G83" s="33" t="str">
+        <v>681</v>
+      </c>
+      <c r="G83" s="33">
         <f>IF(ISBLANK(H83),"",_xlfn.XLOOKUP(H83,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H83" s="98"/>
-      <c r="I83" s="103"/>
-      <c r="J83" s="33">
-        <v>30</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="H83" s="98">
+        <f>E83-1</f>
+        <v>46176</v>
+      </c>
+      <c r="I83" s="103">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J83" s="33"/>
       <c r="K83" s="33" t="s">
-        <v>645</v>
+        <v>682</v>
       </c>
       <c r="L83" s="33" t="s">
-        <v>597</v>
+        <v>142</v>
       </c>
       <c r="M83" s="67" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="N83" s="92"/>
-      <c r="P83" s="92" t="s">
-        <v>601</v>
-      </c>
+      <c r="O83" s="118" t="s">
+        <v>683</v>
+      </c>
+      <c r="P83" s="92"/>
       <c r="AI83" s="91"/>
     </row>
-    <row r="84" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="33" t="e">
+    <row r="84" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="33">
         <f>IF(ISBLANK(E84),"",_xlfn.XLOOKUP(E84,Info!A:A,Info!B:B))</f>
-        <v>#N/A</v>
+        <v>19</v>
       </c>
       <c r="B84" s="33" t="s">
         <v>266</v>
       </c>
       <c r="C84" s="33" t="s">
-        <v>550</v>
+        <v>104</v>
       </c>
       <c r="D84" s="54" t="s">
-        <v>239</v>
-      </c>
-      <c r="E84" s="91" t="s">
-        <v>84</v>
+        <v>261</v>
+      </c>
+      <c r="E84" s="91">
+        <v>46183</v>
       </c>
       <c r="F84" s="54" t="s">
-        <v>618</v>
-      </c>
-      <c r="G84" s="33" t="str">
+        <v>581</v>
+      </c>
+      <c r="G84" s="33">
         <f>IF(ISBLANK(H84),"",_xlfn.XLOOKUP(H84,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H84" s="98"/>
-      <c r="I84" s="103"/>
-      <c r="J84" s="33"/>
+        <v>18</v>
+      </c>
+      <c r="H84" s="98">
+        <v>46176</v>
+      </c>
+      <c r="I84" s="103">
+        <v>0.5</v>
+      </c>
+      <c r="J84" s="33">
+        <v>0</v>
+      </c>
       <c r="K84" s="33"/>
-      <c r="L84" s="33"/>
+      <c r="L84" s="33" t="s">
+        <v>142</v>
+      </c>
       <c r="M84" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="N84" s="92" t="s">
-        <v>615</v>
-      </c>
-      <c r="O84" s="118" t="s">
-        <v>617</v>
-      </c>
+      <c r="N84" s="92"/>
       <c r="P84" s="92" t="s">
-        <v>616</v>
+        <v>587</v>
       </c>
       <c r="AI84" s="91"/>
     </row>
-    <row r="85" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="33">
         <f>IF(ISBLANK(E85),"",_xlfn.XLOOKUP(E85,Info!A:A,Info!B:B))</f>
         <v>16</v>
@@ -12664,7 +12835,7 @@
         <v>266</v>
       </c>
       <c r="C85" s="33" t="s">
-        <v>550</v>
+        <v>187</v>
       </c>
       <c r="D85" s="54" t="s">
         <v>242</v>
@@ -12673,7 +12844,7 @@
         <v>46160</v>
       </c>
       <c r="F85" s="54" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="G85" s="33">
         <f>IF(ISBLANK(H85),"",_xlfn.XLOOKUP(H85,Info!A:A,Info!B:B))</f>
@@ -12695,26 +12866,36 @@
         <v>142</v>
       </c>
       <c r="M85" s="67" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="N85" s="92" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="P85" s="92" t="s">
         <v>263</v>
       </c>
       <c r="AI85" s="91"/>
     </row>
-    <row r="86" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="33" t="str">
+    <row r="86" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="33" t="e">
         <f>IF(ISBLANK(E86),"",_xlfn.XLOOKUP(E86,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="B86" s="33"/>
-      <c r="C86" s="33"/>
-      <c r="D86" s="54"/>
-      <c r="E86" s="91"/>
-      <c r="F86" s="54"/>
+        <v>#N/A</v>
+      </c>
+      <c r="B86" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C86" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="D86" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E86" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="F86" s="54" t="s">
+        <v>578</v>
+      </c>
       <c r="G86" s="33" t="str">
         <f>IF(ISBLANK(H86),"",_xlfn.XLOOKUP(H86,Info!A:A,Info!B:B))</f>
         <v/>
@@ -12722,47 +12903,90 @@
       <c r="H86" s="98"/>
       <c r="I86" s="103"/>
       <c r="J86" s="33"/>
-      <c r="K86" s="33"/>
-      <c r="L86" s="33"/>
-      <c r="M86" s="67"/>
+      <c r="K86" s="33" t="s">
+        <v>597</v>
+      </c>
+      <c r="L86" s="33" t="s">
+        <v>597</v>
+      </c>
+      <c r="M86" s="67" t="s">
+        <v>247</v>
+      </c>
       <c r="N86" s="92"/>
-      <c r="P86" s="92"/>
+      <c r="P86" s="92" t="s">
+        <v>340</v>
+      </c>
       <c r="AI86" s="91"/>
     </row>
-    <row r="87" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="33" t="str">
+    <row r="87" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="33" t="e">
         <f>IF(ISBLANK(E87),"",_xlfn.XLOOKUP(E87,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="B87" s="33"/>
-      <c r="C87" s="33"/>
-      <c r="D87" s="54"/>
-      <c r="E87" s="91"/>
-      <c r="F87" s="54"/>
+        <v>#N/A</v>
+      </c>
+      <c r="B87" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C87" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="D87" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E87" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="F87" s="54" t="s">
+        <v>588</v>
+      </c>
       <c r="G87" s="33" t="str">
         <f>IF(ISBLANK(H87),"",_xlfn.XLOOKUP(H87,Info!A:A,Info!B:B))</f>
         <v/>
       </c>
       <c r="H87" s="98"/>
-      <c r="I87" s="103"/>
-      <c r="J87" s="33"/>
-      <c r="K87" s="33"/>
-      <c r="L87" s="33"/>
-      <c r="M87" s="67"/>
-      <c r="N87" s="92"/>
-      <c r="P87" s="92"/>
+      <c r="I87" s="103">
+        <v>0.625</v>
+      </c>
+      <c r="J87" s="33">
+        <v>30</v>
+      </c>
+      <c r="K87" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="L87" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="M87" s="67" t="s">
+        <v>247</v>
+      </c>
+      <c r="N87" s="92" t="s">
+        <v>345</v>
+      </c>
+      <c r="O87" s="93"/>
+      <c r="P87" s="92" t="s">
+        <v>340</v>
+      </c>
       <c r="AI87" s="91"/>
     </row>
-    <row r="88" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="33" t="str">
+    <row r="88" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="33" t="e">
         <f>IF(ISBLANK(E88),"",_xlfn.XLOOKUP(E88,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="B88" s="33"/>
-      <c r="C88" s="33"/>
-      <c r="D88" s="54"/>
-      <c r="E88" s="91"/>
-      <c r="F88" s="54"/>
+        <v>#N/A</v>
+      </c>
+      <c r="B88" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C88" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="D88" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E88" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="F88" s="54" t="s">
+        <v>585</v>
+      </c>
       <c r="G88" s="33" t="str">
         <f>IF(ISBLANK(H88),"",_xlfn.XLOOKUP(H88,Info!A:A,Info!B:B))</f>
         <v/>
@@ -12770,23 +12994,39 @@
       <c r="H88" s="98"/>
       <c r="I88" s="103"/>
       <c r="J88" s="33"/>
-      <c r="K88" s="33"/>
+      <c r="K88" s="33" t="s">
+        <v>234</v>
+      </c>
       <c r="L88" s="33"/>
-      <c r="M88" s="67"/>
+      <c r="M88" s="67" t="s">
+        <v>247</v>
+      </c>
       <c r="N88" s="92"/>
-      <c r="P88" s="92"/>
+      <c r="P88" s="92" t="s">
+        <v>340</v>
+      </c>
       <c r="AI88" s="91"/>
     </row>
-    <row r="89" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="33" t="str">
+    <row r="89" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="33" t="e">
         <f>IF(ISBLANK(E89),"",_xlfn.XLOOKUP(E89,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="B89" s="33"/>
-      <c r="C89" s="33"/>
-      <c r="D89" s="54"/>
-      <c r="E89" s="91"/>
-      <c r="F89" s="54"/>
+        <v>#N/A</v>
+      </c>
+      <c r="B89" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C89" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="D89" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E89" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="F89" s="54" t="s">
+        <v>636</v>
+      </c>
       <c r="G89" s="33" t="str">
         <f>IF(ISBLANK(H89),"",_xlfn.XLOOKUP(H89,Info!A:A,Info!B:B))</f>
         <v/>
@@ -12794,95 +13034,167 @@
       <c r="H89" s="98"/>
       <c r="I89" s="103"/>
       <c r="J89" s="33"/>
-      <c r="K89" s="33"/>
+      <c r="K89" s="33" t="s">
+        <v>271</v>
+      </c>
       <c r="L89" s="33"/>
-      <c r="M89" s="67"/>
+      <c r="M89" s="67" t="s">
+        <v>247</v>
+      </c>
       <c r="N89" s="92"/>
-      <c r="P89" s="92"/>
+      <c r="P89" s="92" t="s">
+        <v>340</v>
+      </c>
       <c r="AI89" s="91"/>
     </row>
-    <row r="90" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="33" t="str">
+    <row r="90" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="33" t="e">
         <f>IF(ISBLANK(E90),"",_xlfn.XLOOKUP(E90,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="B90" s="33"/>
-      <c r="C90" s="33"/>
-      <c r="D90" s="54"/>
-      <c r="E90" s="91"/>
-      <c r="F90" s="54"/>
+        <v>#N/A</v>
+      </c>
+      <c r="B90" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C90" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="D90" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E90" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="F90" s="54" t="s">
+        <v>637</v>
+      </c>
       <c r="G90" s="33" t="str">
         <f>IF(ISBLANK(H90),"",_xlfn.XLOOKUP(H90,Info!A:A,Info!B:B))</f>
         <v/>
       </c>
-      <c r="H90" s="98"/>
-      <c r="I90" s="103"/>
       <c r="J90" s="33"/>
-      <c r="K90" s="33"/>
+      <c r="K90" s="33" t="s">
+        <v>512</v>
+      </c>
       <c r="L90" s="33"/>
-      <c r="M90" s="67"/>
+      <c r="M90" s="67" t="s">
+        <v>247</v>
+      </c>
       <c r="N90" s="92"/>
-      <c r="P90" s="92"/>
+      <c r="P90" s="92" t="s">
+        <v>340</v>
+      </c>
       <c r="AI90" s="91"/>
     </row>
-    <row r="91" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="33" t="str">
+    <row r="91" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="33" t="e">
         <f>IF(ISBLANK(E91),"",_xlfn.XLOOKUP(E91,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="B91" s="33"/>
-      <c r="C91" s="33"/>
-      <c r="D91" s="54"/>
-      <c r="E91" s="91"/>
-      <c r="F91" s="54"/>
-      <c r="G91" s="33" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B91" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C91" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="D91" s="54" t="s">
+        <v>242</v>
+      </c>
+      <c r="E91" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="F91" s="54" t="s">
+        <v>638</v>
+      </c>
+      <c r="G91" s="33">
         <f>IF(ISBLANK(H91),"",_xlfn.XLOOKUP(H91,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H91" s="98"/>
+        <v>13</v>
+      </c>
+      <c r="H91" s="98">
+        <v>46143</v>
+      </c>
       <c r="I91" s="103"/>
-      <c r="J91" s="33"/>
-      <c r="K91" s="33"/>
-      <c r="L91" s="33"/>
-      <c r="M91" s="67"/>
+      <c r="J91" s="33">
+        <v>15</v>
+      </c>
+      <c r="K91" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="L91" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M91" s="67" t="s">
+        <v>247</v>
+      </c>
       <c r="N91" s="92"/>
-      <c r="P91" s="92"/>
+      <c r="P91" s="92" t="s">
+        <v>258</v>
+      </c>
       <c r="AI91" s="91"/>
     </row>
-    <row r="92" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="33" t="str">
+    <row r="92" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="33" t="e">
         <f>IF(ISBLANK(E92),"",_xlfn.XLOOKUP(E92,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="B92" s="33"/>
-      <c r="C92" s="33"/>
-      <c r="D92" s="54"/>
-      <c r="E92" s="91"/>
-      <c r="F92" s="54"/>
+        <v>#N/A</v>
+      </c>
+      <c r="B92" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C92" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="D92" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E92" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="F92" s="54" t="s">
+        <v>599</v>
+      </c>
       <c r="G92" s="33" t="str">
         <f>IF(ISBLANK(H92),"",_xlfn.XLOOKUP(H92,Info!A:A,Info!B:B))</f>
         <v/>
       </c>
       <c r="H92" s="98"/>
       <c r="I92" s="103"/>
-      <c r="J92" s="33"/>
-      <c r="K92" s="33"/>
-      <c r="L92" s="33"/>
-      <c r="M92" s="67"/>
+      <c r="J92" s="33">
+        <v>30</v>
+      </c>
+      <c r="K92" s="33" t="s">
+        <v>642</v>
+      </c>
+      <c r="L92" s="33" t="s">
+        <v>596</v>
+      </c>
+      <c r="M92" s="67" t="s">
+        <v>247</v>
+      </c>
       <c r="N92" s="92"/>
-      <c r="P92" s="92"/>
+      <c r="P92" s="92" t="s">
+        <v>600</v>
+      </c>
       <c r="AI92" s="91"/>
     </row>
-    <row r="93" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="33" t="str">
+    <row r="93" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="33" t="e">
         <f>IF(ISBLANK(E93),"",_xlfn.XLOOKUP(E93,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="B93" s="33"/>
-      <c r="C93" s="33"/>
-      <c r="D93" s="54"/>
-      <c r="E93" s="91"/>
-      <c r="F93" s="54"/>
+        <v>#N/A</v>
+      </c>
+      <c r="B93" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C93" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="D93" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E93" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="F93" s="54" t="s">
+        <v>676</v>
+      </c>
       <c r="G93" s="33" t="str">
         <f>IF(ISBLANK(H93),"",_xlfn.XLOOKUP(H93,Info!A:A,Info!B:B))</f>
         <v/>
@@ -12890,14 +13202,20 @@
       <c r="H93" s="98"/>
       <c r="I93" s="103"/>
       <c r="J93" s="33"/>
-      <c r="K93" s="33"/>
-      <c r="L93" s="33"/>
-      <c r="M93" s="67"/>
+      <c r="K93" s="33" t="s">
+        <v>677</v>
+      </c>
+      <c r="L93" s="33" t="s">
+        <v>677</v>
+      </c>
+      <c r="M93" s="67" t="s">
+        <v>247</v>
+      </c>
       <c r="N93" s="92"/>
       <c r="P93" s="92"/>
       <c r="AI93" s="91"/>
     </row>
-    <row r="94" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="33" t="str">
         <f>IF(ISBLANK(E94),"",_xlfn.XLOOKUP(E94,Info!A:A,Info!B:B))</f>
         <v/>
@@ -12921,7 +13239,7 @@
       <c r="P94" s="92"/>
       <c r="AI94" s="91"/>
     </row>
-    <row r="95" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="33" t="str">
         <f>IF(ISBLANK(E95),"",_xlfn.XLOOKUP(E95,Info!A:A,Info!B:B))</f>
         <v/>
@@ -12945,7 +13263,7 @@
       <c r="P95" s="92"/>
       <c r="AI95" s="91"/>
     </row>
-    <row r="96" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="33" t="str">
         <f>IF(ISBLANK(E96),"",_xlfn.XLOOKUP(E96,Info!A:A,Info!B:B))</f>
         <v/>
@@ -12969,7 +13287,7 @@
       <c r="P96" s="92"/>
       <c r="AI96" s="91"/>
     </row>
-    <row r="97" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="33" t="str">
         <f>IF(ISBLANK(E97),"",_xlfn.XLOOKUP(E97,Info!A:A,Info!B:B))</f>
         <v/>
@@ -12993,7 +13311,7 @@
       <c r="P97" s="92"/>
       <c r="AI97" s="91"/>
     </row>
-    <row r="98" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="33" t="str">
         <f>IF(ISBLANK(E98),"",_xlfn.XLOOKUP(E98,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13017,7 +13335,7 @@
       <c r="P98" s="92"/>
       <c r="AI98" s="91"/>
     </row>
-    <row r="99" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="33" t="str">
         <f>IF(ISBLANK(E99),"",_xlfn.XLOOKUP(E99,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13041,7 +13359,7 @@
       <c r="P99" s="92"/>
       <c r="AI99" s="91"/>
     </row>
-    <row r="100" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="33" t="str">
         <f>IF(ISBLANK(E100),"",_xlfn.XLOOKUP(E100,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13065,7 +13383,7 @@
       <c r="P100" s="92"/>
       <c r="AI100" s="91"/>
     </row>
-    <row r="101" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="33" t="str">
         <f>IF(ISBLANK(E101),"",_xlfn.XLOOKUP(E101,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13089,7 +13407,7 @@
       <c r="P101" s="92"/>
       <c r="AI101" s="91"/>
     </row>
-    <row r="102" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="33" t="str">
         <f>IF(ISBLANK(E102),"",_xlfn.XLOOKUP(E102,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13113,7 +13431,7 @@
       <c r="P102" s="92"/>
       <c r="AI102" s="91"/>
     </row>
-    <row r="103" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="33" t="str">
         <f>IF(ISBLANK(E103),"",_xlfn.XLOOKUP(E103,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13137,7 +13455,7 @@
       <c r="P103" s="92"/>
       <c r="AI103" s="91"/>
     </row>
-    <row r="104" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="33" t="str">
         <f>IF(ISBLANK(E104),"",_xlfn.XLOOKUP(E104,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13161,7 +13479,7 @@
       <c r="P104" s="92"/>
       <c r="AI104" s="91"/>
     </row>
-    <row r="105" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="33" t="str">
         <f>IF(ISBLANK(E105),"",_xlfn.XLOOKUP(E105,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13185,7 +13503,7 @@
       <c r="P105" s="92"/>
       <c r="AI105" s="91"/>
     </row>
-    <row r="106" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="33" t="str">
         <f>IF(ISBLANK(E106),"",_xlfn.XLOOKUP(E106,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13209,7 +13527,7 @@
       <c r="P106" s="92"/>
       <c r="AI106" s="91"/>
     </row>
-    <row r="107" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="33" t="str">
         <f>IF(ISBLANK(E107),"",_xlfn.XLOOKUP(E107,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13233,7 +13551,7 @@
       <c r="P107" s="92"/>
       <c r="AI107" s="91"/>
     </row>
-    <row r="108" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="33" t="str">
         <f>IF(ISBLANK(E108),"",_xlfn.XLOOKUP(E108,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13257,7 +13575,7 @@
       <c r="P108" s="92"/>
       <c r="AI108" s="91"/>
     </row>
-    <row r="109" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="33" t="str">
         <f>IF(ISBLANK(E109),"",_xlfn.XLOOKUP(E109,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13281,7 +13599,7 @@
       <c r="P109" s="92"/>
       <c r="AI109" s="91"/>
     </row>
-    <row r="110" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="33" t="str">
         <f>IF(ISBLANK(E110),"",_xlfn.XLOOKUP(E110,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13305,7 +13623,7 @@
       <c r="P110" s="92"/>
       <c r="AI110" s="91"/>
     </row>
-    <row r="111" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="33" t="str">
         <f>IF(ISBLANK(E111),"",_xlfn.XLOOKUP(E111,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13329,7 +13647,7 @@
       <c r="P111" s="92"/>
       <c r="AI111" s="91"/>
     </row>
-    <row r="112" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="33" t="str">
         <f>IF(ISBLANK(E112),"",_xlfn.XLOOKUP(E112,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13353,7 +13671,7 @@
       <c r="P112" s="92"/>
       <c r="AI112" s="91"/>
     </row>
-    <row r="113" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="33" t="str">
         <f>IF(ISBLANK(E113),"",_xlfn.XLOOKUP(E113,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13377,7 +13695,7 @@
       <c r="P113" s="92"/>
       <c r="AI113" s="91"/>
     </row>
-    <row r="114" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="33" t="str">
         <f>IF(ISBLANK(E114),"",_xlfn.XLOOKUP(E114,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13401,7 +13719,7 @@
       <c r="P114" s="92"/>
       <c r="AI114" s="91"/>
     </row>
-    <row r="115" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="33" t="str">
         <f>IF(ISBLANK(E115),"",_xlfn.XLOOKUP(E115,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13425,7 +13743,7 @@
       <c r="P115" s="92"/>
       <c r="AI115" s="91"/>
     </row>
-    <row r="116" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="33" t="str">
         <f>IF(ISBLANK(E116),"",_xlfn.XLOOKUP(E116,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13449,7 +13767,7 @@
       <c r="P116" s="92"/>
       <c r="AI116" s="91"/>
     </row>
-    <row r="117" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="33" t="str">
         <f>IF(ISBLANK(E117),"",_xlfn.XLOOKUP(E117,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13473,7 +13791,7 @@
       <c r="P117" s="92"/>
       <c r="AI117" s="91"/>
     </row>
-    <row r="118" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="33" t="str">
         <f>IF(ISBLANK(E118),"",_xlfn.XLOOKUP(E118,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13497,7 +13815,7 @@
       <c r="P118" s="92"/>
       <c r="AI118" s="91"/>
     </row>
-    <row r="119" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="33" t="str">
         <f>IF(ISBLANK(E119),"",_xlfn.XLOOKUP(E119,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13521,7 +13839,7 @@
       <c r="P119" s="92"/>
       <c r="AI119" s="91"/>
     </row>
-    <row r="120" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="33" t="str">
         <f>IF(ISBLANK(E120),"",_xlfn.XLOOKUP(E120,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13545,7 +13863,7 @@
       <c r="P120" s="92"/>
       <c r="AI120" s="91"/>
     </row>
-    <row r="121" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="33" t="str">
         <f>IF(ISBLANK(E121),"",_xlfn.XLOOKUP(E121,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13569,7 +13887,7 @@
       <c r="P121" s="92"/>
       <c r="AI121" s="91"/>
     </row>
-    <row r="122" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="33" t="str">
         <f>IF(ISBLANK(E122),"",_xlfn.XLOOKUP(E122,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13593,7 +13911,7 @@
       <c r="P122" s="92"/>
       <c r="AI122" s="91"/>
     </row>
-    <row r="123" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="33" t="str">
         <f>IF(ISBLANK(E123),"",_xlfn.XLOOKUP(E123,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13617,7 +13935,7 @@
       <c r="P123" s="92"/>
       <c r="AI123" s="91"/>
     </row>
-    <row r="124" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="33" t="str">
         <f>IF(ISBLANK(E124),"",_xlfn.XLOOKUP(E124,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13641,7 +13959,7 @@
       <c r="P124" s="92"/>
       <c r="AI124" s="91"/>
     </row>
-    <row r="125" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="33" t="str">
         <f>IF(ISBLANK(E125),"",_xlfn.XLOOKUP(E125,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13665,7 +13983,7 @@
       <c r="P125" s="92"/>
       <c r="AI125" s="91"/>
     </row>
-    <row r="126" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="33" t="str">
         <f>IF(ISBLANK(E126),"",_xlfn.XLOOKUP(E126,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13689,7 +14007,7 @@
       <c r="P126" s="92"/>
       <c r="AI126" s="91"/>
     </row>
-    <row r="127" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="33" t="str">
         <f>IF(ISBLANK(E127),"",_xlfn.XLOOKUP(E127,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13713,7 +14031,7 @@
       <c r="P127" s="92"/>
       <c r="AI127" s="91"/>
     </row>
-    <row r="128" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="33" t="str">
         <f>IF(ISBLANK(E128),"",_xlfn.XLOOKUP(E128,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13737,7 +14055,7 @@
       <c r="P128" s="92"/>
       <c r="AI128" s="91"/>
     </row>
-    <row r="129" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="33" t="str">
         <f>IF(ISBLANK(E129),"",_xlfn.XLOOKUP(E129,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13761,7 +14079,7 @@
       <c r="P129" s="92"/>
       <c r="AI129" s="91"/>
     </row>
-    <row r="130" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="33" t="str">
         <f>IF(ISBLANK(E130),"",_xlfn.XLOOKUP(E130,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13785,7 +14103,7 @@
       <c r="P130" s="92"/>
       <c r="AI130" s="91"/>
     </row>
-    <row r="131" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="33" t="str">
         <f>IF(ISBLANK(E131),"",_xlfn.XLOOKUP(E131,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13809,7 +14127,7 @@
       <c r="P131" s="92"/>
       <c r="AI131" s="91"/>
     </row>
-    <row r="132" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="33" t="str">
         <f>IF(ISBLANK(E132),"",_xlfn.XLOOKUP(E132,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13833,7 +14151,7 @@
       <c r="P132" s="92"/>
       <c r="AI132" s="91"/>
     </row>
-    <row r="133" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="33" t="str">
         <f>IF(ISBLANK(E133),"",_xlfn.XLOOKUP(E133,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13857,7 +14175,7 @@
       <c r="P133" s="92"/>
       <c r="AI133" s="91"/>
     </row>
-    <row r="134" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="33" t="str">
         <f>IF(ISBLANK(E134),"",_xlfn.XLOOKUP(E134,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13881,7 +14199,7 @@
       <c r="P134" s="92"/>
       <c r="AI134" s="91"/>
     </row>
-    <row r="135" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="33" t="str">
         <f>IF(ISBLANK(E135),"",_xlfn.XLOOKUP(E135,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13905,7 +14223,7 @@
       <c r="P135" s="92"/>
       <c r="AI135" s="91"/>
     </row>
-    <row r="136" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="33" t="str">
         <f>IF(ISBLANK(E136),"",_xlfn.XLOOKUP(E136,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13929,7 +14247,7 @@
       <c r="P136" s="92"/>
       <c r="AI136" s="91"/>
     </row>
-    <row r="137" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="33" t="str">
         <f>IF(ISBLANK(E137),"",_xlfn.XLOOKUP(E137,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13953,7 +14271,7 @@
       <c r="P137" s="92"/>
       <c r="AI137" s="91"/>
     </row>
-    <row r="138" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="33" t="str">
         <f>IF(ISBLANK(E138),"",_xlfn.XLOOKUP(E138,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13977,7 +14295,7 @@
       <c r="P138" s="92"/>
       <c r="AI138" s="91"/>
     </row>
-    <row r="139" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="33" t="str">
         <f>IF(ISBLANK(E139),"",_xlfn.XLOOKUP(E139,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14001,7 +14319,7 @@
       <c r="P139" s="92"/>
       <c r="AI139" s="91"/>
     </row>
-    <row r="140" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="33" t="str">
         <f>IF(ISBLANK(E140),"",_xlfn.XLOOKUP(E140,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14025,7 +14343,7 @@
       <c r="P140" s="92"/>
       <c r="AI140" s="91"/>
     </row>
-    <row r="141" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="33" t="str">
         <f>IF(ISBLANK(E141),"",_xlfn.XLOOKUP(E141,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14049,7 +14367,7 @@
       <c r="P141" s="92"/>
       <c r="AI141" s="91"/>
     </row>
-    <row r="142" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="33" t="str">
         <f>IF(ISBLANK(E142),"",_xlfn.XLOOKUP(E142,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14073,7 +14391,7 @@
       <c r="P142" s="92"/>
       <c r="AI142" s="91"/>
     </row>
-    <row r="143" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="33" t="str">
         <f>IF(ISBLANK(E143),"",_xlfn.XLOOKUP(E143,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14097,7 +14415,7 @@
       <c r="P143" s="92"/>
       <c r="AI143" s="91"/>
     </row>
-    <row r="144" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="33" t="str">
         <f>IF(ISBLANK(E144),"",_xlfn.XLOOKUP(E144,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14121,7 +14439,7 @@
       <c r="P144" s="92"/>
       <c r="AI144" s="91"/>
     </row>
-    <row r="145" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="33" t="str">
         <f>IF(ISBLANK(E145),"",_xlfn.XLOOKUP(E145,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14145,7 +14463,7 @@
       <c r="P145" s="92"/>
       <c r="AI145" s="91"/>
     </row>
-    <row r="146" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="33" t="str">
         <f>IF(ISBLANK(E146),"",_xlfn.XLOOKUP(E146,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14169,7 +14487,7 @@
       <c r="P146" s="92"/>
       <c r="AI146" s="91"/>
     </row>
-    <row r="147" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="33" t="str">
         <f>IF(ISBLANK(E147),"",_xlfn.XLOOKUP(E147,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14193,7 +14511,7 @@
       <c r="P147" s="92"/>
       <c r="AI147" s="91"/>
     </row>
-    <row r="148" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="33" t="str">
         <f>IF(ISBLANK(E148),"",_xlfn.XLOOKUP(E148,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14217,7 +14535,7 @@
       <c r="P148" s="92"/>
       <c r="AI148" s="91"/>
     </row>
-    <row r="149" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="33" t="str">
         <f>IF(ISBLANK(E149),"",_xlfn.XLOOKUP(E149,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14241,7 +14559,7 @@
       <c r="P149" s="92"/>
       <c r="AI149" s="91"/>
     </row>
-    <row r="150" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="33" t="str">
         <f>IF(ISBLANK(E150),"",_xlfn.XLOOKUP(E150,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14265,7 +14583,7 @@
       <c r="P150" s="92"/>
       <c r="AI150" s="91"/>
     </row>
-    <row r="151" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="33" t="str">
         <f>IF(ISBLANK(E151),"",_xlfn.XLOOKUP(E151,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14289,7 +14607,7 @@
       <c r="P151" s="92"/>
       <c r="AI151" s="91"/>
     </row>
-    <row r="152" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="33" t="str">
         <f>IF(ISBLANK(E152),"",_xlfn.XLOOKUP(E152,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14313,7 +14631,7 @@
       <c r="P152" s="92"/>
       <c r="AI152" s="91"/>
     </row>
-    <row r="153" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="33" t="str">
         <f>IF(ISBLANK(E153),"",_xlfn.XLOOKUP(E153,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14337,7 +14655,7 @@
       <c r="P153" s="92"/>
       <c r="AI153" s="91"/>
     </row>
-    <row r="154" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="33" t="str">
         <f>IF(ISBLANK(E154),"",_xlfn.XLOOKUP(E154,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14361,7 +14679,7 @@
       <c r="P154" s="92"/>
       <c r="AI154" s="91"/>
     </row>
-    <row r="155" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="33" t="str">
         <f>IF(ISBLANK(E155),"",_xlfn.XLOOKUP(E155,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14385,7 +14703,7 @@
       <c r="P155" s="92"/>
       <c r="AI155" s="91"/>
     </row>
-    <row r="156" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="33" t="str">
         <f>IF(ISBLANK(E156),"",_xlfn.XLOOKUP(E156,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14409,7 +14727,7 @@
       <c r="P156" s="92"/>
       <c r="AI156" s="91"/>
     </row>
-    <row r="157" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="33" t="str">
         <f>IF(ISBLANK(E157),"",_xlfn.XLOOKUP(E157,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14433,7 +14751,7 @@
       <c r="P157" s="92"/>
       <c r="AI157" s="91"/>
     </row>
-    <row r="158" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="33" t="str">
         <f>IF(ISBLANK(E158),"",_xlfn.XLOOKUP(E158,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14457,7 +14775,7 @@
       <c r="P158" s="92"/>
       <c r="AI158" s="91"/>
     </row>
-    <row r="159" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="33" t="str">
         <f>IF(ISBLANK(E159),"",_xlfn.XLOOKUP(E159,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14481,7 +14799,7 @@
       <c r="P159" s="92"/>
       <c r="AI159" s="91"/>
     </row>
-    <row r="160" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="33" t="str">
         <f>IF(ISBLANK(E160),"",_xlfn.XLOOKUP(E160,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14505,7 +14823,7 @@
       <c r="P160" s="92"/>
       <c r="AI160" s="91"/>
     </row>
-    <row r="161" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="33" t="str">
         <f>IF(ISBLANK(E161),"",_xlfn.XLOOKUP(E161,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14529,7 +14847,7 @@
       <c r="P161" s="92"/>
       <c r="AI161" s="91"/>
     </row>
-    <row r="162" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="33" t="str">
         <f>IF(ISBLANK(E162),"",_xlfn.XLOOKUP(E162,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14553,7 +14871,7 @@
       <c r="P162" s="92"/>
       <c r="AI162" s="91"/>
     </row>
-    <row r="163" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="33" t="str">
         <f>IF(ISBLANK(E163),"",_xlfn.XLOOKUP(E163,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14577,7 +14895,7 @@
       <c r="P163" s="92"/>
       <c r="AI163" s="91"/>
     </row>
-    <row r="164" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="33" t="str">
         <f>IF(ISBLANK(E164),"",_xlfn.XLOOKUP(E164,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14601,7 +14919,7 @@
       <c r="P164" s="92"/>
       <c r="AI164" s="91"/>
     </row>
-    <row r="165" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="33" t="str">
         <f>IF(ISBLANK(E165),"",_xlfn.XLOOKUP(E165,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14625,7 +14943,7 @@
       <c r="P165" s="92"/>
       <c r="AI165" s="91"/>
     </row>
-    <row r="166" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="33" t="str">
         <f>IF(ISBLANK(E166),"",_xlfn.XLOOKUP(E166,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14649,7 +14967,7 @@
       <c r="P166" s="92"/>
       <c r="AI166" s="91"/>
     </row>
-    <row r="167" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="33" t="str">
         <f>IF(ISBLANK(E167),"",_xlfn.XLOOKUP(E167,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14673,7 +14991,7 @@
       <c r="P167" s="92"/>
       <c r="AI167" s="91"/>
     </row>
-    <row r="168" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="33" t="str">
         <f>IF(ISBLANK(E168),"",_xlfn.XLOOKUP(E168,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14697,7 +15015,7 @@
       <c r="P168" s="92"/>
       <c r="AI168" s="91"/>
     </row>
-    <row r="169" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="33" t="str">
         <f>IF(ISBLANK(E169),"",_xlfn.XLOOKUP(E169,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14721,7 +15039,7 @@
       <c r="P169" s="92"/>
       <c r="AI169" s="91"/>
     </row>
-    <row r="170" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="33" t="str">
         <f>IF(ISBLANK(E170),"",_xlfn.XLOOKUP(E170,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14745,7 +15063,7 @@
       <c r="P170" s="92"/>
       <c r="AI170" s="91"/>
     </row>
-    <row r="171" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="33" t="str">
         <f>IF(ISBLANK(E171),"",_xlfn.XLOOKUP(E171,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14769,7 +15087,7 @@
       <c r="P171" s="92"/>
       <c r="AI171" s="91"/>
     </row>
-    <row r="172" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="33" t="str">
         <f>IF(ISBLANK(E172),"",_xlfn.XLOOKUP(E172,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14793,7 +15111,7 @@
       <c r="P172" s="92"/>
       <c r="AI172" s="91"/>
     </row>
-    <row r="173" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="33" t="str">
         <f>IF(ISBLANK(E173),"",_xlfn.XLOOKUP(E173,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14817,7 +15135,7 @@
       <c r="P173" s="92"/>
       <c r="AI173" s="91"/>
     </row>
-    <row r="174" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="33" t="str">
         <f>IF(ISBLANK(E174),"",_xlfn.XLOOKUP(E174,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14841,7 +15159,7 @@
       <c r="P174" s="92"/>
       <c r="AI174" s="91"/>
     </row>
-    <row r="175" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="33" t="str">
         <f>IF(ISBLANK(E175),"",_xlfn.XLOOKUP(E175,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14865,7 +15183,7 @@
       <c r="P175" s="92"/>
       <c r="AI175" s="91"/>
     </row>
-    <row r="176" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="33" t="str">
         <f>IF(ISBLANK(E176),"",_xlfn.XLOOKUP(E176,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14889,7 +15207,7 @@
       <c r="P176" s="92"/>
       <c r="AI176" s="91"/>
     </row>
-    <row r="177" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="33" t="str">
         <f>IF(ISBLANK(E177),"",_xlfn.XLOOKUP(E177,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14913,7 +15231,7 @@
       <c r="P177" s="92"/>
       <c r="AI177" s="91"/>
     </row>
-    <row r="178" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="33" t="str">
         <f>IF(ISBLANK(E178),"",_xlfn.XLOOKUP(E178,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14937,7 +15255,7 @@
       <c r="P178" s="92"/>
       <c r="AI178" s="91"/>
     </row>
-    <row r="179" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="33" t="str">
         <f>IF(ISBLANK(E179),"",_xlfn.XLOOKUP(E179,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14961,7 +15279,7 @@
       <c r="P179" s="92"/>
       <c r="AI179" s="91"/>
     </row>
-    <row r="180" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="33" t="str">
         <f>IF(ISBLANK(E180),"",_xlfn.XLOOKUP(E180,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14985,7 +15303,7 @@
       <c r="P180" s="92"/>
       <c r="AI180" s="91"/>
     </row>
-    <row r="181" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="33" t="str">
         <f>IF(ISBLANK(E181),"",_xlfn.XLOOKUP(E181,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15009,7 +15327,7 @@
       <c r="P181" s="92"/>
       <c r="AI181" s="91"/>
     </row>
-    <row r="182" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="33" t="str">
         <f>IF(ISBLANK(E182),"",_xlfn.XLOOKUP(E182,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15033,7 +15351,7 @@
       <c r="P182" s="92"/>
       <c r="AI182" s="91"/>
     </row>
-    <row r="183" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="33" t="str">
         <f>IF(ISBLANK(E183),"",_xlfn.XLOOKUP(E183,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15057,7 +15375,7 @@
       <c r="P183" s="92"/>
       <c r="AI183" s="91"/>
     </row>
-    <row r="184" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="33" t="str">
         <f>IF(ISBLANK(E184),"",_xlfn.XLOOKUP(E184,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15081,7 +15399,7 @@
       <c r="P184" s="92"/>
       <c r="AI184" s="91"/>
     </row>
-    <row r="185" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="33" t="str">
         <f>IF(ISBLANK(E185),"",_xlfn.XLOOKUP(E185,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15105,7 +15423,7 @@
       <c r="P185" s="92"/>
       <c r="AI185" s="91"/>
     </row>
-    <row r="186" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="33" t="str">
         <f>IF(ISBLANK(E186),"",_xlfn.XLOOKUP(E186,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15129,7 +15447,7 @@
       <c r="P186" s="92"/>
       <c r="AI186" s="91"/>
     </row>
-    <row r="187" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="33" t="str">
         <f>IF(ISBLANK(E187),"",_xlfn.XLOOKUP(E187,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15153,7 +15471,7 @@
       <c r="P187" s="92"/>
       <c r="AI187" s="91"/>
     </row>
-    <row r="188" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="33" t="str">
         <f>IF(ISBLANK(E188),"",_xlfn.XLOOKUP(E188,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15177,7 +15495,7 @@
       <c r="P188" s="92"/>
       <c r="AI188" s="91"/>
     </row>
-    <row r="189" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="33" t="str">
         <f>IF(ISBLANK(E189),"",_xlfn.XLOOKUP(E189,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15201,7 +15519,7 @@
       <c r="P189" s="92"/>
       <c r="AI189" s="91"/>
     </row>
-    <row r="190" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="33" t="str">
         <f>IF(ISBLANK(E190),"",_xlfn.XLOOKUP(E190,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15225,7 +15543,7 @@
       <c r="P190" s="92"/>
       <c r="AI190" s="91"/>
     </row>
-    <row r="191" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="33" t="str">
         <f>IF(ISBLANK(E191),"",_xlfn.XLOOKUP(E191,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15249,7 +15567,7 @@
       <c r="P191" s="92"/>
       <c r="AI191" s="91"/>
     </row>
-    <row r="192" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="33" t="str">
         <f>IF(ISBLANK(E192),"",_xlfn.XLOOKUP(E192,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15273,7 +15591,7 @@
       <c r="P192" s="92"/>
       <c r="AI192" s="91"/>
     </row>
-    <row r="193" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="33" t="str">
         <f>IF(ISBLANK(E193),"",_xlfn.XLOOKUP(E193,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15297,7 +15615,7 @@
       <c r="P193" s="92"/>
       <c r="AI193" s="91"/>
     </row>
-    <row r="194" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="33" t="str">
         <f>IF(ISBLANK(E194),"",_xlfn.XLOOKUP(E194,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15321,7 +15639,7 @@
       <c r="P194" s="92"/>
       <c r="AI194" s="91"/>
     </row>
-    <row r="195" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="33" t="str">
         <f>IF(ISBLANK(E195),"",_xlfn.XLOOKUP(E195,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15345,7 +15663,7 @@
       <c r="P195" s="92"/>
       <c r="AI195" s="91"/>
     </row>
-    <row r="196" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="33" t="str">
         <f>IF(ISBLANK(E196),"",_xlfn.XLOOKUP(E196,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15369,7 +15687,7 @@
       <c r="P196" s="92"/>
       <c r="AI196" s="91"/>
     </row>
-    <row r="197" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="33" t="str">
         <f>IF(ISBLANK(E197),"",_xlfn.XLOOKUP(E197,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15393,7 +15711,7 @@
       <c r="P197" s="92"/>
       <c r="AI197" s="91"/>
     </row>
-    <row r="198" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="33" t="str">
         <f>IF(ISBLANK(E198),"",_xlfn.XLOOKUP(E198,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15417,7 +15735,7 @@
       <c r="P198" s="92"/>
       <c r="AI198" s="91"/>
     </row>
-    <row r="199" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="33" t="str">
         <f>IF(ISBLANK(E199),"",_xlfn.XLOOKUP(E199,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15441,7 +15759,7 @@
       <c r="P199" s="92"/>
       <c r="AI199" s="91"/>
     </row>
-    <row r="200" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="33" t="str">
         <f>IF(ISBLANK(E200),"",_xlfn.XLOOKUP(E200,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15465,7 +15783,7 @@
       <c r="P200" s="92"/>
       <c r="AI200" s="91"/>
     </row>
-    <row r="201" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="33" t="str">
         <f>IF(ISBLANK(E201),"",_xlfn.XLOOKUP(E201,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15489,7 +15807,7 @@
       <c r="P201" s="92"/>
       <c r="AI201" s="91"/>
     </row>
-    <row r="202" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="33" t="str">
         <f>IF(ISBLANK(E202),"",_xlfn.XLOOKUP(E202,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15513,7 +15831,7 @@
       <c r="P202" s="92"/>
       <c r="AI202" s="91"/>
     </row>
-    <row r="203" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="33" t="str">
         <f>IF(ISBLANK(E203),"",_xlfn.XLOOKUP(E203,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15537,7 +15855,7 @@
       <c r="P203" s="92"/>
       <c r="AI203" s="91"/>
     </row>
-    <row r="204" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="33" t="str">
         <f>IF(ISBLANK(E204),"",_xlfn.XLOOKUP(E204,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15561,7 +15879,7 @@
       <c r="P204" s="92"/>
       <c r="AI204" s="91"/>
     </row>
-    <row r="205" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="33" t="str">
         <f>IF(ISBLANK(E205),"",_xlfn.XLOOKUP(E205,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15585,7 +15903,7 @@
       <c r="P205" s="92"/>
       <c r="AI205" s="91"/>
     </row>
-    <row r="206" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="33" t="str">
         <f>IF(ISBLANK(E206),"",_xlfn.XLOOKUP(E206,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15609,7 +15927,7 @@
       <c r="P206" s="92"/>
       <c r="AI206" s="91"/>
     </row>
-    <row r="207" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="33" t="str">
         <f>IF(ISBLANK(E207),"",_xlfn.XLOOKUP(E207,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15633,7 +15951,7 @@
       <c r="P207" s="92"/>
       <c r="AI207" s="91"/>
     </row>
-    <row r="208" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="33" t="str">
         <f>IF(ISBLANK(E208),"",_xlfn.XLOOKUP(E208,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15657,7 +15975,7 @@
       <c r="P208" s="92"/>
       <c r="AI208" s="91"/>
     </row>
-    <row r="209" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="33" t="str">
         <f>IF(ISBLANK(E209),"",_xlfn.XLOOKUP(E209,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15681,7 +15999,7 @@
       <c r="P209" s="92"/>
       <c r="AI209" s="91"/>
     </row>
-    <row r="210" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="33" t="str">
         <f>IF(ISBLANK(E210),"",_xlfn.XLOOKUP(E210,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15705,7 +16023,7 @@
       <c r="P210" s="92"/>
       <c r="AI210" s="91"/>
     </row>
-    <row r="211" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="33" t="str">
         <f>IF(ISBLANK(E211),"",_xlfn.XLOOKUP(E211,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15729,7 +16047,7 @@
       <c r="P211" s="92"/>
       <c r="AI211" s="91"/>
     </row>
-    <row r="212" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="33" t="str">
         <f>IF(ISBLANK(E212),"",_xlfn.XLOOKUP(E212,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15753,7 +16071,7 @@
       <c r="P212" s="92"/>
       <c r="AI212" s="91"/>
     </row>
-    <row r="213" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="33" t="str">
         <f>IF(ISBLANK(E213),"",_xlfn.XLOOKUP(E213,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15777,7 +16095,7 @@
       <c r="P213" s="92"/>
       <c r="AI213" s="91"/>
     </row>
-    <row r="214" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="33" t="str">
         <f>IF(ISBLANK(E214),"",_xlfn.XLOOKUP(E214,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15801,7 +16119,7 @@
       <c r="P214" s="92"/>
       <c r="AI214" s="91"/>
     </row>
-    <row r="215" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="33" t="str">
         <f>IF(ISBLANK(E215),"",_xlfn.XLOOKUP(E215,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15825,7 +16143,7 @@
       <c r="P215" s="92"/>
       <c r="AI215" s="91"/>
     </row>
-    <row r="216" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="33" t="str">
         <f>IF(ISBLANK(E216),"",_xlfn.XLOOKUP(E216,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15849,7 +16167,7 @@
       <c r="P216" s="92"/>
       <c r="AI216" s="91"/>
     </row>
-    <row r="217" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="33" t="str">
         <f>IF(ISBLANK(E217),"",_xlfn.XLOOKUP(E217,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15873,7 +16191,7 @@
       <c r="P217" s="92"/>
       <c r="AI217" s="91"/>
     </row>
-    <row r="218" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="33" t="str">
         <f>IF(ISBLANK(E218),"",_xlfn.XLOOKUP(E218,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15897,7 +16215,7 @@
       <c r="P218" s="92"/>
       <c r="AI218" s="91"/>
     </row>
-    <row r="219" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="33" t="str">
         <f>IF(ISBLANK(E219),"",_xlfn.XLOOKUP(E219,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15921,7 +16239,7 @@
       <c r="P219" s="92"/>
       <c r="AI219" s="91"/>
     </row>
-    <row r="220" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="33" t="str">
         <f>IF(ISBLANK(E220),"",_xlfn.XLOOKUP(E220,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15945,7 +16263,7 @@
       <c r="P220" s="92"/>
       <c r="AI220" s="91"/>
     </row>
-    <row r="221" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="33" t="str">
         <f>IF(ISBLANK(E221),"",_xlfn.XLOOKUP(E221,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15969,7 +16287,7 @@
       <c r="P221" s="92"/>
       <c r="AI221" s="91"/>
     </row>
-    <row r="222" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="33" t="str">
         <f>IF(ISBLANK(E222),"",_xlfn.XLOOKUP(E222,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15993,7 +16311,7 @@
       <c r="P222" s="92"/>
       <c r="AI222" s="91"/>
     </row>
-    <row r="223" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="33" t="str">
         <f>IF(ISBLANK(E223),"",_xlfn.XLOOKUP(E223,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16017,7 +16335,7 @@
       <c r="P223" s="92"/>
       <c r="AI223" s="91"/>
     </row>
-    <row r="224" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="33" t="str">
         <f>IF(ISBLANK(E224),"",_xlfn.XLOOKUP(E224,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16041,7 +16359,7 @@
       <c r="P224" s="92"/>
       <c r="AI224" s="91"/>
     </row>
-    <row r="225" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="33" t="str">
         <f>IF(ISBLANK(E225),"",_xlfn.XLOOKUP(E225,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16065,7 +16383,7 @@
       <c r="P225" s="92"/>
       <c r="AI225" s="91"/>
     </row>
-    <row r="226" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="33" t="str">
         <f>IF(ISBLANK(E226),"",_xlfn.XLOOKUP(E226,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16089,7 +16407,7 @@
       <c r="P226" s="92"/>
       <c r="AI226" s="91"/>
     </row>
-    <row r="227" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="33" t="str">
         <f>IF(ISBLANK(E227),"",_xlfn.XLOOKUP(E227,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16113,7 +16431,7 @@
       <c r="P227" s="92"/>
       <c r="AI227" s="91"/>
     </row>
-    <row r="228" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="33" t="str">
         <f>IF(ISBLANK(E228),"",_xlfn.XLOOKUP(E228,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16137,7 +16455,7 @@
       <c r="P228" s="92"/>
       <c r="AI228" s="91"/>
     </row>
-    <row r="229" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="33" t="str">
         <f>IF(ISBLANK(E229),"",_xlfn.XLOOKUP(E229,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16161,7 +16479,7 @@
       <c r="P229" s="92"/>
       <c r="AI229" s="91"/>
     </row>
-    <row r="230" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="33" t="str">
         <f>IF(ISBLANK(E230),"",_xlfn.XLOOKUP(E230,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16185,7 +16503,7 @@
       <c r="P230" s="92"/>
       <c r="AI230" s="91"/>
     </row>
-    <row r="231" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="33" t="str">
         <f>IF(ISBLANK(E231),"",_xlfn.XLOOKUP(E231,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16209,7 +16527,7 @@
       <c r="P231" s="92"/>
       <c r="AI231" s="91"/>
     </row>
-    <row r="232" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="33" t="str">
         <f>IF(ISBLANK(E232),"",_xlfn.XLOOKUP(E232,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16233,7 +16551,7 @@
       <c r="P232" s="92"/>
       <c r="AI232" s="91"/>
     </row>
-    <row r="233" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="33" t="str">
         <f>IF(ISBLANK(E233),"",_xlfn.XLOOKUP(E233,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16257,7 +16575,7 @@
       <c r="P233" s="92"/>
       <c r="AI233" s="91"/>
     </row>
-    <row r="234" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="33" t="str">
         <f>IF(ISBLANK(E234),"",_xlfn.XLOOKUP(E234,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16281,7 +16599,7 @@
       <c r="P234" s="92"/>
       <c r="AI234" s="91"/>
     </row>
-    <row r="235" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="33" t="str">
         <f>IF(ISBLANK(E235),"",_xlfn.XLOOKUP(E235,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16305,7 +16623,7 @@
       <c r="P235" s="92"/>
       <c r="AI235" s="91"/>
     </row>
-    <row r="236" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="33" t="str">
         <f>IF(ISBLANK(E236),"",_xlfn.XLOOKUP(E236,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16329,7 +16647,7 @@
       <c r="P236" s="92"/>
       <c r="AI236" s="91"/>
     </row>
-    <row r="237" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="33" t="str">
         <f>IF(ISBLANK(E237),"",_xlfn.XLOOKUP(E237,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16353,7 +16671,7 @@
       <c r="P237" s="92"/>
       <c r="AI237" s="91"/>
     </row>
-    <row r="238" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="33" t="str">
         <f>IF(ISBLANK(E238),"",_xlfn.XLOOKUP(E238,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16377,7 +16695,7 @@
       <c r="P238" s="92"/>
       <c r="AI238" s="91"/>
     </row>
-    <row r="239" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="33" t="str">
         <f>IF(ISBLANK(E239),"",_xlfn.XLOOKUP(E239,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16401,7 +16719,7 @@
       <c r="P239" s="92"/>
       <c r="AI239" s="91"/>
     </row>
-    <row r="240" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="33" t="str">
         <f>IF(ISBLANK(E240),"",_xlfn.XLOOKUP(E240,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16425,7 +16743,7 @@
       <c r="P240" s="92"/>
       <c r="AI240" s="91"/>
     </row>
-    <row r="241" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="33" t="str">
         <f>IF(ISBLANK(E241),"",_xlfn.XLOOKUP(E241,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16449,7 +16767,7 @@
       <c r="P241" s="92"/>
       <c r="AI241" s="91"/>
     </row>
-    <row r="242" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="33" t="str">
         <f>IF(ISBLANK(E242),"",_xlfn.XLOOKUP(E242,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16473,7 +16791,7 @@
       <c r="P242" s="92"/>
       <c r="AI242" s="91"/>
     </row>
-    <row r="243" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="33" t="str">
         <f>IF(ISBLANK(E243),"",_xlfn.XLOOKUP(E243,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16497,7 +16815,7 @@
       <c r="P243" s="92"/>
       <c r="AI243" s="91"/>
     </row>
-    <row r="244" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="33" t="str">
         <f>IF(ISBLANK(E244),"",_xlfn.XLOOKUP(E244,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16521,7 +16839,7 @@
       <c r="P244" s="92"/>
       <c r="AI244" s="91"/>
     </row>
-    <row r="245" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="33" t="str">
         <f>IF(ISBLANK(E245),"",_xlfn.XLOOKUP(E245,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16545,7 +16863,7 @@
       <c r="P245" s="92"/>
       <c r="AI245" s="91"/>
     </row>
-    <row r="246" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="33" t="str">
         <f>IF(ISBLANK(E246),"",_xlfn.XLOOKUP(E246,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16569,7 +16887,7 @@
       <c r="P246" s="92"/>
       <c r="AI246" s="91"/>
     </row>
-    <row r="247" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="33" t="str">
         <f>IF(ISBLANK(E247),"",_xlfn.XLOOKUP(E247,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16593,7 +16911,7 @@
       <c r="P247" s="92"/>
       <c r="AI247" s="91"/>
     </row>
-    <row r="248" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="33" t="str">
         <f>IF(ISBLANK(E248),"",_xlfn.XLOOKUP(E248,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16617,7 +16935,7 @@
       <c r="P248" s="92"/>
       <c r="AI248" s="91"/>
     </row>
-    <row r="249" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="33" t="str">
         <f>IF(ISBLANK(E249),"",_xlfn.XLOOKUP(E249,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16641,7 +16959,7 @@
       <c r="P249" s="92"/>
       <c r="AI249" s="91"/>
     </row>
-    <row r="250" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="33" t="str">
         <f>IF(ISBLANK(E250),"",_xlfn.XLOOKUP(E250,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16665,7 +16983,7 @@
       <c r="P250" s="92"/>
       <c r="AI250" s="91"/>
     </row>
-    <row r="251" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="33" t="str">
         <f>IF(ISBLANK(E251),"",_xlfn.XLOOKUP(E251,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16689,7 +17007,7 @@
       <c r="P251" s="92"/>
       <c r="AI251" s="91"/>
     </row>
-    <row r="252" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="33" t="str">
         <f>IF(ISBLANK(E252),"",_xlfn.XLOOKUP(E252,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16713,7 +17031,7 @@
       <c r="P252" s="92"/>
       <c r="AI252" s="91"/>
     </row>
-    <row r="253" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="33" t="str">
         <f>IF(ISBLANK(E253),"",_xlfn.XLOOKUP(E253,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16737,7 +17055,7 @@
       <c r="P253" s="92"/>
       <c r="AI253" s="91"/>
     </row>
-    <row r="254" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="33" t="str">
         <f>IF(ISBLANK(E254),"",_xlfn.XLOOKUP(E254,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16761,7 +17079,7 @@
       <c r="P254" s="92"/>
       <c r="AI254" s="91"/>
     </row>
-    <row r="255" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="33" t="str">
         <f>IF(ISBLANK(E255),"",_xlfn.XLOOKUP(E255,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16785,7 +17103,7 @@
       <c r="P255" s="92"/>
       <c r="AI255" s="91"/>
     </row>
-    <row r="256" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="33" t="str">
         <f>IF(ISBLANK(E256),"",_xlfn.XLOOKUP(E256,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16809,7 +17127,7 @@
       <c r="P256" s="92"/>
       <c r="AI256" s="91"/>
     </row>
-    <row r="257" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="33" t="str">
         <f>IF(ISBLANK(E257),"",_xlfn.XLOOKUP(E257,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16833,7 +17151,7 @@
       <c r="P257" s="92"/>
       <c r="AI257" s="91"/>
     </row>
-    <row r="258" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="33" t="str">
         <f>IF(ISBLANK(E258),"",_xlfn.XLOOKUP(E258,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16857,7 +17175,7 @@
       <c r="P258" s="92"/>
       <c r="AI258" s="91"/>
     </row>
-    <row r="259" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="33" t="str">
         <f>IF(ISBLANK(E259),"",_xlfn.XLOOKUP(E259,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16881,7 +17199,7 @@
       <c r="P259" s="92"/>
       <c r="AI259" s="91"/>
     </row>
-    <row r="260" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="33" t="str">
         <f>IF(ISBLANK(E260),"",_xlfn.XLOOKUP(E260,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16905,7 +17223,7 @@
       <c r="P260" s="92"/>
       <c r="AI260" s="91"/>
     </row>
-    <row r="261" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="33" t="str">
         <f>IF(ISBLANK(E261),"",_xlfn.XLOOKUP(E261,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16929,7 +17247,7 @@
       <c r="P261" s="92"/>
       <c r="AI261" s="91"/>
     </row>
-    <row r="262" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="33" t="str">
         <f>IF(ISBLANK(E262),"",_xlfn.XLOOKUP(E262,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16953,7 +17271,7 @@
       <c r="P262" s="92"/>
       <c r="AI262" s="91"/>
     </row>
-    <row r="263" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="33" t="str">
         <f>IF(ISBLANK(E263),"",_xlfn.XLOOKUP(E263,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16977,7 +17295,7 @@
       <c r="P263" s="92"/>
       <c r="AI263" s="91"/>
     </row>
-    <row r="264" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="33" t="str">
         <f>IF(ISBLANK(E264),"",_xlfn.XLOOKUP(E264,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17001,7 +17319,7 @@
       <c r="P264" s="92"/>
       <c r="AI264" s="91"/>
     </row>
-    <row r="265" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="33" t="str">
         <f>IF(ISBLANK(E265),"",_xlfn.XLOOKUP(E265,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17025,7 +17343,7 @@
       <c r="P265" s="92"/>
       <c r="AI265" s="91"/>
     </row>
-    <row r="266" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="33" t="str">
         <f>IF(ISBLANK(E266),"",_xlfn.XLOOKUP(E266,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17049,7 +17367,7 @@
       <c r="P266" s="92"/>
       <c r="AI266" s="91"/>
     </row>
-    <row r="267" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="33" t="str">
         <f>IF(ISBLANK(E267),"",_xlfn.XLOOKUP(E267,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17073,7 +17391,7 @@
       <c r="P267" s="92"/>
       <c r="AI267" s="91"/>
     </row>
-    <row r="268" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="33" t="str">
         <f>IF(ISBLANK(E268),"",_xlfn.XLOOKUP(E268,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17097,7 +17415,7 @@
       <c r="P268" s="92"/>
       <c r="AI268" s="91"/>
     </row>
-    <row r="269" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="33" t="str">
         <f>IF(ISBLANK(E269),"",_xlfn.XLOOKUP(E269,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17121,7 +17439,7 @@
       <c r="P269" s="92"/>
       <c r="AI269" s="91"/>
     </row>
-    <row r="270" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="33" t="str">
         <f>IF(ISBLANK(E270),"",_xlfn.XLOOKUP(E270,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17145,7 +17463,7 @@
       <c r="P270" s="92"/>
       <c r="AI270" s="91"/>
     </row>
-    <row r="271" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="33" t="str">
         <f>IF(ISBLANK(E271),"",_xlfn.XLOOKUP(E271,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17169,7 +17487,7 @@
       <c r="P271" s="92"/>
       <c r="AI271" s="91"/>
     </row>
-    <row r="272" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="33" t="str">
         <f>IF(ISBLANK(E272),"",_xlfn.XLOOKUP(E272,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17193,7 +17511,7 @@
       <c r="P272" s="92"/>
       <c r="AI272" s="91"/>
     </row>
-    <row r="273" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="33" t="str">
         <f>IF(ISBLANK(E273),"",_xlfn.XLOOKUP(E273,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17217,7 +17535,7 @@
       <c r="P273" s="92"/>
       <c r="AI273" s="91"/>
     </row>
-    <row r="274" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="33" t="str">
         <f>IF(ISBLANK(E274),"",_xlfn.XLOOKUP(E274,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17241,7 +17559,7 @@
       <c r="P274" s="92"/>
       <c r="AI274" s="91"/>
     </row>
-    <row r="275" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="33" t="str">
         <f>IF(ISBLANK(E275),"",_xlfn.XLOOKUP(E275,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17265,7 +17583,7 @@
       <c r="P275" s="92"/>
       <c r="AI275" s="91"/>
     </row>
-    <row r="276" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="33" t="str">
         <f>IF(ISBLANK(E276),"",_xlfn.XLOOKUP(E276,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17289,7 +17607,7 @@
       <c r="P276" s="92"/>
       <c r="AI276" s="91"/>
     </row>
-    <row r="277" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="33" t="str">
         <f>IF(ISBLANK(E277),"",_xlfn.XLOOKUP(E277,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17313,7 +17631,7 @@
       <c r="P277" s="92"/>
       <c r="AI277" s="91"/>
     </row>
-    <row r="278" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="33" t="str">
         <f>IF(ISBLANK(E278),"",_xlfn.XLOOKUP(E278,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17337,7 +17655,7 @@
       <c r="P278" s="92"/>
       <c r="AI278" s="91"/>
     </row>
-    <row r="279" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="33" t="str">
         <f>IF(ISBLANK(E279),"",_xlfn.XLOOKUP(E279,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17361,7 +17679,7 @@
       <c r="P279" s="92"/>
       <c r="AI279" s="91"/>
     </row>
-    <row r="280" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="33" t="str">
         <f>IF(ISBLANK(E280),"",_xlfn.XLOOKUP(E280,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17385,7 +17703,7 @@
       <c r="P280" s="92"/>
       <c r="AI280" s="91"/>
     </row>
-    <row r="281" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="33" t="str">
         <f>IF(ISBLANK(E281),"",_xlfn.XLOOKUP(E281,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17409,7 +17727,7 @@
       <c r="P281" s="92"/>
       <c r="AI281" s="91"/>
     </row>
-    <row r="282" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="33" t="str">
         <f>IF(ISBLANK(E282),"",_xlfn.XLOOKUP(E282,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17433,7 +17751,7 @@
       <c r="P282" s="92"/>
       <c r="AI282" s="91"/>
     </row>
-    <row r="283" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="33" t="str">
         <f>IF(ISBLANK(E283),"",_xlfn.XLOOKUP(E283,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17457,7 +17775,7 @@
       <c r="P283" s="92"/>
       <c r="AI283" s="91"/>
     </row>
-    <row r="284" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="33" t="str">
         <f>IF(ISBLANK(E284),"",_xlfn.XLOOKUP(E284,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17481,7 +17799,7 @@
       <c r="P284" s="92"/>
       <c r="AI284" s="91"/>
     </row>
-    <row r="285" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="33" t="str">
         <f>IF(ISBLANK(E285),"",_xlfn.XLOOKUP(E285,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17505,7 +17823,7 @@
       <c r="P285" s="92"/>
       <c r="AI285" s="91"/>
     </row>
-    <row r="286" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="33" t="str">
         <f>IF(ISBLANK(E286),"",_xlfn.XLOOKUP(E286,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17529,7 +17847,7 @@
       <c r="P286" s="92"/>
       <c r="AI286" s="91"/>
     </row>
-    <row r="287" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="33" t="str">
         <f>IF(ISBLANK(E287),"",_xlfn.XLOOKUP(E287,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17553,7 +17871,7 @@
       <c r="P287" s="92"/>
       <c r="AI287" s="91"/>
     </row>
-    <row r="288" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="33" t="str">
         <f>IF(ISBLANK(E288),"",_xlfn.XLOOKUP(E288,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17577,7 +17895,7 @@
       <c r="P288" s="92"/>
       <c r="AI288" s="91"/>
     </row>
-    <row r="289" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="33" t="str">
         <f>IF(ISBLANK(E289),"",_xlfn.XLOOKUP(E289,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17601,7 +17919,7 @@
       <c r="P289" s="92"/>
       <c r="AI289" s="91"/>
     </row>
-    <row r="290" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="33" t="str">
         <f>IF(ISBLANK(E290),"",_xlfn.XLOOKUP(E290,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17625,7 +17943,7 @@
       <c r="P290" s="92"/>
       <c r="AI290" s="91"/>
     </row>
-    <row r="291" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="33" t="str">
         <f>IF(ISBLANK(E291),"",_xlfn.XLOOKUP(E291,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17649,7 +17967,7 @@
       <c r="P291" s="92"/>
       <c r="AI291" s="91"/>
     </row>
-    <row r="292" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="33" t="str">
         <f>IF(ISBLANK(E292),"",_xlfn.XLOOKUP(E292,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17673,7 +17991,7 @@
       <c r="P292" s="92"/>
       <c r="AI292" s="91"/>
     </row>
-    <row r="293" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="33" t="str">
         <f>IF(ISBLANK(E293),"",_xlfn.XLOOKUP(E293,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17697,7 +18015,7 @@
       <c r="P293" s="92"/>
       <c r="AI293" s="91"/>
     </row>
-    <row r="294" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="33" t="str">
         <f>IF(ISBLANK(E294),"",_xlfn.XLOOKUP(E294,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17721,7 +18039,7 @@
       <c r="P294" s="92"/>
       <c r="AI294" s="91"/>
     </row>
-    <row r="295" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="33" t="str">
         <f>IF(ISBLANK(E295),"",_xlfn.XLOOKUP(E295,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17745,7 +18063,7 @@
       <c r="P295" s="92"/>
       <c r="AI295" s="91"/>
     </row>
-    <row r="296" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="33" t="str">
         <f>IF(ISBLANK(E296),"",_xlfn.XLOOKUP(E296,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17769,7 +18087,7 @@
       <c r="P296" s="92"/>
       <c r="AI296" s="91"/>
     </row>
-    <row r="297" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="33" t="str">
         <f>IF(ISBLANK(E297),"",_xlfn.XLOOKUP(E297,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17793,7 +18111,7 @@
       <c r="P297" s="92"/>
       <c r="AI297" s="91"/>
     </row>
-    <row r="298" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="33" t="str">
         <f>IF(ISBLANK(E298),"",_xlfn.XLOOKUP(E298,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17817,7 +18135,7 @@
       <c r="P298" s="92"/>
       <c r="AI298" s="91"/>
     </row>
-    <row r="299" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="33" t="str">
         <f>IF(ISBLANK(E299),"",_xlfn.XLOOKUP(E299,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17841,7 +18159,7 @@
       <c r="P299" s="92"/>
       <c r="AI299" s="91"/>
     </row>
-    <row r="300" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="33" t="str">
         <f>IF(ISBLANK(E300),"",_xlfn.XLOOKUP(E300,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17865,7 +18183,7 @@
       <c r="P300" s="92"/>
       <c r="AI300" s="91"/>
     </row>
-    <row r="301" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="33" t="str">
         <f>IF(ISBLANK(E301),"",_xlfn.XLOOKUP(E301,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17889,7 +18207,7 @@
       <c r="P301" s="92"/>
       <c r="AI301" s="91"/>
     </row>
-    <row r="302" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="33" t="str">
         <f>IF(ISBLANK(E302),"",_xlfn.XLOOKUP(E302,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17913,7 +18231,7 @@
       <c r="P302" s="92"/>
       <c r="AI302" s="91"/>
     </row>
-    <row r="303" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="33" t="str">
         <f>IF(ISBLANK(E303),"",_xlfn.XLOOKUP(E303,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17937,7 +18255,7 @@
       <c r="P303" s="92"/>
       <c r="AI303" s="91"/>
     </row>
-    <row r="304" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="33" t="str">
         <f>IF(ISBLANK(E304),"",_xlfn.XLOOKUP(E304,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17961,7 +18279,7 @@
       <c r="P304" s="92"/>
       <c r="AI304" s="91"/>
     </row>
-    <row r="305" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="33" t="str">
         <f>IF(ISBLANK(E305),"",_xlfn.XLOOKUP(E305,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17985,7 +18303,7 @@
       <c r="P305" s="92"/>
       <c r="AI305" s="91"/>
     </row>
-    <row r="306" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="33" t="str">
         <f>IF(ISBLANK(E306),"",_xlfn.XLOOKUP(E306,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18009,7 +18327,7 @@
       <c r="P306" s="92"/>
       <c r="AI306" s="91"/>
     </row>
-    <row r="307" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="33" t="str">
         <f>IF(ISBLANK(E307),"",_xlfn.XLOOKUP(E307,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18033,7 +18351,7 @@
       <c r="P307" s="92"/>
       <c r="AI307" s="91"/>
     </row>
-    <row r="308" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="33" t="str">
         <f>IF(ISBLANK(E308),"",_xlfn.XLOOKUP(E308,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18057,7 +18375,7 @@
       <c r="P308" s="92"/>
       <c r="AI308" s="91"/>
     </row>
-    <row r="309" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="33" t="str">
         <f>IF(ISBLANK(E309),"",_xlfn.XLOOKUP(E309,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18081,7 +18399,7 @@
       <c r="P309" s="92"/>
       <c r="AI309" s="91"/>
     </row>
-    <row r="310" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="33" t="str">
         <f>IF(ISBLANK(E310),"",_xlfn.XLOOKUP(E310,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18105,7 +18423,7 @@
       <c r="P310" s="92"/>
       <c r="AI310" s="91"/>
     </row>
-    <row r="311" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="33" t="str">
         <f>IF(ISBLANK(E311),"",_xlfn.XLOOKUP(E311,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18129,7 +18447,7 @@
       <c r="P311" s="92"/>
       <c r="AI311" s="91"/>
     </row>
-    <row r="312" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="33" t="str">
         <f>IF(ISBLANK(E312),"",_xlfn.XLOOKUP(E312,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18153,7 +18471,7 @@
       <c r="P312" s="92"/>
       <c r="AI312" s="91"/>
     </row>
-    <row r="313" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="33" t="str">
         <f>IF(ISBLANK(E313),"",_xlfn.XLOOKUP(E313,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18177,7 +18495,7 @@
       <c r="P313" s="92"/>
       <c r="AI313" s="91"/>
     </row>
-    <row r="314" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="33" t="str">
         <f>IF(ISBLANK(E314),"",_xlfn.XLOOKUP(E314,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18201,7 +18519,7 @@
       <c r="P314" s="92"/>
       <c r="AI314" s="91"/>
     </row>
-    <row r="315" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="33" t="str">
         <f>IF(ISBLANK(E315),"",_xlfn.XLOOKUP(E315,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18225,7 +18543,7 @@
       <c r="P315" s="92"/>
       <c r="AI315" s="91"/>
     </row>
-    <row r="316" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="33" t="str">
         <f>IF(ISBLANK(E316),"",_xlfn.XLOOKUP(E316,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18249,7 +18567,7 @@
       <c r="P316" s="92"/>
       <c r="AI316" s="91"/>
     </row>
-    <row r="317" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="33" t="str">
         <f>IF(ISBLANK(E317),"",_xlfn.XLOOKUP(E317,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18273,7 +18591,7 @@
       <c r="P317" s="92"/>
       <c r="AI317" s="91"/>
     </row>
-    <row r="318" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="33" t="str">
         <f>IF(ISBLANK(E318),"",_xlfn.XLOOKUP(E318,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18297,7 +18615,7 @@
       <c r="P318" s="92"/>
       <c r="AI318" s="91"/>
     </row>
-    <row r="319" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="33" t="str">
         <f>IF(ISBLANK(E319),"",_xlfn.XLOOKUP(E319,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18321,7 +18639,7 @@
       <c r="P319" s="92"/>
       <c r="AI319" s="91"/>
     </row>
-    <row r="320" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="33" t="str">
         <f>IF(ISBLANK(E320),"",_xlfn.XLOOKUP(E320,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18345,7 +18663,7 @@
       <c r="P320" s="92"/>
       <c r="AI320" s="91"/>
     </row>
-    <row r="321" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="33" t="str">
         <f>IF(ISBLANK(E321),"",_xlfn.XLOOKUP(E321,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18369,7 +18687,7 @@
       <c r="P321" s="92"/>
       <c r="AI321" s="91"/>
     </row>
-    <row r="322" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="33" t="str">
         <f>IF(ISBLANK(E322),"",_xlfn.XLOOKUP(E322,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18393,7 +18711,7 @@
       <c r="P322" s="92"/>
       <c r="AI322" s="91"/>
     </row>
-    <row r="323" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="33" t="str">
         <f>IF(ISBLANK(E323),"",_xlfn.XLOOKUP(E323,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18417,7 +18735,7 @@
       <c r="P323" s="92"/>
       <c r="AI323" s="91"/>
     </row>
-    <row r="324" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="33" t="str">
         <f>IF(ISBLANK(E324),"",_xlfn.XLOOKUP(E324,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18441,7 +18759,7 @@
       <c r="P324" s="92"/>
       <c r="AI324" s="91"/>
     </row>
-    <row r="325" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="33" t="str">
         <f>IF(ISBLANK(E325),"",_xlfn.XLOOKUP(E325,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18465,7 +18783,7 @@
       <c r="P325" s="92"/>
       <c r="AI325" s="91"/>
     </row>
-    <row r="326" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="33" t="str">
         <f>IF(ISBLANK(E326),"",_xlfn.XLOOKUP(E326,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18489,7 +18807,7 @@
       <c r="P326" s="92"/>
       <c r="AI326" s="91"/>
     </row>
-    <row r="327" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="33" t="str">
         <f>IF(ISBLANK(E327),"",_xlfn.XLOOKUP(E327,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18513,7 +18831,7 @@
       <c r="P327" s="92"/>
       <c r="AI327" s="91"/>
     </row>
-    <row r="328" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="33" t="str">
         <f>IF(ISBLANK(E328),"",_xlfn.XLOOKUP(E328,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18537,7 +18855,7 @@
       <c r="P328" s="92"/>
       <c r="AI328" s="91"/>
     </row>
-    <row r="329" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="33" t="str">
         <f>IF(ISBLANK(E329),"",_xlfn.XLOOKUP(E329,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18561,7 +18879,7 @@
       <c r="P329" s="92"/>
       <c r="AI329" s="91"/>
     </row>
-    <row r="330" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="33" t="str">
         <f>IF(ISBLANK(E330),"",_xlfn.XLOOKUP(E330,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18585,7 +18903,7 @@
       <c r="P330" s="92"/>
       <c r="AI330" s="91"/>
     </row>
-    <row r="331" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="33" t="str">
         <f>IF(ISBLANK(E331),"",_xlfn.XLOOKUP(E331,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18609,7 +18927,7 @@
       <c r="P331" s="92"/>
       <c r="AI331" s="91"/>
     </row>
-    <row r="332" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="33" t="str">
         <f>IF(ISBLANK(E332),"",_xlfn.XLOOKUP(E332,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18633,7 +18951,7 @@
       <c r="P332" s="92"/>
       <c r="AI332" s="91"/>
     </row>
-    <row r="333" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="33" t="str">
         <f>IF(ISBLANK(E333),"",_xlfn.XLOOKUP(E333,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18657,7 +18975,7 @@
       <c r="P333" s="92"/>
       <c r="AI333" s="91"/>
     </row>
-    <row r="334" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="33" t="str">
         <f>IF(ISBLANK(E334),"",_xlfn.XLOOKUP(E334,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18681,7 +18999,7 @@
       <c r="P334" s="92"/>
       <c r="AI334" s="91"/>
     </row>
-    <row r="335" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="33" t="str">
         <f>IF(ISBLANK(E335),"",_xlfn.XLOOKUP(E335,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18705,7 +19023,7 @@
       <c r="P335" s="92"/>
       <c r="AI335" s="91"/>
     </row>
-    <row r="336" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="33" t="str">
         <f>IF(ISBLANK(E336),"",_xlfn.XLOOKUP(E336,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18729,7 +19047,7 @@
       <c r="P336" s="92"/>
       <c r="AI336" s="91"/>
     </row>
-    <row r="337" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="33" t="str">
         <f>IF(ISBLANK(E337),"",_xlfn.XLOOKUP(E337,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18753,7 +19071,7 @@
       <c r="P337" s="92"/>
       <c r="AI337" s="91"/>
     </row>
-    <row r="338" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="33" t="str">
         <f>IF(ISBLANK(E338),"",_xlfn.XLOOKUP(E338,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18777,7 +19095,7 @@
       <c r="P338" s="92"/>
       <c r="AI338" s="91"/>
     </row>
-    <row r="339" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="33" t="str">
         <f>IF(ISBLANK(E339),"",_xlfn.XLOOKUP(E339,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18801,7 +19119,7 @@
       <c r="P339" s="92"/>
       <c r="AI339" s="91"/>
     </row>
-    <row r="340" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="33" t="str">
         <f>IF(ISBLANK(E340),"",_xlfn.XLOOKUP(E340,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18825,7 +19143,7 @@
       <c r="P340" s="92"/>
       <c r="AI340" s="91"/>
     </row>
-    <row r="341" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="33" t="str">
         <f>IF(ISBLANK(E341),"",_xlfn.XLOOKUP(E341,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18849,7 +19167,7 @@
       <c r="P341" s="92"/>
       <c r="AI341" s="91"/>
     </row>
-    <row r="342" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="33" t="str">
         <f>IF(ISBLANK(E342),"",_xlfn.XLOOKUP(E342,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18873,7 +19191,7 @@
       <c r="P342" s="92"/>
       <c r="AI342" s="91"/>
     </row>
-    <row r="343" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="33" t="str">
         <f>IF(ISBLANK(E343),"",_xlfn.XLOOKUP(E343,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18897,7 +19215,7 @@
       <c r="P343" s="92"/>
       <c r="AI343" s="91"/>
     </row>
-    <row r="344" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="33" t="str">
         <f>IF(ISBLANK(E344),"",_xlfn.XLOOKUP(E344,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18921,7 +19239,7 @@
       <c r="P344" s="92"/>
       <c r="AI344" s="91"/>
     </row>
-    <row r="345" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="33" t="str">
         <f>IF(ISBLANK(E345),"",_xlfn.XLOOKUP(E345,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18945,7 +19263,7 @@
       <c r="P345" s="92"/>
       <c r="AI345" s="91"/>
     </row>
-    <row r="346" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="33" t="str">
         <f>IF(ISBLANK(E346),"",_xlfn.XLOOKUP(E346,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18969,7 +19287,7 @@
       <c r="P346" s="92"/>
       <c r="AI346" s="91"/>
     </row>
-    <row r="347" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="33" t="str">
         <f>IF(ISBLANK(E347),"",_xlfn.XLOOKUP(E347,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18993,7 +19311,7 @@
       <c r="P347" s="92"/>
       <c r="AI347" s="91"/>
     </row>
-    <row r="348" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="33" t="str">
         <f>IF(ISBLANK(E348),"",_xlfn.XLOOKUP(E348,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19017,7 +19335,7 @@
       <c r="P348" s="92"/>
       <c r="AI348" s="91"/>
     </row>
-    <row r="349" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="33" t="str">
         <f>IF(ISBLANK(E349),"",_xlfn.XLOOKUP(E349,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19041,7 +19359,7 @@
       <c r="P349" s="92"/>
       <c r="AI349" s="91"/>
     </row>
-    <row r="350" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="33" t="str">
         <f>IF(ISBLANK(E350),"",_xlfn.XLOOKUP(E350,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19065,7 +19383,7 @@
       <c r="P350" s="92"/>
       <c r="AI350" s="91"/>
     </row>
-    <row r="351" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="33" t="str">
         <f>IF(ISBLANK(E351),"",_xlfn.XLOOKUP(E351,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19089,7 +19407,7 @@
       <c r="P351" s="92"/>
       <c r="AI351" s="91"/>
     </row>
-    <row r="352" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="33" t="str">
         <f>IF(ISBLANK(E352),"",_xlfn.XLOOKUP(E352,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19113,7 +19431,7 @@
       <c r="P352" s="92"/>
       <c r="AI352" s="91"/>
     </row>
-    <row r="353" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="33" t="str">
         <f>IF(ISBLANK(E353),"",_xlfn.XLOOKUP(E353,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19137,7 +19455,7 @@
       <c r="P353" s="92"/>
       <c r="AI353" s="91"/>
     </row>
-    <row r="354" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="33" t="str">
         <f>IF(ISBLANK(E354),"",_xlfn.XLOOKUP(E354,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19161,7 +19479,7 @@
       <c r="P354" s="92"/>
       <c r="AI354" s="91"/>
     </row>
-    <row r="355" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="33" t="str">
         <f>IF(ISBLANK(E355),"",_xlfn.XLOOKUP(E355,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19185,7 +19503,7 @@
       <c r="P355" s="92"/>
       <c r="AI355" s="91"/>
     </row>
-    <row r="356" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="33" t="str">
         <f>IF(ISBLANK(E356),"",_xlfn.XLOOKUP(E356,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19209,7 +19527,7 @@
       <c r="P356" s="92"/>
       <c r="AI356" s="91"/>
     </row>
-    <row r="357" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="33" t="str">
         <f>IF(ISBLANK(E357),"",_xlfn.XLOOKUP(E357,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19233,7 +19551,7 @@
       <c r="P357" s="92"/>
       <c r="AI357" s="91"/>
     </row>
-    <row r="358" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="33" t="str">
         <f>IF(ISBLANK(E358),"",_xlfn.XLOOKUP(E358,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19257,7 +19575,7 @@
       <c r="P358" s="92"/>
       <c r="AI358" s="91"/>
     </row>
-    <row r="359" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="33" t="str">
         <f>IF(ISBLANK(E359),"",_xlfn.XLOOKUP(E359,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19281,7 +19599,7 @@
       <c r="P359" s="92"/>
       <c r="AI359" s="91"/>
     </row>
-    <row r="360" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="33" t="str">
         <f>IF(ISBLANK(E360),"",_xlfn.XLOOKUP(E360,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19305,7 +19623,7 @@
       <c r="P360" s="92"/>
       <c r="AI360" s="91"/>
     </row>
-    <row r="361" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="33" t="str">
         <f>IF(ISBLANK(E361),"",_xlfn.XLOOKUP(E361,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19329,7 +19647,7 @@
       <c r="P361" s="92"/>
       <c r="AI361" s="91"/>
     </row>
-    <row r="362" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="33" t="str">
         <f>IF(ISBLANK(E362),"",_xlfn.XLOOKUP(E362,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19353,7 +19671,7 @@
       <c r="P362" s="92"/>
       <c r="AI362" s="91"/>
     </row>
-    <row r="363" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="33" t="str">
         <f>IF(ISBLANK(E363),"",_xlfn.XLOOKUP(E363,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19377,7 +19695,7 @@
       <c r="P363" s="92"/>
       <c r="AI363" s="91"/>
     </row>
-    <row r="364" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="33" t="str">
         <f>IF(ISBLANK(E364),"",_xlfn.XLOOKUP(E364,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19401,7 +19719,7 @@
       <c r="P364" s="92"/>
       <c r="AI364" s="91"/>
     </row>
-    <row r="365" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="33" t="str">
         <f>IF(ISBLANK(E365),"",_xlfn.XLOOKUP(E365,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19425,7 +19743,7 @@
       <c r="P365" s="92"/>
       <c r="AI365" s="91"/>
     </row>
-    <row r="366" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="33" t="str">
         <f>IF(ISBLANK(E366),"",_xlfn.XLOOKUP(E366,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19449,7 +19767,7 @@
       <c r="P366" s="92"/>
       <c r="AI366" s="91"/>
     </row>
-    <row r="367" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="33" t="str">
         <f>IF(ISBLANK(E367),"",_xlfn.XLOOKUP(E367,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19473,7 +19791,7 @@
       <c r="P367" s="92"/>
       <c r="AI367" s="91"/>
     </row>
-    <row r="368" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="33" t="str">
         <f>IF(ISBLANK(E368),"",_xlfn.XLOOKUP(E368,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19497,7 +19815,7 @@
       <c r="P368" s="92"/>
       <c r="AI368" s="91"/>
     </row>
-    <row r="369" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="33" t="str">
         <f>IF(ISBLANK(E369),"",_xlfn.XLOOKUP(E369,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19521,7 +19839,7 @@
       <c r="P369" s="92"/>
       <c r="AI369" s="91"/>
     </row>
-    <row r="370" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="33" t="str">
         <f>IF(ISBLANK(E370),"",_xlfn.XLOOKUP(E370,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19545,7 +19863,7 @@
       <c r="P370" s="92"/>
       <c r="AI370" s="91"/>
     </row>
-    <row r="371" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="33" t="str">
         <f>IF(ISBLANK(E371),"",_xlfn.XLOOKUP(E371,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19569,7 +19887,7 @@
       <c r="P371" s="92"/>
       <c r="AI371" s="91"/>
     </row>
-    <row r="372" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="33" t="str">
         <f>IF(ISBLANK(E372),"",_xlfn.XLOOKUP(E372,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19593,7 +19911,7 @@
       <c r="P372" s="92"/>
       <c r="AI372" s="91"/>
     </row>
-    <row r="373" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="33" t="str">
         <f>IF(ISBLANK(E373),"",_xlfn.XLOOKUP(E373,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19617,7 +19935,7 @@
       <c r="P373" s="92"/>
       <c r="AI373" s="91"/>
     </row>
-    <row r="374" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="33" t="str">
         <f>IF(ISBLANK(E374),"",_xlfn.XLOOKUP(E374,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19641,7 +19959,7 @@
       <c r="P374" s="92"/>
       <c r="AI374" s="91"/>
     </row>
-    <row r="375" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="33" t="str">
         <f>IF(ISBLANK(E375),"",_xlfn.XLOOKUP(E375,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19665,7 +19983,7 @@
       <c r="P375" s="92"/>
       <c r="AI375" s="91"/>
     </row>
-    <row r="376" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="33" t="str">
         <f>IF(ISBLANK(E376),"",_xlfn.XLOOKUP(E376,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19689,7 +20007,7 @@
       <c r="P376" s="92"/>
       <c r="AI376" s="91"/>
     </row>
-    <row r="377" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="33" t="str">
         <f>IF(ISBLANK(E377),"",_xlfn.XLOOKUP(E377,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19713,7 +20031,7 @@
       <c r="P377" s="92"/>
       <c r="AI377" s="91"/>
     </row>
-    <row r="378" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="33" t="str">
         <f>IF(ISBLANK(E378),"",_xlfn.XLOOKUP(E378,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19737,7 +20055,7 @@
       <c r="P378" s="92"/>
       <c r="AI378" s="91"/>
     </row>
-    <row r="379" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="33" t="str">
         <f>IF(ISBLANK(E379),"",_xlfn.XLOOKUP(E379,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19761,7 +20079,7 @@
       <c r="P379" s="92"/>
       <c r="AI379" s="91"/>
     </row>
-    <row r="380" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="33" t="str">
         <f>IF(ISBLANK(E380),"",_xlfn.XLOOKUP(E380,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19785,7 +20103,7 @@
       <c r="P380" s="92"/>
       <c r="AI380" s="91"/>
     </row>
-    <row r="381" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="33" t="str">
         <f>IF(ISBLANK(E381),"",_xlfn.XLOOKUP(E381,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19809,7 +20127,7 @@
       <c r="P381" s="92"/>
       <c r="AI381" s="91"/>
     </row>
-    <row r="382" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="33" t="str">
         <f>IF(ISBLANK(E382),"",_xlfn.XLOOKUP(E382,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19833,7 +20151,7 @@
       <c r="P382" s="92"/>
       <c r="AI382" s="91"/>
     </row>
-    <row r="383" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="33" t="str">
         <f>IF(ISBLANK(E383),"",_xlfn.XLOOKUP(E383,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19857,7 +20175,7 @@
       <c r="P383" s="92"/>
       <c r="AI383" s="91"/>
     </row>
-    <row r="384" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="33" t="str">
         <f>IF(ISBLANK(E384),"",_xlfn.XLOOKUP(E384,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19881,7 +20199,7 @@
       <c r="P384" s="92"/>
       <c r="AI384" s="91"/>
     </row>
-    <row r="385" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="33" t="str">
         <f>IF(ISBLANK(E385),"",_xlfn.XLOOKUP(E385,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19905,7 +20223,7 @@
       <c r="P385" s="92"/>
       <c r="AI385" s="91"/>
     </row>
-    <row r="386" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="33" t="str">
         <f>IF(ISBLANK(E386),"",_xlfn.XLOOKUP(E386,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19929,7 +20247,7 @@
       <c r="P386" s="92"/>
       <c r="AI386" s="91"/>
     </row>
-    <row r="387" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="33" t="str">
         <f>IF(ISBLANK(E387),"",_xlfn.XLOOKUP(E387,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19953,7 +20271,7 @@
       <c r="P387" s="92"/>
       <c r="AI387" s="91"/>
     </row>
-    <row r="388" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="33" t="str">
         <f>IF(ISBLANK(E388),"",_xlfn.XLOOKUP(E388,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19977,7 +20295,7 @@
       <c r="P388" s="92"/>
       <c r="AI388" s="91"/>
     </row>
-    <row r="389" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="33" t="str">
         <f>IF(ISBLANK(E389),"",_xlfn.XLOOKUP(E389,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20001,7 +20319,7 @@
       <c r="P389" s="92"/>
       <c r="AI389" s="91"/>
     </row>
-    <row r="390" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="33" t="str">
         <f>IF(ISBLANK(E390),"",_xlfn.XLOOKUP(E390,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20025,7 +20343,7 @@
       <c r="P390" s="92"/>
       <c r="AI390" s="91"/>
     </row>
-    <row r="391" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="33" t="str">
         <f>IF(ISBLANK(E391),"",_xlfn.XLOOKUP(E391,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20049,7 +20367,7 @@
       <c r="P391" s="92"/>
       <c r="AI391" s="91"/>
     </row>
-    <row r="392" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="33" t="str">
         <f>IF(ISBLANK(E392),"",_xlfn.XLOOKUP(E392,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20073,7 +20391,7 @@
       <c r="P392" s="92"/>
       <c r="AI392" s="91"/>
     </row>
-    <row r="393" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="33" t="str">
         <f>IF(ISBLANK(E393),"",_xlfn.XLOOKUP(E393,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20097,7 +20415,7 @@
       <c r="P393" s="92"/>
       <c r="AI393" s="91"/>
     </row>
-    <row r="394" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="33" t="str">
         <f>IF(ISBLANK(E394),"",_xlfn.XLOOKUP(E394,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20121,7 +20439,7 @@
       <c r="P394" s="92"/>
       <c r="AI394" s="91"/>
     </row>
-    <row r="395" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="33" t="str">
         <f>IF(ISBLANK(E395),"",_xlfn.XLOOKUP(E395,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20145,7 +20463,7 @@
       <c r="P395" s="92"/>
       <c r="AI395" s="91"/>
     </row>
-    <row r="396" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="33" t="str">
         <f>IF(ISBLANK(E396),"",_xlfn.XLOOKUP(E396,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20169,7 +20487,7 @@
       <c r="P396" s="92"/>
       <c r="AI396" s="91"/>
     </row>
-    <row r="397" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="33" t="str">
         <f>IF(ISBLANK(E397),"",_xlfn.XLOOKUP(E397,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20193,7 +20511,7 @@
       <c r="P397" s="92"/>
       <c r="AI397" s="91"/>
     </row>
-    <row r="398" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="33" t="str">
         <f>IF(ISBLANK(E398),"",_xlfn.XLOOKUP(E398,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20217,7 +20535,7 @@
       <c r="P398" s="92"/>
       <c r="AI398" s="91"/>
     </row>
-    <row r="399" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="33" t="str">
         <f>IF(ISBLANK(E399),"",_xlfn.XLOOKUP(E399,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20241,7 +20559,7 @@
       <c r="P399" s="92"/>
       <c r="AI399" s="91"/>
     </row>
-    <row r="400" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="33" t="str">
         <f>IF(ISBLANK(E400),"",_xlfn.XLOOKUP(E400,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20265,7 +20583,7 @@
       <c r="P400" s="92"/>
       <c r="AI400" s="91"/>
     </row>
-    <row r="401" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="33" t="str">
         <f>IF(ISBLANK(E401),"",_xlfn.XLOOKUP(E401,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20289,7 +20607,7 @@
       <c r="P401" s="92"/>
       <c r="AI401" s="91"/>
     </row>
-    <row r="402" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="33" t="str">
         <f>IF(ISBLANK(E402),"",_xlfn.XLOOKUP(E402,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20313,7 +20631,7 @@
       <c r="P402" s="92"/>
       <c r="AI402" s="91"/>
     </row>
-    <row r="403" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="33" t="str">
         <f>IF(ISBLANK(E403),"",_xlfn.XLOOKUP(E403,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20337,7 +20655,7 @@
       <c r="P403" s="92"/>
       <c r="AI403" s="91"/>
     </row>
-    <row r="404" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="33" t="str">
         <f>IF(ISBLANK(E404),"",_xlfn.XLOOKUP(E404,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20361,7 +20679,7 @@
       <c r="P404" s="92"/>
       <c r="AI404" s="91"/>
     </row>
-    <row r="405" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="33" t="str">
         <f>IF(ISBLANK(E405),"",_xlfn.XLOOKUP(E405,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20385,7 +20703,7 @@
       <c r="P405" s="92"/>
       <c r="AI405" s="91"/>
     </row>
-    <row r="406" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="33" t="str">
         <f>IF(ISBLANK(E406),"",_xlfn.XLOOKUP(E406,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20395,7 +20713,7 @@
         <v/>
       </c>
     </row>
-    <row r="407" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="33" t="str">
         <f>IF(ISBLANK(E407),"",_xlfn.XLOOKUP(E407,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20405,7 +20723,7 @@
         <v/>
       </c>
     </row>
-    <row r="408" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="33" t="str">
         <f>IF(ISBLANK(E408),"",_xlfn.XLOOKUP(E408,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20415,7 +20733,7 @@
         <v/>
       </c>
     </row>
-    <row r="409" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="33" t="str">
         <f>IF(ISBLANK(E409),"",_xlfn.XLOOKUP(E409,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20425,7 +20743,7 @@
         <v/>
       </c>
     </row>
-    <row r="410" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="33" t="str">
         <f>IF(ISBLANK(E410),"",_xlfn.XLOOKUP(E410,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20435,7 +20753,7 @@
         <v/>
       </c>
     </row>
-    <row r="411" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="33" t="str">
         <f>IF(ISBLANK(E411),"",_xlfn.XLOOKUP(E411,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20445,7 +20763,7 @@
         <v/>
       </c>
     </row>
-    <row r="412" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="33" t="str">
         <f>IF(ISBLANK(E412),"",_xlfn.XLOOKUP(E412,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20455,7 +20773,7 @@
         <v/>
       </c>
     </row>
-    <row r="413" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="33" t="str">
         <f>IF(ISBLANK(E413),"",_xlfn.XLOOKUP(E413,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20465,7 +20783,7 @@
         <v/>
       </c>
     </row>
-    <row r="414" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="33" t="str">
         <f>IF(ISBLANK(E414),"",_xlfn.XLOOKUP(E414,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20475,7 +20793,7 @@
         <v/>
       </c>
     </row>
-    <row r="415" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="33" t="str">
         <f>IF(ISBLANK(E415),"",_xlfn.XLOOKUP(E415,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20485,7 +20803,7 @@
         <v/>
       </c>
     </row>
-    <row r="416" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="33" t="str">
         <f>IF(ISBLANK(E416),"",_xlfn.XLOOKUP(E416,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20495,7 +20813,7 @@
         <v/>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="33" t="str">
         <f>IF(ISBLANK(E417),"",_xlfn.XLOOKUP(E417,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20505,7 +20823,7 @@
         <v/>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="33" t="str">
         <f>IF(ISBLANK(E418),"",_xlfn.XLOOKUP(E418,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20515,7 +20833,7 @@
         <v/>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="33" t="str">
         <f>IF(ISBLANK(E419),"",_xlfn.XLOOKUP(E419,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20525,7 +20843,7 @@
         <v/>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="33" t="str">
         <f>IF(ISBLANK(E420),"",_xlfn.XLOOKUP(E420,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20535,7 +20853,7 @@
         <v/>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="33" t="str">
         <f>IF(ISBLANK(E421),"",_xlfn.XLOOKUP(E421,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20545,7 +20863,7 @@
         <v/>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="33" t="str">
         <f>IF(ISBLANK(E422),"",_xlfn.XLOOKUP(E422,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20555,7 +20873,7 @@
         <v/>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="33" t="str">
         <f>IF(ISBLANK(E423),"",_xlfn.XLOOKUP(E423,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20565,7 +20883,7 @@
         <v/>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="33" t="str">
         <f>IF(ISBLANK(E424),"",_xlfn.XLOOKUP(E424,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20575,7 +20893,7 @@
         <v/>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="33" t="str">
         <f>IF(ISBLANK(E425),"",_xlfn.XLOOKUP(E425,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20585,7 +20903,7 @@
         <v/>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="33" t="str">
         <f>IF(ISBLANK(E426),"",_xlfn.XLOOKUP(E426,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20595,7 +20913,7 @@
         <v/>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="33" t="str">
         <f>IF(ISBLANK(E427),"",_xlfn.XLOOKUP(E427,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20605,7 +20923,7 @@
         <v/>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="33" t="str">
         <f>IF(ISBLANK(E428),"",_xlfn.XLOOKUP(E428,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20615,7 +20933,7 @@
         <v/>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="33" t="str">
         <f>IF(ISBLANK(E429),"",_xlfn.XLOOKUP(E429,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20625,7 +20943,7 @@
         <v/>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="33" t="str">
         <f>IF(ISBLANK(E430),"",_xlfn.XLOOKUP(E430,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20635,7 +20953,7 @@
         <v/>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="33" t="str">
         <f>IF(ISBLANK(E431),"",_xlfn.XLOOKUP(E431,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20645,7 +20963,7 @@
         <v/>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="33" t="str">
         <f>IF(ISBLANK(E432),"",_xlfn.XLOOKUP(E432,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20655,7 +20973,7 @@
         <v/>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="33" t="str">
         <f>IF(ISBLANK(E433),"",_xlfn.XLOOKUP(E433,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20665,7 +20983,7 @@
         <v/>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="33" t="str">
         <f>IF(ISBLANK(E434),"",_xlfn.XLOOKUP(E434,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20675,7 +20993,7 @@
         <v/>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="33" t="str">
         <f>IF(ISBLANK(E435),"",_xlfn.XLOOKUP(E435,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20685,7 +21003,7 @@
         <v/>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="33" t="str">
         <f>IF(ISBLANK(E436),"",_xlfn.XLOOKUP(E436,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20695,7 +21013,7 @@
         <v/>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="33" t="str">
         <f>IF(ISBLANK(E437),"",_xlfn.XLOOKUP(E437,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20705,7 +21023,7 @@
         <v/>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="33" t="str">
         <f>IF(ISBLANK(E438),"",_xlfn.XLOOKUP(E438,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20715,7 +21033,7 @@
         <v/>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="33" t="str">
         <f>IF(ISBLANK(E439),"",_xlfn.XLOOKUP(E439,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20725,7 +21043,7 @@
         <v/>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="33" t="str">
         <f>IF(ISBLANK(E440),"",_xlfn.XLOOKUP(E440,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20735,7 +21053,7 @@
         <v/>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="33" t="str">
         <f>IF(ISBLANK(E441),"",_xlfn.XLOOKUP(E441,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20745,7 +21063,7 @@
         <v/>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="33" t="str">
         <f>IF(ISBLANK(E442),"",_xlfn.XLOOKUP(E442,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20755,7 +21073,7 @@
         <v/>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="33" t="str">
         <f>IF(ISBLANK(E443),"",_xlfn.XLOOKUP(E443,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20765,7 +21083,7 @@
         <v/>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="33" t="str">
         <f>IF(ISBLANK(E444),"",_xlfn.XLOOKUP(E444,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20775,7 +21093,7 @@
         <v/>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="33" t="str">
         <f>IF(ISBLANK(E445),"",_xlfn.XLOOKUP(E445,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20785,7 +21103,7 @@
         <v/>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="33" t="str">
         <f>IF(ISBLANK(E446),"",_xlfn.XLOOKUP(E446,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20797,15 +21115,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P446" xr:uid="{C106C93E-E4E6-4212-A1AE-6CCBA718A489}">
-    <filterColumn colId="2">
-      <filters blank="1">
-        <filter val="Pending Scheduling"/>
-        <filter val="Scheduled"/>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Spec Building Analysis for Northeast"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A73:P446">
-      <sortCondition ref="E1:E446"/>
-    </sortState>
   </autoFilter>
   <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
@@ -20864,8 +21178,15 @@
     <hyperlink ref="O6" r:id="rId53" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_01_29 Northeast Spec Bld Analysis.pptx?d=w9c538d8635b94c129ba00ea7eac27a0e&amp;csf=1&amp;web=1&amp;e=Cn3L1m" xr:uid="{4A6DDCAA-2AC4-4B9D-9AB3-D4FFDD8113C4}"/>
     <hyperlink ref="O71" r:id="rId54" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_08 SteerCo.pptx?d=wd863957755e742f8bfaaadcb434b30d7&amp;csf=1&amp;web=1&amp;e=6FERxe" xr:uid="{A06FD16C-22D9-4F10-9FC7-D919C3472D73}"/>
     <hyperlink ref="O73" r:id="rId55" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_14 SteerCo.pptx?d=wfcde045a0ff1452686c02d98bf7836c7&amp;csf=1&amp;web=1&amp;e=8aJxB1" xr:uid="{46143575-5EB8-4C9E-807B-5850612A768D}"/>
-    <hyperlink ref="O84" r:id="rId56" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_30 NextGen Burn Testing OpEx Required.pptx?d=wd99f0bea311e458c940769f98e41f64d&amp;csf=1&amp;web=1&amp;e=TJNOEa" xr:uid="{73104FA3-48DC-41E6-A8B4-8FCD3A15AD50}"/>
+    <hyperlink ref="O76" r:id="rId56" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_04_30 NextGen Burn Testing OpEx Required.pptx?d=wd99f0bea311e458c940769f98e41f64d&amp;csf=1&amp;web=1&amp;e=TJNOEa" xr:uid="{73104FA3-48DC-41E6-A8B4-8FCD3A15AD50}"/>
     <hyperlink ref="O75" r:id="rId57" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_20 SteerCo Wallkill Scenarios.pptx?d=waa33fa32cdff4b44be75eb893feb1364&amp;csf=1&amp;web=1&amp;e=oF1OhE" xr:uid="{ADF03195-F8AA-4911-8755-98E024B646AF}"/>
+    <hyperlink ref="O77" r:id="rId58" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_29 SteerCo.pptx?d=wd4bf34084cad4345b5323486aceca160&amp;csf=1&amp;web=1&amp;e=ry0ytr" xr:uid="{E787E7E7-F1B4-4FE9-9850-C4EE80F415F2}"/>
+    <hyperlink ref="O78" r:id="rId59" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_29 SteerCo.pptx?d=wd4bf34084cad4345b5323486aceca160&amp;csf=1&amp;web=1&amp;e=ry0ytr" xr:uid="{51CFE043-3687-4844-8FC3-CCF032FDD675}"/>
+    <hyperlink ref="O79" r:id="rId60" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_29 SteerCo.pptx?d=wd4bf34084cad4345b5323486aceca160&amp;csf=1&amp;web=1&amp;e=ry0ytr" xr:uid="{66AC0D8F-D33C-4E7D-A671-90F23D778338}"/>
+    <hyperlink ref="O80" r:id="rId61" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_05_29 SteerCo.pptx?d=wd4bf34084cad4345b5323486aceca160&amp;csf=1&amp;web=1&amp;e=ry0ytr" xr:uid="{B8B6089A-8C95-4A22-82A6-71A0AC2F0AFA}"/>
+    <hyperlink ref="O83" r:id="rId62" display="https://teams.wal-mart.com/:x:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/Budget/FC Network Budget Tracker.xlsx?d=wc91d9e182616493abca9cc4b3b011c4b&amp;csf=1&amp;web=1&amp;e=N6ghi6" xr:uid="{F8CC47B5-7D0B-4A07-9C92-2D4E5E81571F}"/>
+    <hyperlink ref="O81" r:id="rId63" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_06_03 SteerCo.pptx?d=wbba6787004134eac8707fef9bde4884f&amp;csf=1&amp;web=1&amp;e=SF8qgC" xr:uid="{D97203FD-9B99-4C43-9A7C-FCFDAFD20434}"/>
+    <hyperlink ref="O82" r:id="rId64" display="https://teams.wal-mart.com/:p:/r/sites/TechnologyandAutomation/Shared Documents/PMO/Fulfillment/NextGens/02. Presentations/01.  Steer Co Presentations/26_06_03 SteerCo.pptx?d=wbba6787004134eac8707fef9bde4884f&amp;csf=1&amp;web=1&amp;e=SF8qgC" xr:uid="{CCC0EA12-ED53-4F78-B2EE-A024626815FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20876,7 +21197,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:R68"/>
+  <dimension ref="A1:R72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" customWidth="1"/>
@@ -20911,8 +21232,8 @@
       <c r="H1" s="98" t="s">
         <v>266</v>
       </c>
-      <c r="Q1" s="141" t="s">
-        <v>658</v>
+      <c r="Q1" s="140" t="s">
+        <v>655</v>
       </c>
       <c r="R1" s="97"/>
     </row>
@@ -20941,8 +21262,8 @@
       <c r="H2" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="Q2" s="142" t="s">
-        <v>659</v>
+      <c r="Q2" s="141" t="s">
+        <v>656</v>
       </c>
       <c r="R2" s="97"/>
     </row>
@@ -20971,8 +21292,8 @@
       <c r="H3" s="105" t="s">
         <v>377</v>
       </c>
-      <c r="Q3" s="143" t="s">
-        <v>660</v>
+      <c r="Q3" s="142" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -21041,16 +21362,16 @@
         <v>317</v>
       </c>
       <c r="E6" s="33" t="s">
+        <v>538</v>
+      </c>
+      <c r="F6" s="33" t="s">
         <v>539</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="G6" s="33" t="s">
         <v>540</v>
       </c>
-      <c r="G6" s="33" t="s">
+      <c r="H6" s="33" t="s">
         <v>541</v>
-      </c>
-      <c r="H6" s="33" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -21083,40 +21404,30 @@
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="138" t="s">
+      <c r="A8" s="137" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>538</v>
-      </c>
-      <c r="B9" s="98">
-        <v>45792</v>
-      </c>
-      <c r="C9" s="98">
-        <v>45979</v>
-      </c>
-      <c r="D9" s="98">
-        <v>45979</v>
-      </c>
-      <c r="E9" s="98">
-        <v>46128</v>
-      </c>
-      <c r="F9" s="98">
-        <v>46128</v>
-      </c>
-      <c r="G9" s="98">
-        <v>46128</v>
-      </c>
-      <c r="H9" s="98">
-        <v>46128</v>
-      </c>
-      <c r="I9" s="96"/>
+      <c r="A9" s="107" t="s">
+        <v>667</v>
+      </c>
+      <c r="E9" s="135">
+        <v>46164</v>
+      </c>
+      <c r="F9" s="135">
+        <v>46164</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>276</v>
+        <v>537</v>
       </c>
       <c r="B10" s="98">
         <v>45792</v>
@@ -21125,37 +21436,37 @@
         <v>45979</v>
       </c>
       <c r="D10" s="98">
-        <v>45860</v>
-      </c>
-      <c r="E10" s="98" t="s">
-        <v>84</v>
-      </c>
-      <c r="F10" s="98" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" s="98" t="s">
-        <v>84</v>
-      </c>
-      <c r="H10" s="98" t="s">
-        <v>84</v>
+        <v>45979</v>
+      </c>
+      <c r="E10" s="98">
+        <v>46128</v>
+      </c>
+      <c r="F10" s="98">
+        <v>46128</v>
+      </c>
+      <c r="G10" s="98">
+        <v>46128</v>
+      </c>
+      <c r="H10" s="98">
+        <v>46128</v>
       </c>
       <c r="I10" s="96"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B11" s="98">
-        <v>45855</v>
+        <v>45792</v>
       </c>
       <c r="C11" s="98">
-        <v>46080</v>
+        <v>45979</v>
       </c>
       <c r="D11" s="98">
-        <v>45993</v>
-      </c>
-      <c r="E11" s="98" t="s">
-        <v>84</v>
+        <v>45860</v>
+      </c>
+      <c r="E11" s="98">
+        <v>46259</v>
       </c>
       <c r="F11" s="98" t="s">
         <v>84</v>
@@ -21170,19 +21481,19 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B12" s="98">
-        <v>45971</v>
-      </c>
-      <c r="C12" s="131">
+        <v>45855</v>
+      </c>
+      <c r="C12" s="98">
         <v>46080</v>
       </c>
       <c r="D12" s="98">
-        <v>46080</v>
-      </c>
-      <c r="E12" s="98" t="s">
-        <v>84</v>
+        <v>45993</v>
+      </c>
+      <c r="E12" s="98">
+        <v>46259</v>
       </c>
       <c r="F12" s="98" t="s">
         <v>84</v>
@@ -21197,19 +21508,19 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>547</v>
+        <v>278</v>
       </c>
       <c r="B13" s="98">
         <v>45971</v>
       </c>
-      <c r="C13" s="98">
-        <v>46253</v>
-      </c>
-      <c r="D13" s="131">
-        <v>46164</v>
-      </c>
-      <c r="E13" s="98" t="s">
-        <v>84</v>
+      <c r="C13" s="131">
+        <v>46080</v>
+      </c>
+      <c r="D13" s="98">
+        <v>46080</v>
+      </c>
+      <c r="E13" s="98">
+        <v>46279</v>
       </c>
       <c r="F13" s="98" t="s">
         <v>84</v>
@@ -21224,7 +21535,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>279</v>
+        <v>546</v>
       </c>
       <c r="B14" s="98">
         <v>45971</v>
@@ -21232,11 +21543,11 @@
       <c r="C14" s="98">
         <v>46253</v>
       </c>
-      <c r="D14" s="98">
-        <v>46253</v>
-      </c>
-      <c r="E14" s="98" t="s">
-        <v>84</v>
+      <c r="D14" s="131">
+        <v>46164</v>
+      </c>
+      <c r="E14" s="98">
+        <v>46279</v>
       </c>
       <c r="F14" s="98" t="s">
         <v>84</v>
@@ -21250,380 +21561,378 @@
       <c r="I14" s="96"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="97" t="s">
-        <v>303</v>
+      <c r="A15" t="s">
+        <v>279</v>
       </c>
       <c r="B15" s="98">
-        <v>45800</v>
+        <v>45971</v>
       </c>
       <c r="C15" s="98">
-        <v>46114</v>
+        <v>46253</v>
       </c>
       <c r="D15" s="98">
-        <v>45952</v>
+        <v>46253</v>
       </c>
       <c r="E15" s="98">
-        <v>46248</v>
-      </c>
-      <c r="F15" s="131">
-        <v>46248</v>
-      </c>
-      <c r="G15" s="98">
-        <v>46283</v>
-      </c>
-      <c r="H15" s="98">
-        <v>46283</v>
+        <v>46332</v>
+      </c>
+      <c r="F15" s="98" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="98" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="98" t="s">
+        <v>84</v>
       </c>
       <c r="I15" s="96"/>
-      <c r="K15" s="117"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="97" t="s">
-        <v>578</v>
-      </c>
-      <c r="B16" s="140">
-        <v>45859</v>
-      </c>
-      <c r="C16" s="140">
-        <v>46083</v>
-      </c>
-      <c r="D16" s="140">
-        <v>45992</v>
-      </c>
-      <c r="E16" s="98"/>
-      <c r="F16" s="131"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="98"/>
+        <v>303</v>
+      </c>
+      <c r="B16" s="98">
+        <v>45800</v>
+      </c>
+      <c r="C16" s="98">
+        <v>46114</v>
+      </c>
+      <c r="D16" s="98">
+        <v>45952</v>
+      </c>
+      <c r="E16" s="98">
+        <v>46248</v>
+      </c>
+      <c r="F16" s="131">
+        <v>46248</v>
+      </c>
+      <c r="G16" s="98">
+        <v>46283</v>
+      </c>
+      <c r="H16" s="98">
+        <v>46283</v>
+      </c>
       <c r="I16" s="96"/>
       <c r="K16" s="117"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="97" t="s">
+        <v>577</v>
+      </c>
+      <c r="B17" s="139">
+        <v>45859</v>
+      </c>
+      <c r="C17" s="139">
+        <v>46083</v>
+      </c>
+      <c r="D17" s="139">
+        <v>45992</v>
+      </c>
+      <c r="E17" s="98"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="98"/>
+      <c r="I17" s="96"/>
+      <c r="K17" s="117"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>280</v>
       </c>
-      <c r="B17" s="98">
+      <c r="B18" s="98">
         <v>45958</v>
       </c>
-      <c r="C17" s="98">
+      <c r="C18" s="98">
         <v>46199</v>
       </c>
-      <c r="D17" s="98">
+      <c r="D18" s="98">
         <v>46080</v>
       </c>
-      <c r="E17" s="136">
-        <v>46367</v>
-      </c>
-      <c r="F17" s="136">
+      <c r="E18" s="136">
+        <v>46332</v>
+      </c>
+      <c r="F18" s="136">
         <v>46269</v>
       </c>
-      <c r="G17" s="136">
+      <c r="G18" s="136">
         <v>46395</v>
       </c>
-      <c r="H17" s="136">
+      <c r="H18" s="136">
         <v>46395</v>
       </c>
-      <c r="I17" s="96"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="97" t="s">
+      <c r="I18" s="96"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="97" t="s">
         <v>281</v>
       </c>
-      <c r="B18" s="98">
+      <c r="B19" s="98">
         <v>45982</v>
       </c>
-      <c r="C18" s="98">
+      <c r="C19" s="98">
         <v>46227</v>
       </c>
-      <c r="D18" s="98">
+      <c r="D19" s="98">
         <v>46115</v>
       </c>
-      <c r="E18" s="136">
+      <c r="E19" s="136">
+        <v>46374</v>
+      </c>
+      <c r="F19" s="136">
         <v>46416</v>
       </c>
-      <c r="F18" s="136">
-        <v>46416</v>
-      </c>
-      <c r="G18" s="136">
+      <c r="G19" s="136">
         <v>46430</v>
       </c>
-      <c r="H18" s="136">
+      <c r="H19" s="136">
         <v>46430</v>
       </c>
-      <c r="I18" s="96"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="I19" s="96"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>282</v>
       </c>
-      <c r="B19" s="98">
+      <c r="B20" s="98">
         <v>46087</v>
       </c>
-      <c r="C19" s="98">
+      <c r="C20" s="98">
         <v>46269</v>
       </c>
-      <c r="D19" s="98">
+      <c r="D20" s="98">
         <v>46171</v>
       </c>
-      <c r="E19" s="136">
+      <c r="E20" s="136">
+        <v>46423</v>
+      </c>
+      <c r="F20" s="136">
         <v>46451</v>
       </c>
-      <c r="F19" s="136">
-        <v>46451</v>
-      </c>
-      <c r="G19" s="136">
+      <c r="G20" s="136">
         <v>46465</v>
       </c>
-      <c r="H19" s="136">
+      <c r="H20" s="136">
         <v>46465</v>
       </c>
-      <c r="I19" s="96"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="97" t="s">
+      <c r="I20" s="96"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="97" t="s">
         <v>283</v>
       </c>
-      <c r="B20" s="98">
+      <c r="B21" s="98">
         <v>46122</v>
       </c>
-      <c r="C20" s="98">
+      <c r="C21" s="98">
         <v>46297</v>
       </c>
-      <c r="D20" s="98">
+      <c r="D21" s="98">
         <v>46206</v>
       </c>
-      <c r="E20" s="136">
+      <c r="E21" s="136">
+        <v>46458</v>
+      </c>
+      <c r="F21" s="136">
         <v>46486</v>
       </c>
-      <c r="F20" s="136">
-        <v>46486</v>
-      </c>
-      <c r="G20" s="136">
+      <c r="G21" s="136">
         <v>46500</v>
       </c>
-      <c r="H20" s="136">
+      <c r="H21" s="136">
         <v>46500</v>
       </c>
-      <c r="I20" s="96"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="I21" s="96"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>284</v>
       </c>
-      <c r="B21" s="98">
+      <c r="B22" s="98">
         <v>46143</v>
       </c>
-      <c r="C21" s="98">
+      <c r="C22" s="98">
         <v>46339</v>
       </c>
-      <c r="D21" s="98">
+      <c r="D22" s="98">
         <v>46241</v>
       </c>
-      <c r="E21" s="136">
+      <c r="E22" s="136">
+        <v>46493</v>
+      </c>
+      <c r="F22" s="136">
         <v>46521</v>
       </c>
-      <c r="F21" s="136">
-        <v>46521</v>
-      </c>
-      <c r="G21" s="136">
+      <c r="G22" s="136">
         <v>46535</v>
       </c>
-      <c r="H21" s="136">
+      <c r="H22" s="136">
         <v>46535</v>
       </c>
-      <c r="I21" s="96"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="I22" s="96"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>285</v>
       </c>
-      <c r="B22" s="98">
+      <c r="B23" s="98">
         <v>46153</v>
       </c>
-      <c r="C22" s="98">
+      <c r="C23" s="98">
         <v>46370</v>
       </c>
-      <c r="D22" s="98">
+      <c r="D23" s="98">
         <v>46132</v>
       </c>
-      <c r="E22" s="136">
+      <c r="E23" s="136"/>
+      <c r="F23" s="136">
         <v>46531</v>
       </c>
-      <c r="F22" s="136">
-        <v>46531</v>
-      </c>
-      <c r="G22" s="136">
+      <c r="G23" s="136">
         <v>46545</v>
       </c>
-      <c r="H22" s="136">
+      <c r="H23" s="136">
         <v>46545</v>
       </c>
-      <c r="I22" s="96"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="I23" s="96"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>286</v>
       </c>
-      <c r="B23" s="98">
+      <c r="B24" s="98">
         <v>46248</v>
       </c>
-      <c r="C23" s="98">
+      <c r="C24" s="98">
         <v>46465</v>
       </c>
-      <c r="D23" s="98">
+      <c r="D24" s="98">
         <v>46780</v>
       </c>
-      <c r="E23" s="136">
+      <c r="E24" s="136">
         <v>46731</v>
       </c>
-      <c r="F23" s="136">
+      <c r="F24" s="136">
         <v>46731</v>
       </c>
-      <c r="G23" s="136">
+      <c r="G24" s="136">
         <v>46913</v>
       </c>
-      <c r="H23" s="136">
+      <c r="H24" s="136">
         <v>46913</v>
       </c>
-      <c r="I23" s="96"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="97" t="s">
+      <c r="I24" s="96"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="97" t="s">
         <v>287</v>
       </c>
-      <c r="B24" s="98">
+      <c r="B25" s="98">
         <v>46272</v>
       </c>
-      <c r="C24" s="98">
+      <c r="C25" s="98">
         <v>46496</v>
       </c>
-      <c r="D24" s="98">
+      <c r="D25" s="98">
         <v>46811</v>
       </c>
-      <c r="E24" s="136">
+      <c r="E25" s="136">
         <v>46762</v>
       </c>
-      <c r="F24" s="136">
+      <c r="F25" s="136">
         <v>46762</v>
       </c>
-      <c r="G24" s="136">
+      <c r="G25" s="136">
         <v>46944</v>
       </c>
-      <c r="H24" s="136">
+      <c r="H25" s="136">
         <v>46944</v>
       </c>
-      <c r="I24" s="96"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="97" t="s">
+      <c r="I25" s="96"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="97" t="s">
         <v>325</v>
       </c>
-      <c r="B25" s="98">
+      <c r="B26" s="98">
         <v>46878</v>
       </c>
-      <c r="C25" s="98">
+      <c r="C26" s="98">
         <v>47102</v>
       </c>
-      <c r="D25" s="98">
+      <c r="D26" s="98">
         <v>47417</v>
       </c>
-      <c r="E25" s="136">
+      <c r="E26" s="136">
         <v>47375</v>
       </c>
-      <c r="F25" s="136">
+      <c r="F26" s="136">
         <v>47375</v>
       </c>
-      <c r="G25" s="136">
+      <c r="G26" s="136">
         <v>47543</v>
       </c>
-      <c r="H25" s="136">
+      <c r="H26" s="136">
         <v>47543</v>
       </c>
-      <c r="I25" s="96"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="97" t="s">
+      <c r="I26" s="96"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="97" t="s">
         <v>288</v>
       </c>
-      <c r="B26" s="98">
+      <c r="B27" s="98">
         <v>47056</v>
       </c>
-      <c r="C26" s="98">
+      <c r="C27" s="98">
         <v>47291</v>
       </c>
-      <c r="D26" s="98">
+      <c r="D27" s="98">
         <v>47616</v>
       </c>
-      <c r="E26" s="136">
+      <c r="E27" s="136">
         <v>47553</v>
       </c>
-      <c r="F26" s="136">
+      <c r="F27" s="136">
         <v>47553</v>
       </c>
-      <c r="G26" s="136">
+      <c r="G27" s="136">
         <v>47735</v>
       </c>
-      <c r="H26" s="136">
+      <c r="H27" s="136">
         <v>47735</v>
       </c>
-      <c r="I26" s="96"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="97" t="s">
+      <c r="I27" s="96"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="97" t="s">
         <v>289</v>
       </c>
-      <c r="B27" s="98">
+      <c r="B28" s="98">
         <v>47245</v>
       </c>
-      <c r="C27" s="98">
+      <c r="C28" s="98">
         <v>47455</v>
       </c>
-      <c r="D27" s="98">
+      <c r="D28" s="98">
         <v>47791</v>
       </c>
-      <c r="E27" s="136">
+      <c r="E28" s="136">
         <v>47728</v>
       </c>
-      <c r="F27" s="136">
+      <c r="F28" s="136">
         <v>47728</v>
       </c>
-      <c r="G27" s="136">
+      <c r="G28" s="136">
         <v>47917</v>
       </c>
-      <c r="H27" s="136">
+      <c r="H28" s="136">
         <v>47917</v>
       </c>
-      <c r="I27" s="96"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="97" t="s">
-        <v>537</v>
-      </c>
-      <c r="B28" s="98" t="s">
-        <v>348</v>
-      </c>
-      <c r="C28" s="98" t="s">
-        <v>349</v>
-      </c>
-      <c r="D28" s="98" t="s">
-        <v>350</v>
-      </c>
-      <c r="E28" s="136" t="s">
-        <v>350</v>
-      </c>
-      <c r="F28" s="136" t="s">
-        <v>350</v>
-      </c>
-      <c r="G28" s="136" t="s">
-        <v>350</v>
-      </c>
-      <c r="H28" s="136" t="s">
-        <v>350</v>
-      </c>
       <c r="I28" s="96"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="97" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="B29" s="98" t="s">
         <v>348</v>
@@ -21648,57 +21957,57 @@
       </c>
       <c r="I29" s="96"/>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="139" t="s">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="97" t="s">
+        <v>542</v>
+      </c>
+      <c r="B30" s="98" t="s">
+        <v>348</v>
+      </c>
+      <c r="C30" s="98" t="s">
+        <v>349</v>
+      </c>
+      <c r="D30" s="98" t="s">
+        <v>350</v>
+      </c>
+      <c r="E30" s="136" t="s">
+        <v>350</v>
+      </c>
+      <c r="F30" s="136" t="s">
+        <v>350</v>
+      </c>
+      <c r="G30" s="136" t="s">
+        <v>350</v>
+      </c>
+      <c r="H30" s="136" t="s">
+        <v>350</v>
+      </c>
+      <c r="I30" s="96"/>
+    </row>
+    <row r="31" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="138" t="s">
         <v>324</v>
       </c>
-      <c r="C30" s="98"/>
-      <c r="D30" s="98"/>
-      <c r="E30" s="98"/>
-      <c r="F30" s="98"/>
-      <c r="G30" s="98"/>
-      <c r="H30" s="98"/>
-      <c r="I30" s="96"/>
-    </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="94" t="s">
+      <c r="C31" s="98"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="98"/>
+      <c r="H31" s="98"/>
+      <c r="I31" s="96"/>
+    </row>
+    <row r="32" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="94" t="s">
         <v>291</v>
       </c>
-      <c r="B31" s="98">
+      <c r="B32" s="98">
         <v>46107</v>
       </c>
-      <c r="C31" s="98">
+      <c r="C32" s="98">
         <v>46307</v>
       </c>
-      <c r="D31" s="98">
-        <v>46209</v>
-      </c>
-      <c r="E31" s="98" t="s">
-        <v>84</v>
-      </c>
-      <c r="F31" s="98" t="s">
-        <v>84</v>
-      </c>
-      <c r="G31" s="98" t="s">
-        <v>84</v>
-      </c>
-      <c r="H31" s="98" t="s">
-        <v>84</v>
-      </c>
-      <c r="I31" s="96"/>
-    </row>
-    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="94" t="s">
-        <v>292</v>
-      </c>
-      <c r="B32" s="98">
-        <v>46100</v>
-      </c>
-      <c r="C32" s="98">
-        <v>46317</v>
-      </c>
       <c r="D32" s="98">
-        <v>46212</v>
+        <v>46188</v>
       </c>
       <c r="E32" s="98" t="s">
         <v>84</v>
@@ -21715,17 +22024,17 @@
       <c r="I32" s="96"/>
     </row>
     <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="95" t="s">
-        <v>293</v>
+      <c r="A33" s="94" t="s">
+        <v>292</v>
       </c>
       <c r="B33" s="98">
-        <v>46108</v>
+        <v>46100</v>
       </c>
       <c r="C33" s="98">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="D33" s="98">
-        <v>46213</v>
+        <v>46198</v>
       </c>
       <c r="E33" s="98" t="s">
         <v>84</v>
@@ -21742,17 +22051,17 @@
       <c r="I33" s="96"/>
     </row>
     <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="94" t="s">
-        <v>334</v>
+      <c r="A34" s="95" t="s">
+        <v>293</v>
       </c>
       <c r="B34" s="98">
-        <v>46111</v>
+        <v>46108</v>
       </c>
       <c r="C34" s="98">
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="D34" s="98">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="E34" s="98" t="s">
         <v>84</v>
@@ -21769,17 +22078,17 @@
       <c r="I34" s="96"/>
     </row>
     <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="95" t="s">
-        <v>294</v>
+      <c r="A35" s="94" t="s">
+        <v>334</v>
       </c>
       <c r="B35" s="98">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C35" s="98">
-        <v>46309</v>
+        <v>46321</v>
       </c>
       <c r="D35" s="98">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="E35" s="98" t="s">
         <v>84</v>
@@ -21796,17 +22105,17 @@
       <c r="I35" s="96"/>
     </row>
     <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="94" t="s">
-        <v>295</v>
+      <c r="A36" s="95" t="s">
+        <v>294</v>
       </c>
       <c r="B36" s="98">
-        <v>46114</v>
+        <v>46107</v>
       </c>
       <c r="C36" s="98">
-        <v>46317</v>
+        <v>46309</v>
       </c>
       <c r="D36" s="98">
-        <v>46217</v>
+        <v>46211</v>
       </c>
       <c r="E36" s="98" t="s">
         <v>84</v>
@@ -21823,17 +22132,17 @@
       <c r="I36" s="96"/>
     </row>
     <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="95" t="s">
-        <v>296</v>
+      <c r="A37" s="94" t="s">
+        <v>295</v>
       </c>
       <c r="B37" s="98">
-        <v>46122</v>
+        <v>46114</v>
       </c>
       <c r="C37" s="98">
-        <v>46323</v>
+        <v>46317</v>
       </c>
       <c r="D37" s="98">
-        <v>46224</v>
+        <v>46217</v>
       </c>
       <c r="E37" s="98" t="s">
         <v>84</v>
@@ -21850,17 +22159,17 @@
       <c r="I37" s="96"/>
     </row>
     <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="94" t="s">
-        <v>259</v>
+      <c r="A38" s="95" t="s">
+        <v>296</v>
       </c>
       <c r="B38" s="98">
-        <v>46127</v>
+        <v>46122</v>
       </c>
       <c r="C38" s="98">
-        <v>46330</v>
+        <v>46323</v>
       </c>
       <c r="D38" s="98">
-        <v>46231</v>
+        <v>46224</v>
       </c>
       <c r="E38" s="98" t="s">
         <v>84</v>
@@ -21877,17 +22186,17 @@
       <c r="I38" s="96"/>
     </row>
     <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="95" t="s">
-        <v>424</v>
+      <c r="A39" s="94" t="s">
+        <v>259</v>
       </c>
       <c r="B39" s="98">
-        <v>46139</v>
+        <v>46127</v>
       </c>
       <c r="C39" s="98">
-        <v>46341</v>
-      </c>
-      <c r="D39" s="119">
-        <v>46230</v>
+        <v>46330</v>
+      </c>
+      <c r="D39" s="98">
+        <v>46231</v>
       </c>
       <c r="E39" s="98" t="s">
         <v>84</v>
@@ -21904,17 +22213,17 @@
       <c r="I39" s="96"/>
     </row>
     <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="94" t="s">
-        <v>297</v>
+      <c r="A40" s="95" t="s">
+        <v>424</v>
       </c>
       <c r="B40" s="98">
-        <v>46146</v>
+        <v>46139</v>
       </c>
       <c r="C40" s="98">
-        <v>46345</v>
+        <v>46341</v>
       </c>
       <c r="D40" s="98">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="E40" s="98" t="s">
         <v>84</v>
@@ -21931,17 +22240,17 @@
       <c r="I40" s="96"/>
     </row>
     <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="95" t="s">
-        <v>298</v>
+      <c r="A41" s="94" t="s">
+        <v>297</v>
       </c>
       <c r="B41" s="98">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="C41" s="98">
         <v>46345</v>
       </c>
       <c r="D41" s="98">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="E41" s="98" t="s">
         <v>84</v>
@@ -21958,17 +22267,17 @@
       <c r="I41" s="96"/>
     </row>
     <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="94" t="s">
-        <v>261</v>
+      <c r="A42" s="95" t="s">
+        <v>298</v>
       </c>
       <c r="B42" s="98">
-        <v>46153</v>
+        <v>46147</v>
       </c>
       <c r="C42" s="98">
-        <v>46358</v>
+        <v>46345</v>
       </c>
       <c r="D42" s="98">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="E42" s="98" t="s">
         <v>84</v>
@@ -21985,26 +22294,38 @@
       <c r="I42" s="96"/>
     </row>
     <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="95" t="s">
-        <v>594</v>
+      <c r="A43" s="94" t="s">
+        <v>261</v>
       </c>
       <c r="B43" s="98">
+        <v>46153</v>
+      </c>
+      <c r="C43" s="98">
+        <v>46358</v>
+      </c>
+      <c r="D43" s="98">
+        <v>46244</v>
+      </c>
+      <c r="E43" s="98" t="s">
+        <v>84</v>
+      </c>
+      <c r="F43" s="98" t="s">
+        <v>84</v>
+      </c>
+      <c r="G43" s="98" t="s">
+        <v>84</v>
+      </c>
+      <c r="H43" s="98" t="s">
+        <v>84</v>
+      </c>
+      <c r="I43" s="96"/>
+    </row>
+    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="95" t="s">
+        <v>593</v>
+      </c>
+      <c r="B44" s="98">
         <v>46148</v>
-      </c>
-      <c r="C43" s="98"/>
-      <c r="D43" s="98"/>
-      <c r="E43" s="98"/>
-      <c r="F43" s="98"/>
-      <c r="G43" s="98"/>
-      <c r="H43" s="98"/>
-      <c r="I43" s="96"/>
-    </row>
-    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="94" t="s">
-        <v>595</v>
-      </c>
-      <c r="B44" s="98">
-        <v>46154</v>
       </c>
       <c r="C44" s="98"/>
       <c r="D44" s="98"/>
@@ -22015,258 +22336,246 @@
       <c r="I44" s="96"/>
     </row>
     <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="95" t="s">
-        <v>299</v>
+      <c r="A45" s="94" t="s">
+        <v>594</v>
       </c>
       <c r="B45" s="98">
         <v>46154</v>
       </c>
-      <c r="C45" s="98">
+      <c r="C45" s="98"/>
+      <c r="D45" s="98"/>
+      <c r="E45" s="98"/>
+      <c r="F45" s="98"/>
+      <c r="G45" s="98"/>
+      <c r="H45" s="98"/>
+      <c r="I45" s="96"/>
+    </row>
+    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="95" t="s">
+        <v>299</v>
+      </c>
+      <c r="B46" s="98">
+        <v>46154</v>
+      </c>
+      <c r="C46" s="98">
         <v>46357</v>
       </c>
-      <c r="D45" s="98">
+      <c r="D46" s="98">
         <v>46245</v>
       </c>
-      <c r="E45" s="98" t="s">
+      <c r="E46" s="98" t="s">
         <v>84</v>
       </c>
-      <c r="F45" s="98" t="s">
+      <c r="F46" s="98" t="s">
         <v>84</v>
       </c>
-      <c r="G45" s="98" t="s">
+      <c r="G46" s="98" t="s">
         <v>84</v>
       </c>
-      <c r="H45" s="98" t="s">
+      <c r="H46" s="98" t="s">
         <v>84</v>
       </c>
-      <c r="I45" s="96"/>
-    </row>
-    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="94" t="s">
+      <c r="I46" s="96"/>
+    </row>
+    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="94" t="s">
         <v>262</v>
       </c>
-      <c r="B46" s="98">
+      <c r="B47" s="98">
         <v>46162</v>
       </c>
-      <c r="C46" s="98">
+      <c r="C47" s="98">
         <v>46366</v>
       </c>
-      <c r="D46" s="98">
+      <c r="D47" s="98">
         <v>46253</v>
       </c>
-      <c r="E46" s="136">
+      <c r="E47" s="136">
         <v>46555</v>
       </c>
-      <c r="F46" s="136">
+      <c r="F47" s="136">
         <v>46555</v>
       </c>
-      <c r="G46" s="136">
+      <c r="G47" s="136">
         <v>46583</v>
       </c>
-      <c r="H46" s="136">
+      <c r="H47" s="136">
         <v>46583</v>
       </c>
-      <c r="I46" s="96"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="138" t="s">
+      <c r="I47" s="96"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="137" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>527</v>
-      </c>
-      <c r="B48" s="98">
-        <f t="shared" ref="B48:H48" si="0">B17-30</f>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>526</v>
+      </c>
+      <c r="B49" s="98">
+        <f t="shared" ref="B49:H49" si="0">B18-30</f>
         <v>45928</v>
       </c>
-      <c r="C48" s="98">
+      <c r="C49" s="98">
         <f t="shared" si="0"/>
         <v>46169</v>
       </c>
-      <c r="D48" s="98">
+      <c r="D49" s="98">
         <f t="shared" si="0"/>
         <v>46050</v>
       </c>
-      <c r="E48" s="98">
+      <c r="E49" s="98">
         <f t="shared" si="0"/>
-        <v>46337</v>
-      </c>
-      <c r="F48" s="98">
+        <v>46302</v>
+      </c>
+      <c r="F49" s="98">
         <f t="shared" si="0"/>
         <v>46239</v>
       </c>
-      <c r="G48" s="98">
+      <c r="G49" s="98">
         <f t="shared" si="0"/>
         <v>46365</v>
       </c>
-      <c r="H48" s="98">
+      <c r="H49" s="98">
         <f t="shared" si="0"/>
         <v>46365</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>528</v>
-      </c>
-      <c r="B49" s="98">
-        <f t="shared" ref="B49:H49" si="1">B19-30</f>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>527</v>
+      </c>
+      <c r="B50" s="98">
+        <f t="shared" ref="B50:H50" si="1">B20-30</f>
         <v>46057</v>
       </c>
-      <c r="C49" s="98">
+      <c r="C50" s="98">
         <f t="shared" si="1"/>
         <v>46239</v>
       </c>
-      <c r="D49" s="98">
+      <c r="D50" s="98">
         <f t="shared" si="1"/>
         <v>46141</v>
       </c>
-      <c r="E49" s="98">
+      <c r="E50" s="98">
+        <f t="shared" si="1"/>
+        <v>46393</v>
+      </c>
+      <c r="F50" s="98">
         <f t="shared" si="1"/>
         <v>46421</v>
       </c>
-      <c r="F49" s="98">
-        <f t="shared" si="1"/>
-        <v>46421</v>
-      </c>
-      <c r="G49" s="98">
+      <c r="G50" s="98">
         <f t="shared" si="1"/>
         <v>46435</v>
       </c>
-      <c r="H49" s="98">
+      <c r="H50" s="98">
         <f t="shared" si="1"/>
         <v>46435</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>529</v>
-      </c>
-      <c r="B50" s="98">
-        <f t="shared" ref="B50:H50" si="2">B21-30</f>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>528</v>
+      </c>
+      <c r="B51" s="98">
+        <f t="shared" ref="B51:H51" si="2">B22-30</f>
         <v>46113</v>
       </c>
-      <c r="C50" s="98">
+      <c r="C51" s="98">
         <f t="shared" si="2"/>
         <v>46309</v>
       </c>
-      <c r="D50" s="98">
+      <c r="D51" s="98">
         <f t="shared" si="2"/>
         <v>46211</v>
       </c>
-      <c r="E50" s="98">
+      <c r="E51" s="98">
+        <f t="shared" si="2"/>
+        <v>46463</v>
+      </c>
+      <c r="F51" s="98">
         <f t="shared" si="2"/>
         <v>46491</v>
       </c>
-      <c r="F50" s="98">
-        <f t="shared" si="2"/>
-        <v>46491</v>
-      </c>
-      <c r="G50" s="98">
+      <c r="G51" s="98">
         <f t="shared" si="2"/>
         <v>46505</v>
       </c>
-      <c r="H50" s="98">
+      <c r="H51" s="98">
         <f t="shared" si="2"/>
         <v>46505</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>530</v>
-      </c>
-      <c r="B51" s="98">
-        <f t="shared" ref="B51:C51" si="3">B46+7</f>
-        <v>46169</v>
-      </c>
-      <c r="C51" s="98">
-        <f t="shared" si="3"/>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>529</v>
+      </c>
+      <c r="B52" s="98">
+        <v>46183</v>
+      </c>
+      <c r="C52" s="98">
+        <f t="shared" ref="C52" si="3">C47+7</f>
         <v>46373</v>
       </c>
-      <c r="D51" s="98">
-        <f>D46+7</f>
+      <c r="D52" s="98">
+        <f>D47+7</f>
         <v>46260</v>
       </c>
-      <c r="E51" s="98">
-        <f t="shared" ref="E51:H51" si="4">E46+7</f>
+      <c r="E52" s="98">
+        <f t="shared" ref="E52:H52" si="4">E47+7</f>
         <v>46562</v>
       </c>
-      <c r="F51" s="98">
+      <c r="F52" s="98">
         <f t="shared" si="4"/>
         <v>46562</v>
       </c>
-      <c r="G51" s="98">
+      <c r="G52" s="98">
         <f t="shared" si="4"/>
         <v>46590</v>
       </c>
-      <c r="H51" s="98">
+      <c r="H52" s="98">
         <f t="shared" si="4"/>
         <v>46590</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>524</v>
-      </c>
-      <c r="B52" s="98">
-        <f t="shared" ref="B52:C52" si="5">B26-517</f>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>523</v>
+      </c>
+      <c r="B53" s="98">
+        <f t="shared" ref="B53:C53" si="5">B27-517</f>
         <v>46539</v>
       </c>
-      <c r="C52" s="98">
+      <c r="C53" s="98">
         <f t="shared" si="5"/>
         <v>46774</v>
       </c>
-      <c r="D52" s="98">
-        <f>D26-517</f>
+      <c r="D53" s="98">
+        <f>D27-517</f>
         <v>47099</v>
       </c>
-      <c r="E52" s="98">
-        <f>E26-517</f>
+      <c r="E53" s="98">
+        <f>E27-517</f>
         <v>47036</v>
       </c>
-      <c r="F52" s="98">
-        <f t="shared" ref="F52:H52" si="6">F26-517</f>
+      <c r="F53" s="98">
+        <f t="shared" ref="F53:H53" si="6">F27-517</f>
         <v>47036</v>
       </c>
-      <c r="G52" s="98">
+      <c r="G53" s="98">
         <f t="shared" si="6"/>
         <v>47218</v>
       </c>
-      <c r="H52" s="98">
+      <c r="H53" s="98">
         <f t="shared" si="6"/>
         <v>47218</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>525</v>
-      </c>
-      <c r="B53" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="C53" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="D53" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="E53" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="F53" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="G53" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="H53" s="33" t="s">
-        <v>84</v>
-      </c>
-    </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B54" s="33" t="s">
         <v>84</v>
@@ -22291,50 +22600,49 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="138" t="s">
+      <c r="A55" t="s">
+        <v>525</v>
+      </c>
+      <c r="B55" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="D55" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="E55" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F55" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="G55" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="H55" s="33" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="137" t="s">
         <v>414</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>416</v>
-      </c>
-      <c r="B56" s="98">
-        <v>46097</v>
-      </c>
-      <c r="C56" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="D56" s="98">
-        <f>D57-14</f>
-        <v>46174</v>
-      </c>
-      <c r="E56" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="F56" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="G56" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="H56" s="33" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B57" s="98">
-        <v>46118</v>
+        <v>46097</v>
       </c>
       <c r="C57" s="33" t="s">
         <v>84</v>
       </c>
       <c r="D57" s="98">
-        <f>D31-21</f>
-        <v>46188</v>
+        <f>D58-14</f>
+        <v>46153</v>
       </c>
       <c r="E57" s="33" t="s">
         <v>84</v>
@@ -22351,16 +22659,17 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B58" s="98">
-        <v>46122</v>
+        <v>46118</v>
       </c>
       <c r="C58" s="33" t="s">
         <v>84</v>
       </c>
       <c r="D58" s="98">
-        <v>46206</v>
+        <f>D32-21</f>
+        <v>46167</v>
       </c>
       <c r="E58" s="33" t="s">
         <v>84</v>
@@ -22377,16 +22686,16 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>415</v>
-      </c>
-      <c r="B59" s="98" t="s">
-        <v>84</v>
+        <v>418</v>
+      </c>
+      <c r="B59" s="98">
+        <v>46122</v>
       </c>
       <c r="C59" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="D59" s="33" t="s">
-        <v>84</v>
+      <c r="D59" s="98">
+        <v>46181</v>
       </c>
       <c r="E59" s="33" t="s">
         <v>84</v>
@@ -22403,10 +22712,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>241</v>
-      </c>
-      <c r="B60" s="98">
-        <v>46121</v>
+        <v>415</v>
+      </c>
+      <c r="B60" s="98" t="s">
+        <v>84</v>
       </c>
       <c r="C60" s="33" t="s">
         <v>84</v>
@@ -22429,16 +22738,16 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>419</v>
+        <v>241</v>
       </c>
       <c r="B61" s="98">
-        <v>46143</v>
+        <v>46121</v>
       </c>
       <c r="C61" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="D61" s="33" t="s">
-        <v>84</v>
+      <c r="D61" s="135">
+        <v>46226</v>
       </c>
       <c r="E61" s="33" t="s">
         <v>84</v>
@@ -22455,16 +22764,16 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B62" s="98">
-        <v>46160</v>
+        <v>46143</v>
       </c>
       <c r="C62" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="D62" s="33" t="s">
-        <v>84</v>
+      <c r="D62" s="135">
+        <v>46241</v>
       </c>
       <c r="E62" s="33" t="s">
         <v>84</v>
@@ -22481,104 +22790,164 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>610</v>
-      </c>
-      <c r="B63" s="98" t="s">
-        <v>125</v>
-      </c>
-      <c r="C63" s="98" t="s">
-        <v>125</v>
-      </c>
-      <c r="D63" s="98">
-        <v>46171</v>
-      </c>
-      <c r="E63" s="98" t="s">
-        <v>125</v>
-      </c>
-      <c r="F63" s="98" t="s">
-        <v>125</v>
-      </c>
-      <c r="G63" s="98" t="s">
-        <v>125</v>
-      </c>
-      <c r="H63" s="98" t="s">
-        <v>125</v>
+        <v>420</v>
+      </c>
+      <c r="B63" s="98">
+        <v>46160</v>
+      </c>
+      <c r="C63" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="D63" s="135">
+        <v>46252</v>
+      </c>
+      <c r="E63" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F63" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="G63" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="H63" s="33" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>544</v>
+        <v>679</v>
       </c>
       <c r="B64" s="98">
-        <v>45800</v>
-      </c>
-      <c r="C64" s="135">
-        <v>46113</v>
-      </c>
-      <c r="D64" s="135">
-        <v>45983</v>
-      </c>
-      <c r="E64" s="137">
-        <v>46231</v>
-      </c>
-      <c r="F64" s="137">
-        <v>46259</v>
-      </c>
-      <c r="G64" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="H64" s="33" t="s">
-        <v>84</v>
+        <v>46183</v>
+      </c>
+      <c r="C64" s="98">
+        <f>C47+8</f>
+        <v>46374</v>
+      </c>
+      <c r="D64" s="98">
+        <f>D47+14</f>
+        <v>46267</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>548</v>
-      </c>
-      <c r="B65" s="98">
-        <v>46141</v>
-      </c>
-      <c r="C65" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="D65" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="E65" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="F65" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="G65" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="H65" s="33" t="s">
-        <v>84</v>
+        <v>609</v>
+      </c>
+      <c r="B65" s="98" t="s">
+        <v>125</v>
+      </c>
+      <c r="C65" s="98" t="s">
+        <v>125</v>
+      </c>
+      <c r="D65" s="98">
+        <v>46170</v>
+      </c>
+      <c r="E65" s="98" t="s">
+        <v>125</v>
+      </c>
+      <c r="F65" s="98" t="s">
+        <v>125</v>
+      </c>
+      <c r="G65" s="98" t="s">
+        <v>125</v>
+      </c>
+      <c r="H65" s="98" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>611</v>
-      </c>
-      <c r="D66" s="135">
-        <v>46171</v>
+        <v>547</v>
+      </c>
+      <c r="B66" s="98">
+        <v>46141</v>
+      </c>
+      <c r="C66" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="D66" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="E66" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F66" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="G66" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="H66" s="33" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D67" s="135">
-        <v>46185</v>
+        <v>46198</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>619</v>
-      </c>
-      <c r="C68" s="135">
+      <c r="A68" s="137" t="s">
+        <v>668</v>
+      </c>
+      <c r="D68" s="135"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>543</v>
+      </c>
+      <c r="B69" s="98">
+        <v>45800</v>
+      </c>
+      <c r="C69" s="135">
+        <v>46113</v>
+      </c>
+      <c r="D69" s="135">
+        <v>45983</v>
+      </c>
+      <c r="E69" s="135">
         <v>46231</v>
+      </c>
+      <c r="F69" s="135">
+        <v>46259</v>
+      </c>
+      <c r="G69" s="135">
+        <v>46240</v>
+      </c>
+      <c r="H69" s="135">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>616</v>
+      </c>
+      <c r="C70" s="135">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>666</v>
+      </c>
+      <c r="C71" s="135">
+        <f>D47</f>
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>669</v>
+      </c>
+      <c r="B72" s="98">
+        <v>46235</v>
+      </c>
+      <c r="C72" s="135">
+        <v>46296</v>
       </c>
     </row>
   </sheetData>
@@ -22607,7 +22976,7 @@
     <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24.7109375" customWidth="1"/>
     <col min="12" max="12" width="9.140625" style="1"/>
-    <col min="14" max="14" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="14.140625" customWidth="1"/>
     <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="47.28515625" customWidth="1"/>
@@ -22693,7 +23062,7 @@
         <v>84</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>473</v>
+        <v>684</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>444</v>
@@ -22723,7 +23092,7 @@
         <v>0.89726877040261155</v>
       </c>
       <c r="S2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -22752,7 +23121,7 @@
         <v>4844</v>
       </c>
       <c r="I3" s="130" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>444</v>
@@ -22765,7 +23134,7 @@
         <v>298</v>
       </c>
       <c r="N3" s="123">
-        <v>195514000</v>
+        <v>1394669978</v>
       </c>
       <c r="O3" s="123">
         <v>100633569</v>
@@ -22779,10 +23148,10 @@
       </c>
       <c r="R3" s="124">
         <f>Q3/N3</f>
-        <v>0.6280226326503473</v>
+        <v>8.8040338529463927E-2</v>
       </c>
       <c r="S3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -22811,7 +23180,7 @@
         <v>84</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>451</v>
@@ -22841,7 +23210,7 @@
         <v>0.79850407978241156</v>
       </c>
       <c r="S4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="T4" s="125" t="s">
         <v>218</v>
@@ -22994,7 +23363,7 @@
         <v>218</v>
       </c>
       <c r="S7" s="127" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -23047,7 +23416,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -23100,7 +23469,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -23126,7 +23495,7 @@
         <v>84</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>451</v>
@@ -23153,7 +23522,7 @@
         <v>0.11600000000000001</v>
       </c>
       <c r="S10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -23206,7 +23575,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -23320,28 +23689,28 @@
         <v>396</v>
       </c>
       <c r="N1" s="97" t="s">
+        <v>659</v>
+      </c>
+      <c r="O1" s="97" t="s">
+        <v>659</v>
+      </c>
+      <c r="P1" s="97" t="s">
+        <v>659</v>
+      </c>
+      <c r="Q1" s="115" t="s">
+        <v>659</v>
+      </c>
+      <c r="R1" s="115" t="s">
+        <v>659</v>
+      </c>
+      <c r="S1" s="115" t="s">
+        <v>659</v>
+      </c>
+      <c r="T1" s="115" t="s">
+        <v>661</v>
+      </c>
+      <c r="U1" s="115" t="s">
         <v>662</v>
-      </c>
-      <c r="O1" s="97" t="s">
-        <v>662</v>
-      </c>
-      <c r="P1" s="97" t="s">
-        <v>662</v>
-      </c>
-      <c r="Q1" s="115" t="s">
-        <v>662</v>
-      </c>
-      <c r="R1" s="115" t="s">
-        <v>662</v>
-      </c>
-      <c r="S1" s="115" t="s">
-        <v>662</v>
-      </c>
-      <c r="T1" s="115" t="s">
-        <v>664</v>
-      </c>
-      <c r="U1" s="115" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -23355,7 +23724,7 @@
         <v>381</v>
       </c>
       <c r="D2" s="115" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="E2" s="115" t="s">
         <v>386</v>
@@ -23460,13 +23829,13 @@
         <v>390</v>
       </c>
       <c r="Q3" s="115" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="R3" s="115" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="S3" s="115" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="T3" s="115" t="s">
         <v>390</v>
@@ -23733,7 +24102,7 @@
       <c r="M2" s="112" t="s">
         <v>351</v>
       </c>
-      <c r="N2" s="144">
+      <c r="N2" s="143">
         <v>1</v>
       </c>
     </row>
@@ -23753,7 +24122,7 @@
       <c r="M3" s="113" t="s">
         <v>352</v>
       </c>
-      <c r="N3" s="145"/>
+      <c r="N3" s="144"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="109">
@@ -23771,7 +24140,7 @@
       <c r="M4" s="114" t="s">
         <v>353</v>
       </c>
-      <c r="N4" s="146"/>
+      <c r="N4" s="145"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="109">
@@ -23789,7 +24158,7 @@
       <c r="M5" s="112" t="s">
         <v>354</v>
       </c>
-      <c r="N5" s="144">
+      <c r="N5" s="143">
         <v>2</v>
       </c>
     </row>
@@ -23809,7 +24178,7 @@
       <c r="M6" s="113" t="s">
         <v>355</v>
       </c>
-      <c r="N6" s="145"/>
+      <c r="N6" s="144"/>
     </row>
     <row r="7" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="109">
@@ -23827,7 +24196,7 @@
       <c r="M7" s="114" t="s">
         <v>356</v>
       </c>
-      <c r="N7" s="146"/>
+      <c r="N7" s="145"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="109">
@@ -23845,7 +24214,7 @@
       <c r="M8" s="112" t="s">
         <v>357</v>
       </c>
-      <c r="N8" s="144">
+      <c r="N8" s="143">
         <v>3</v>
       </c>
     </row>
@@ -23865,7 +24234,7 @@
       <c r="M9" s="113" t="s">
         <v>358</v>
       </c>
-      <c r="N9" s="145"/>
+      <c r="N9" s="144"/>
     </row>
     <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="109">
@@ -23883,7 +24252,7 @@
       <c r="M10" s="114" t="s">
         <v>359</v>
       </c>
-      <c r="N10" s="146"/>
+      <c r="N10" s="145"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="109">
@@ -23901,7 +24270,7 @@
       <c r="M11" s="112" t="s">
         <v>360</v>
       </c>
-      <c r="N11" s="144">
+      <c r="N11" s="143">
         <v>4</v>
       </c>
     </row>
@@ -23921,7 +24290,7 @@
       <c r="M12" s="113" t="s">
         <v>361</v>
       </c>
-      <c r="N12" s="145"/>
+      <c r="N12" s="144"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="109">
@@ -23939,7 +24308,7 @@
       <c r="M13" s="114" t="s">
         <v>362</v>
       </c>
-      <c r="N13" s="146"/>
+      <c r="N13" s="145"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="109">
@@ -27143,6 +27512,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E2EBBACD82105340A91324964E93FF49" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7329edaaee89349510b5fe31ddec06b8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a8552d75-6f1f-4d52-93a3-fcd36dc2752d" xmlns:ns3="1785dff3-9909-4165-bde0-36ec47a4b18f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="52e457d9bdc8fb3aec099fc7d60c5993" ns2:_="" ns3:_="">
     <xsd:import namespace="a8552d75-6f1f-4d52-93a3-fcd36dc2752d"/>
@@ -27377,33 +27755,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{752F9F6E-B88F-40CF-A00D-5A52044E6B25}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="1785dff3-9909-4165-bde0-36ec47a4b18f"/>
     <ds:schemaRef ds:uri="a8552d75-6f1f-4d52-93a3-fcd36dc2752d"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1785dff3-9909-4165-bde0-36ec47a4b18f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8993D78-ABDB-48CF-A6AD-3E9555EB10CC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89752E9E-F7C9-411F-9EA3-B9C1D8EEB123}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27420,12 +27797,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8993D78-ABDB-48CF-A6AD-3E9555EB10CC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/NG Scheduling.xlsx
+++ b/NG Scheduling.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://my.wal-mart.com/personal/k0m0eg1_homeoffice_wal-mart_com/Documents/Desktop/Code Puppy Saved Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2344" documentId="8_{3CD9A91E-A1DC-493E-B251-6A7E654DFCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45BE24A5-DC1A-4982-9B2C-8D57ADB6FF3B}"/>
+  <xr:revisionPtr revIDLastSave="2377" documentId="8_{3CD9A91E-A1DC-493E-B251-6A7E654DFCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5217EE18-9E55-4556-86F0-942B1BB0F450}"/>
   <bookViews>
-    <workbookView xWindow="17385" yWindow="2370" windowWidth="29385" windowHeight="17580" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21030" yWindow="2445" windowWidth="23940" windowHeight="17760" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TUE FC Asset Plan SteerCo" sheetId="2" state="hidden" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NG Budget'!$A$1:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NG Scheduling'!$A$1:$P$446</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NG Scheduling'!$A$1:$P$445</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TUE FC Asset Plan SteerCo'!$A$3:$H$91</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -190,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="690">
   <si>
     <t>Fulfillment New Assets SteerCo (Tuesday's)</t>
   </si>
@@ -1516,9 +1516,6 @@
     <t>This was cancelled since the meeting was moved post REC</t>
   </si>
   <si>
-    <t>BRR Approval for MSP, DEN, &amp; SEA</t>
-  </si>
-  <si>
     <t>Buckeye: Transportation &amp; Solar Land Requirements</t>
   </si>
   <si>
@@ -2245,9 +2242,6 @@
     <t>Ellen Sloneker, Phil Herr</t>
   </si>
   <si>
-    <t>BDR for MSP, DEN, SEA Sign-off (Confirm path to 150M capacity ramp by FY)</t>
-  </si>
-  <si>
     <t>Adam Dunbar, Barat Smith, Zach Freeze, Karen Slatton</t>
   </si>
   <si>
@@ -2543,6 +2537,18 @@
   </si>
   <si>
     <t>26_06_03 SteerCo.pptx</t>
+  </si>
+  <si>
+    <t>Buckeye Business Case (CapEx &amp; IRR)</t>
+  </si>
+  <si>
+    <t>CPC (Non-Discussion)</t>
+  </si>
+  <si>
+    <t>NextGen vs Store Comparison</t>
+  </si>
+  <si>
+    <t>Wallkill vs DWF Comparison</t>
   </si>
 </sst>
 </file>
@@ -8498,7 +8504,7 @@
   <sheetPr filterMode="1">
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:AI446"/>
+  <dimension ref="A1:AI445"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10.85546875" style="33" bestFit="1" customWidth="1"/>
@@ -8542,7 +8548,7 @@
         <v>335</v>
       </c>
       <c r="H1" s="106" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="I1" s="102" t="s">
         <v>337</v>
@@ -8551,7 +8557,7 @@
         <v>4</v>
       </c>
       <c r="K1" s="66" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="L1" s="88" t="s">
         <v>270</v>
@@ -8560,13 +8566,13 @@
         <v>238</v>
       </c>
       <c r="N1" s="87" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="O1" s="87" t="s">
         <v>253</v>
       </c>
       <c r="P1" s="88" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AI1" s="99" t="s">
         <v>336</v>
@@ -8574,7 +8580,7 @@
     </row>
     <row r="2" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>266</v>
@@ -8583,13 +8589,13 @@
         <v>187</v>
       </c>
       <c r="D2" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E2" s="132">
         <v>46044</v>
       </c>
       <c r="F2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G2" s="33" t="str">
         <f>A2</f>
@@ -8612,17 +8618,17 @@
         <v>142</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="N2" s="32" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="P2" s="92"/>
       <c r="AI2" s="91"/>
     </row>
     <row r="3" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>266</v>
@@ -8631,13 +8637,13 @@
         <v>187</v>
       </c>
       <c r="D3" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E3" s="132">
         <v>46044</v>
       </c>
       <c r="F3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G3" s="33" t="str">
         <f>A3</f>
@@ -8660,7 +8666,7 @@
         <v>142</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="P3" s="92"/>
       <c r="AI3" s="91">
@@ -8670,7 +8676,7 @@
     </row>
     <row r="4" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>266</v>
@@ -8679,13 +8685,13 @@
         <v>187</v>
       </c>
       <c r="D4" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E4" s="132">
         <v>46044</v>
       </c>
       <c r="F4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G4" s="33" t="str">
         <f>A4</f>
@@ -8708,10 +8714,10 @@
         <v>142</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N4" s="32" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="P4" s="92"/>
       <c r="AI4" s="91">
@@ -8721,7 +8727,7 @@
     </row>
     <row r="5" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>266</v>
@@ -8736,7 +8742,7 @@
         <v>46045</v>
       </c>
       <c r="F5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G5" s="33" t="str">
         <f>A5</f>
@@ -8762,7 +8768,7 @@
         <v>237</v>
       </c>
       <c r="N5" s="32" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="P5" s="92"/>
       <c r="AI5" s="91">
@@ -8770,7 +8776,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="6" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="e">
         <f>IF(ISBLANK(E6),"",_xlfn.XLOOKUP(E6,Info!A:A,Info!B:B))</f>
         <v>#N/A</v>
@@ -8788,7 +8794,7 @@
         <v>46051</v>
       </c>
       <c r="F6" s="54" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="G6" s="33" t="e">
         <f>IF(ISBLANK(H6),"",_xlfn.XLOOKUP(H6,Info!A:A,Info!B:B))</f>
@@ -8814,13 +8820,13 @@
         <v>247</v>
       </c>
       <c r="N6" s="92" t="s">
+        <v>599</v>
+      </c>
+      <c r="O6" s="118" t="s">
+        <v>600</v>
+      </c>
+      <c r="P6" s="92" t="s">
         <v>601</v>
-      </c>
-      <c r="O6" s="118" t="s">
-        <v>602</v>
-      </c>
-      <c r="P6" s="92" t="s">
-        <v>603</v>
       </c>
       <c r="AI6" s="91">
         <f t="shared" si="1"/>
@@ -8839,13 +8845,13 @@
         <v>187</v>
       </c>
       <c r="D7" s="134" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E7" s="132">
         <v>46056</v>
       </c>
       <c r="F7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G7" s="33">
         <f>IF(ISBLANK(H7),"",_xlfn.XLOOKUP(H7,Info!A:A,Info!B:B))</f>
@@ -8868,10 +8874,10 @@
         <v>142</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="N7" s="92" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="P7" s="92"/>
       <c r="AI7" s="91">
@@ -8891,13 +8897,13 @@
         <v>187</v>
       </c>
       <c r="D8" s="134" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E8" s="132">
         <v>46056</v>
       </c>
       <c r="F8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G8" s="33">
         <f>IF(ISBLANK(H8),"",_xlfn.XLOOKUP(H8,Info!A:A,Info!B:B))</f>
@@ -8920,10 +8926,10 @@
         <v>142</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="N8" s="92" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="P8" s="92"/>
       <c r="AI8" s="91">
@@ -8943,13 +8949,13 @@
         <v>187</v>
       </c>
       <c r="D9" s="134" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E9" s="132">
         <v>46056</v>
       </c>
       <c r="F9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G9" s="33">
         <f>IF(ISBLANK(H9),"",_xlfn.XLOOKUP(H9,Info!A:A,Info!B:B))</f>
@@ -8972,7 +8978,7 @@
         <v>142</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="N9" s="92"/>
       <c r="P9" s="92"/>
@@ -8993,13 +8999,13 @@
         <v>187</v>
       </c>
       <c r="D10" s="134" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E10" s="132">
         <v>46056</v>
       </c>
       <c r="F10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G10" s="33">
         <f>IF(ISBLANK(H10),"",_xlfn.XLOOKUP(H10,Info!A:A,Info!B:B))</f>
@@ -9022,10 +9028,10 @@
         <v>142</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N10" s="92" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="P10" s="92"/>
       <c r="AI10" s="91">
@@ -9045,13 +9051,13 @@
         <v>187</v>
       </c>
       <c r="D11" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E11" s="132">
         <v>46073</v>
       </c>
       <c r="F11" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G11" s="33">
         <f>IF(ISBLANK(H11),"",_xlfn.XLOOKUP(H11,Info!A:A,Info!B:B))</f>
@@ -9074,10 +9080,10 @@
         <v>142</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N11" s="32" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="P11" s="92"/>
       <c r="AI11" s="91">
@@ -9097,13 +9103,13 @@
         <v>187</v>
       </c>
       <c r="D12" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E12" s="132">
         <v>46073</v>
       </c>
       <c r="F12" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G12" s="33">
         <f>IF(ISBLANK(H12),"",_xlfn.XLOOKUP(H12,Info!A:A,Info!B:B))</f>
@@ -9126,13 +9132,13 @@
         <v>142</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="N12" s="32" t="s">
+        <v>517</v>
+      </c>
+      <c r="O12" s="118" t="s">
         <v>518</v>
-      </c>
-      <c r="O12" s="118" t="s">
-        <v>519</v>
       </c>
       <c r="P12" s="92"/>
       <c r="AI12" s="91">
@@ -9152,13 +9158,13 @@
         <v>187</v>
       </c>
       <c r="D13" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E13" s="132">
         <v>46079</v>
       </c>
       <c r="F13" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G13" s="33">
         <f>IF(ISBLANK(H13),"",_xlfn.XLOOKUP(H13,Info!A:A,Info!B:B))</f>
@@ -9202,13 +9208,13 @@
         <v>187</v>
       </c>
       <c r="D14" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E14" s="132">
         <v>46079</v>
       </c>
       <c r="F14" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G14" s="33">
         <f>IF(ISBLANK(H14),"",_xlfn.XLOOKUP(H14,Info!A:A,Info!B:B))</f>
@@ -9225,16 +9231,16 @@
         <v>30</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="O14" s="118" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="P14" s="92"/>
       <c r="AI14" s="91">
@@ -9254,13 +9260,13 @@
         <v>187</v>
       </c>
       <c r="D15" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E15" s="132">
         <v>46079</v>
       </c>
       <c r="F15" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G15" s="33">
         <f>IF(ISBLANK(H15),"",_xlfn.XLOOKUP(H15,Info!A:A,Info!B:B))</f>
@@ -9277,16 +9283,16 @@
         <v>30</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="O15" s="118" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="P15" s="92"/>
       <c r="AI15" s="91">
@@ -9312,7 +9318,7 @@
         <v>46080</v>
       </c>
       <c r="F16" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G16" s="33">
         <f>IF(ISBLANK(H16),"",_xlfn.XLOOKUP(H16,Info!A:A,Info!B:B))</f>
@@ -9335,7 +9341,7 @@
         <v>243</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N16" s="92"/>
       <c r="P16" s="92"/>
@@ -9362,7 +9368,7 @@
         <v>46080</v>
       </c>
       <c r="F17" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G17" s="33">
         <f>IF(ISBLANK(H17),"",_xlfn.XLOOKUP(H17,Info!A:A,Info!B:B))</f>
@@ -9379,13 +9385,13 @@
         <v>30</v>
       </c>
       <c r="K17" s="33" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="L17" s="33" t="s">
         <v>243</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="N17" s="92"/>
       <c r="P17" s="92"/>
@@ -9406,13 +9412,13 @@
         <v>187</v>
       </c>
       <c r="D18" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E18" s="132">
         <v>46083</v>
       </c>
       <c r="F18" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G18" s="33">
         <f>IF(ISBLANK(H18),"",_xlfn.XLOOKUP(H18,Info!A:A,Info!B:B))</f>
@@ -9429,13 +9435,13 @@
         <v>30</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="P18" s="92"/>
       <c r="AI18" s="91">
@@ -9461,7 +9467,7 @@
         <v>46083</v>
       </c>
       <c r="F19" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G19" s="33">
         <f>IF(ISBLANK(H19),"",_xlfn.XLOOKUP(H19,Info!A:A,Info!B:B))</f>
@@ -9478,13 +9484,13 @@
         <v>30</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L19" s="33" t="s">
         <v>142</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N19" s="92"/>
       <c r="P19" s="92"/>
@@ -9505,13 +9511,13 @@
         <v>187</v>
       </c>
       <c r="D20" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E20" s="132">
         <v>46086</v>
       </c>
       <c r="F20" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G20" s="33">
         <f>IF(ISBLANK(H20),"",_xlfn.XLOOKUP(H20,Info!A:A,Info!B:B))</f>
@@ -9537,7 +9543,7 @@
         <v>237</v>
       </c>
       <c r="O20" s="118" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="P20" s="92"/>
       <c r="AI20" s="91">
@@ -9557,13 +9563,13 @@
         <v>187</v>
       </c>
       <c r="D21" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E21" s="132">
         <v>46086</v>
       </c>
       <c r="F21" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G21" s="33">
         <f>IF(ISBLANK(H21),"",_xlfn.XLOOKUP(H21,Info!A:A,Info!B:B))</f>
@@ -9589,10 +9595,10 @@
         <v>237</v>
       </c>
       <c r="N21" s="32" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="O21" s="118" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="P21" s="92"/>
       <c r="AI21" s="91">
@@ -9612,13 +9618,13 @@
         <v>187</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E22" s="132">
         <v>46086</v>
       </c>
       <c r="F22" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G22" s="33">
         <f>IF(ISBLANK(H22),"",_xlfn.XLOOKUP(H22,Info!A:A,Info!B:B))</f>
@@ -9635,7 +9641,7 @@
         <v>30</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>142</v>
@@ -9644,7 +9650,7 @@
         <v>237</v>
       </c>
       <c r="O22" s="118" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AI22" s="91"/>
     </row>
@@ -9660,13 +9666,13 @@
         <v>187</v>
       </c>
       <c r="D23" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E23" s="132">
         <v>46086</v>
       </c>
       <c r="F23" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G23" s="33">
         <f>IF(ISBLANK(H23),"",_xlfn.XLOOKUP(H23,Info!A:A,Info!B:B))</f>
@@ -9692,7 +9698,7 @@
         <v>237</v>
       </c>
       <c r="O23" s="118" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="P23" s="92"/>
       <c r="AI23" s="91"/>
@@ -9709,13 +9715,13 @@
         <v>187</v>
       </c>
       <c r="D24" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E24" s="132">
         <v>46093</v>
       </c>
       <c r="F24" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G24" s="33">
         <f>IF(ISBLANK(H24),"",_xlfn.XLOOKUP(H24,Info!A:A,Info!B:B))</f>
@@ -9732,19 +9738,19 @@
         <v>30</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="N24" s="32" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="O24" s="118" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="P24" s="92"/>
       <c r="AI24" s="91"/>
@@ -9761,13 +9767,13 @@
         <v>187</v>
       </c>
       <c r="D25" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E25" s="132">
         <v>46093</v>
       </c>
       <c r="F25" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G25" s="33">
         <f>IF(ISBLANK(H25),"",_xlfn.XLOOKUP(H25,Info!A:A,Info!B:B))</f>
@@ -9793,7 +9799,7 @@
         <v>237</v>
       </c>
       <c r="O25" s="118" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="P25" s="92"/>
       <c r="AI25" s="91"/>
@@ -9810,13 +9816,13 @@
         <v>187</v>
       </c>
       <c r="D26" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E26" s="132">
         <v>46093</v>
       </c>
       <c r="F26" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G26" s="33">
         <f>IF(ISBLANK(H26),"",_xlfn.XLOOKUP(H26,Info!A:A,Info!B:B))</f>
@@ -9842,7 +9848,7 @@
         <v>237</v>
       </c>
       <c r="O26" s="118" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="P26" s="92"/>
       <c r="AI26" s="91"/>
@@ -9859,13 +9865,13 @@
         <v>187</v>
       </c>
       <c r="D27" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E27" s="132">
         <v>46093</v>
       </c>
       <c r="F27" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G27" s="33">
         <f>IF(ISBLANK(H27),"",_xlfn.XLOOKUP(H27,Info!A:A,Info!B:B))</f>
@@ -9882,19 +9888,19 @@
         <v>30</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N27" s="32" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="O27" s="118" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="P27" s="92"/>
       <c r="AI27" s="91"/>
@@ -9911,13 +9917,13 @@
         <v>187</v>
       </c>
       <c r="D28" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E28" s="132">
         <v>46100</v>
       </c>
       <c r="F28" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G28" s="33">
         <f>IF(ISBLANK(H28),"",_xlfn.XLOOKUP(H28,Info!A:A,Info!B:B))</f>
@@ -9940,13 +9946,13 @@
         <v>142</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N28" s="32" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="O28" s="118" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P28" s="92"/>
       <c r="AI28" s="91"/>
@@ -9992,7 +9998,7 @@
         <v>142</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="N29" s="92"/>
       <c r="P29" s="92"/>
@@ -10010,13 +10016,13 @@
         <v>187</v>
       </c>
       <c r="D30" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E30" s="132">
         <v>46100</v>
       </c>
       <c r="F30" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G30" s="33">
         <f>IF(ISBLANK(H30),"",_xlfn.XLOOKUP(H30,Info!A:A,Info!B:B))</f>
@@ -10039,13 +10045,13 @@
         <v>142</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N30" s="32" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="O30" s="118" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P30" s="92"/>
       <c r="AI30" s="91"/>
@@ -10062,13 +10068,13 @@
         <v>187</v>
       </c>
       <c r="D31" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E31" s="132">
         <v>46100</v>
       </c>
       <c r="F31" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G31" s="33">
         <f>IF(ISBLANK(H31),"",_xlfn.XLOOKUP(H31,Info!A:A,Info!B:B))</f>
@@ -10085,16 +10091,16 @@
         <v>30</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>142</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="O31" s="118" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P31" s="92"/>
       <c r="AI31" s="91"/>
@@ -10111,13 +10117,13 @@
         <v>187</v>
       </c>
       <c r="D32" s="54" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E32" s="91">
         <v>46114</v>
       </c>
       <c r="F32" s="54" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G32" s="33">
         <f>IF(ISBLANK(H32),"",_xlfn.XLOOKUP(H32,Info!A:A,Info!B:B))</f>
@@ -10134,20 +10140,20 @@
         <v>60</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L32" s="33"/>
       <c r="M32" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N32" s="92" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="O32" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P32" s="92" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AI32" s="91"/>
     </row>
@@ -10267,7 +10273,7 @@
         <v>46114</v>
       </c>
       <c r="F35" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G35" s="33">
         <f>IF(ISBLANK(H35),"",_xlfn.XLOOKUP(H35,Info!A:A,Info!B:B))</f>
@@ -10365,7 +10371,7 @@
         <v>46114</v>
       </c>
       <c r="F37" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G37" s="33">
         <f>IF(ISBLANK(H37),"",_xlfn.XLOOKUP(H37,Info!A:A,Info!B:B))</f>
@@ -10457,13 +10463,13 @@
         <v>187</v>
       </c>
       <c r="D39" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E39" s="132">
         <v>46115</v>
       </c>
       <c r="F39" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G39" s="33">
         <f>IF(ISBLANK(H39),"",_xlfn.XLOOKUP(H39,Info!A:A,Info!B:B))</f>
@@ -10486,13 +10492,13 @@
         <v>142</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N39" s="32" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="O39" s="118" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="P39" s="92"/>
       <c r="AI39" s="91"/>
@@ -10562,13 +10568,13 @@
         <v>187</v>
       </c>
       <c r="D41" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E41" s="132">
         <v>46115</v>
       </c>
       <c r="F41" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G41" s="33">
         <f>IF(ISBLANK(H41),"",_xlfn.XLOOKUP(H41,Info!A:A,Info!B:B))</f>
@@ -10591,13 +10597,13 @@
         <v>142</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N41" s="32" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="O41" s="118" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="P41" s="92"/>
       <c r="AI41" s="91"/>
@@ -10669,7 +10675,7 @@
         <v>46115</v>
       </c>
       <c r="F43" s="54" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G43" s="33">
         <f>IF(ISBLANK(H43),"",_xlfn.XLOOKUP(H43,Info!A:A,Info!B:B))</f>
@@ -10691,11 +10697,11 @@
         <v>142</v>
       </c>
       <c r="M43" s="67" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="N43" s="92"/>
       <c r="O43" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P43" s="92" t="s">
         <v>249</v>
@@ -10714,7 +10720,7 @@
         <v>187</v>
       </c>
       <c r="D44" s="54" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E44" s="91">
         <v>46119</v>
@@ -10767,7 +10773,7 @@
         <v>46119</v>
       </c>
       <c r="F45" s="54" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G45" s="33">
         <f>IF(ISBLANK(H45),"",_xlfn.XLOOKUP(H45,Info!A:A,Info!B:B))</f>
@@ -10784,20 +10790,20 @@
         <v>60</v>
       </c>
       <c r="K45" s="33" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L45" s="33"/>
       <c r="M45" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N45" s="92" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="O45" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P45" s="92" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AI45" s="91"/>
     </row>
@@ -10819,7 +10825,7 @@
         <v>46121</v>
       </c>
       <c r="F46" s="54" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G46" s="33">
         <f>IF(ISBLANK(H46),"",_xlfn.XLOOKUP(H46,Info!A:A,Info!B:B))</f>
@@ -10841,11 +10847,11 @@
         <v>142</v>
       </c>
       <c r="M46" s="67" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="N46" s="92"/>
       <c r="O46" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P46" s="92" t="s">
         <v>249</v>
@@ -10870,7 +10876,7 @@
         <v>46121</v>
       </c>
       <c r="F47" s="54" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G47" s="33">
         <f>IF(ISBLANK(H47),"",_xlfn.XLOOKUP(H47,Info!A:A,Info!B:B))</f>
@@ -10892,7 +10898,7 @@
         <v>142</v>
       </c>
       <c r="M47" s="67" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="N47" s="92"/>
       <c r="O47" s="93" t="s">
@@ -10947,7 +10953,7 @@
         <v>264</v>
       </c>
       <c r="O48" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P48" s="92" t="s">
         <v>344</v>
@@ -10972,7 +10978,7 @@
         <v>46125</v>
       </c>
       <c r="F49" s="54" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G49" s="33">
         <f>IF(ISBLANK(H49),"",_xlfn.XLOOKUP(H49,Info!A:A,Info!B:B))</f>
@@ -10989,20 +10995,20 @@
         <v>60</v>
       </c>
       <c r="K49" s="33" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L49" s="33"/>
       <c r="M49" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N49" s="92" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="O49" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P49" s="92" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AI49" s="91"/>
     </row>
@@ -11018,13 +11024,13 @@
         <v>187</v>
       </c>
       <c r="D50" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E50" s="91">
         <v>46125</v>
       </c>
       <c r="F50" s="54" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G50" s="33">
         <f>IF(ISBLANK(H50),"",_xlfn.XLOOKUP(H50,Info!A:A,Info!B:B))</f>
@@ -11049,10 +11055,10 @@
         <v>247</v>
       </c>
       <c r="N50" s="92" t="s">
+        <v>411</v>
+      </c>
+      <c r="O50" s="118" t="s">
         <v>412</v>
-      </c>
-      <c r="O50" s="118" t="s">
-        <v>413</v>
       </c>
       <c r="P50" s="92" t="s">
         <v>340</v>
@@ -11099,16 +11105,16 @@
         <v>142</v>
       </c>
       <c r="M51" s="67" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N51" s="92" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="O51" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P51" s="92" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AI51" s="91"/>
     </row>
@@ -11153,13 +11159,13 @@
         <v>271</v>
       </c>
       <c r="M52" s="67" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N52" s="92" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="O52" s="93" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P52" s="92" t="s">
         <v>340</v>
@@ -11184,7 +11190,7 @@
         <v>46129</v>
       </c>
       <c r="F53" s="54" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G53" s="33">
         <f>IF(ISBLANK(H53),"",_xlfn.XLOOKUP(H53,Info!A:A,Info!B:B))</f>
@@ -11201,19 +11207,19 @@
         <v>30</v>
       </c>
       <c r="K53" s="33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L53" s="33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="M53" s="67" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="N53" s="92" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="O53" s="93" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P53" s="92" t="s">
         <v>343</v>
@@ -11238,7 +11244,7 @@
         <v>46133</v>
       </c>
       <c r="F54" s="54" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G54" s="33">
         <f>IF(ISBLANK(H54),"",_xlfn.XLOOKUP(H54,Info!A:A,Info!B:B))</f>
@@ -11255,20 +11261,20 @@
         <v>60</v>
       </c>
       <c r="K54" s="33" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L54" s="33"/>
       <c r="M54" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N54" s="92" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="O54" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P54" s="92" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AI54" s="91"/>
     </row>
@@ -11290,7 +11296,7 @@
         <v>46133</v>
       </c>
       <c r="F55" s="54" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G55" s="33">
         <f>IF(ISBLANK(H55),"",_xlfn.XLOOKUP(H55,Info!A:A,Info!B:B))</f>
@@ -11319,7 +11325,7 @@
         <v>275</v>
       </c>
       <c r="O55" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P55" s="92" t="s">
         <v>274</v>
@@ -11370,7 +11376,7 @@
         <v>247</v>
       </c>
       <c r="N56" s="92" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="O56" s="93" t="s">
         <v>341</v>
@@ -11398,7 +11404,7 @@
         <v>46135</v>
       </c>
       <c r="F57" s="54" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G57" s="33">
         <f>IF(ISBLANK(H57),"",_xlfn.XLOOKUP(H57,Info!A:A,Info!B:B))</f>
@@ -11415,20 +11421,20 @@
         <v>60</v>
       </c>
       <c r="K57" s="33" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L57" s="33"/>
       <c r="M57" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N57" s="92" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="O57" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P57" s="92" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="AI57" s="91"/>
     </row>
@@ -11444,13 +11450,13 @@
         <v>187</v>
       </c>
       <c r="D58" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E58" s="91">
         <v>46135</v>
       </c>
       <c r="F58" s="54" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G58" s="33">
         <f>IF(ISBLANK(H58),"",_xlfn.XLOOKUP(H58,Info!A:A,Info!B:B))</f>
@@ -11467,16 +11473,16 @@
         <v>15</v>
       </c>
       <c r="K58" s="33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L58" s="33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="M58" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N58" s="92" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="O58" s="93" t="s">
         <v>341</v>
@@ -11502,7 +11508,7 @@
         <v>46136</v>
       </c>
       <c r="F59" s="54" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G59" s="33">
         <f>IF(ISBLANK(H59),"",_xlfn.XLOOKUP(H59,Info!A:A,Info!B:B))</f>
@@ -11527,13 +11533,13 @@
         <v>247</v>
       </c>
       <c r="N59" s="92" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="O59" s="118" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="P59" s="92" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AI59" s="91"/>
     </row>
@@ -11555,7 +11561,7 @@
         <v>46139</v>
       </c>
       <c r="F60" s="54" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G60" s="33">
         <f>IF(ISBLANK(H60),"",_xlfn.XLOOKUP(H60,Info!A:A,Info!B:B))</f>
@@ -11572,20 +11578,20 @@
         <v>60</v>
       </c>
       <c r="K60" s="33" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="L60" s="33"/>
       <c r="M60" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N60" s="92" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="O60" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P60" s="92" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AI60" s="91"/>
     </row>
@@ -11601,13 +11607,13 @@
         <v>187</v>
       </c>
       <c r="D61" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E61" s="91">
         <v>46139</v>
       </c>
       <c r="F61" s="54" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G61" s="33">
         <f>IF(ISBLANK(H61),"",_xlfn.XLOOKUP(H61,Info!A:A,Info!B:B))</f>
@@ -11632,7 +11638,7 @@
         <v>237</v>
       </c>
       <c r="O61" s="118" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P61" s="92" t="s">
         <v>340</v>
@@ -11657,7 +11663,7 @@
         <v>46142</v>
       </c>
       <c r="F62" s="54" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G62" s="33">
         <f>IF(ISBLANK(H62),"",_xlfn.XLOOKUP(H62,Info!A:A,Info!B:B))</f>
@@ -11683,10 +11689,10 @@
         <v>247</v>
       </c>
       <c r="N62" s="92" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="O62" s="118" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="P62" s="92" t="s">
         <v>340</v>
@@ -11738,7 +11744,7 @@
       </c>
       <c r="N63" s="92"/>
       <c r="O63" s="118" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="P63" s="92" t="s">
         <v>340</v>
@@ -11763,7 +11769,7 @@
         <v>46143</v>
       </c>
       <c r="F64" s="54" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G64" s="33">
         <f>IF(ISBLANK(H64),"",_xlfn.XLOOKUP(H64,Info!A:A,Info!B:B))</f>
@@ -11786,14 +11792,14 @@
         <v>142</v>
       </c>
       <c r="M64" s="67" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="N64" s="92"/>
       <c r="O64" s="93" t="s">
+        <v>649</v>
+      </c>
+      <c r="P64" s="92" t="s">
         <v>651</v>
-      </c>
-      <c r="P64" s="92" t="s">
-        <v>653</v>
       </c>
       <c r="AI64" s="91"/>
     </row>
@@ -11815,7 +11821,7 @@
         <v>46143</v>
       </c>
       <c r="F65" s="54" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G65" s="33">
         <f>IF(ISBLANK(H65),"",_xlfn.XLOOKUP(H65,Info!A:A,Info!B:B))</f>
@@ -11832,20 +11838,20 @@
         <v>60</v>
       </c>
       <c r="K65" s="33" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L65" s="33"/>
       <c r="M65" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N65" s="92" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="O65" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P65" s="92" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AI65" s="91"/>
     </row>
@@ -11883,7 +11889,7 @@
         <v>30</v>
       </c>
       <c r="K66" s="33" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L66" s="33" t="s">
         <v>142</v>
@@ -11895,10 +11901,10 @@
         <v>264</v>
       </c>
       <c r="O66" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P66" s="92" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AI66" s="91"/>
     </row>
@@ -11920,7 +11926,7 @@
         <v>46146</v>
       </c>
       <c r="F67" s="54" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G67" s="33">
         <f>IF(ISBLANK(H67),"",_xlfn.XLOOKUP(H67,Info!A:A,Info!B:B))</f>
@@ -11936,7 +11942,7 @@
         <v>20</v>
       </c>
       <c r="K67" s="33" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="L67" s="33" t="s">
         <v>142</v>
@@ -11945,13 +11951,13 @@
         <v>247</v>
       </c>
       <c r="N67" s="92" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="O67" s="118" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="P67" s="92" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AI67" s="91"/>
     </row>
@@ -11973,7 +11979,7 @@
         <v>46146</v>
       </c>
       <c r="F68" s="54" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G68" s="33">
         <f>IF(ISBLANK(H68),"",_xlfn.XLOOKUP(H68,Info!A:A,Info!B:B))</f>
@@ -11989,19 +11995,19 @@
         <v>20</v>
       </c>
       <c r="K68" s="33" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="L68" s="33" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="M68" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N68" s="92" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="O68" s="118" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="P68" s="92" t="s">
         <v>340</v>
@@ -12026,7 +12032,7 @@
         <v>46146</v>
       </c>
       <c r="F69" s="54" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G69" s="33">
         <f>IF(ISBLANK(H69),"",_xlfn.XLOOKUP(H69,Info!A:A,Info!B:B))</f>
@@ -12052,7 +12058,7 @@
       </c>
       <c r="N69" s="92"/>
       <c r="O69" s="118" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="P69" s="92"/>
       <c r="AI69" s="91"/>
@@ -12075,7 +12081,7 @@
         <v>46147</v>
       </c>
       <c r="F70" s="54" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G70" s="33">
         <f>IF(ISBLANK(H70),"",_xlfn.XLOOKUP(H70,Info!A:A,Info!B:B))</f>
@@ -12092,20 +12098,20 @@
         <v>60</v>
       </c>
       <c r="K70" s="33" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L70" s="33"/>
       <c r="M70" s="67" t="s">
         <v>237</v>
       </c>
       <c r="N70" s="92" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="O70" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P70" s="92" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AI70" s="91"/>
     </row>
@@ -12127,7 +12133,7 @@
         <v>46150</v>
       </c>
       <c r="F71" s="54" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G71" s="33">
         <f>IF(ISBLANK(H71),"",_xlfn.XLOOKUP(H71,Info!A:A,Info!B:B))</f>
@@ -12153,10 +12159,10 @@
         <v>247</v>
       </c>
       <c r="N71" s="92" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="O71" s="118" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="P71" s="92"/>
       <c r="AI71" s="91"/>
@@ -12173,7 +12179,7 @@
         <v>187</v>
       </c>
       <c r="D72" s="54" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E72" s="91">
         <v>46154</v>
@@ -12204,13 +12210,13 @@
         <v>247</v>
       </c>
       <c r="N72" s="92" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="O72" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P72" s="92" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AI72" s="91"/>
     </row>
@@ -12232,7 +12238,7 @@
         <v>46156</v>
       </c>
       <c r="F73" s="54" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G73" s="33">
         <f>IF(ISBLANK(H73),"",_xlfn.XLOOKUP(H73,Info!A:A,Info!B:B))</f>
@@ -12249,7 +12255,7 @@
         <v>60</v>
       </c>
       <c r="K73" s="33" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="L73" s="33" t="s">
         <v>244</v>
@@ -12259,7 +12265,7 @@
       </c>
       <c r="N73" s="92"/>
       <c r="O73" s="118" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="P73" s="92" t="s">
         <v>340</v>
@@ -12312,10 +12318,10 @@
         <v>264</v>
       </c>
       <c r="O74" s="93" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P74" s="92" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="AI74" s="91"/>
     </row>
@@ -12337,7 +12343,7 @@
         <v>46162</v>
       </c>
       <c r="F75" s="54" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G75" s="33">
         <f>IF(ISBLANK(H75),"",_xlfn.XLOOKUP(H75,Info!A:A,Info!B:B))</f>
@@ -12363,10 +12369,10 @@
         <v>247</v>
       </c>
       <c r="N75" s="92" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="O75" s="118" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="P75" s="92"/>
       <c r="AI75" s="91"/>
@@ -12389,7 +12395,7 @@
         <v>46162</v>
       </c>
       <c r="F76" s="54" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="G76" s="33">
         <f>IF(ISBLANK(H76),"",_xlfn.XLOOKUP(H76,Info!A:A,Info!B:B))</f>
@@ -12405,7 +12411,7 @@
         <v>10</v>
       </c>
       <c r="K76" s="33" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="L76" s="33" t="s">
         <v>142</v>
@@ -12414,13 +12420,13 @@
         <v>247</v>
       </c>
       <c r="N76" s="92" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="O76" s="118" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="P76" s="92" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AI76" s="91"/>
     </row>
@@ -12442,7 +12448,7 @@
         <v>46171</v>
       </c>
       <c r="F77" s="54" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G77" s="33">
         <f>IF(ISBLANK(H77),"",_xlfn.XLOOKUP(H77,Info!A:A,Info!B:B))</f>
@@ -12459,19 +12465,19 @@
         <v>10</v>
       </c>
       <c r="K77" s="33" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="L77" s="33" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="M77" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N77" s="92" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="O77" s="118" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="P77" s="92" t="s">
         <v>340</v>
@@ -12496,7 +12502,7 @@
         <v>46171</v>
       </c>
       <c r="F78" s="54" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="G78" s="33">
         <f>IF(ISBLANK(H78),"",_xlfn.XLOOKUP(H78,Info!A:A,Info!B:B))</f>
@@ -12513,7 +12519,7 @@
         <v>45</v>
       </c>
       <c r="K78" s="33" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="L78" s="33" t="s">
         <v>244</v>
@@ -12523,10 +12529,10 @@
       </c>
       <c r="N78" s="92"/>
       <c r="O78" s="118" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="P78" s="92" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="AI78" s="91"/>
     </row>
@@ -12548,7 +12554,7 @@
         <v>46171</v>
       </c>
       <c r="F79" s="54" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="G79" s="33">
         <f>IF(ISBLANK(H79),"",_xlfn.XLOOKUP(H79,Info!A:A,Info!B:B))</f>
@@ -12565,17 +12571,17 @@
         <v>15</v>
       </c>
       <c r="K79" s="33" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L79" s="33" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="M79" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N79" s="92"/>
       <c r="O79" s="118" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="P79" s="92"/>
       <c r="AI79" s="91"/>
@@ -12598,7 +12604,7 @@
         <v>46171</v>
       </c>
       <c r="F80" s="54" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G80" s="33">
         <f>IF(ISBLANK(H80),"",_xlfn.XLOOKUP(H80,Info!A:A,Info!B:B))</f>
@@ -12615,22 +12621,22 @@
         <v>15</v>
       </c>
       <c r="K80" s="33" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L80" s="33" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M80" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N80" s="92"/>
       <c r="O80" s="118" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="P80" s="92"/>
       <c r="AI80" s="91"/>
     </row>
-    <row r="81" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="33">
         <f>IF(ISBLANK(E81),"",_xlfn.XLOOKUP(E81,Info!A:A,Info!B:B))</f>
         <v>18</v>
@@ -12648,7 +12654,7 @@
         <v>46176</v>
       </c>
       <c r="F81" s="54" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G81" s="33">
         <f>IF(ISBLANK(H81),"",_xlfn.XLOOKUP(H81,Info!A:A,Info!B:B))</f>
@@ -12664,24 +12670,24 @@
         <v>30</v>
       </c>
       <c r="K81" s="33" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L81" s="33" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M81" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N81" s="92"/>
       <c r="O81" s="118" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="P81" s="92" t="s">
         <v>340</v>
       </c>
       <c r="AI81" s="91"/>
     </row>
-    <row r="82" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="33">
         <f>IF(ISBLANK(E82),"",_xlfn.XLOOKUP(E82,Info!A:A,Info!B:B))</f>
         <v>18</v>
@@ -12699,7 +12705,7 @@
         <v>46176</v>
       </c>
       <c r="F82" s="54" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="G82" s="33">
         <f>IF(ISBLANK(H82),"",_xlfn.XLOOKUP(H82,Info!A:A,Info!B:B))</f>
@@ -12725,14 +12731,14 @@
       </c>
       <c r="N82" s="92"/>
       <c r="O82" s="118" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="P82" s="92" t="s">
         <v>340</v>
       </c>
       <c r="AI82" s="91"/>
     </row>
-    <row r="83" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="33">
         <f>IF(ISBLANK(E83),"",_xlfn.XLOOKUP(E83,Info!A:A,Info!B:B))</f>
         <v>18</v>
@@ -12744,13 +12750,13 @@
         <v>104</v>
       </c>
       <c r="D83" s="54" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E83" s="91">
         <v>46177</v>
       </c>
       <c r="F83" s="54" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="G83" s="33">
         <f>IF(ISBLANK(H83),"",_xlfn.XLOOKUP(H83,Info!A:A,Info!B:B))</f>
@@ -12765,7 +12771,7 @@
       </c>
       <c r="J83" s="33"/>
       <c r="K83" s="33" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="L83" s="33" t="s">
         <v>142</v>
@@ -12775,12 +12781,12 @@
       </c>
       <c r="N83" s="92"/>
       <c r="O83" s="118" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="P83" s="92"/>
       <c r="AI83" s="91"/>
     </row>
-    <row r="84" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="33">
         <f>IF(ISBLANK(E84),"",_xlfn.XLOOKUP(E84,Info!A:A,Info!B:B))</f>
         <v>19</v>
@@ -12792,13 +12798,13 @@
         <v>104</v>
       </c>
       <c r="D84" s="54" t="s">
-        <v>261</v>
+        <v>687</v>
       </c>
       <c r="E84" s="91">
         <v>46183</v>
       </c>
       <c r="F84" s="54" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G84" s="33">
         <f>IF(ISBLANK(H84),"",_xlfn.XLOOKUP(H84,Info!A:A,Info!B:B))</f>
@@ -12822,7 +12828,7 @@
       </c>
       <c r="N84" s="92"/>
       <c r="P84" s="92" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AI84" s="91"/>
     </row>
@@ -12844,7 +12850,7 @@
         <v>46160</v>
       </c>
       <c r="F85" s="54" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G85" s="33">
         <f>IF(ISBLANK(H85),"",_xlfn.XLOOKUP(H85,Info!A:A,Info!B:B))</f>
@@ -12866,48 +12872,55 @@
         <v>142</v>
       </c>
       <c r="M85" s="67" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="N85" s="92" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="P85" s="92" t="s">
         <v>263</v>
       </c>
       <c r="AI85" s="91"/>
     </row>
-    <row r="86" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="33" t="e">
+    <row r="86" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="33">
         <f>IF(ISBLANK(E86),"",_xlfn.XLOOKUP(E86,Info!A:A,Info!B:B))</f>
-        <v>#N/A</v>
+        <v>19</v>
       </c>
       <c r="B86" s="33" t="s">
         <v>266</v>
       </c>
       <c r="C86" s="33" t="s">
-        <v>549</v>
+        <v>104</v>
       </c>
       <c r="D86" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="E86" s="91" t="s">
-        <v>84</v>
+      <c r="E86" s="91">
+        <v>46184</v>
       </c>
       <c r="F86" s="54" t="s">
-        <v>578</v>
-      </c>
-      <c r="G86" s="33" t="str">
+        <v>688</v>
+      </c>
+      <c r="G86" s="33">
         <f>IF(ISBLANK(H86),"",_xlfn.XLOOKUP(H86,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H86" s="98"/>
-      <c r="I86" s="103"/>
-      <c r="J86" s="33"/>
+        <v>19</v>
+      </c>
+      <c r="H86" s="98">
+        <f>E86-1</f>
+        <v>46183</v>
+      </c>
+      <c r="I86" s="103">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J86" s="33">
+        <v>15</v>
+      </c>
       <c r="K86" s="33" t="s">
-        <v>597</v>
+        <v>235</v>
       </c>
       <c r="L86" s="33" t="s">
-        <v>597</v>
+        <v>235</v>
       </c>
       <c r="M86" s="67" t="s">
         <v>247</v>
@@ -12918,56 +12931,56 @@
       </c>
       <c r="AI86" s="91"/>
     </row>
-    <row r="87" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="33" t="e">
+    <row r="87" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="33">
         <f>IF(ISBLANK(E87),"",_xlfn.XLOOKUP(E87,Info!A:A,Info!B:B))</f>
-        <v>#N/A</v>
+        <v>19</v>
       </c>
       <c r="B87" s="33" t="s">
         <v>266</v>
       </c>
       <c r="C87" s="33" t="s">
-        <v>549</v>
+        <v>104</v>
       </c>
       <c r="D87" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="E87" s="91" t="s">
-        <v>84</v>
+      <c r="E87" s="91">
+        <v>46184</v>
       </c>
       <c r="F87" s="54" t="s">
-        <v>588</v>
-      </c>
-      <c r="G87" s="33" t="str">
+        <v>689</v>
+      </c>
+      <c r="G87" s="33">
         <f>IF(ISBLANK(H87),"",_xlfn.XLOOKUP(H87,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H87" s="98"/>
+        <v>19</v>
+      </c>
+      <c r="H87" s="98">
+        <f>E87-1</f>
+        <v>46183</v>
+      </c>
       <c r="I87" s="103">
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J87" s="33">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K87" s="33" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="L87" s="33" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="M87" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="N87" s="92" t="s">
-        <v>345</v>
-      </c>
-      <c r="O87" s="93"/>
+      <c r="N87" s="92"/>
       <c r="P87" s="92" t="s">
         <v>340</v>
       </c>
       <c r="AI87" s="91"/>
     </row>
-    <row r="88" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="33" t="e">
         <f>IF(ISBLANK(E88),"",_xlfn.XLOOKUP(E88,Info!A:A,Info!B:B))</f>
         <v>#N/A</v>
@@ -12976,7 +12989,7 @@
         <v>266</v>
       </c>
       <c r="C88" s="33" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D88" s="54" t="s">
         <v>239</v>
@@ -12985,7 +12998,7 @@
         <v>84</v>
       </c>
       <c r="F88" s="54" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="G88" s="33" t="str">
         <f>IF(ISBLANK(H88),"",_xlfn.XLOOKUP(H88,Info!A:A,Info!B:B))</f>
@@ -12995,9 +13008,11 @@
       <c r="I88" s="103"/>
       <c r="J88" s="33"/>
       <c r="K88" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="L88" s="33"/>
+        <v>595</v>
+      </c>
+      <c r="L88" s="33" t="s">
+        <v>595</v>
+      </c>
       <c r="M88" s="67" t="s">
         <v>247</v>
       </c>
@@ -13007,7 +13022,7 @@
       </c>
       <c r="AI88" s="91"/>
     </row>
-    <row r="89" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="33" t="e">
         <f>IF(ISBLANK(E89),"",_xlfn.XLOOKUP(E89,Info!A:A,Info!B:B))</f>
         <v>#N/A</v>
@@ -13016,7 +13031,7 @@
         <v>266</v>
       </c>
       <c r="C89" s="33" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D89" s="54" t="s">
         <v>239</v>
@@ -13025,7 +13040,7 @@
         <v>84</v>
       </c>
       <c r="F89" s="54" t="s">
-        <v>636</v>
+        <v>584</v>
       </c>
       <c r="G89" s="33" t="str">
         <f>IF(ISBLANK(H89),"",_xlfn.XLOOKUP(H89,Info!A:A,Info!B:B))</f>
@@ -13035,7 +13050,7 @@
       <c r="I89" s="103"/>
       <c r="J89" s="33"/>
       <c r="K89" s="33" t="s">
-        <v>271</v>
+        <v>234</v>
       </c>
       <c r="L89" s="33"/>
       <c r="M89" s="67" t="s">
@@ -13047,7 +13062,7 @@
       </c>
       <c r="AI89" s="91"/>
     </row>
-    <row r="90" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="33" t="e">
         <f>IF(ISBLANK(E90),"",_xlfn.XLOOKUP(E90,Info!A:A,Info!B:B))</f>
         <v>#N/A</v>
@@ -13056,7 +13071,7 @@
         <v>266</v>
       </c>
       <c r="C90" s="33" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D90" s="54" t="s">
         <v>239</v>
@@ -13065,15 +13080,17 @@
         <v>84</v>
       </c>
       <c r="F90" s="54" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G90" s="33" t="str">
         <f>IF(ISBLANK(H90),"",_xlfn.XLOOKUP(H90,Info!A:A,Info!B:B))</f>
         <v/>
       </c>
+      <c r="H90" s="98"/>
+      <c r="I90" s="103"/>
       <c r="J90" s="33"/>
       <c r="K90" s="33" t="s">
-        <v>512</v>
+        <v>271</v>
       </c>
       <c r="L90" s="33"/>
       <c r="M90" s="67" t="s">
@@ -13085,7 +13102,7 @@
       </c>
       <c r="AI90" s="91"/>
     </row>
-    <row r="91" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="33" t="e">
         <f>IF(ISBLANK(E91),"",_xlfn.XLOOKUP(E91,Info!A:A,Info!B:B))</f>
         <v>#N/A</v>
@@ -13094,44 +13111,36 @@
         <v>266</v>
       </c>
       <c r="C91" s="33" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D91" s="54" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E91" s="91" t="s">
         <v>84</v>
       </c>
       <c r="F91" s="54" t="s">
-        <v>638</v>
-      </c>
-      <c r="G91" s="33">
+        <v>635</v>
+      </c>
+      <c r="G91" s="33" t="str">
         <f>IF(ISBLANK(H91),"",_xlfn.XLOOKUP(H91,Info!A:A,Info!B:B))</f>
-        <v>13</v>
-      </c>
-      <c r="H91" s="98">
-        <v>46143</v>
-      </c>
-      <c r="I91" s="103"/>
-      <c r="J91" s="33">
-        <v>15</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J91" s="33"/>
       <c r="K91" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="L91" s="33" t="s">
-        <v>142</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="L91" s="33"/>
       <c r="M91" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N91" s="92"/>
       <c r="P91" s="92" t="s">
-        <v>258</v>
+        <v>340</v>
       </c>
       <c r="AI91" s="91"/>
     </row>
-    <row r="92" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="33" t="e">
         <f>IF(ISBLANK(E92),"",_xlfn.XLOOKUP(E92,Info!A:A,Info!B:B))</f>
         <v>#N/A</v>
@@ -13140,42 +13149,44 @@
         <v>266</v>
       </c>
       <c r="C92" s="33" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D92" s="54" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E92" s="91" t="s">
         <v>84</v>
       </c>
       <c r="F92" s="54" t="s">
-        <v>599</v>
-      </c>
-      <c r="G92" s="33" t="str">
+        <v>636</v>
+      </c>
+      <c r="G92" s="33">
         <f>IF(ISBLANK(H92),"",_xlfn.XLOOKUP(H92,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="H92" s="98"/>
+        <v>13</v>
+      </c>
+      <c r="H92" s="98">
+        <v>46143</v>
+      </c>
       <c r="I92" s="103"/>
       <c r="J92" s="33">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K92" s="33" t="s">
-        <v>642</v>
+        <v>142</v>
       </c>
       <c r="L92" s="33" t="s">
-        <v>596</v>
+        <v>142</v>
       </c>
       <c r="M92" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N92" s="92"/>
       <c r="P92" s="92" t="s">
-        <v>600</v>
+        <v>258</v>
       </c>
       <c r="AI92" s="91"/>
     </row>
-    <row r="93" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="33" t="e">
         <f>IF(ISBLANK(E93),"",_xlfn.XLOOKUP(E93,Info!A:A,Info!B:B))</f>
         <v>#N/A</v>
@@ -13184,7 +13195,7 @@
         <v>266</v>
       </c>
       <c r="C93" s="33" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D93" s="54" t="s">
         <v>239</v>
@@ -13193,7 +13204,7 @@
         <v>84</v>
       </c>
       <c r="F93" s="54" t="s">
-        <v>676</v>
+        <v>597</v>
       </c>
       <c r="G93" s="33" t="str">
         <f>IF(ISBLANK(H93),"",_xlfn.XLOOKUP(H93,Info!A:A,Info!B:B))</f>
@@ -13201,30 +13212,44 @@
       </c>
       <c r="H93" s="98"/>
       <c r="I93" s="103"/>
-      <c r="J93" s="33"/>
+      <c r="J93" s="33">
+        <v>30</v>
+      </c>
       <c r="K93" s="33" t="s">
-        <v>677</v>
+        <v>640</v>
       </c>
       <c r="L93" s="33" t="s">
-        <v>677</v>
+        <v>594</v>
       </c>
       <c r="M93" s="67" t="s">
         <v>247</v>
       </c>
       <c r="N93" s="92"/>
-      <c r="P93" s="92"/>
+      <c r="P93" s="92" t="s">
+        <v>598</v>
+      </c>
       <c r="AI93" s="91"/>
     </row>
-    <row r="94" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="33" t="str">
+    <row r="94" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="33" t="e">
         <f>IF(ISBLANK(E94),"",_xlfn.XLOOKUP(E94,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="B94" s="33"/>
-      <c r="C94" s="33"/>
-      <c r="D94" s="54"/>
-      <c r="E94" s="91"/>
-      <c r="F94" s="54"/>
+        <v>#N/A</v>
+      </c>
+      <c r="B94" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C94" s="33" t="s">
+        <v>548</v>
+      </c>
+      <c r="D94" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="E94" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="F94" s="54" t="s">
+        <v>674</v>
+      </c>
       <c r="G94" s="33" t="str">
         <f>IF(ISBLANK(H94),"",_xlfn.XLOOKUP(H94,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13232,23 +13257,35 @@
       <c r="H94" s="98"/>
       <c r="I94" s="103"/>
       <c r="J94" s="33"/>
-      <c r="K94" s="33"/>
-      <c r="L94" s="33"/>
-      <c r="M94" s="67"/>
+      <c r="K94" s="33" t="s">
+        <v>675</v>
+      </c>
+      <c r="L94" s="33" t="s">
+        <v>675</v>
+      </c>
+      <c r="M94" s="67" t="s">
+        <v>247</v>
+      </c>
       <c r="N94" s="92"/>
       <c r="P94" s="92"/>
       <c r="AI94" s="91"/>
     </row>
-    <row r="95" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="33" t="str">
         <f>IF(ISBLANK(E95),"",_xlfn.XLOOKUP(E95,Info!A:A,Info!B:B))</f>
         <v/>
       </c>
-      <c r="B95" s="33"/>
+      <c r="B95" s="33" t="s">
+        <v>266</v>
+      </c>
       <c r="C95" s="33"/>
-      <c r="D95" s="54"/>
+      <c r="D95" s="54" t="s">
+        <v>239</v>
+      </c>
       <c r="E95" s="91"/>
-      <c r="F95" s="54"/>
+      <c r="F95" s="54" t="s">
+        <v>686</v>
+      </c>
       <c r="G95" s="33" t="str">
         <f>IF(ISBLANK(H95),"",_xlfn.XLOOKUP(H95,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13258,12 +13295,14 @@
       <c r="J95" s="33"/>
       <c r="K95" s="33"/>
       <c r="L95" s="33"/>
-      <c r="M95" s="67"/>
+      <c r="M95" s="67" t="s">
+        <v>247</v>
+      </c>
       <c r="N95" s="92"/>
       <c r="P95" s="92"/>
       <c r="AI95" s="91"/>
     </row>
-    <row r="96" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="33" t="str">
         <f>IF(ISBLANK(E96),"",_xlfn.XLOOKUP(E96,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13287,7 +13326,7 @@
       <c r="P96" s="92"/>
       <c r="AI96" s="91"/>
     </row>
-    <row r="97" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="33" t="str">
         <f>IF(ISBLANK(E97),"",_xlfn.XLOOKUP(E97,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13311,7 +13350,7 @@
       <c r="P97" s="92"/>
       <c r="AI97" s="91"/>
     </row>
-    <row r="98" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="33" t="str">
         <f>IF(ISBLANK(E98),"",_xlfn.XLOOKUP(E98,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13335,7 +13374,7 @@
       <c r="P98" s="92"/>
       <c r="AI98" s="91"/>
     </row>
-    <row r="99" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="33" t="str">
         <f>IF(ISBLANK(E99),"",_xlfn.XLOOKUP(E99,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13359,7 +13398,7 @@
       <c r="P99" s="92"/>
       <c r="AI99" s="91"/>
     </row>
-    <row r="100" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="33" t="str">
         <f>IF(ISBLANK(E100),"",_xlfn.XLOOKUP(E100,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13383,7 +13422,7 @@
       <c r="P100" s="92"/>
       <c r="AI100" s="91"/>
     </row>
-    <row r="101" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="33" t="str">
         <f>IF(ISBLANK(E101),"",_xlfn.XLOOKUP(E101,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13407,7 +13446,7 @@
       <c r="P101" s="92"/>
       <c r="AI101" s="91"/>
     </row>
-    <row r="102" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="33" t="str">
         <f>IF(ISBLANK(E102),"",_xlfn.XLOOKUP(E102,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13431,7 +13470,7 @@
       <c r="P102" s="92"/>
       <c r="AI102" s="91"/>
     </row>
-    <row r="103" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="33" t="str">
         <f>IF(ISBLANK(E103),"",_xlfn.XLOOKUP(E103,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13455,7 +13494,7 @@
       <c r="P103" s="92"/>
       <c r="AI103" s="91"/>
     </row>
-    <row r="104" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="33" t="str">
         <f>IF(ISBLANK(E104),"",_xlfn.XLOOKUP(E104,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13479,7 +13518,7 @@
       <c r="P104" s="92"/>
       <c r="AI104" s="91"/>
     </row>
-    <row r="105" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="33" t="str">
         <f>IF(ISBLANK(E105),"",_xlfn.XLOOKUP(E105,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13503,7 +13542,7 @@
       <c r="P105" s="92"/>
       <c r="AI105" s="91"/>
     </row>
-    <row r="106" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="33" t="str">
         <f>IF(ISBLANK(E106),"",_xlfn.XLOOKUP(E106,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13527,7 +13566,7 @@
       <c r="P106" s="92"/>
       <c r="AI106" s="91"/>
     </row>
-    <row r="107" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="33" t="str">
         <f>IF(ISBLANK(E107),"",_xlfn.XLOOKUP(E107,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13551,7 +13590,7 @@
       <c r="P107" s="92"/>
       <c r="AI107" s="91"/>
     </row>
-    <row r="108" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="33" t="str">
         <f>IF(ISBLANK(E108),"",_xlfn.XLOOKUP(E108,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13575,7 +13614,7 @@
       <c r="P108" s="92"/>
       <c r="AI108" s="91"/>
     </row>
-    <row r="109" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="33" t="str">
         <f>IF(ISBLANK(E109),"",_xlfn.XLOOKUP(E109,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13599,7 +13638,7 @@
       <c r="P109" s="92"/>
       <c r="AI109" s="91"/>
     </row>
-    <row r="110" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="33" t="str">
         <f>IF(ISBLANK(E110),"",_xlfn.XLOOKUP(E110,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13623,7 +13662,7 @@
       <c r="P110" s="92"/>
       <c r="AI110" s="91"/>
     </row>
-    <row r="111" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="33" t="str">
         <f>IF(ISBLANK(E111),"",_xlfn.XLOOKUP(E111,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13647,7 +13686,7 @@
       <c r="P111" s="92"/>
       <c r="AI111" s="91"/>
     </row>
-    <row r="112" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="33" t="str">
         <f>IF(ISBLANK(E112),"",_xlfn.XLOOKUP(E112,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13671,7 +13710,7 @@
       <c r="P112" s="92"/>
       <c r="AI112" s="91"/>
     </row>
-    <row r="113" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="33" t="str">
         <f>IF(ISBLANK(E113),"",_xlfn.XLOOKUP(E113,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13695,7 +13734,7 @@
       <c r="P113" s="92"/>
       <c r="AI113" s="91"/>
     </row>
-    <row r="114" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="33" t="str">
         <f>IF(ISBLANK(E114),"",_xlfn.XLOOKUP(E114,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13719,7 +13758,7 @@
       <c r="P114" s="92"/>
       <c r="AI114" s="91"/>
     </row>
-    <row r="115" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="33" t="str">
         <f>IF(ISBLANK(E115),"",_xlfn.XLOOKUP(E115,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13743,7 +13782,7 @@
       <c r="P115" s="92"/>
       <c r="AI115" s="91"/>
     </row>
-    <row r="116" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="33" t="str">
         <f>IF(ISBLANK(E116),"",_xlfn.XLOOKUP(E116,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13767,7 +13806,7 @@
       <c r="P116" s="92"/>
       <c r="AI116" s="91"/>
     </row>
-    <row r="117" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="33" t="str">
         <f>IF(ISBLANK(E117),"",_xlfn.XLOOKUP(E117,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13791,7 +13830,7 @@
       <c r="P117" s="92"/>
       <c r="AI117" s="91"/>
     </row>
-    <row r="118" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="33" t="str">
         <f>IF(ISBLANK(E118),"",_xlfn.XLOOKUP(E118,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13815,7 +13854,7 @@
       <c r="P118" s="92"/>
       <c r="AI118" s="91"/>
     </row>
-    <row r="119" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="33" t="str">
         <f>IF(ISBLANK(E119),"",_xlfn.XLOOKUP(E119,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13839,7 +13878,7 @@
       <c r="P119" s="92"/>
       <c r="AI119" s="91"/>
     </row>
-    <row r="120" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="33" t="str">
         <f>IF(ISBLANK(E120),"",_xlfn.XLOOKUP(E120,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13863,7 +13902,7 @@
       <c r="P120" s="92"/>
       <c r="AI120" s="91"/>
     </row>
-    <row r="121" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="33" t="str">
         <f>IF(ISBLANK(E121),"",_xlfn.XLOOKUP(E121,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13887,7 +13926,7 @@
       <c r="P121" s="92"/>
       <c r="AI121" s="91"/>
     </row>
-    <row r="122" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="33" t="str">
         <f>IF(ISBLANK(E122),"",_xlfn.XLOOKUP(E122,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13911,7 +13950,7 @@
       <c r="P122" s="92"/>
       <c r="AI122" s="91"/>
     </row>
-    <row r="123" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="33" t="str">
         <f>IF(ISBLANK(E123),"",_xlfn.XLOOKUP(E123,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13935,7 +13974,7 @@
       <c r="P123" s="92"/>
       <c r="AI123" s="91"/>
     </row>
-    <row r="124" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="33" t="str">
         <f>IF(ISBLANK(E124),"",_xlfn.XLOOKUP(E124,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13959,7 +13998,7 @@
       <c r="P124" s="92"/>
       <c r="AI124" s="91"/>
     </row>
-    <row r="125" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="33" t="str">
         <f>IF(ISBLANK(E125),"",_xlfn.XLOOKUP(E125,Info!A:A,Info!B:B))</f>
         <v/>
@@ -13983,7 +14022,7 @@
       <c r="P125" s="92"/>
       <c r="AI125" s="91"/>
     </row>
-    <row r="126" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="33" t="str">
         <f>IF(ISBLANK(E126),"",_xlfn.XLOOKUP(E126,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14007,7 +14046,7 @@
       <c r="P126" s="92"/>
       <c r="AI126" s="91"/>
     </row>
-    <row r="127" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="33" t="str">
         <f>IF(ISBLANK(E127),"",_xlfn.XLOOKUP(E127,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14031,7 +14070,7 @@
       <c r="P127" s="92"/>
       <c r="AI127" s="91"/>
     </row>
-    <row r="128" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="33" t="str">
         <f>IF(ISBLANK(E128),"",_xlfn.XLOOKUP(E128,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14055,7 +14094,7 @@
       <c r="P128" s="92"/>
       <c r="AI128" s="91"/>
     </row>
-    <row r="129" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="33" t="str">
         <f>IF(ISBLANK(E129),"",_xlfn.XLOOKUP(E129,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14079,7 +14118,7 @@
       <c r="P129" s="92"/>
       <c r="AI129" s="91"/>
     </row>
-    <row r="130" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="33" t="str">
         <f>IF(ISBLANK(E130),"",_xlfn.XLOOKUP(E130,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14103,7 +14142,7 @@
       <c r="P130" s="92"/>
       <c r="AI130" s="91"/>
     </row>
-    <row r="131" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="33" t="str">
         <f>IF(ISBLANK(E131),"",_xlfn.XLOOKUP(E131,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14123,11 +14162,11 @@
       <c r="K131" s="33"/>
       <c r="L131" s="33"/>
       <c r="M131" s="67"/>
-      <c r="N131" s="92"/>
+      <c r="N131" s="50"/>
       <c r="P131" s="92"/>
       <c r="AI131" s="91"/>
     </row>
-    <row r="132" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="33" t="str">
         <f>IF(ISBLANK(E132),"",_xlfn.XLOOKUP(E132,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14151,7 +14190,7 @@
       <c r="P132" s="92"/>
       <c r="AI132" s="91"/>
     </row>
-    <row r="133" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="33" t="str">
         <f>IF(ISBLANK(E133),"",_xlfn.XLOOKUP(E133,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14175,7 +14214,7 @@
       <c r="P133" s="92"/>
       <c r="AI133" s="91"/>
     </row>
-    <row r="134" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="33" t="str">
         <f>IF(ISBLANK(E134),"",_xlfn.XLOOKUP(E134,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14199,7 +14238,7 @@
       <c r="P134" s="92"/>
       <c r="AI134" s="91"/>
     </row>
-    <row r="135" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="33" t="str">
         <f>IF(ISBLANK(E135),"",_xlfn.XLOOKUP(E135,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14223,7 +14262,7 @@
       <c r="P135" s="92"/>
       <c r="AI135" s="91"/>
     </row>
-    <row r="136" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="33" t="str">
         <f>IF(ISBLANK(E136),"",_xlfn.XLOOKUP(E136,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14247,7 +14286,7 @@
       <c r="P136" s="92"/>
       <c r="AI136" s="91"/>
     </row>
-    <row r="137" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="33" t="str">
         <f>IF(ISBLANK(E137),"",_xlfn.XLOOKUP(E137,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14271,7 +14310,7 @@
       <c r="P137" s="92"/>
       <c r="AI137" s="91"/>
     </row>
-    <row r="138" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="33" t="str">
         <f>IF(ISBLANK(E138),"",_xlfn.XLOOKUP(E138,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14295,7 +14334,7 @@
       <c r="P138" s="92"/>
       <c r="AI138" s="91"/>
     </row>
-    <row r="139" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="33" t="str">
         <f>IF(ISBLANK(E139),"",_xlfn.XLOOKUP(E139,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14319,7 +14358,7 @@
       <c r="P139" s="92"/>
       <c r="AI139" s="91"/>
     </row>
-    <row r="140" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="33" t="str">
         <f>IF(ISBLANK(E140),"",_xlfn.XLOOKUP(E140,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14343,7 +14382,7 @@
       <c r="P140" s="92"/>
       <c r="AI140" s="91"/>
     </row>
-    <row r="141" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="33" t="str">
         <f>IF(ISBLANK(E141),"",_xlfn.XLOOKUP(E141,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14367,7 +14406,7 @@
       <c r="P141" s="92"/>
       <c r="AI141" s="91"/>
     </row>
-    <row r="142" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="33" t="str">
         <f>IF(ISBLANK(E142),"",_xlfn.XLOOKUP(E142,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14391,7 +14430,7 @@
       <c r="P142" s="92"/>
       <c r="AI142" s="91"/>
     </row>
-    <row r="143" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="33" t="str">
         <f>IF(ISBLANK(E143),"",_xlfn.XLOOKUP(E143,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14415,7 +14454,7 @@
       <c r="P143" s="92"/>
       <c r="AI143" s="91"/>
     </row>
-    <row r="144" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="33" t="str">
         <f>IF(ISBLANK(E144),"",_xlfn.XLOOKUP(E144,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14439,7 +14478,7 @@
       <c r="P144" s="92"/>
       <c r="AI144" s="91"/>
     </row>
-    <row r="145" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="33" t="str">
         <f>IF(ISBLANK(E145),"",_xlfn.XLOOKUP(E145,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14463,7 +14502,7 @@
       <c r="P145" s="92"/>
       <c r="AI145" s="91"/>
     </row>
-    <row r="146" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="33" t="str">
         <f>IF(ISBLANK(E146),"",_xlfn.XLOOKUP(E146,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14487,7 +14526,7 @@
       <c r="P146" s="92"/>
       <c r="AI146" s="91"/>
     </row>
-    <row r="147" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="33" t="str">
         <f>IF(ISBLANK(E147),"",_xlfn.XLOOKUP(E147,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14511,7 +14550,7 @@
       <c r="P147" s="92"/>
       <c r="AI147" s="91"/>
     </row>
-    <row r="148" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="33" t="str">
         <f>IF(ISBLANK(E148),"",_xlfn.XLOOKUP(E148,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14535,7 +14574,7 @@
       <c r="P148" s="92"/>
       <c r="AI148" s="91"/>
     </row>
-    <row r="149" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="33" t="str">
         <f>IF(ISBLANK(E149),"",_xlfn.XLOOKUP(E149,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14559,7 +14598,7 @@
       <c r="P149" s="92"/>
       <c r="AI149" s="91"/>
     </row>
-    <row r="150" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="33" t="str">
         <f>IF(ISBLANK(E150),"",_xlfn.XLOOKUP(E150,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14583,7 +14622,7 @@
       <c r="P150" s="92"/>
       <c r="AI150" s="91"/>
     </row>
-    <row r="151" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="33" t="str">
         <f>IF(ISBLANK(E151),"",_xlfn.XLOOKUP(E151,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14607,7 +14646,7 @@
       <c r="P151" s="92"/>
       <c r="AI151" s="91"/>
     </row>
-    <row r="152" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="33" t="str">
         <f>IF(ISBLANK(E152),"",_xlfn.XLOOKUP(E152,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14631,7 +14670,7 @@
       <c r="P152" s="92"/>
       <c r="AI152" s="91"/>
     </row>
-    <row r="153" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="33" t="str">
         <f>IF(ISBLANK(E153),"",_xlfn.XLOOKUP(E153,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14655,7 +14694,7 @@
       <c r="P153" s="92"/>
       <c r="AI153" s="91"/>
     </row>
-    <row r="154" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="33" t="str">
         <f>IF(ISBLANK(E154),"",_xlfn.XLOOKUP(E154,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14679,7 +14718,7 @@
       <c r="P154" s="92"/>
       <c r="AI154" s="91"/>
     </row>
-    <row r="155" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="33" t="str">
         <f>IF(ISBLANK(E155),"",_xlfn.XLOOKUP(E155,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14703,7 +14742,7 @@
       <c r="P155" s="92"/>
       <c r="AI155" s="91"/>
     </row>
-    <row r="156" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="33" t="str">
         <f>IF(ISBLANK(E156),"",_xlfn.XLOOKUP(E156,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14727,7 +14766,7 @@
       <c r="P156" s="92"/>
       <c r="AI156" s="91"/>
     </row>
-    <row r="157" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="33" t="str">
         <f>IF(ISBLANK(E157),"",_xlfn.XLOOKUP(E157,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14751,7 +14790,7 @@
       <c r="P157" s="92"/>
       <c r="AI157" s="91"/>
     </row>
-    <row r="158" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="33" t="str">
         <f>IF(ISBLANK(E158),"",_xlfn.XLOOKUP(E158,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14775,7 +14814,7 @@
       <c r="P158" s="92"/>
       <c r="AI158" s="91"/>
     </row>
-    <row r="159" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="33" t="str">
         <f>IF(ISBLANK(E159),"",_xlfn.XLOOKUP(E159,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14799,7 +14838,7 @@
       <c r="P159" s="92"/>
       <c r="AI159" s="91"/>
     </row>
-    <row r="160" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="33" t="str">
         <f>IF(ISBLANK(E160),"",_xlfn.XLOOKUP(E160,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14823,7 +14862,7 @@
       <c r="P160" s="92"/>
       <c r="AI160" s="91"/>
     </row>
-    <row r="161" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="33" t="str">
         <f>IF(ISBLANK(E161),"",_xlfn.XLOOKUP(E161,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14847,7 +14886,7 @@
       <c r="P161" s="92"/>
       <c r="AI161" s="91"/>
     </row>
-    <row r="162" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="33" t="str">
         <f>IF(ISBLANK(E162),"",_xlfn.XLOOKUP(E162,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14871,7 +14910,7 @@
       <c r="P162" s="92"/>
       <c r="AI162" s="91"/>
     </row>
-    <row r="163" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="33" t="str">
         <f>IF(ISBLANK(E163),"",_xlfn.XLOOKUP(E163,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14895,7 +14934,7 @@
       <c r="P163" s="92"/>
       <c r="AI163" s="91"/>
     </row>
-    <row r="164" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="33" t="str">
         <f>IF(ISBLANK(E164),"",_xlfn.XLOOKUP(E164,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14919,7 +14958,7 @@
       <c r="P164" s="92"/>
       <c r="AI164" s="91"/>
     </row>
-    <row r="165" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="33" t="str">
         <f>IF(ISBLANK(E165),"",_xlfn.XLOOKUP(E165,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14943,7 +14982,7 @@
       <c r="P165" s="92"/>
       <c r="AI165" s="91"/>
     </row>
-    <row r="166" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="33" t="str">
         <f>IF(ISBLANK(E166),"",_xlfn.XLOOKUP(E166,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14967,7 +15006,7 @@
       <c r="P166" s="92"/>
       <c r="AI166" s="91"/>
     </row>
-    <row r="167" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="33" t="str">
         <f>IF(ISBLANK(E167),"",_xlfn.XLOOKUP(E167,Info!A:A,Info!B:B))</f>
         <v/>
@@ -14991,7 +15030,7 @@
       <c r="P167" s="92"/>
       <c r="AI167" s="91"/>
     </row>
-    <row r="168" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="33" t="str">
         <f>IF(ISBLANK(E168),"",_xlfn.XLOOKUP(E168,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15015,7 +15054,7 @@
       <c r="P168" s="92"/>
       <c r="AI168" s="91"/>
     </row>
-    <row r="169" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="33" t="str">
         <f>IF(ISBLANK(E169),"",_xlfn.XLOOKUP(E169,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15039,7 +15078,7 @@
       <c r="P169" s="92"/>
       <c r="AI169" s="91"/>
     </row>
-    <row r="170" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="33" t="str">
         <f>IF(ISBLANK(E170),"",_xlfn.XLOOKUP(E170,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15063,7 +15102,7 @@
       <c r="P170" s="92"/>
       <c r="AI170" s="91"/>
     </row>
-    <row r="171" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="33" t="str">
         <f>IF(ISBLANK(E171),"",_xlfn.XLOOKUP(E171,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15087,7 +15126,7 @@
       <c r="P171" s="92"/>
       <c r="AI171" s="91"/>
     </row>
-    <row r="172" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="33" t="str">
         <f>IF(ISBLANK(E172),"",_xlfn.XLOOKUP(E172,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15111,7 +15150,7 @@
       <c r="P172" s="92"/>
       <c r="AI172" s="91"/>
     </row>
-    <row r="173" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="33" t="str">
         <f>IF(ISBLANK(E173),"",_xlfn.XLOOKUP(E173,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15135,7 +15174,7 @@
       <c r="P173" s="92"/>
       <c r="AI173" s="91"/>
     </row>
-    <row r="174" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="33" t="str">
         <f>IF(ISBLANK(E174),"",_xlfn.XLOOKUP(E174,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15159,7 +15198,7 @@
       <c r="P174" s="92"/>
       <c r="AI174" s="91"/>
     </row>
-    <row r="175" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="33" t="str">
         <f>IF(ISBLANK(E175),"",_xlfn.XLOOKUP(E175,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15183,7 +15222,7 @@
       <c r="P175" s="92"/>
       <c r="AI175" s="91"/>
     </row>
-    <row r="176" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="33" t="str">
         <f>IF(ISBLANK(E176),"",_xlfn.XLOOKUP(E176,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15207,7 +15246,7 @@
       <c r="P176" s="92"/>
       <c r="AI176" s="91"/>
     </row>
-    <row r="177" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="33" t="str">
         <f>IF(ISBLANK(E177),"",_xlfn.XLOOKUP(E177,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15231,7 +15270,7 @@
       <c r="P177" s="92"/>
       <c r="AI177" s="91"/>
     </row>
-    <row r="178" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="33" t="str">
         <f>IF(ISBLANK(E178),"",_xlfn.XLOOKUP(E178,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15255,7 +15294,7 @@
       <c r="P178" s="92"/>
       <c r="AI178" s="91"/>
     </row>
-    <row r="179" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="33" t="str">
         <f>IF(ISBLANK(E179),"",_xlfn.XLOOKUP(E179,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15279,7 +15318,7 @@
       <c r="P179" s="92"/>
       <c r="AI179" s="91"/>
     </row>
-    <row r="180" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="33" t="str">
         <f>IF(ISBLANK(E180),"",_xlfn.XLOOKUP(E180,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15303,7 +15342,7 @@
       <c r="P180" s="92"/>
       <c r="AI180" s="91"/>
     </row>
-    <row r="181" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="33" t="str">
         <f>IF(ISBLANK(E181),"",_xlfn.XLOOKUP(E181,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15327,7 +15366,7 @@
       <c r="P181" s="92"/>
       <c r="AI181" s="91"/>
     </row>
-    <row r="182" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="33" t="str">
         <f>IF(ISBLANK(E182),"",_xlfn.XLOOKUP(E182,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15351,7 +15390,7 @@
       <c r="P182" s="92"/>
       <c r="AI182" s="91"/>
     </row>
-    <row r="183" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="33" t="str">
         <f>IF(ISBLANK(E183),"",_xlfn.XLOOKUP(E183,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15375,7 +15414,7 @@
       <c r="P183" s="92"/>
       <c r="AI183" s="91"/>
     </row>
-    <row r="184" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="33" t="str">
         <f>IF(ISBLANK(E184),"",_xlfn.XLOOKUP(E184,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15399,7 +15438,7 @@
       <c r="P184" s="92"/>
       <c r="AI184" s="91"/>
     </row>
-    <row r="185" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="33" t="str">
         <f>IF(ISBLANK(E185),"",_xlfn.XLOOKUP(E185,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15423,7 +15462,7 @@
       <c r="P185" s="92"/>
       <c r="AI185" s="91"/>
     </row>
-    <row r="186" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="33" t="str">
         <f>IF(ISBLANK(E186),"",_xlfn.XLOOKUP(E186,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15447,7 +15486,7 @@
       <c r="P186" s="92"/>
       <c r="AI186" s="91"/>
     </row>
-    <row r="187" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="33" t="str">
         <f>IF(ISBLANK(E187),"",_xlfn.XLOOKUP(E187,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15471,7 +15510,7 @@
       <c r="P187" s="92"/>
       <c r="AI187" s="91"/>
     </row>
-    <row r="188" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="33" t="str">
         <f>IF(ISBLANK(E188),"",_xlfn.XLOOKUP(E188,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15495,7 +15534,7 @@
       <c r="P188" s="92"/>
       <c r="AI188" s="91"/>
     </row>
-    <row r="189" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="33" t="str">
         <f>IF(ISBLANK(E189),"",_xlfn.XLOOKUP(E189,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15519,7 +15558,7 @@
       <c r="P189" s="92"/>
       <c r="AI189" s="91"/>
     </row>
-    <row r="190" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="33" t="str">
         <f>IF(ISBLANK(E190),"",_xlfn.XLOOKUP(E190,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15543,7 +15582,7 @@
       <c r="P190" s="92"/>
       <c r="AI190" s="91"/>
     </row>
-    <row r="191" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="33" t="str">
         <f>IF(ISBLANK(E191),"",_xlfn.XLOOKUP(E191,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15567,7 +15606,7 @@
       <c r="P191" s="92"/>
       <c r="AI191" s="91"/>
     </row>
-    <row r="192" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="33" t="str">
         <f>IF(ISBLANK(E192),"",_xlfn.XLOOKUP(E192,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15591,7 +15630,7 @@
       <c r="P192" s="92"/>
       <c r="AI192" s="91"/>
     </row>
-    <row r="193" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="33" t="str">
         <f>IF(ISBLANK(E193),"",_xlfn.XLOOKUP(E193,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15615,7 +15654,7 @@
       <c r="P193" s="92"/>
       <c r="AI193" s="91"/>
     </row>
-    <row r="194" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="33" t="str">
         <f>IF(ISBLANK(E194),"",_xlfn.XLOOKUP(E194,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15639,7 +15678,7 @@
       <c r="P194" s="92"/>
       <c r="AI194" s="91"/>
     </row>
-    <row r="195" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="33" t="str">
         <f>IF(ISBLANK(E195),"",_xlfn.XLOOKUP(E195,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15663,7 +15702,7 @@
       <c r="P195" s="92"/>
       <c r="AI195" s="91"/>
     </row>
-    <row r="196" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="33" t="str">
         <f>IF(ISBLANK(E196),"",_xlfn.XLOOKUP(E196,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15687,7 +15726,7 @@
       <c r="P196" s="92"/>
       <c r="AI196" s="91"/>
     </row>
-    <row r="197" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="33" t="str">
         <f>IF(ISBLANK(E197),"",_xlfn.XLOOKUP(E197,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15711,7 +15750,7 @@
       <c r="P197" s="92"/>
       <c r="AI197" s="91"/>
     </row>
-    <row r="198" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="33" t="str">
         <f>IF(ISBLANK(E198),"",_xlfn.XLOOKUP(E198,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15735,7 +15774,7 @@
       <c r="P198" s="92"/>
       <c r="AI198" s="91"/>
     </row>
-    <row r="199" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="33" t="str">
         <f>IF(ISBLANK(E199),"",_xlfn.XLOOKUP(E199,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15759,7 +15798,7 @@
       <c r="P199" s="92"/>
       <c r="AI199" s="91"/>
     </row>
-    <row r="200" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="33" t="str">
         <f>IF(ISBLANK(E200),"",_xlfn.XLOOKUP(E200,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15783,7 +15822,7 @@
       <c r="P200" s="92"/>
       <c r="AI200" s="91"/>
     </row>
-    <row r="201" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="33" t="str">
         <f>IF(ISBLANK(E201),"",_xlfn.XLOOKUP(E201,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15807,7 +15846,7 @@
       <c r="P201" s="92"/>
       <c r="AI201" s="91"/>
     </row>
-    <row r="202" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="33" t="str">
         <f>IF(ISBLANK(E202),"",_xlfn.XLOOKUP(E202,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15831,7 +15870,7 @@
       <c r="P202" s="92"/>
       <c r="AI202" s="91"/>
     </row>
-    <row r="203" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="33" t="str">
         <f>IF(ISBLANK(E203),"",_xlfn.XLOOKUP(E203,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15855,7 +15894,7 @@
       <c r="P203" s="92"/>
       <c r="AI203" s="91"/>
     </row>
-    <row r="204" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="33" t="str">
         <f>IF(ISBLANK(E204),"",_xlfn.XLOOKUP(E204,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15879,7 +15918,7 @@
       <c r="P204" s="92"/>
       <c r="AI204" s="91"/>
     </row>
-    <row r="205" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="33" t="str">
         <f>IF(ISBLANK(E205),"",_xlfn.XLOOKUP(E205,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15903,7 +15942,7 @@
       <c r="P205" s="92"/>
       <c r="AI205" s="91"/>
     </row>
-    <row r="206" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="33" t="str">
         <f>IF(ISBLANK(E206),"",_xlfn.XLOOKUP(E206,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15927,7 +15966,7 @@
       <c r="P206" s="92"/>
       <c r="AI206" s="91"/>
     </row>
-    <row r="207" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="33" t="str">
         <f>IF(ISBLANK(E207),"",_xlfn.XLOOKUP(E207,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15951,7 +15990,7 @@
       <c r="P207" s="92"/>
       <c r="AI207" s="91"/>
     </row>
-    <row r="208" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="33" t="str">
         <f>IF(ISBLANK(E208),"",_xlfn.XLOOKUP(E208,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15975,7 +16014,7 @@
       <c r="P208" s="92"/>
       <c r="AI208" s="91"/>
     </row>
-    <row r="209" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="33" t="str">
         <f>IF(ISBLANK(E209),"",_xlfn.XLOOKUP(E209,Info!A:A,Info!B:B))</f>
         <v/>
@@ -15999,7 +16038,7 @@
       <c r="P209" s="92"/>
       <c r="AI209" s="91"/>
     </row>
-    <row r="210" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="33" t="str">
         <f>IF(ISBLANK(E210),"",_xlfn.XLOOKUP(E210,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16023,7 +16062,7 @@
       <c r="P210" s="92"/>
       <c r="AI210" s="91"/>
     </row>
-    <row r="211" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="33" t="str">
         <f>IF(ISBLANK(E211),"",_xlfn.XLOOKUP(E211,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16047,7 +16086,7 @@
       <c r="P211" s="92"/>
       <c r="AI211" s="91"/>
     </row>
-    <row r="212" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="33" t="str">
         <f>IF(ISBLANK(E212),"",_xlfn.XLOOKUP(E212,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16071,7 +16110,7 @@
       <c r="P212" s="92"/>
       <c r="AI212" s="91"/>
     </row>
-    <row r="213" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="33" t="str">
         <f>IF(ISBLANK(E213),"",_xlfn.XLOOKUP(E213,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16095,7 +16134,7 @@
       <c r="P213" s="92"/>
       <c r="AI213" s="91"/>
     </row>
-    <row r="214" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="33" t="str">
         <f>IF(ISBLANK(E214),"",_xlfn.XLOOKUP(E214,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16119,7 +16158,7 @@
       <c r="P214" s="92"/>
       <c r="AI214" s="91"/>
     </row>
-    <row r="215" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="33" t="str">
         <f>IF(ISBLANK(E215),"",_xlfn.XLOOKUP(E215,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16143,7 +16182,7 @@
       <c r="P215" s="92"/>
       <c r="AI215" s="91"/>
     </row>
-    <row r="216" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="33" t="str">
         <f>IF(ISBLANK(E216),"",_xlfn.XLOOKUP(E216,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16167,7 +16206,7 @@
       <c r="P216" s="92"/>
       <c r="AI216" s="91"/>
     </row>
-    <row r="217" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="33" t="str">
         <f>IF(ISBLANK(E217),"",_xlfn.XLOOKUP(E217,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16191,7 +16230,7 @@
       <c r="P217" s="92"/>
       <c r="AI217" s="91"/>
     </row>
-    <row r="218" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="33" t="str">
         <f>IF(ISBLANK(E218),"",_xlfn.XLOOKUP(E218,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16215,7 +16254,7 @@
       <c r="P218" s="92"/>
       <c r="AI218" s="91"/>
     </row>
-    <row r="219" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="33" t="str">
         <f>IF(ISBLANK(E219),"",_xlfn.XLOOKUP(E219,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16239,7 +16278,7 @@
       <c r="P219" s="92"/>
       <c r="AI219" s="91"/>
     </row>
-    <row r="220" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="33" t="str">
         <f>IF(ISBLANK(E220),"",_xlfn.XLOOKUP(E220,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16263,7 +16302,7 @@
       <c r="P220" s="92"/>
       <c r="AI220" s="91"/>
     </row>
-    <row r="221" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="33" t="str">
         <f>IF(ISBLANK(E221),"",_xlfn.XLOOKUP(E221,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16287,7 +16326,7 @@
       <c r="P221" s="92"/>
       <c r="AI221" s="91"/>
     </row>
-    <row r="222" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="33" t="str">
         <f>IF(ISBLANK(E222),"",_xlfn.XLOOKUP(E222,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16311,7 +16350,7 @@
       <c r="P222" s="92"/>
       <c r="AI222" s="91"/>
     </row>
-    <row r="223" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="33" t="str">
         <f>IF(ISBLANK(E223),"",_xlfn.XLOOKUP(E223,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16335,7 +16374,7 @@
       <c r="P223" s="92"/>
       <c r="AI223" s="91"/>
     </row>
-    <row r="224" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="33" t="str">
         <f>IF(ISBLANK(E224),"",_xlfn.XLOOKUP(E224,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16359,7 +16398,7 @@
       <c r="P224" s="92"/>
       <c r="AI224" s="91"/>
     </row>
-    <row r="225" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="33" t="str">
         <f>IF(ISBLANK(E225),"",_xlfn.XLOOKUP(E225,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16383,7 +16422,7 @@
       <c r="P225" s="92"/>
       <c r="AI225" s="91"/>
     </row>
-    <row r="226" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="33" t="str">
         <f>IF(ISBLANK(E226),"",_xlfn.XLOOKUP(E226,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16407,7 +16446,7 @@
       <c r="P226" s="92"/>
       <c r="AI226" s="91"/>
     </row>
-    <row r="227" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="33" t="str">
         <f>IF(ISBLANK(E227),"",_xlfn.XLOOKUP(E227,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16431,7 +16470,7 @@
       <c r="P227" s="92"/>
       <c r="AI227" s="91"/>
     </row>
-    <row r="228" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="33" t="str">
         <f>IF(ISBLANK(E228),"",_xlfn.XLOOKUP(E228,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16455,7 +16494,7 @@
       <c r="P228" s="92"/>
       <c r="AI228" s="91"/>
     </row>
-    <row r="229" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="33" t="str">
         <f>IF(ISBLANK(E229),"",_xlfn.XLOOKUP(E229,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16479,7 +16518,7 @@
       <c r="P229" s="92"/>
       <c r="AI229" s="91"/>
     </row>
-    <row r="230" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="33" t="str">
         <f>IF(ISBLANK(E230),"",_xlfn.XLOOKUP(E230,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16503,7 +16542,7 @@
       <c r="P230" s="92"/>
       <c r="AI230" s="91"/>
     </row>
-    <row r="231" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="33" t="str">
         <f>IF(ISBLANK(E231),"",_xlfn.XLOOKUP(E231,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16527,7 +16566,7 @@
       <c r="P231" s="92"/>
       <c r="AI231" s="91"/>
     </row>
-    <row r="232" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="33" t="str">
         <f>IF(ISBLANK(E232),"",_xlfn.XLOOKUP(E232,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16551,7 +16590,7 @@
       <c r="P232" s="92"/>
       <c r="AI232" s="91"/>
     </row>
-    <row r="233" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="33" t="str">
         <f>IF(ISBLANK(E233),"",_xlfn.XLOOKUP(E233,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16575,7 +16614,7 @@
       <c r="P233" s="92"/>
       <c r="AI233" s="91"/>
     </row>
-    <row r="234" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="33" t="str">
         <f>IF(ISBLANK(E234),"",_xlfn.XLOOKUP(E234,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16599,7 +16638,7 @@
       <c r="P234" s="92"/>
       <c r="AI234" s="91"/>
     </row>
-    <row r="235" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="33" t="str">
         <f>IF(ISBLANK(E235),"",_xlfn.XLOOKUP(E235,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16623,7 +16662,7 @@
       <c r="P235" s="92"/>
       <c r="AI235" s="91"/>
     </row>
-    <row r="236" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="33" t="str">
         <f>IF(ISBLANK(E236),"",_xlfn.XLOOKUP(E236,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16647,7 +16686,7 @@
       <c r="P236" s="92"/>
       <c r="AI236" s="91"/>
     </row>
-    <row r="237" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="33" t="str">
         <f>IF(ISBLANK(E237),"",_xlfn.XLOOKUP(E237,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16671,7 +16710,7 @@
       <c r="P237" s="92"/>
       <c r="AI237" s="91"/>
     </row>
-    <row r="238" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="33" t="str">
         <f>IF(ISBLANK(E238),"",_xlfn.XLOOKUP(E238,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16695,7 +16734,7 @@
       <c r="P238" s="92"/>
       <c r="AI238" s="91"/>
     </row>
-    <row r="239" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="33" t="str">
         <f>IF(ISBLANK(E239),"",_xlfn.XLOOKUP(E239,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16719,7 +16758,7 @@
       <c r="P239" s="92"/>
       <c r="AI239" s="91"/>
     </row>
-    <row r="240" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="33" t="str">
         <f>IF(ISBLANK(E240),"",_xlfn.XLOOKUP(E240,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16743,7 +16782,7 @@
       <c r="P240" s="92"/>
       <c r="AI240" s="91"/>
     </row>
-    <row r="241" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="33" t="str">
         <f>IF(ISBLANK(E241),"",_xlfn.XLOOKUP(E241,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16767,7 +16806,7 @@
       <c r="P241" s="92"/>
       <c r="AI241" s="91"/>
     </row>
-    <row r="242" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="33" t="str">
         <f>IF(ISBLANK(E242),"",_xlfn.XLOOKUP(E242,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16791,7 +16830,7 @@
       <c r="P242" s="92"/>
       <c r="AI242" s="91"/>
     </row>
-    <row r="243" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="33" t="str">
         <f>IF(ISBLANK(E243),"",_xlfn.XLOOKUP(E243,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16815,7 +16854,7 @@
       <c r="P243" s="92"/>
       <c r="AI243" s="91"/>
     </row>
-    <row r="244" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="33" t="str">
         <f>IF(ISBLANK(E244),"",_xlfn.XLOOKUP(E244,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16839,7 +16878,7 @@
       <c r="P244" s="92"/>
       <c r="AI244" s="91"/>
     </row>
-    <row r="245" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="33" t="str">
         <f>IF(ISBLANK(E245),"",_xlfn.XLOOKUP(E245,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16863,7 +16902,7 @@
       <c r="P245" s="92"/>
       <c r="AI245" s="91"/>
     </row>
-    <row r="246" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="33" t="str">
         <f>IF(ISBLANK(E246),"",_xlfn.XLOOKUP(E246,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16887,7 +16926,7 @@
       <c r="P246" s="92"/>
       <c r="AI246" s="91"/>
     </row>
-    <row r="247" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="33" t="str">
         <f>IF(ISBLANK(E247),"",_xlfn.XLOOKUP(E247,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16911,7 +16950,7 @@
       <c r="P247" s="92"/>
       <c r="AI247" s="91"/>
     </row>
-    <row r="248" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="33" t="str">
         <f>IF(ISBLANK(E248),"",_xlfn.XLOOKUP(E248,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16935,7 +16974,7 @@
       <c r="P248" s="92"/>
       <c r="AI248" s="91"/>
     </row>
-    <row r="249" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="33" t="str">
         <f>IF(ISBLANK(E249),"",_xlfn.XLOOKUP(E249,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16959,7 +16998,7 @@
       <c r="P249" s="92"/>
       <c r="AI249" s="91"/>
     </row>
-    <row r="250" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="33" t="str">
         <f>IF(ISBLANK(E250),"",_xlfn.XLOOKUP(E250,Info!A:A,Info!B:B))</f>
         <v/>
@@ -16983,7 +17022,7 @@
       <c r="P250" s="92"/>
       <c r="AI250" s="91"/>
     </row>
-    <row r="251" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="33" t="str">
         <f>IF(ISBLANK(E251),"",_xlfn.XLOOKUP(E251,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17007,7 +17046,7 @@
       <c r="P251" s="92"/>
       <c r="AI251" s="91"/>
     </row>
-    <row r="252" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="33" t="str">
         <f>IF(ISBLANK(E252),"",_xlfn.XLOOKUP(E252,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17031,7 +17070,7 @@
       <c r="P252" s="92"/>
       <c r="AI252" s="91"/>
     </row>
-    <row r="253" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="33" t="str">
         <f>IF(ISBLANK(E253),"",_xlfn.XLOOKUP(E253,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17055,7 +17094,7 @@
       <c r="P253" s="92"/>
       <c r="AI253" s="91"/>
     </row>
-    <row r="254" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="33" t="str">
         <f>IF(ISBLANK(E254),"",_xlfn.XLOOKUP(E254,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17079,7 +17118,7 @@
       <c r="P254" s="92"/>
       <c r="AI254" s="91"/>
     </row>
-    <row r="255" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="33" t="str">
         <f>IF(ISBLANK(E255),"",_xlfn.XLOOKUP(E255,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17103,7 +17142,7 @@
       <c r="P255" s="92"/>
       <c r="AI255" s="91"/>
     </row>
-    <row r="256" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="33" t="str">
         <f>IF(ISBLANK(E256),"",_xlfn.XLOOKUP(E256,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17127,7 +17166,7 @@
       <c r="P256" s="92"/>
       <c r="AI256" s="91"/>
     </row>
-    <row r="257" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="33" t="str">
         <f>IF(ISBLANK(E257),"",_xlfn.XLOOKUP(E257,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17151,7 +17190,7 @@
       <c r="P257" s="92"/>
       <c r="AI257" s="91"/>
     </row>
-    <row r="258" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="33" t="str">
         <f>IF(ISBLANK(E258),"",_xlfn.XLOOKUP(E258,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17175,7 +17214,7 @@
       <c r="P258" s="92"/>
       <c r="AI258" s="91"/>
     </row>
-    <row r="259" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="33" t="str">
         <f>IF(ISBLANK(E259),"",_xlfn.XLOOKUP(E259,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17199,7 +17238,7 @@
       <c r="P259" s="92"/>
       <c r="AI259" s="91"/>
     </row>
-    <row r="260" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="33" t="str">
         <f>IF(ISBLANK(E260),"",_xlfn.XLOOKUP(E260,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17223,7 +17262,7 @@
       <c r="P260" s="92"/>
       <c r="AI260" s="91"/>
     </row>
-    <row r="261" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="33" t="str">
         <f>IF(ISBLANK(E261),"",_xlfn.XLOOKUP(E261,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17247,7 +17286,7 @@
       <c r="P261" s="92"/>
       <c r="AI261" s="91"/>
     </row>
-    <row r="262" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="33" t="str">
         <f>IF(ISBLANK(E262),"",_xlfn.XLOOKUP(E262,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17271,7 +17310,7 @@
       <c r="P262" s="92"/>
       <c r="AI262" s="91"/>
     </row>
-    <row r="263" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="33" t="str">
         <f>IF(ISBLANK(E263),"",_xlfn.XLOOKUP(E263,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17295,7 +17334,7 @@
       <c r="P263" s="92"/>
       <c r="AI263" s="91"/>
     </row>
-    <row r="264" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="33" t="str">
         <f>IF(ISBLANK(E264),"",_xlfn.XLOOKUP(E264,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17319,7 +17358,7 @@
       <c r="P264" s="92"/>
       <c r="AI264" s="91"/>
     </row>
-    <row r="265" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="33" t="str">
         <f>IF(ISBLANK(E265),"",_xlfn.XLOOKUP(E265,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17343,7 +17382,7 @@
       <c r="P265" s="92"/>
       <c r="AI265" s="91"/>
     </row>
-    <row r="266" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="33" t="str">
         <f>IF(ISBLANK(E266),"",_xlfn.XLOOKUP(E266,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17367,7 +17406,7 @@
       <c r="P266" s="92"/>
       <c r="AI266" s="91"/>
     </row>
-    <row r="267" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="33" t="str">
         <f>IF(ISBLANK(E267),"",_xlfn.XLOOKUP(E267,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17391,7 +17430,7 @@
       <c r="P267" s="92"/>
       <c r="AI267" s="91"/>
     </row>
-    <row r="268" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="33" t="str">
         <f>IF(ISBLANK(E268),"",_xlfn.XLOOKUP(E268,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17415,7 +17454,7 @@
       <c r="P268" s="92"/>
       <c r="AI268" s="91"/>
     </row>
-    <row r="269" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="33" t="str">
         <f>IF(ISBLANK(E269),"",_xlfn.XLOOKUP(E269,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17439,7 +17478,7 @@
       <c r="P269" s="92"/>
       <c r="AI269" s="91"/>
     </row>
-    <row r="270" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="33" t="str">
         <f>IF(ISBLANK(E270),"",_xlfn.XLOOKUP(E270,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17463,7 +17502,7 @@
       <c r="P270" s="92"/>
       <c r="AI270" s="91"/>
     </row>
-    <row r="271" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="33" t="str">
         <f>IF(ISBLANK(E271),"",_xlfn.XLOOKUP(E271,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17487,7 +17526,7 @@
       <c r="P271" s="92"/>
       <c r="AI271" s="91"/>
     </row>
-    <row r="272" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="33" t="str">
         <f>IF(ISBLANK(E272),"",_xlfn.XLOOKUP(E272,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17511,7 +17550,7 @@
       <c r="P272" s="92"/>
       <c r="AI272" s="91"/>
     </row>
-    <row r="273" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="33" t="str">
         <f>IF(ISBLANK(E273),"",_xlfn.XLOOKUP(E273,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17535,7 +17574,7 @@
       <c r="P273" s="92"/>
       <c r="AI273" s="91"/>
     </row>
-    <row r="274" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="33" t="str">
         <f>IF(ISBLANK(E274),"",_xlfn.XLOOKUP(E274,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17559,7 +17598,7 @@
       <c r="P274" s="92"/>
       <c r="AI274" s="91"/>
     </row>
-    <row r="275" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="33" t="str">
         <f>IF(ISBLANK(E275),"",_xlfn.XLOOKUP(E275,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17583,7 +17622,7 @@
       <c r="P275" s="92"/>
       <c r="AI275" s="91"/>
     </row>
-    <row r="276" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="33" t="str">
         <f>IF(ISBLANK(E276),"",_xlfn.XLOOKUP(E276,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17607,7 +17646,7 @@
       <c r="P276" s="92"/>
       <c r="AI276" s="91"/>
     </row>
-    <row r="277" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="33" t="str">
         <f>IF(ISBLANK(E277),"",_xlfn.XLOOKUP(E277,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17631,7 +17670,7 @@
       <c r="P277" s="92"/>
       <c r="AI277" s="91"/>
     </row>
-    <row r="278" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="33" t="str">
         <f>IF(ISBLANK(E278),"",_xlfn.XLOOKUP(E278,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17655,7 +17694,7 @@
       <c r="P278" s="92"/>
       <c r="AI278" s="91"/>
     </row>
-    <row r="279" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="33" t="str">
         <f>IF(ISBLANK(E279),"",_xlfn.XLOOKUP(E279,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17679,7 +17718,7 @@
       <c r="P279" s="92"/>
       <c r="AI279" s="91"/>
     </row>
-    <row r="280" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="33" t="str">
         <f>IF(ISBLANK(E280),"",_xlfn.XLOOKUP(E280,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17703,7 +17742,7 @@
       <c r="P280" s="92"/>
       <c r="AI280" s="91"/>
     </row>
-    <row r="281" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="33" t="str">
         <f>IF(ISBLANK(E281),"",_xlfn.XLOOKUP(E281,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17727,7 +17766,7 @@
       <c r="P281" s="92"/>
       <c r="AI281" s="91"/>
     </row>
-    <row r="282" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="33" t="str">
         <f>IF(ISBLANK(E282),"",_xlfn.XLOOKUP(E282,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17751,7 +17790,7 @@
       <c r="P282" s="92"/>
       <c r="AI282" s="91"/>
     </row>
-    <row r="283" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="33" t="str">
         <f>IF(ISBLANK(E283),"",_xlfn.XLOOKUP(E283,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17775,7 +17814,7 @@
       <c r="P283" s="92"/>
       <c r="AI283" s="91"/>
     </row>
-    <row r="284" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="33" t="str">
         <f>IF(ISBLANK(E284),"",_xlfn.XLOOKUP(E284,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17799,7 +17838,7 @@
       <c r="P284" s="92"/>
       <c r="AI284" s="91"/>
     </row>
-    <row r="285" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="33" t="str">
         <f>IF(ISBLANK(E285),"",_xlfn.XLOOKUP(E285,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17823,7 +17862,7 @@
       <c r="P285" s="92"/>
       <c r="AI285" s="91"/>
     </row>
-    <row r="286" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="33" t="str">
         <f>IF(ISBLANK(E286),"",_xlfn.XLOOKUP(E286,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17847,7 +17886,7 @@
       <c r="P286" s="92"/>
       <c r="AI286" s="91"/>
     </row>
-    <row r="287" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="33" t="str">
         <f>IF(ISBLANK(E287),"",_xlfn.XLOOKUP(E287,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17871,7 +17910,7 @@
       <c r="P287" s="92"/>
       <c r="AI287" s="91"/>
     </row>
-    <row r="288" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="33" t="str">
         <f>IF(ISBLANK(E288),"",_xlfn.XLOOKUP(E288,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17895,7 +17934,7 @@
       <c r="P288" s="92"/>
       <c r="AI288" s="91"/>
     </row>
-    <row r="289" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="33" t="str">
         <f>IF(ISBLANK(E289),"",_xlfn.XLOOKUP(E289,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17919,7 +17958,7 @@
       <c r="P289" s="92"/>
       <c r="AI289" s="91"/>
     </row>
-    <row r="290" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="33" t="str">
         <f>IF(ISBLANK(E290),"",_xlfn.XLOOKUP(E290,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17943,7 +17982,7 @@
       <c r="P290" s="92"/>
       <c r="AI290" s="91"/>
     </row>
-    <row r="291" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="33" t="str">
         <f>IF(ISBLANK(E291),"",_xlfn.XLOOKUP(E291,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17967,7 +18006,7 @@
       <c r="P291" s="92"/>
       <c r="AI291" s="91"/>
     </row>
-    <row r="292" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="33" t="str">
         <f>IF(ISBLANK(E292),"",_xlfn.XLOOKUP(E292,Info!A:A,Info!B:B))</f>
         <v/>
@@ -17991,7 +18030,7 @@
       <c r="P292" s="92"/>
       <c r="AI292" s="91"/>
     </row>
-    <row r="293" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="33" t="str">
         <f>IF(ISBLANK(E293),"",_xlfn.XLOOKUP(E293,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18015,7 +18054,7 @@
       <c r="P293" s="92"/>
       <c r="AI293" s="91"/>
     </row>
-    <row r="294" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="33" t="str">
         <f>IF(ISBLANK(E294),"",_xlfn.XLOOKUP(E294,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18039,7 +18078,7 @@
       <c r="P294" s="92"/>
       <c r="AI294" s="91"/>
     </row>
-    <row r="295" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="33" t="str">
         <f>IF(ISBLANK(E295),"",_xlfn.XLOOKUP(E295,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18063,7 +18102,7 @@
       <c r="P295" s="92"/>
       <c r="AI295" s="91"/>
     </row>
-    <row r="296" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="33" t="str">
         <f>IF(ISBLANK(E296),"",_xlfn.XLOOKUP(E296,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18087,7 +18126,7 @@
       <c r="P296" s="92"/>
       <c r="AI296" s="91"/>
     </row>
-    <row r="297" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="33" t="str">
         <f>IF(ISBLANK(E297),"",_xlfn.XLOOKUP(E297,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18111,7 +18150,7 @@
       <c r="P297" s="92"/>
       <c r="AI297" s="91"/>
     </row>
-    <row r="298" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="33" t="str">
         <f>IF(ISBLANK(E298),"",_xlfn.XLOOKUP(E298,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18135,7 +18174,7 @@
       <c r="P298" s="92"/>
       <c r="AI298" s="91"/>
     </row>
-    <row r="299" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="33" t="str">
         <f>IF(ISBLANK(E299),"",_xlfn.XLOOKUP(E299,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18159,7 +18198,7 @@
       <c r="P299" s="92"/>
       <c r="AI299" s="91"/>
     </row>
-    <row r="300" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="33" t="str">
         <f>IF(ISBLANK(E300),"",_xlfn.XLOOKUP(E300,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18183,7 +18222,7 @@
       <c r="P300" s="92"/>
       <c r="AI300" s="91"/>
     </row>
-    <row r="301" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="33" t="str">
         <f>IF(ISBLANK(E301),"",_xlfn.XLOOKUP(E301,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18207,7 +18246,7 @@
       <c r="P301" s="92"/>
       <c r="AI301" s="91"/>
     </row>
-    <row r="302" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A302" s="33" t="str">
         <f>IF(ISBLANK(E302),"",_xlfn.XLOOKUP(E302,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18231,7 +18270,7 @@
       <c r="P302" s="92"/>
       <c r="AI302" s="91"/>
     </row>
-    <row r="303" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="33" t="str">
         <f>IF(ISBLANK(E303),"",_xlfn.XLOOKUP(E303,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18255,7 +18294,7 @@
       <c r="P303" s="92"/>
       <c r="AI303" s="91"/>
     </row>
-    <row r="304" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="33" t="str">
         <f>IF(ISBLANK(E304),"",_xlfn.XLOOKUP(E304,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18279,7 +18318,7 @@
       <c r="P304" s="92"/>
       <c r="AI304" s="91"/>
     </row>
-    <row r="305" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A305" s="33" t="str">
         <f>IF(ISBLANK(E305),"",_xlfn.XLOOKUP(E305,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18303,7 +18342,7 @@
       <c r="P305" s="92"/>
       <c r="AI305" s="91"/>
     </row>
-    <row r="306" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="33" t="str">
         <f>IF(ISBLANK(E306),"",_xlfn.XLOOKUP(E306,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18327,7 +18366,7 @@
       <c r="P306" s="92"/>
       <c r="AI306" s="91"/>
     </row>
-    <row r="307" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="33" t="str">
         <f>IF(ISBLANK(E307),"",_xlfn.XLOOKUP(E307,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18351,7 +18390,7 @@
       <c r="P307" s="92"/>
       <c r="AI307" s="91"/>
     </row>
-    <row r="308" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="33" t="str">
         <f>IF(ISBLANK(E308),"",_xlfn.XLOOKUP(E308,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18375,7 +18414,7 @@
       <c r="P308" s="92"/>
       <c r="AI308" s="91"/>
     </row>
-    <row r="309" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="33" t="str">
         <f>IF(ISBLANK(E309),"",_xlfn.XLOOKUP(E309,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18399,7 +18438,7 @@
       <c r="P309" s="92"/>
       <c r="AI309" s="91"/>
     </row>
-    <row r="310" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="33" t="str">
         <f>IF(ISBLANK(E310),"",_xlfn.XLOOKUP(E310,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18423,7 +18462,7 @@
       <c r="P310" s="92"/>
       <c r="AI310" s="91"/>
     </row>
-    <row r="311" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="33" t="str">
         <f>IF(ISBLANK(E311),"",_xlfn.XLOOKUP(E311,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18447,7 +18486,7 @@
       <c r="P311" s="92"/>
       <c r="AI311" s="91"/>
     </row>
-    <row r="312" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="33" t="str">
         <f>IF(ISBLANK(E312),"",_xlfn.XLOOKUP(E312,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18471,7 +18510,7 @@
       <c r="P312" s="92"/>
       <c r="AI312" s="91"/>
     </row>
-    <row r="313" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="33" t="str">
         <f>IF(ISBLANK(E313),"",_xlfn.XLOOKUP(E313,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18495,7 +18534,7 @@
       <c r="P313" s="92"/>
       <c r="AI313" s="91"/>
     </row>
-    <row r="314" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="33" t="str">
         <f>IF(ISBLANK(E314),"",_xlfn.XLOOKUP(E314,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18519,7 +18558,7 @@
       <c r="P314" s="92"/>
       <c r="AI314" s="91"/>
     </row>
-    <row r="315" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A315" s="33" t="str">
         <f>IF(ISBLANK(E315),"",_xlfn.XLOOKUP(E315,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18543,7 +18582,7 @@
       <c r="P315" s="92"/>
       <c r="AI315" s="91"/>
     </row>
-    <row r="316" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A316" s="33" t="str">
         <f>IF(ISBLANK(E316),"",_xlfn.XLOOKUP(E316,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18567,7 +18606,7 @@
       <c r="P316" s="92"/>
       <c r="AI316" s="91"/>
     </row>
-    <row r="317" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="33" t="str">
         <f>IF(ISBLANK(E317),"",_xlfn.XLOOKUP(E317,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18591,7 +18630,7 @@
       <c r="P317" s="92"/>
       <c r="AI317" s="91"/>
     </row>
-    <row r="318" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A318" s="33" t="str">
         <f>IF(ISBLANK(E318),"",_xlfn.XLOOKUP(E318,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18615,7 +18654,7 @@
       <c r="P318" s="92"/>
       <c r="AI318" s="91"/>
     </row>
-    <row r="319" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="33" t="str">
         <f>IF(ISBLANK(E319),"",_xlfn.XLOOKUP(E319,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18639,7 +18678,7 @@
       <c r="P319" s="92"/>
       <c r="AI319" s="91"/>
     </row>
-    <row r="320" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="33" t="str">
         <f>IF(ISBLANK(E320),"",_xlfn.XLOOKUP(E320,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18663,7 +18702,7 @@
       <c r="P320" s="92"/>
       <c r="AI320" s="91"/>
     </row>
-    <row r="321" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="33" t="str">
         <f>IF(ISBLANK(E321),"",_xlfn.XLOOKUP(E321,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18687,7 +18726,7 @@
       <c r="P321" s="92"/>
       <c r="AI321" s="91"/>
     </row>
-    <row r="322" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="33" t="str">
         <f>IF(ISBLANK(E322),"",_xlfn.XLOOKUP(E322,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18711,7 +18750,7 @@
       <c r="P322" s="92"/>
       <c r="AI322" s="91"/>
     </row>
-    <row r="323" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="33" t="str">
         <f>IF(ISBLANK(E323),"",_xlfn.XLOOKUP(E323,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18735,7 +18774,7 @@
       <c r="P323" s="92"/>
       <c r="AI323" s="91"/>
     </row>
-    <row r="324" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="33" t="str">
         <f>IF(ISBLANK(E324),"",_xlfn.XLOOKUP(E324,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18759,7 +18798,7 @@
       <c r="P324" s="92"/>
       <c r="AI324" s="91"/>
     </row>
-    <row r="325" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="33" t="str">
         <f>IF(ISBLANK(E325),"",_xlfn.XLOOKUP(E325,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18783,7 +18822,7 @@
       <c r="P325" s="92"/>
       <c r="AI325" s="91"/>
     </row>
-    <row r="326" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="33" t="str">
         <f>IF(ISBLANK(E326),"",_xlfn.XLOOKUP(E326,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18807,7 +18846,7 @@
       <c r="P326" s="92"/>
       <c r="AI326" s="91"/>
     </row>
-    <row r="327" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="33" t="str">
         <f>IF(ISBLANK(E327),"",_xlfn.XLOOKUP(E327,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18831,7 +18870,7 @@
       <c r="P327" s="92"/>
       <c r="AI327" s="91"/>
     </row>
-    <row r="328" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="33" t="str">
         <f>IF(ISBLANK(E328),"",_xlfn.XLOOKUP(E328,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18855,7 +18894,7 @@
       <c r="P328" s="92"/>
       <c r="AI328" s="91"/>
     </row>
-    <row r="329" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="33" t="str">
         <f>IF(ISBLANK(E329),"",_xlfn.XLOOKUP(E329,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18879,7 +18918,7 @@
       <c r="P329" s="92"/>
       <c r="AI329" s="91"/>
     </row>
-    <row r="330" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="33" t="str">
         <f>IF(ISBLANK(E330),"",_xlfn.XLOOKUP(E330,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18903,7 +18942,7 @@
       <c r="P330" s="92"/>
       <c r="AI330" s="91"/>
     </row>
-    <row r="331" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="33" t="str">
         <f>IF(ISBLANK(E331),"",_xlfn.XLOOKUP(E331,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18927,7 +18966,7 @@
       <c r="P331" s="92"/>
       <c r="AI331" s="91"/>
     </row>
-    <row r="332" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="33" t="str">
         <f>IF(ISBLANK(E332),"",_xlfn.XLOOKUP(E332,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18951,7 +18990,7 @@
       <c r="P332" s="92"/>
       <c r="AI332" s="91"/>
     </row>
-    <row r="333" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A333" s="33" t="str">
         <f>IF(ISBLANK(E333),"",_xlfn.XLOOKUP(E333,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18975,7 +19014,7 @@
       <c r="P333" s="92"/>
       <c r="AI333" s="91"/>
     </row>
-    <row r="334" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="33" t="str">
         <f>IF(ISBLANK(E334),"",_xlfn.XLOOKUP(E334,Info!A:A,Info!B:B))</f>
         <v/>
@@ -18999,7 +19038,7 @@
       <c r="P334" s="92"/>
       <c r="AI334" s="91"/>
     </row>
-    <row r="335" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A335" s="33" t="str">
         <f>IF(ISBLANK(E335),"",_xlfn.XLOOKUP(E335,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19023,7 +19062,7 @@
       <c r="P335" s="92"/>
       <c r="AI335" s="91"/>
     </row>
-    <row r="336" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A336" s="33" t="str">
         <f>IF(ISBLANK(E336),"",_xlfn.XLOOKUP(E336,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19047,7 +19086,7 @@
       <c r="P336" s="92"/>
       <c r="AI336" s="91"/>
     </row>
-    <row r="337" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A337" s="33" t="str">
         <f>IF(ISBLANK(E337),"",_xlfn.XLOOKUP(E337,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19071,7 +19110,7 @@
       <c r="P337" s="92"/>
       <c r="AI337" s="91"/>
     </row>
-    <row r="338" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A338" s="33" t="str">
         <f>IF(ISBLANK(E338),"",_xlfn.XLOOKUP(E338,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19095,7 +19134,7 @@
       <c r="P338" s="92"/>
       <c r="AI338" s="91"/>
     </row>
-    <row r="339" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A339" s="33" t="str">
         <f>IF(ISBLANK(E339),"",_xlfn.XLOOKUP(E339,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19119,7 +19158,7 @@
       <c r="P339" s="92"/>
       <c r="AI339" s="91"/>
     </row>
-    <row r="340" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A340" s="33" t="str">
         <f>IF(ISBLANK(E340),"",_xlfn.XLOOKUP(E340,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19143,7 +19182,7 @@
       <c r="P340" s="92"/>
       <c r="AI340" s="91"/>
     </row>
-    <row r="341" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A341" s="33" t="str">
         <f>IF(ISBLANK(E341),"",_xlfn.XLOOKUP(E341,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19167,7 +19206,7 @@
       <c r="P341" s="92"/>
       <c r="AI341" s="91"/>
     </row>
-    <row r="342" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A342" s="33" t="str">
         <f>IF(ISBLANK(E342),"",_xlfn.XLOOKUP(E342,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19191,7 +19230,7 @@
       <c r="P342" s="92"/>
       <c r="AI342" s="91"/>
     </row>
-    <row r="343" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A343" s="33" t="str">
         <f>IF(ISBLANK(E343),"",_xlfn.XLOOKUP(E343,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19215,7 +19254,7 @@
       <c r="P343" s="92"/>
       <c r="AI343" s="91"/>
     </row>
-    <row r="344" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="33" t="str">
         <f>IF(ISBLANK(E344),"",_xlfn.XLOOKUP(E344,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19239,7 +19278,7 @@
       <c r="P344" s="92"/>
       <c r="AI344" s="91"/>
     </row>
-    <row r="345" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="33" t="str">
         <f>IF(ISBLANK(E345),"",_xlfn.XLOOKUP(E345,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19263,7 +19302,7 @@
       <c r="P345" s="92"/>
       <c r="AI345" s="91"/>
     </row>
-    <row r="346" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="33" t="str">
         <f>IF(ISBLANK(E346),"",_xlfn.XLOOKUP(E346,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19287,7 +19326,7 @@
       <c r="P346" s="92"/>
       <c r="AI346" s="91"/>
     </row>
-    <row r="347" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="33" t="str">
         <f>IF(ISBLANK(E347),"",_xlfn.XLOOKUP(E347,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19311,7 +19350,7 @@
       <c r="P347" s="92"/>
       <c r="AI347" s="91"/>
     </row>
-    <row r="348" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A348" s="33" t="str">
         <f>IF(ISBLANK(E348),"",_xlfn.XLOOKUP(E348,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19335,7 +19374,7 @@
       <c r="P348" s="92"/>
       <c r="AI348" s="91"/>
     </row>
-    <row r="349" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="33" t="str">
         <f>IF(ISBLANK(E349),"",_xlfn.XLOOKUP(E349,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19359,7 +19398,7 @@
       <c r="P349" s="92"/>
       <c r="AI349" s="91"/>
     </row>
-    <row r="350" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A350" s="33" t="str">
         <f>IF(ISBLANK(E350),"",_xlfn.XLOOKUP(E350,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19383,7 +19422,7 @@
       <c r="P350" s="92"/>
       <c r="AI350" s="91"/>
     </row>
-    <row r="351" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A351" s="33" t="str">
         <f>IF(ISBLANK(E351),"",_xlfn.XLOOKUP(E351,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19407,7 +19446,7 @@
       <c r="P351" s="92"/>
       <c r="AI351" s="91"/>
     </row>
-    <row r="352" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A352" s="33" t="str">
         <f>IF(ISBLANK(E352),"",_xlfn.XLOOKUP(E352,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19431,7 +19470,7 @@
       <c r="P352" s="92"/>
       <c r="AI352" s="91"/>
     </row>
-    <row r="353" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A353" s="33" t="str">
         <f>IF(ISBLANK(E353),"",_xlfn.XLOOKUP(E353,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19455,7 +19494,7 @@
       <c r="P353" s="92"/>
       <c r="AI353" s="91"/>
     </row>
-    <row r="354" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A354" s="33" t="str">
         <f>IF(ISBLANK(E354),"",_xlfn.XLOOKUP(E354,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19479,7 +19518,7 @@
       <c r="P354" s="92"/>
       <c r="AI354" s="91"/>
     </row>
-    <row r="355" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A355" s="33" t="str">
         <f>IF(ISBLANK(E355),"",_xlfn.XLOOKUP(E355,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19503,7 +19542,7 @@
       <c r="P355" s="92"/>
       <c r="AI355" s="91"/>
     </row>
-    <row r="356" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A356" s="33" t="str">
         <f>IF(ISBLANK(E356),"",_xlfn.XLOOKUP(E356,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19527,7 +19566,7 @@
       <c r="P356" s="92"/>
       <c r="AI356" s="91"/>
     </row>
-    <row r="357" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A357" s="33" t="str">
         <f>IF(ISBLANK(E357),"",_xlfn.XLOOKUP(E357,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19551,7 +19590,7 @@
       <c r="P357" s="92"/>
       <c r="AI357" s="91"/>
     </row>
-    <row r="358" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A358" s="33" t="str">
         <f>IF(ISBLANK(E358),"",_xlfn.XLOOKUP(E358,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19575,7 +19614,7 @@
       <c r="P358" s="92"/>
       <c r="AI358" s="91"/>
     </row>
-    <row r="359" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A359" s="33" t="str">
         <f>IF(ISBLANK(E359),"",_xlfn.XLOOKUP(E359,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19599,7 +19638,7 @@
       <c r="P359" s="92"/>
       <c r="AI359" s="91"/>
     </row>
-    <row r="360" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A360" s="33" t="str">
         <f>IF(ISBLANK(E360),"",_xlfn.XLOOKUP(E360,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19623,7 +19662,7 @@
       <c r="P360" s="92"/>
       <c r="AI360" s="91"/>
     </row>
-    <row r="361" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A361" s="33" t="str">
         <f>IF(ISBLANK(E361),"",_xlfn.XLOOKUP(E361,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19647,7 +19686,7 @@
       <c r="P361" s="92"/>
       <c r="AI361" s="91"/>
     </row>
-    <row r="362" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A362" s="33" t="str">
         <f>IF(ISBLANK(E362),"",_xlfn.XLOOKUP(E362,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19671,7 +19710,7 @@
       <c r="P362" s="92"/>
       <c r="AI362" s="91"/>
     </row>
-    <row r="363" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A363" s="33" t="str">
         <f>IF(ISBLANK(E363),"",_xlfn.XLOOKUP(E363,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19695,7 +19734,7 @@
       <c r="P363" s="92"/>
       <c r="AI363" s="91"/>
     </row>
-    <row r="364" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A364" s="33" t="str">
         <f>IF(ISBLANK(E364),"",_xlfn.XLOOKUP(E364,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19719,7 +19758,7 @@
       <c r="P364" s="92"/>
       <c r="AI364" s="91"/>
     </row>
-    <row r="365" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A365" s="33" t="str">
         <f>IF(ISBLANK(E365),"",_xlfn.XLOOKUP(E365,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19743,7 +19782,7 @@
       <c r="P365" s="92"/>
       <c r="AI365" s="91"/>
     </row>
-    <row r="366" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A366" s="33" t="str">
         <f>IF(ISBLANK(E366),"",_xlfn.XLOOKUP(E366,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19767,7 +19806,7 @@
       <c r="P366" s="92"/>
       <c r="AI366" s="91"/>
     </row>
-    <row r="367" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A367" s="33" t="str">
         <f>IF(ISBLANK(E367),"",_xlfn.XLOOKUP(E367,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19791,7 +19830,7 @@
       <c r="P367" s="92"/>
       <c r="AI367" s="91"/>
     </row>
-    <row r="368" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A368" s="33" t="str">
         <f>IF(ISBLANK(E368),"",_xlfn.XLOOKUP(E368,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19815,7 +19854,7 @@
       <c r="P368" s="92"/>
       <c r="AI368" s="91"/>
     </row>
-    <row r="369" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A369" s="33" t="str">
         <f>IF(ISBLANK(E369),"",_xlfn.XLOOKUP(E369,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19839,7 +19878,7 @@
       <c r="P369" s="92"/>
       <c r="AI369" s="91"/>
     </row>
-    <row r="370" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A370" s="33" t="str">
         <f>IF(ISBLANK(E370),"",_xlfn.XLOOKUP(E370,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19863,7 +19902,7 @@
       <c r="P370" s="92"/>
       <c r="AI370" s="91"/>
     </row>
-    <row r="371" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A371" s="33" t="str">
         <f>IF(ISBLANK(E371),"",_xlfn.XLOOKUP(E371,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19887,7 +19926,7 @@
       <c r="P371" s="92"/>
       <c r="AI371" s="91"/>
     </row>
-    <row r="372" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A372" s="33" t="str">
         <f>IF(ISBLANK(E372),"",_xlfn.XLOOKUP(E372,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19911,7 +19950,7 @@
       <c r="P372" s="92"/>
       <c r="AI372" s="91"/>
     </row>
-    <row r="373" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A373" s="33" t="str">
         <f>IF(ISBLANK(E373),"",_xlfn.XLOOKUP(E373,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19935,7 +19974,7 @@
       <c r="P373" s="92"/>
       <c r="AI373" s="91"/>
     </row>
-    <row r="374" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A374" s="33" t="str">
         <f>IF(ISBLANK(E374),"",_xlfn.XLOOKUP(E374,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19959,7 +19998,7 @@
       <c r="P374" s="92"/>
       <c r="AI374" s="91"/>
     </row>
-    <row r="375" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A375" s="33" t="str">
         <f>IF(ISBLANK(E375),"",_xlfn.XLOOKUP(E375,Info!A:A,Info!B:B))</f>
         <v/>
@@ -19983,7 +20022,7 @@
       <c r="P375" s="92"/>
       <c r="AI375" s="91"/>
     </row>
-    <row r="376" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A376" s="33" t="str">
         <f>IF(ISBLANK(E376),"",_xlfn.XLOOKUP(E376,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20007,7 +20046,7 @@
       <c r="P376" s="92"/>
       <c r="AI376" s="91"/>
     </row>
-    <row r="377" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A377" s="33" t="str">
         <f>IF(ISBLANK(E377),"",_xlfn.XLOOKUP(E377,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20031,7 +20070,7 @@
       <c r="P377" s="92"/>
       <c r="AI377" s="91"/>
     </row>
-    <row r="378" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A378" s="33" t="str">
         <f>IF(ISBLANK(E378),"",_xlfn.XLOOKUP(E378,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20055,7 +20094,7 @@
       <c r="P378" s="92"/>
       <c r="AI378" s="91"/>
     </row>
-    <row r="379" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A379" s="33" t="str">
         <f>IF(ISBLANK(E379),"",_xlfn.XLOOKUP(E379,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20079,7 +20118,7 @@
       <c r="P379" s="92"/>
       <c r="AI379" s="91"/>
     </row>
-    <row r="380" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A380" s="33" t="str">
         <f>IF(ISBLANK(E380),"",_xlfn.XLOOKUP(E380,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20103,7 +20142,7 @@
       <c r="P380" s="92"/>
       <c r="AI380" s="91"/>
     </row>
-    <row r="381" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A381" s="33" t="str">
         <f>IF(ISBLANK(E381),"",_xlfn.XLOOKUP(E381,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20127,7 +20166,7 @@
       <c r="P381" s="92"/>
       <c r="AI381" s="91"/>
     </row>
-    <row r="382" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A382" s="33" t="str">
         <f>IF(ISBLANK(E382),"",_xlfn.XLOOKUP(E382,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20151,7 +20190,7 @@
       <c r="P382" s="92"/>
       <c r="AI382" s="91"/>
     </row>
-    <row r="383" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A383" s="33" t="str">
         <f>IF(ISBLANK(E383),"",_xlfn.XLOOKUP(E383,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20175,7 +20214,7 @@
       <c r="P383" s="92"/>
       <c r="AI383" s="91"/>
     </row>
-    <row r="384" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A384" s="33" t="str">
         <f>IF(ISBLANK(E384),"",_xlfn.XLOOKUP(E384,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20199,7 +20238,7 @@
       <c r="P384" s="92"/>
       <c r="AI384" s="91"/>
     </row>
-    <row r="385" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A385" s="33" t="str">
         <f>IF(ISBLANK(E385),"",_xlfn.XLOOKUP(E385,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20223,7 +20262,7 @@
       <c r="P385" s="92"/>
       <c r="AI385" s="91"/>
     </row>
-    <row r="386" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A386" s="33" t="str">
         <f>IF(ISBLANK(E386),"",_xlfn.XLOOKUP(E386,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20247,7 +20286,7 @@
       <c r="P386" s="92"/>
       <c r="AI386" s="91"/>
     </row>
-    <row r="387" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A387" s="33" t="str">
         <f>IF(ISBLANK(E387),"",_xlfn.XLOOKUP(E387,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20271,7 +20310,7 @@
       <c r="P387" s="92"/>
       <c r="AI387" s="91"/>
     </row>
-    <row r="388" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A388" s="33" t="str">
         <f>IF(ISBLANK(E388),"",_xlfn.XLOOKUP(E388,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20295,7 +20334,7 @@
       <c r="P388" s="92"/>
       <c r="AI388" s="91"/>
     </row>
-    <row r="389" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A389" s="33" t="str">
         <f>IF(ISBLANK(E389),"",_xlfn.XLOOKUP(E389,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20319,7 +20358,7 @@
       <c r="P389" s="92"/>
       <c r="AI389" s="91"/>
     </row>
-    <row r="390" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A390" s="33" t="str">
         <f>IF(ISBLANK(E390),"",_xlfn.XLOOKUP(E390,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20343,7 +20382,7 @@
       <c r="P390" s="92"/>
       <c r="AI390" s="91"/>
     </row>
-    <row r="391" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A391" s="33" t="str">
         <f>IF(ISBLANK(E391),"",_xlfn.XLOOKUP(E391,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20367,7 +20406,7 @@
       <c r="P391" s="92"/>
       <c r="AI391" s="91"/>
     </row>
-    <row r="392" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A392" s="33" t="str">
         <f>IF(ISBLANK(E392),"",_xlfn.XLOOKUP(E392,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20391,7 +20430,7 @@
       <c r="P392" s="92"/>
       <c r="AI392" s="91"/>
     </row>
-    <row r="393" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A393" s="33" t="str">
         <f>IF(ISBLANK(E393),"",_xlfn.XLOOKUP(E393,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20415,7 +20454,7 @@
       <c r="P393" s="92"/>
       <c r="AI393" s="91"/>
     </row>
-    <row r="394" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A394" s="33" t="str">
         <f>IF(ISBLANK(E394),"",_xlfn.XLOOKUP(E394,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20439,7 +20478,7 @@
       <c r="P394" s="92"/>
       <c r="AI394" s="91"/>
     </row>
-    <row r="395" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A395" s="33" t="str">
         <f>IF(ISBLANK(E395),"",_xlfn.XLOOKUP(E395,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20463,7 +20502,7 @@
       <c r="P395" s="92"/>
       <c r="AI395" s="91"/>
     </row>
-    <row r="396" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A396" s="33" t="str">
         <f>IF(ISBLANK(E396),"",_xlfn.XLOOKUP(E396,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20487,7 +20526,7 @@
       <c r="P396" s="92"/>
       <c r="AI396" s="91"/>
     </row>
-    <row r="397" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A397" s="33" t="str">
         <f>IF(ISBLANK(E397),"",_xlfn.XLOOKUP(E397,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20511,7 +20550,7 @@
       <c r="P397" s="92"/>
       <c r="AI397" s="91"/>
     </row>
-    <row r="398" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A398" s="33" t="str">
         <f>IF(ISBLANK(E398),"",_xlfn.XLOOKUP(E398,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20535,7 +20574,7 @@
       <c r="P398" s="92"/>
       <c r="AI398" s="91"/>
     </row>
-    <row r="399" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A399" s="33" t="str">
         <f>IF(ISBLANK(E399),"",_xlfn.XLOOKUP(E399,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20559,7 +20598,7 @@
       <c r="P399" s="92"/>
       <c r="AI399" s="91"/>
     </row>
-    <row r="400" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A400" s="33" t="str">
         <f>IF(ISBLANK(E400),"",_xlfn.XLOOKUP(E400,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20583,7 +20622,7 @@
       <c r="P400" s="92"/>
       <c r="AI400" s="91"/>
     </row>
-    <row r="401" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A401" s="33" t="str">
         <f>IF(ISBLANK(E401),"",_xlfn.XLOOKUP(E401,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20607,7 +20646,7 @@
       <c r="P401" s="92"/>
       <c r="AI401" s="91"/>
     </row>
-    <row r="402" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A402" s="33" t="str">
         <f>IF(ISBLANK(E402),"",_xlfn.XLOOKUP(E402,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20631,7 +20670,7 @@
       <c r="P402" s="92"/>
       <c r="AI402" s="91"/>
     </row>
-    <row r="403" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A403" s="33" t="str">
         <f>IF(ISBLANK(E403),"",_xlfn.XLOOKUP(E403,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20655,7 +20694,7 @@
       <c r="P403" s="92"/>
       <c r="AI403" s="91"/>
     </row>
-    <row r="404" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:35" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A404" s="33" t="str">
         <f>IF(ISBLANK(E404),"",_xlfn.XLOOKUP(E404,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20679,31 +20718,17 @@
       <c r="P404" s="92"/>
       <c r="AI404" s="91"/>
     </row>
-    <row r="405" spans="1:35" s="32" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A405" s="33" t="str">
         <f>IF(ISBLANK(E405),"",_xlfn.XLOOKUP(E405,Info!A:A,Info!B:B))</f>
         <v/>
       </c>
-      <c r="B405" s="33"/>
-      <c r="C405" s="33"/>
-      <c r="D405" s="54"/>
-      <c r="E405" s="91"/>
-      <c r="F405" s="54"/>
       <c r="G405" s="33" t="str">
         <f>IF(ISBLANK(H405),"",_xlfn.XLOOKUP(H405,Info!A:A,Info!B:B))</f>
         <v/>
       </c>
-      <c r="H405" s="98"/>
-      <c r="I405" s="103"/>
-      <c r="J405" s="33"/>
-      <c r="K405" s="33"/>
-      <c r="L405" s="33"/>
-      <c r="M405" s="67"/>
-      <c r="N405" s="50"/>
-      <c r="P405" s="92"/>
-      <c r="AI405" s="91"/>
-    </row>
-    <row r="406" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="406" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A406" s="33" t="str">
         <f>IF(ISBLANK(E406),"",_xlfn.XLOOKUP(E406,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20713,7 +20738,7 @@
         <v/>
       </c>
     </row>
-    <row r="407" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A407" s="33" t="str">
         <f>IF(ISBLANK(E407),"",_xlfn.XLOOKUP(E407,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20723,7 +20748,7 @@
         <v/>
       </c>
     </row>
-    <row r="408" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A408" s="33" t="str">
         <f>IF(ISBLANK(E408),"",_xlfn.XLOOKUP(E408,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20733,7 +20758,7 @@
         <v/>
       </c>
     </row>
-    <row r="409" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A409" s="33" t="str">
         <f>IF(ISBLANK(E409),"",_xlfn.XLOOKUP(E409,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20743,7 +20768,7 @@
         <v/>
       </c>
     </row>
-    <row r="410" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A410" s="33" t="str">
         <f>IF(ISBLANK(E410),"",_xlfn.XLOOKUP(E410,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20753,7 +20778,7 @@
         <v/>
       </c>
     </row>
-    <row r="411" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A411" s="33" t="str">
         <f>IF(ISBLANK(E411),"",_xlfn.XLOOKUP(E411,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20763,7 +20788,7 @@
         <v/>
       </c>
     </row>
-    <row r="412" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A412" s="33" t="str">
         <f>IF(ISBLANK(E412),"",_xlfn.XLOOKUP(E412,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20773,7 +20798,7 @@
         <v/>
       </c>
     </row>
-    <row r="413" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A413" s="33" t="str">
         <f>IF(ISBLANK(E413),"",_xlfn.XLOOKUP(E413,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20783,7 +20808,7 @@
         <v/>
       </c>
     </row>
-    <row r="414" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A414" s="33" t="str">
         <f>IF(ISBLANK(E414),"",_xlfn.XLOOKUP(E414,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20793,7 +20818,7 @@
         <v/>
       </c>
     </row>
-    <row r="415" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A415" s="33" t="str">
         <f>IF(ISBLANK(E415),"",_xlfn.XLOOKUP(E415,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20803,7 +20828,7 @@
         <v/>
       </c>
     </row>
-    <row r="416" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A416" s="33" t="str">
         <f>IF(ISBLANK(E416),"",_xlfn.XLOOKUP(E416,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20813,7 +20838,7 @@
         <v/>
       </c>
     </row>
-    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417" s="33" t="str">
         <f>IF(ISBLANK(E417),"",_xlfn.XLOOKUP(E417,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20823,7 +20848,7 @@
         <v/>
       </c>
     </row>
-    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="33" t="str">
         <f>IF(ISBLANK(E418),"",_xlfn.XLOOKUP(E418,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20833,7 +20858,7 @@
         <v/>
       </c>
     </row>
-    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" s="33" t="str">
         <f>IF(ISBLANK(E419),"",_xlfn.XLOOKUP(E419,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20843,7 +20868,7 @@
         <v/>
       </c>
     </row>
-    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" s="33" t="str">
         <f>IF(ISBLANK(E420),"",_xlfn.XLOOKUP(E420,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20853,7 +20878,7 @@
         <v/>
       </c>
     </row>
-    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" s="33" t="str">
         <f>IF(ISBLANK(E421),"",_xlfn.XLOOKUP(E421,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20863,7 +20888,7 @@
         <v/>
       </c>
     </row>
-    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" s="33" t="str">
         <f>IF(ISBLANK(E422),"",_xlfn.XLOOKUP(E422,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20873,7 +20898,7 @@
         <v/>
       </c>
     </row>
-    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" s="33" t="str">
         <f>IF(ISBLANK(E423),"",_xlfn.XLOOKUP(E423,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20883,7 +20908,7 @@
         <v/>
       </c>
     </row>
-    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" s="33" t="str">
         <f>IF(ISBLANK(E424),"",_xlfn.XLOOKUP(E424,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20893,7 +20918,7 @@
         <v/>
       </c>
     </row>
-    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" s="33" t="str">
         <f>IF(ISBLANK(E425),"",_xlfn.XLOOKUP(E425,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20903,7 +20928,7 @@
         <v/>
       </c>
     </row>
-    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" s="33" t="str">
         <f>IF(ISBLANK(E426),"",_xlfn.XLOOKUP(E426,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20913,7 +20938,7 @@
         <v/>
       </c>
     </row>
-    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" s="33" t="str">
         <f>IF(ISBLANK(E427),"",_xlfn.XLOOKUP(E427,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20923,7 +20948,7 @@
         <v/>
       </c>
     </row>
-    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" s="33" t="str">
         <f>IF(ISBLANK(E428),"",_xlfn.XLOOKUP(E428,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20933,7 +20958,7 @@
         <v/>
       </c>
     </row>
-    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" s="33" t="str">
         <f>IF(ISBLANK(E429),"",_xlfn.XLOOKUP(E429,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20943,7 +20968,7 @@
         <v/>
       </c>
     </row>
-    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" s="33" t="str">
         <f>IF(ISBLANK(E430),"",_xlfn.XLOOKUP(E430,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20953,7 +20978,7 @@
         <v/>
       </c>
     </row>
-    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" s="33" t="str">
         <f>IF(ISBLANK(E431),"",_xlfn.XLOOKUP(E431,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20963,7 +20988,7 @@
         <v/>
       </c>
     </row>
-    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" s="33" t="str">
         <f>IF(ISBLANK(E432),"",_xlfn.XLOOKUP(E432,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20973,7 +20998,7 @@
         <v/>
       </c>
     </row>
-    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" s="33" t="str">
         <f>IF(ISBLANK(E433),"",_xlfn.XLOOKUP(E433,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20983,7 +21008,7 @@
         <v/>
       </c>
     </row>
-    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" s="33" t="str">
         <f>IF(ISBLANK(E434),"",_xlfn.XLOOKUP(E434,Info!A:A,Info!B:B))</f>
         <v/>
@@ -20993,7 +21018,7 @@
         <v/>
       </c>
     </row>
-    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" s="33" t="str">
         <f>IF(ISBLANK(E435),"",_xlfn.XLOOKUP(E435,Info!A:A,Info!B:B))</f>
         <v/>
@@ -21003,7 +21028,7 @@
         <v/>
       </c>
     </row>
-    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" s="33" t="str">
         <f>IF(ISBLANK(E436),"",_xlfn.XLOOKUP(E436,Info!A:A,Info!B:B))</f>
         <v/>
@@ -21013,7 +21038,7 @@
         <v/>
       </c>
     </row>
-    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" s="33" t="str">
         <f>IF(ISBLANK(E437),"",_xlfn.XLOOKUP(E437,Info!A:A,Info!B:B))</f>
         <v/>
@@ -21023,7 +21048,7 @@
         <v/>
       </c>
     </row>
-    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" s="33" t="str">
         <f>IF(ISBLANK(E438),"",_xlfn.XLOOKUP(E438,Info!A:A,Info!B:B))</f>
         <v/>
@@ -21033,7 +21058,7 @@
         <v/>
       </c>
     </row>
-    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" s="33" t="str">
         <f>IF(ISBLANK(E439),"",_xlfn.XLOOKUP(E439,Info!A:A,Info!B:B))</f>
         <v/>
@@ -21043,7 +21068,7 @@
         <v/>
       </c>
     </row>
-    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" s="33" t="str">
         <f>IF(ISBLANK(E440),"",_xlfn.XLOOKUP(E440,Info!A:A,Info!B:B))</f>
         <v/>
@@ -21053,7 +21078,7 @@
         <v/>
       </c>
     </row>
-    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" s="33" t="str">
         <f>IF(ISBLANK(E441),"",_xlfn.XLOOKUP(E441,Info!A:A,Info!B:B))</f>
         <v/>
@@ -21063,7 +21088,7 @@
         <v/>
       </c>
     </row>
-    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" s="33" t="str">
         <f>IF(ISBLANK(E442),"",_xlfn.XLOOKUP(E442,Info!A:A,Info!B:B))</f>
         <v/>
@@ -21073,7 +21098,7 @@
         <v/>
       </c>
     </row>
-    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" s="33" t="str">
         <f>IF(ISBLANK(E443),"",_xlfn.XLOOKUP(E443,Info!A:A,Info!B:B))</f>
         <v/>
@@ -21083,7 +21108,7 @@
         <v/>
       </c>
     </row>
-    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" s="33" t="str">
         <f>IF(ISBLANK(E444),"",_xlfn.XLOOKUP(E444,Info!A:A,Info!B:B))</f>
         <v/>
@@ -21093,7 +21118,7 @@
         <v/>
       </c>
     </row>
-    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="33" t="str">
         <f>IF(ISBLANK(E445),"",_xlfn.XLOOKUP(E445,Info!A:A,Info!B:B))</f>
         <v/>
@@ -21103,23 +21128,17 @@
         <v/>
       </c>
     </row>
-    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A446" s="33" t="str">
-        <f>IF(ISBLANK(E446),"",_xlfn.XLOOKUP(E446,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-      <c r="G446" s="33" t="str">
-        <f>IF(ISBLANK(H446),"",_xlfn.XLOOKUP(H446,Info!A:A,Info!B:B))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P446" xr:uid="{C106C93E-E4E6-4212-A1AE-6CCBA718A489}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="Spec Building Analysis for Northeast"/>
+  <autoFilter ref="A1:P445" xr:uid="{C106C93E-E4E6-4212-A1AE-6CCBA718A489}">
+    <filterColumn colId="2">
+      <filters blank="1">
+        <filter val="Pending Scheduling"/>
+        <filter val="Scheduled"/>
       </filters>
     </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A81:P445">
+      <sortCondition ref="E1:E445"/>
+    </sortState>
   </autoFilter>
   <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
@@ -21233,7 +21252,7 @@
         <v>266</v>
       </c>
       <c r="Q1" s="140" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="R1" s="97"/>
     </row>
@@ -21263,37 +21282,37 @@
         <v>309</v>
       </c>
       <c r="Q2" s="141" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="R2" s="97"/>
     </row>
     <row r="3" spans="1:18" s="97" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="97" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B3" s="104" t="s">
         <v>300</v>
       </c>
       <c r="C3" s="105" t="s">
+        <v>372</v>
+      </c>
+      <c r="D3" s="105" t="s">
         <v>373</v>
       </c>
-      <c r="D3" s="105" t="s">
+      <c r="E3" s="105" t="s">
+        <v>394</v>
+      </c>
+      <c r="F3" s="105" t="s">
         <v>374</v>
       </c>
-      <c r="E3" s="105" t="s">
-        <v>395</v>
-      </c>
-      <c r="F3" s="105" t="s">
+      <c r="G3" s="105" t="s">
         <v>375</v>
       </c>
-      <c r="G3" s="105" t="s">
+      <c r="H3" s="105" t="s">
         <v>376</v>
       </c>
-      <c r="H3" s="105" t="s">
-        <v>377</v>
-      </c>
       <c r="Q3" s="142" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -21362,16 +21381,16 @@
         <v>317</v>
       </c>
       <c r="E6" s="33" t="s">
+        <v>537</v>
+      </c>
+      <c r="F6" s="33" t="s">
         <v>538</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="G6" s="33" t="s">
         <v>539</v>
       </c>
-      <c r="G6" s="33" t="s">
+      <c r="H6" s="33" t="s">
         <v>540</v>
-      </c>
-      <c r="H6" s="33" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -21410,7 +21429,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="107" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E9" s="135">
         <v>46164</v>
@@ -21427,7 +21446,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B10" s="98">
         <v>45792</v>
@@ -21535,7 +21554,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B14" s="98">
         <v>45971</v>
@@ -21617,7 +21636,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="97" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B17" s="139">
         <v>45859</v>
@@ -21827,7 +21846,7 @@
         <v>287</v>
       </c>
       <c r="B25" s="98">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="C25" s="98">
         <v>46496</v>
@@ -21854,7 +21873,7 @@
         <v>325</v>
       </c>
       <c r="B26" s="98">
-        <v>46878</v>
+        <v>46941</v>
       </c>
       <c r="C26" s="98">
         <v>47102</v>
@@ -21932,55 +21951,55 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="97" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B29" s="98" t="s">
+        <v>347</v>
+      </c>
+      <c r="C29" s="98" t="s">
         <v>348</v>
       </c>
-      <c r="C29" s="98" t="s">
+      <c r="D29" s="98" t="s">
         <v>349</v>
       </c>
-      <c r="D29" s="98" t="s">
-        <v>350</v>
-      </c>
       <c r="E29" s="136" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F29" s="136" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G29" s="136" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H29" s="136" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I29" s="96"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="97" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B30" s="98" t="s">
+        <v>347</v>
+      </c>
+      <c r="C30" s="98" t="s">
         <v>348</v>
       </c>
-      <c r="C30" s="98" t="s">
+      <c r="D30" s="98" t="s">
         <v>349</v>
       </c>
-      <c r="D30" s="98" t="s">
-        <v>350</v>
-      </c>
       <c r="E30" s="136" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F30" s="136" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G30" s="136" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H30" s="136" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I30" s="96"/>
     </row>
@@ -22214,7 +22233,7 @@
     </row>
     <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="95" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B40" s="98">
         <v>46139</v>
@@ -22322,7 +22341,7 @@
     </row>
     <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="95" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B44" s="98">
         <v>46148</v>
@@ -22337,7 +22356,7 @@
     </row>
     <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="94" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B45" s="98">
         <v>46154</v>
@@ -22411,7 +22430,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B49" s="98">
         <f t="shared" ref="B49:H49" si="0">B18-30</f>
@@ -22444,7 +22463,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B50" s="98">
         <f t="shared" ref="B50:H50" si="1">B20-30</f>
@@ -22477,7 +22496,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B51" s="98">
         <f t="shared" ref="B51:H51" si="2">B22-30</f>
@@ -22510,7 +22529,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B52" s="98">
         <v>46183</v>
@@ -22542,7 +22561,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B53" s="98">
         <f t="shared" ref="B53:C53" si="5">B27-517</f>
@@ -22575,7 +22594,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B54" s="33" t="s">
         <v>84</v>
@@ -22601,7 +22620,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B55" s="33" t="s">
         <v>84</v>
@@ -22627,12 +22646,12 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="137" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B57" s="98">
         <v>46097</v>
@@ -22659,7 +22678,7 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B58" s="98">
         <v>46118</v>
@@ -22686,7 +22705,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B59" s="98">
         <v>46122</v>
@@ -22712,7 +22731,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B60" s="98" t="s">
         <v>84</v>
@@ -22764,7 +22783,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B62" s="98">
         <v>46143</v>
@@ -22790,7 +22809,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B63" s="98">
         <v>46160</v>
@@ -22816,7 +22835,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B64" s="98">
         <v>46183</v>
@@ -22832,7 +22851,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B65" s="98" t="s">
         <v>125</v>
@@ -22858,7 +22877,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B66" s="98">
         <v>46141</v>
@@ -22884,7 +22903,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D67" s="135">
         <v>46198</v>
@@ -22892,13 +22911,13 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="137" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D68" s="135"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B69" s="98">
         <v>45800</v>
@@ -22924,7 +22943,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C70" s="135">
         <v>46231</v>
@@ -22932,7 +22951,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C71" s="135">
         <f>D47</f>
@@ -22941,7 +22960,7 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B72" s="98">
         <v>46235</v>
@@ -22985,52 +23004,52 @@
   <sheetData>
     <row r="1" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="120" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1" s="120" t="s">
         <v>425</v>
       </c>
-      <c r="B1" s="120" t="s">
+      <c r="C1" s="120" t="s">
         <v>426</v>
       </c>
-      <c r="C1" s="120" t="s">
+      <c r="D1" s="120" t="s">
         <v>427</v>
       </c>
-      <c r="D1" s="120" t="s">
+      <c r="E1" s="120" t="s">
         <v>428</v>
       </c>
-      <c r="E1" s="120" t="s">
+      <c r="F1" s="120" t="s">
         <v>429</v>
       </c>
-      <c r="F1" s="120" t="s">
+      <c r="G1" s="120" t="s">
         <v>430</v>
       </c>
-      <c r="G1" s="120" t="s">
+      <c r="H1" s="120" t="s">
         <v>431</v>
       </c>
-      <c r="H1" s="120" t="s">
+      <c r="I1" s="120" t="s">
         <v>432</v>
-      </c>
-      <c r="I1" s="120" t="s">
-        <v>433</v>
       </c>
       <c r="J1" s="120" t="s">
         <v>310</v>
       </c>
       <c r="K1" s="120" t="s">
+        <v>433</v>
+      </c>
+      <c r="N1" s="121" t="s">
         <v>434</v>
       </c>
-      <c r="N1" s="121" t="s">
+      <c r="O1" s="121" t="s">
+        <v>470</v>
+      </c>
+      <c r="P1" s="121" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q1" s="121" t="s">
         <v>435</v>
       </c>
-      <c r="O1" s="121" t="s">
-        <v>471</v>
-      </c>
-      <c r="P1" s="121" t="s">
-        <v>472</v>
-      </c>
-      <c r="Q1" s="121" t="s">
+      <c r="R1" s="121" t="s">
         <v>436</v>
-      </c>
-      <c r="R1" s="121" t="s">
-        <v>437</v>
       </c>
       <c r="S1" s="121" t="s">
         <v>8</v>
@@ -23041,31 +23060,31 @@
         <v>17</v>
       </c>
       <c r="B2" s="122" t="s">
+        <v>437</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>443</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K2" t="str">
         <f>CONCATENATE(C2,"|",G2,"|",H2)</f>
@@ -23092,7 +23111,7 @@
         <v>0.89726877040261155</v>
       </c>
       <c r="S2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -23100,31 +23119,31 @@
         <v>17</v>
       </c>
       <c r="B3" s="122" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>447</v>
       </c>
       <c r="H3" s="1">
         <v>4844</v>
       </c>
       <c r="I3" s="130" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K3" t="str">
         <f>CONCATENATE(C3,"|",G3,"|",H3)</f>
@@ -23151,7 +23170,7 @@
         <v>8.8040338529463927E-2</v>
       </c>
       <c r="S3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -23159,31 +23178,31 @@
         <v>17</v>
       </c>
       <c r="B4" s="122" t="s">
+        <v>447</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>450</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K4" t="str">
         <f>CONCATENATE(C4,"|",G4,"|",H4)</f>
@@ -23210,7 +23229,7 @@
         <v>0.79850407978241156</v>
       </c>
       <c r="S4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="T4" s="125" t="s">
         <v>218</v>
@@ -23218,19 +23237,19 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B5" s="126" t="s">
+        <v>451</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="D5" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>442</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>317</v>
@@ -23239,10 +23258,10 @@
         <v>7028</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K5" t="str">
         <f>CONCATENATE(C5,"|",G5,"|",H5)</f>
@@ -23271,31 +23290,31 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B6" s="126" t="s">
+        <v>453</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>456</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K6" t="str">
         <f>CONCATENATE(C6,"|",G6,"|",H6)</f>
@@ -23324,31 +23343,31 @@
     </row>
     <row r="7" spans="1:20" s="127" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="128" t="s">
+        <v>456</v>
+      </c>
+      <c r="C7" s="129" t="s">
         <v>457</v>
       </c>
-      <c r="C7" s="129" t="s">
+      <c r="D7" s="129" t="s">
+        <v>439</v>
+      </c>
+      <c r="E7" s="129" t="s">
+        <v>440</v>
+      </c>
+      <c r="F7" s="129" t="s">
+        <v>441</v>
+      </c>
+      <c r="G7" s="129" t="s">
         <v>458</v>
-      </c>
-      <c r="D7" s="129" t="s">
-        <v>440</v>
-      </c>
-      <c r="E7" s="129" t="s">
-        <v>441</v>
-      </c>
-      <c r="F7" s="129" t="s">
-        <v>442</v>
-      </c>
-      <c r="G7" s="129" t="s">
-        <v>459</v>
       </c>
       <c r="H7" s="129" t="s">
         <v>84</v>
       </c>
       <c r="I7" s="129" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" ref="K7:K10" si="1">CONCATENATE(C7,"|",G7,"|",H7)</f>
@@ -23363,36 +23382,36 @@
         <v>218</v>
       </c>
       <c r="S7" s="127" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B8" s="126" t="s">
+        <v>459</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>462</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="1"/>
@@ -23416,36 +23435,36 @@
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B9" s="126" t="s">
+        <v>462</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>465</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="1"/>
@@ -23469,36 +23488,36 @@
         <v>0</v>
       </c>
       <c r="S9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B10" s="126" t="s">
+        <v>465</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
@@ -23522,36 +23541,36 @@
         <v>0.11600000000000001</v>
       </c>
       <c r="S10" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B11" s="126" t="s">
+        <v>468</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="D11" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="G11" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K11" t="str">
         <f>CONCATENATE(C11,"|",G11,"|",H11)</f>
@@ -23575,7 +23594,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -23650,132 +23669,132 @@
   <sheetData>
     <row r="1" spans="1:22" s="97" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="97" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B1" s="104" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C1" s="104" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F1" s="104" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G1" s="104" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1" s="104" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I1" s="104" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J1" s="104" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K1" s="104" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="L1" s="104" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M1" s="104" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="N1" s="97" t="s">
+        <v>657</v>
+      </c>
+      <c r="O1" s="97" t="s">
+        <v>657</v>
+      </c>
+      <c r="P1" s="97" t="s">
+        <v>657</v>
+      </c>
+      <c r="Q1" s="115" t="s">
+        <v>657</v>
+      </c>
+      <c r="R1" s="115" t="s">
+        <v>657</v>
+      </c>
+      <c r="S1" s="115" t="s">
+        <v>657</v>
+      </c>
+      <c r="T1" s="115" t="s">
         <v>659</v>
       </c>
-      <c r="O1" s="97" t="s">
-        <v>659</v>
-      </c>
-      <c r="P1" s="97" t="s">
-        <v>659</v>
-      </c>
-      <c r="Q1" s="115" t="s">
-        <v>659</v>
-      </c>
-      <c r="R1" s="115" t="s">
-        <v>659</v>
-      </c>
-      <c r="S1" s="115" t="s">
-        <v>659</v>
-      </c>
-      <c r="T1" s="115" t="s">
-        <v>661</v>
-      </c>
       <c r="U1" s="115" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="97" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B2" s="115" t="s">
+        <v>384</v>
+      </c>
+      <c r="C2" s="115" t="s">
+        <v>380</v>
+      </c>
+      <c r="D2" s="115" t="s">
+        <v>656</v>
+      </c>
+      <c r="E2" s="115" t="s">
         <v>385</v>
       </c>
-      <c r="C2" s="115" t="s">
-        <v>381</v>
-      </c>
-      <c r="D2" s="115" t="s">
-        <v>658</v>
-      </c>
-      <c r="E2" s="115" t="s">
-        <v>386</v>
-      </c>
       <c r="F2" s="115" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G2" s="104" t="s">
         <v>300</v>
       </c>
       <c r="H2" s="105" t="s">
+        <v>372</v>
+      </c>
+      <c r="I2" s="105" t="s">
         <v>373</v>
       </c>
-      <c r="I2" s="105" t="s">
+      <c r="J2" s="105" t="s">
+        <v>394</v>
+      </c>
+      <c r="K2" s="105" t="s">
         <v>374</v>
       </c>
-      <c r="J2" s="105" t="s">
-        <v>395</v>
-      </c>
-      <c r="K2" s="105" t="s">
+      <c r="L2" s="105" t="s">
         <v>375</v>
       </c>
-      <c r="L2" s="105" t="s">
+      <c r="M2" s="105" t="s">
         <v>376</v>
       </c>
-      <c r="M2" s="105" t="s">
-        <v>377</v>
-      </c>
       <c r="N2" s="105" t="s">
+        <v>396</v>
+      </c>
+      <c r="O2" s="105" t="s">
         <v>397</v>
       </c>
-      <c r="O2" s="105" t="s">
-        <v>398</v>
-      </c>
       <c r="P2" s="105" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q2" s="105" t="s">
         <v>401</v>
       </c>
-      <c r="Q2" s="105" t="s">
+      <c r="R2" s="105" t="s">
         <v>402</v>
       </c>
-      <c r="R2" s="105" t="s">
+      <c r="S2" s="105" t="s">
         <v>403</v>
       </c>
-      <c r="S2" s="105" t="s">
+      <c r="T2" s="105" t="s">
         <v>404</v>
       </c>
-      <c r="T2" s="105" t="s">
-        <v>405</v>
-      </c>
       <c r="U2" s="105" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="V2" s="105"/>
     </row>
@@ -23784,64 +23803,64 @@
         <v>2</v>
       </c>
       <c r="B3" s="115" t="s">
+        <v>389</v>
+      </c>
+      <c r="C3" s="115" t="s">
+        <v>389</v>
+      </c>
+      <c r="D3" s="115" t="s">
+        <v>389</v>
+      </c>
+      <c r="E3" s="115" t="s">
+        <v>389</v>
+      </c>
+      <c r="F3" s="115" t="s">
+        <v>389</v>
+      </c>
+      <c r="G3" s="104" t="s">
         <v>390</v>
       </c>
-      <c r="C3" s="115" t="s">
-        <v>390</v>
-      </c>
-      <c r="D3" s="115" t="s">
-        <v>390</v>
-      </c>
-      <c r="E3" s="115" t="s">
-        <v>390</v>
-      </c>
-      <c r="F3" s="115" t="s">
-        <v>390</v>
-      </c>
-      <c r="G3" s="104" t="s">
+      <c r="H3" s="104" t="s">
         <v>391</v>
       </c>
-      <c r="H3" s="104" t="s">
+      <c r="I3" s="104" t="s">
         <v>392</v>
       </c>
-      <c r="I3" s="104" t="s">
+      <c r="J3" s="104" t="s">
         <v>393</v>
       </c>
-      <c r="J3" s="104" t="s">
-        <v>394</v>
-      </c>
       <c r="K3" s="104" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L3" s="104" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="M3" s="104" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="N3" s="115" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O3" s="115" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="P3" s="115" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Q3" s="115" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="R3" s="115" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="S3" s="115" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="T3" s="115" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="U3" s="115" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -23885,13 +23904,13 @@
         <v>332</v>
       </c>
       <c r="N4" s="96" t="s">
+        <v>398</v>
+      </c>
+      <c r="O4" s="98" t="s">
         <v>399</v>
       </c>
-      <c r="O4" s="98" t="s">
-        <v>400</v>
-      </c>
       <c r="P4" s="117" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -23934,64 +23953,64 @@
         <v>288</v>
       </c>
       <c r="B7" s="115" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C7" s="115" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D7" s="115" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E7" s="115" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F7" s="115" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G7" s="115" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H7" s="115" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I7" s="115" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J7" s="115" t="s">
+        <v>370</v>
+      </c>
+      <c r="K7" s="115" t="s">
+        <v>370</v>
+      </c>
+      <c r="L7" s="115" t="s">
         <v>371</v>
       </c>
-      <c r="K7" s="115" t="s">
+      <c r="M7" s="115" t="s">
         <v>371</v>
       </c>
-      <c r="L7" s="115" t="s">
-        <v>372</v>
-      </c>
-      <c r="M7" s="115" t="s">
-        <v>372</v>
-      </c>
       <c r="N7" s="115" t="s">
+        <v>405</v>
+      </c>
+      <c r="O7" s="115" t="s">
         <v>406</v>
       </c>
-      <c r="O7" s="115" t="s">
+      <c r="P7" s="115" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q7" s="115" t="s">
+        <v>408</v>
+      </c>
+      <c r="R7" s="115" t="s">
+        <v>408</v>
+      </c>
+      <c r="S7" s="115" t="s">
+        <v>408</v>
+      </c>
+      <c r="T7" s="115" t="s">
         <v>407</v>
       </c>
-      <c r="P7" s="115" t="s">
-        <v>406</v>
-      </c>
-      <c r="Q7" s="115" t="s">
-        <v>409</v>
-      </c>
-      <c r="R7" s="115" t="s">
-        <v>409</v>
-      </c>
-      <c r="S7" s="115" t="s">
-        <v>409</v>
-      </c>
-      <c r="T7" s="115" t="s">
-        <v>408</v>
-      </c>
       <c r="U7" s="115" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="V7" s="115"/>
     </row>
@@ -24000,39 +24019,39 @@
         <v>289</v>
       </c>
       <c r="B8" s="115" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C8" s="115" t="s">
+        <v>381</v>
+      </c>
+      <c r="D8" s="115" t="s">
         <v>382</v>
-      </c>
-      <c r="D8" s="115" t="s">
-        <v>383</v>
       </c>
       <c r="E8" s="115"/>
       <c r="F8" s="115"/>
       <c r="G8" s="115" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H8" s="115" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I8" s="115" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J8" s="115" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K8" s="115" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L8" s="115" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M8" s="115" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="N8" s="115" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="O8" s="115"/>
       <c r="P8" s="115"/>
@@ -24040,10 +24059,10 @@
       <c r="R8" s="115"/>
       <c r="S8" s="115"/>
       <c r="T8" s="115" t="s">
+        <v>405</v>
+      </c>
+      <c r="U8" s="115" t="s">
         <v>406</v>
-      </c>
-      <c r="U8" s="115" t="s">
-        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -24074,16 +24093,16 @@
         <v>268</v>
       </c>
       <c r="I1" s="111" t="s">
+        <v>362</v>
+      </c>
+      <c r="J1" s="111" t="s">
         <v>363</v>
       </c>
-      <c r="J1" s="111" t="s">
-        <v>364</v>
-      </c>
       <c r="M1" s="111" t="s">
+        <v>362</v>
+      </c>
+      <c r="N1" s="111" t="s">
         <v>363</v>
-      </c>
-      <c r="N1" s="111" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -24094,13 +24113,13 @@
         <v>1</v>
       </c>
       <c r="I2" s="108" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J2" s="108">
         <v>1</v>
       </c>
       <c r="M2" s="112" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N2" s="143">
         <v>1</v>
@@ -24114,13 +24133,13 @@
         <v>1</v>
       </c>
       <c r="I3" s="108" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J3" s="108">
         <v>1</v>
       </c>
       <c r="M3" s="113" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="N3" s="144"/>
     </row>
@@ -24132,13 +24151,13 @@
         <v>1</v>
       </c>
       <c r="I4" s="108" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J4" s="108">
         <v>1</v>
       </c>
       <c r="M4" s="114" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="N4" s="145"/>
     </row>
@@ -24150,13 +24169,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="108" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J5" s="108">
         <v>2</v>
       </c>
       <c r="M5" s="112" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="N5" s="143">
         <v>2</v>
@@ -24170,13 +24189,13 @@
         <v>1</v>
       </c>
       <c r="I6" s="108" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J6" s="108">
         <v>2</v>
       </c>
       <c r="M6" s="113" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N6" s="144"/>
     </row>
@@ -24188,13 +24207,13 @@
         <v>1</v>
       </c>
       <c r="I7" s="108" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J7" s="108">
         <v>2</v>
       </c>
       <c r="M7" s="114" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N7" s="145"/>
     </row>
@@ -24206,13 +24225,13 @@
         <v>2</v>
       </c>
       <c r="I8" s="108" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J8" s="108">
         <v>3</v>
       </c>
       <c r="M8" s="112" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N8" s="143">
         <v>3</v>
@@ -24226,13 +24245,13 @@
         <v>2</v>
       </c>
       <c r="I9" s="108" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J9" s="108">
         <v>3</v>
       </c>
       <c r="M9" s="113" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="N9" s="144"/>
     </row>
@@ -24244,13 +24263,13 @@
         <v>2</v>
       </c>
       <c r="I10" s="108" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J10" s="108">
         <v>3</v>
       </c>
       <c r="M10" s="114" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="N10" s="145"/>
     </row>
@@ -24262,13 +24281,13 @@
         <v>2</v>
       </c>
       <c r="I11" s="108" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J11" s="108">
         <v>4</v>
       </c>
       <c r="M11" s="112" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="N11" s="143">
         <v>4</v>
@@ -24282,13 +24301,13 @@
         <v>2</v>
       </c>
       <c r="I12" s="108" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J12" s="108">
         <v>4</v>
       </c>
       <c r="M12" s="113" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="N12" s="144"/>
     </row>
@@ -24300,13 +24319,13 @@
         <v>2</v>
       </c>
       <c r="I13" s="108" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J13" s="108">
         <v>4</v>
       </c>
       <c r="M13" s="114" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N13" s="145"/>
     </row>
